--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -691,7 +691,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="1196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2582" uniqueCount="1203">
   <si>
     <t>handle</t>
   </si>
@@ -1289,6 +1289,27 @@
   </si>
   <si>
     <t>1K-2K</t>
+  </si>
+  <si>
+    <t>Hibiscus</t>
+  </si>
+  <si>
+    <t>Ashwagandha Coffee</t>
+  </si>
+  <si>
+    <t>Turmeric Curcumin</t>
+  </si>
+  <si>
+    <t>Spearmint</t>
+  </si>
+  <si>
+    <t>Lemon Ginger</t>
+  </si>
+  <si>
+    <t>Green Burner</t>
+  </si>
+  <si>
+    <t>Turmeric Ginger</t>
   </si>
   <si>
     <t>Free sample from TikTok Shop (FBT)</t>
@@ -4011,17 +4032,20 @@
       <c r="C2" t="s">
         <v>417</v>
       </c>
+      <c r="D2" t="s">
+        <v>425</v>
+      </c>
       <c r="E2" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F2" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="G2" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4034,17 +4058,20 @@
       <c r="C3" t="s">
         <v>418</v>
       </c>
+      <c r="D3" t="s">
+        <v>426</v>
+      </c>
       <c r="E3" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F3" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="G3" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4057,17 +4084,20 @@
       <c r="C4" t="s">
         <v>419</v>
       </c>
+      <c r="D4" t="s">
+        <v>426</v>
+      </c>
       <c r="E4" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F4" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="G4" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4080,17 +4110,20 @@
       <c r="C5" t="s">
         <v>419</v>
       </c>
+      <c r="D5" t="s">
+        <v>426</v>
+      </c>
       <c r="E5" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F5" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="G5" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -4103,17 +4136,20 @@
       <c r="C6" t="s">
         <v>417</v>
       </c>
+      <c r="D6" t="s">
+        <v>426</v>
+      </c>
       <c r="E6" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F6" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="G6" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4126,17 +4162,20 @@
       <c r="C7" t="s">
         <v>419</v>
       </c>
+      <c r="D7" t="s">
+        <v>427</v>
+      </c>
       <c r="E7" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F7" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="G7" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4149,17 +4188,20 @@
       <c r="C8" t="s">
         <v>417</v>
       </c>
+      <c r="D8" t="s">
+        <v>426</v>
+      </c>
       <c r="E8" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F8" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="G8" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4172,17 +4214,20 @@
       <c r="C9" t="s">
         <v>417</v>
       </c>
+      <c r="D9" t="s">
+        <v>426</v>
+      </c>
       <c r="E9" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F9" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="G9" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -4195,17 +4240,20 @@
       <c r="C10" t="s">
         <v>418</v>
       </c>
+      <c r="D10" t="s">
+        <v>426</v>
+      </c>
       <c r="E10" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F10" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="G10" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -4218,17 +4266,20 @@
       <c r="C11" t="s">
         <v>420</v>
       </c>
+      <c r="D11" t="s">
+        <v>426</v>
+      </c>
       <c r="E11" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F11" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="G11" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -4241,17 +4292,20 @@
       <c r="C12" t="s">
         <v>419</v>
       </c>
+      <c r="D12" t="s">
+        <v>426</v>
+      </c>
       <c r="E12" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F12" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="G12" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -4264,17 +4318,20 @@
       <c r="C13" t="s">
         <v>420</v>
       </c>
+      <c r="D13" t="s">
+        <v>426</v>
+      </c>
       <c r="E13" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F13" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="G13" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -4287,17 +4344,20 @@
       <c r="C14" t="s">
         <v>421</v>
       </c>
+      <c r="D14" t="s">
+        <v>426</v>
+      </c>
       <c r="E14" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F14" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="G14" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -4310,17 +4370,20 @@
       <c r="C15" t="s">
         <v>417</v>
       </c>
+      <c r="D15" t="s">
+        <v>426</v>
+      </c>
       <c r="E15" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F15" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="G15" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -4333,17 +4396,20 @@
       <c r="C16" t="s">
         <v>419</v>
       </c>
+      <c r="D16" t="s">
+        <v>428</v>
+      </c>
       <c r="E16" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F16" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="G16" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -4356,17 +4422,20 @@
       <c r="C17" t="s">
         <v>419</v>
       </c>
+      <c r="D17" t="s">
+        <v>428</v>
+      </c>
       <c r="E17" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F17" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="G17" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -4379,17 +4448,20 @@
       <c r="C18" t="s">
         <v>418</v>
       </c>
+      <c r="D18" t="s">
+        <v>426</v>
+      </c>
       <c r="E18" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F18" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="G18" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -4402,17 +4474,20 @@
       <c r="C19" t="s">
         <v>419</v>
       </c>
+      <c r="D19" t="s">
+        <v>426</v>
+      </c>
       <c r="E19" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F19" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="G19" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -4425,17 +4500,20 @@
       <c r="C20" t="s">
         <v>419</v>
       </c>
+      <c r="D20" t="s">
+        <v>426</v>
+      </c>
       <c r="E20" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F20" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="G20" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -4448,17 +4526,20 @@
       <c r="C21" t="s">
         <v>417</v>
       </c>
+      <c r="D21" t="s">
+        <v>425</v>
+      </c>
       <c r="E21" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F21" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="G21" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -4471,17 +4552,20 @@
       <c r="C22" t="s">
         <v>419</v>
       </c>
+      <c r="D22" t="s">
+        <v>425</v>
+      </c>
       <c r="E22" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F22" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="G22" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -4494,17 +4578,20 @@
       <c r="C23" t="s">
         <v>419</v>
       </c>
+      <c r="D23" t="s">
+        <v>426</v>
+      </c>
       <c r="E23" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F23" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="G23" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -4517,17 +4604,20 @@
       <c r="C24" t="s">
         <v>418</v>
       </c>
+      <c r="D24" t="s">
+        <v>425</v>
+      </c>
       <c r="E24" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F24" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="G24" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -4540,17 +4630,20 @@
       <c r="C25" t="s">
         <v>418</v>
       </c>
+      <c r="D25" t="s">
+        <v>426</v>
+      </c>
       <c r="E25" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F25" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="G25" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -4563,17 +4656,20 @@
       <c r="C26" t="s">
         <v>417</v>
       </c>
+      <c r="D26" t="s">
+        <v>426</v>
+      </c>
       <c r="E26" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F26" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="G26" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -4586,17 +4682,20 @@
       <c r="C27" t="s">
         <v>419</v>
       </c>
+      <c r="D27" t="s">
+        <v>426</v>
+      </c>
       <c r="E27" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F27" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="G27" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -4609,17 +4708,20 @@
       <c r="C28" t="s">
         <v>417</v>
       </c>
+      <c r="D28" t="s">
+        <v>426</v>
+      </c>
       <c r="E28" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F28" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="G28" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -4632,17 +4734,20 @@
       <c r="C29" t="s">
         <v>417</v>
       </c>
+      <c r="D29" t="s">
+        <v>427</v>
+      </c>
       <c r="E29" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F29" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="G29" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -4655,17 +4760,20 @@
       <c r="C30" t="s">
         <v>417</v>
       </c>
+      <c r="D30" t="s">
+        <v>426</v>
+      </c>
       <c r="E30" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F30" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="G30" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -4678,17 +4786,20 @@
       <c r="C31" t="s">
         <v>419</v>
       </c>
+      <c r="D31" t="s">
+        <v>426</v>
+      </c>
       <c r="E31" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F31" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="G31" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -4701,17 +4812,20 @@
       <c r="C32" t="s">
         <v>419</v>
       </c>
+      <c r="D32" t="s">
+        <v>425</v>
+      </c>
       <c r="E32" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F32" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="G32" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -4724,17 +4838,20 @@
       <c r="C33" t="s">
         <v>419</v>
       </c>
+      <c r="D33" t="s">
+        <v>426</v>
+      </c>
       <c r="E33" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F33" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="G33" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -4747,17 +4864,20 @@
       <c r="C34" t="s">
         <v>419</v>
       </c>
+      <c r="D34" t="s">
+        <v>426</v>
+      </c>
       <c r="E34" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F34" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="G34" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -4770,17 +4890,20 @@
       <c r="C35" t="s">
         <v>418</v>
       </c>
+      <c r="D35" t="s">
+        <v>426</v>
+      </c>
       <c r="E35" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F35" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="G35" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -4793,17 +4916,20 @@
       <c r="C36" t="s">
         <v>418</v>
       </c>
+      <c r="D36" t="s">
+        <v>426</v>
+      </c>
       <c r="E36" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F36" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="G36" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -4816,17 +4942,20 @@
       <c r="C37" t="s">
         <v>422</v>
       </c>
+      <c r="D37" t="s">
+        <v>426</v>
+      </c>
       <c r="E37" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F37" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="G37" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -4839,17 +4968,20 @@
       <c r="C38" t="s">
         <v>419</v>
       </c>
+      <c r="D38" t="s">
+        <v>426</v>
+      </c>
       <c r="E38" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F38" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="G38" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -4862,17 +4994,20 @@
       <c r="C39" t="s">
         <v>419</v>
       </c>
+      <c r="D39" t="s">
+        <v>426</v>
+      </c>
       <c r="E39" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F39" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="G39" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -4885,17 +5020,20 @@
       <c r="C40" t="s">
         <v>419</v>
       </c>
+      <c r="D40" t="s">
+        <v>426</v>
+      </c>
       <c r="E40" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F40" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="G40" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -4908,17 +5046,20 @@
       <c r="C41" t="s">
         <v>422</v>
       </c>
+      <c r="D41" t="s">
+        <v>427</v>
+      </c>
       <c r="E41" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F41" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="G41" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -4931,17 +5072,20 @@
       <c r="C42" t="s">
         <v>418</v>
       </c>
+      <c r="D42" t="s">
+        <v>426</v>
+      </c>
       <c r="E42" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F42" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="G42" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -4954,17 +5098,20 @@
       <c r="C43" t="s">
         <v>422</v>
       </c>
+      <c r="D43" t="s">
+        <v>426</v>
+      </c>
       <c r="E43" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F43" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="G43" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -4977,17 +5124,20 @@
       <c r="C44" t="s">
         <v>419</v>
       </c>
+      <c r="D44" t="s">
+        <v>426</v>
+      </c>
       <c r="E44" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F44" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="G44" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -5000,17 +5150,20 @@
       <c r="C45" t="s">
         <v>419</v>
       </c>
+      <c r="D45" t="s">
+        <v>426</v>
+      </c>
       <c r="E45" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F45" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="G45" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -5023,17 +5176,20 @@
       <c r="C46" t="s">
         <v>419</v>
       </c>
+      <c r="D46" t="s">
+        <v>428</v>
+      </c>
       <c r="E46" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F46" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="G46" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -5046,17 +5202,20 @@
       <c r="C47" t="s">
         <v>419</v>
       </c>
+      <c r="D47" t="s">
+        <v>426</v>
+      </c>
       <c r="E47" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F47" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="G47" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -5069,17 +5228,20 @@
       <c r="C48" t="s">
         <v>419</v>
       </c>
+      <c r="D48" t="s">
+        <v>426</v>
+      </c>
       <c r="E48" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F48" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="G48" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -5092,17 +5254,20 @@
       <c r="C49" t="s">
         <v>420</v>
       </c>
+      <c r="D49" t="s">
+        <v>426</v>
+      </c>
       <c r="E49" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F49" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="G49" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -5115,17 +5280,20 @@
       <c r="C50" t="s">
         <v>419</v>
       </c>
+      <c r="D50" t="s">
+        <v>426</v>
+      </c>
       <c r="E50" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F50" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="G50" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -5138,17 +5306,20 @@
       <c r="C51" t="s">
         <v>417</v>
       </c>
+      <c r="D51" t="s">
+        <v>426</v>
+      </c>
       <c r="E51" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F51" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="G51" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -5161,17 +5332,20 @@
       <c r="C52" t="s">
         <v>419</v>
       </c>
+      <c r="D52" t="s">
+        <v>427</v>
+      </c>
       <c r="E52" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F52" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="G52" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -5184,17 +5358,20 @@
       <c r="C53" t="s">
         <v>423</v>
       </c>
+      <c r="D53" t="s">
+        <v>426</v>
+      </c>
       <c r="E53" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F53" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="G53" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -5207,17 +5384,20 @@
       <c r="C54" t="s">
         <v>419</v>
       </c>
+      <c r="D54" t="s">
+        <v>426</v>
+      </c>
       <c r="E54" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F54" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="G54" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -5230,17 +5410,20 @@
       <c r="C55" t="s">
         <v>419</v>
       </c>
+      <c r="D55" t="s">
+        <v>426</v>
+      </c>
       <c r="E55" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F55" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="G55" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -5253,17 +5436,20 @@
       <c r="C56" t="s">
         <v>419</v>
       </c>
+      <c r="D56" t="s">
+        <v>426</v>
+      </c>
       <c r="E56" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F56" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="G56" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -5276,17 +5462,20 @@
       <c r="C57" t="s">
         <v>422</v>
       </c>
+      <c r="D57" t="s">
+        <v>426</v>
+      </c>
       <c r="E57" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F57" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="G57" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -5299,17 +5488,20 @@
       <c r="C58" t="s">
         <v>419</v>
       </c>
+      <c r="D58" t="s">
+        <v>426</v>
+      </c>
       <c r="E58" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F58" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="G58" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -5322,17 +5514,20 @@
       <c r="C59" t="s">
         <v>419</v>
       </c>
+      <c r="D59" t="s">
+        <v>426</v>
+      </c>
       <c r="E59" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F59" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="G59" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -5345,17 +5540,20 @@
       <c r="C60" t="s">
         <v>418</v>
       </c>
+      <c r="D60" t="s">
+        <v>426</v>
+      </c>
       <c r="E60" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F60" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="G60" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -5368,17 +5566,20 @@
       <c r="C61" t="s">
         <v>419</v>
       </c>
+      <c r="D61" t="s">
+        <v>426</v>
+      </c>
       <c r="E61" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F61" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="G61" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -5391,17 +5592,20 @@
       <c r="C62" t="s">
         <v>420</v>
       </c>
+      <c r="D62" t="s">
+        <v>425</v>
+      </c>
       <c r="E62" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F62" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="G62" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -5414,17 +5618,20 @@
       <c r="C63" t="s">
         <v>419</v>
       </c>
+      <c r="D63" t="s">
+        <v>426</v>
+      </c>
       <c r="E63" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F63" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="G63" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -5437,17 +5644,20 @@
       <c r="C64" t="s">
         <v>419</v>
       </c>
+      <c r="D64" t="s">
+        <v>426</v>
+      </c>
       <c r="E64" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F64" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="G64" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -5460,17 +5670,20 @@
       <c r="C65" t="s">
         <v>419</v>
       </c>
+      <c r="D65" t="s">
+        <v>426</v>
+      </c>
       <c r="E65" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F65" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="G65" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -5483,17 +5696,20 @@
       <c r="C66" t="s">
         <v>419</v>
       </c>
+      <c r="D66" t="s">
+        <v>426</v>
+      </c>
       <c r="E66" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F66" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="G66" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -5506,17 +5722,20 @@
       <c r="C67" t="s">
         <v>418</v>
       </c>
+      <c r="D67" t="s">
+        <v>426</v>
+      </c>
       <c r="E67" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F67" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="G67" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -5529,17 +5748,20 @@
       <c r="C68" t="s">
         <v>419</v>
       </c>
+      <c r="D68" t="s">
+        <v>426</v>
+      </c>
       <c r="E68" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F68" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="G68" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -5552,17 +5774,20 @@
       <c r="C69" t="s">
         <v>418</v>
       </c>
+      <c r="D69" t="s">
+        <v>426</v>
+      </c>
       <c r="E69" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F69" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="G69" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -5575,17 +5800,20 @@
       <c r="C70" t="s">
         <v>419</v>
       </c>
+      <c r="D70" t="s">
+        <v>426</v>
+      </c>
       <c r="E70" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F70" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="G70" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -5598,17 +5826,20 @@
       <c r="C71" t="s">
         <v>419</v>
       </c>
+      <c r="D71" t="s">
+        <v>426</v>
+      </c>
       <c r="E71" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F71" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="G71" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -5621,17 +5852,20 @@
       <c r="C72" t="s">
         <v>418</v>
       </c>
+      <c r="D72" t="s">
+        <v>426</v>
+      </c>
       <c r="E72" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F72" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="G72" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -5644,17 +5878,20 @@
       <c r="C73" t="s">
         <v>419</v>
       </c>
+      <c r="D73" t="s">
+        <v>426</v>
+      </c>
       <c r="E73" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F73" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="G73" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -5667,17 +5904,20 @@
       <c r="C74" t="s">
         <v>418</v>
       </c>
+      <c r="D74" t="s">
+        <v>426</v>
+      </c>
       <c r="E74" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F74" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="G74" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -5690,323 +5930,380 @@
       <c r="C75" t="s">
         <v>419</v>
       </c>
+      <c r="D75" t="s">
+        <v>429</v>
+      </c>
       <c r="E75" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F75" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="G75" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
         <v>82</v>
       </c>
+      <c r="D76" t="s">
+        <v>426</v>
+      </c>
       <c r="E76" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F76" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="G76" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" t="s">
         <v>83</v>
       </c>
+      <c r="D77" t="s">
+        <v>430</v>
+      </c>
       <c r="E77" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F77" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="G77" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
         <v>84</v>
       </c>
+      <c r="D78" t="s">
+        <v>429</v>
+      </c>
       <c r="E78" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F78" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="G78" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
         <v>85</v>
       </c>
+      <c r="D79" t="s">
+        <v>429</v>
+      </c>
       <c r="E79" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F79" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="G79" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
         <v>86</v>
       </c>
+      <c r="D80" t="s">
+        <v>431</v>
+      </c>
       <c r="E80" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F80" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="G80" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" t="s">
         <v>87</v>
       </c>
+      <c r="D81" t="s">
+        <v>429</v>
+      </c>
       <c r="E81" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F81" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="G81" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" t="s">
         <v>88</v>
       </c>
+      <c r="D82" t="s">
+        <v>429</v>
+      </c>
       <c r="E82" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F82" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="G82" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" t="s">
         <v>89</v>
       </c>
+      <c r="D83" t="s">
+        <v>429</v>
+      </c>
       <c r="E83" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F83" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="G83" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" t="s">
         <v>90</v>
       </c>
+      <c r="D84" t="s">
+        <v>429</v>
+      </c>
       <c r="E84" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F84" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="G84" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
         <v>91</v>
       </c>
+      <c r="D85" t="s">
+        <v>429</v>
+      </c>
       <c r="E85" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F85" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="G85" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
         <v>92</v>
       </c>
+      <c r="D86" t="s">
+        <v>428</v>
+      </c>
       <c r="E86" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F86" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="G86" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" t="s">
         <v>93</v>
       </c>
+      <c r="D87" t="s">
+        <v>429</v>
+      </c>
       <c r="E87" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F87" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="G87" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" t="s">
         <v>94</v>
       </c>
+      <c r="D88" t="s">
+        <v>429</v>
+      </c>
       <c r="E88" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F88" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="G88" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" t="s">
         <v>95</v>
       </c>
+      <c r="D89" t="s">
+        <v>429</v>
+      </c>
       <c r="E89" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F89" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="G89" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
         <v>96</v>
       </c>
+      <c r="D90" t="s">
+        <v>429</v>
+      </c>
       <c r="E90" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F90" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="G90" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" t="s">
         <v>97</v>
       </c>
+      <c r="D91" t="s">
+        <v>429</v>
+      </c>
       <c r="E91" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F91" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="G91" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" t="s">
         <v>98</v>
       </c>
+      <c r="D92" t="s">
+        <v>429</v>
+      </c>
       <c r="E92" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F92" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="G92" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" t="s">
         <v>99</v>
       </c>
+      <c r="D93" t="s">
+        <v>428</v>
+      </c>
       <c r="E93" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F93" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="G93" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -6019,578 +6316,680 @@
       <c r="C94" t="s">
         <v>421</v>
       </c>
+      <c r="D94" t="s">
+        <v>429</v>
+      </c>
       <c r="E94" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F94" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="G94" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" t="s">
         <v>101</v>
       </c>
+      <c r="D95" t="s">
+        <v>429</v>
+      </c>
       <c r="E95" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F95" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="G95" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" t="s">
         <v>102</v>
       </c>
+      <c r="D96" t="s">
+        <v>429</v>
+      </c>
       <c r="E96" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F96" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="G96" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" t="s">
         <v>103</v>
       </c>
+      <c r="D97" t="s">
+        <v>426</v>
+      </c>
       <c r="E97" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F97" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="G97" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" t="s">
         <v>104</v>
       </c>
+      <c r="D98" t="s">
+        <v>429</v>
+      </c>
       <c r="E98" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F98" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="G98" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" t="s">
         <v>105</v>
       </c>
+      <c r="D99" t="s">
+        <v>431</v>
+      </c>
       <c r="E99" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F99" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="G99" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" t="s">
         <v>106</v>
       </c>
+      <c r="D100" t="s">
+        <v>429</v>
+      </c>
       <c r="E100" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F100" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="G100" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" t="s">
         <v>107</v>
       </c>
+      <c r="D101" t="s">
+        <v>429</v>
+      </c>
       <c r="E101" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F101" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="G101" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" t="s">
         <v>108</v>
       </c>
+      <c r="D102" t="s">
+        <v>429</v>
+      </c>
       <c r="E102" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F102" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="G102" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" t="s">
         <v>109</v>
       </c>
+      <c r="D103" t="s">
+        <v>429</v>
+      </c>
       <c r="E103" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F103" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="G103" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" t="s">
         <v>110</v>
       </c>
+      <c r="D104" t="s">
+        <v>429</v>
+      </c>
       <c r="E104" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F104" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="G104" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" t="s">
         <v>111</v>
       </c>
+      <c r="D105" t="s">
+        <v>429</v>
+      </c>
       <c r="E105" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F105" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="G105" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" t="s">
         <v>112</v>
       </c>
+      <c r="D106" t="s">
+        <v>429</v>
+      </c>
       <c r="E106" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F106" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="G106" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" t="s">
         <v>113</v>
       </c>
+      <c r="D107" t="s">
+        <v>429</v>
+      </c>
       <c r="E107" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F107" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="G107" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" t="s">
         <v>114</v>
       </c>
+      <c r="D108" t="s">
+        <v>429</v>
+      </c>
       <c r="E108" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F108" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="G108" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" t="s">
         <v>115</v>
       </c>
+      <c r="D109" t="s">
+        <v>429</v>
+      </c>
       <c r="E109" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F109" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="G109" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" t="s">
         <v>116</v>
       </c>
+      <c r="D110" t="s">
+        <v>429</v>
+      </c>
       <c r="E110" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F110" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="G110" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" t="s">
         <v>117</v>
       </c>
+      <c r="D111" t="s">
+        <v>429</v>
+      </c>
       <c r="E111" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F111" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="G111" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" t="s">
         <v>118</v>
       </c>
+      <c r="D112" t="s">
+        <v>429</v>
+      </c>
       <c r="E112" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F112" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="G112" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" t="s">
         <v>119</v>
       </c>
+      <c r="D113" t="s">
+        <v>429</v>
+      </c>
       <c r="E113" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F113" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="G113" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" t="s">
         <v>120</v>
       </c>
+      <c r="D114" t="s">
+        <v>426</v>
+      </c>
       <c r="E114" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F114" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="G114" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" t="s">
         <v>121</v>
       </c>
+      <c r="D115" t="s">
+        <v>429</v>
+      </c>
       <c r="E115" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F115" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="G115" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" t="s">
         <v>122</v>
       </c>
+      <c r="D116" t="s">
+        <v>429</v>
+      </c>
       <c r="E116" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F116" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="G116" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" t="s">
         <v>123</v>
       </c>
+      <c r="D117" t="s">
+        <v>431</v>
+      </c>
       <c r="E117" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F117" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="G117" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" t="s">
         <v>124</v>
       </c>
+      <c r="D118" t="s">
+        <v>429</v>
+      </c>
       <c r="E118" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F118" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="G118" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" t="s">
         <v>125</v>
       </c>
+      <c r="D119" t="s">
+        <v>429</v>
+      </c>
       <c r="E119" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F119" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="G119" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>911</v>
+        <v>918</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" t="s">
         <v>126</v>
       </c>
+      <c r="D120" t="s">
+        <v>429</v>
+      </c>
       <c r="E120" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F120" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="G120" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" t="s">
         <v>127</v>
       </c>
+      <c r="D121" t="s">
+        <v>429</v>
+      </c>
       <c r="E121" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F121" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="G121" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" t="s">
         <v>128</v>
       </c>
+      <c r="D122" t="s">
+        <v>429</v>
+      </c>
       <c r="E122" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F122" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="G122" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
         <v>129</v>
       </c>
+      <c r="D123" t="s">
+        <v>430</v>
+      </c>
       <c r="E123" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F123" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="G123" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
         <v>130</v>
       </c>
+      <c r="D124" t="s">
+        <v>430</v>
+      </c>
       <c r="E124" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F124" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="G124" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
         <v>131</v>
       </c>
+      <c r="D125" t="s">
+        <v>429</v>
+      </c>
       <c r="E125" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F125" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G125" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
         <v>132</v>
       </c>
+      <c r="D126" t="s">
+        <v>430</v>
+      </c>
       <c r="E126" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F126" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="G126" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
         <v>133</v>
       </c>
+      <c r="D127" t="s">
+        <v>429</v>
+      </c>
       <c r="E127" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F127" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="G127" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>919</v>
+        <v>926</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -6603,51 +7002,60 @@
       <c r="C128" t="s">
         <v>419</v>
       </c>
+      <c r="D128" t="s">
+        <v>429</v>
+      </c>
       <c r="E128" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F128" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="G128" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>920</v>
+        <v>927</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
         <v>135</v>
       </c>
+      <c r="D129" t="s">
+        <v>429</v>
+      </c>
       <c r="E129" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F129" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="G129" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
         <v>136</v>
       </c>
+      <c r="D130" t="s">
+        <v>429</v>
+      </c>
       <c r="E130" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F130" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="G130" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -6660,1887 +7068,2220 @@
       <c r="C131" t="s">
         <v>419</v>
       </c>
+      <c r="D131" t="s">
+        <v>429</v>
+      </c>
       <c r="E131" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F131" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="G131" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" t="s">
         <v>138</v>
       </c>
+      <c r="D132" t="s">
+        <v>429</v>
+      </c>
       <c r="E132" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F132" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="G132" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" t="s">
         <v>139</v>
       </c>
+      <c r="D133" t="s">
+        <v>429</v>
+      </c>
       <c r="E133" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F133" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="G133" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" t="s">
         <v>140</v>
       </c>
+      <c r="D134" t="s">
+        <v>429</v>
+      </c>
       <c r="E134" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F134" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="G134" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" t="s">
         <v>141</v>
       </c>
+      <c r="D135" t="s">
+        <v>429</v>
+      </c>
       <c r="E135" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F135" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G135" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>927</v>
+        <v>934</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" t="s">
         <v>142</v>
       </c>
+      <c r="D136" t="s">
+        <v>429</v>
+      </c>
       <c r="E136" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F136" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="G136" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" t="s">
         <v>143</v>
       </c>
+      <c r="D137" t="s">
+        <v>426</v>
+      </c>
       <c r="E137" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F137" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="G137" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" t="s">
         <v>144</v>
       </c>
+      <c r="D138" t="s">
+        <v>426</v>
+      </c>
       <c r="E138" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F138" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="G138" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" t="s">
         <v>145</v>
       </c>
+      <c r="D139" t="s">
+        <v>430</v>
+      </c>
       <c r="E139" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F139" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="G139" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" t="s">
         <v>146</v>
       </c>
+      <c r="D140" t="s">
+        <v>429</v>
+      </c>
       <c r="E140" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F140" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="G140" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" t="s">
         <v>147</v>
       </c>
+      <c r="D141" t="s">
+        <v>429</v>
+      </c>
       <c r="E141" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F141" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G141" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>933</v>
+        <v>940</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" t="s">
         <v>148</v>
       </c>
+      <c r="D142" t="s">
+        <v>429</v>
+      </c>
       <c r="E142" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F142" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G142" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>934</v>
+        <v>941</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" t="s">
         <v>149</v>
       </c>
+      <c r="D143" t="s">
+        <v>429</v>
+      </c>
       <c r="E143" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F143" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="G143" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>935</v>
+        <v>942</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" t="s">
         <v>150</v>
       </c>
+      <c r="D144" t="s">
+        <v>430</v>
+      </c>
       <c r="E144" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F144" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="G144" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>936</v>
+        <v>943</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" t="s">
         <v>151</v>
       </c>
+      <c r="D145" t="s">
+        <v>429</v>
+      </c>
       <c r="E145" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F145" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="G145" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>937</v>
+        <v>944</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" t="s">
         <v>152</v>
       </c>
+      <c r="D146" t="s">
+        <v>429</v>
+      </c>
       <c r="E146" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F146" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="G146" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>938</v>
+        <v>945</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" t="s">
         <v>153</v>
       </c>
+      <c r="D147" t="s">
+        <v>429</v>
+      </c>
       <c r="E147" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F147" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="G147" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>939</v>
+        <v>946</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" t="s">
         <v>154</v>
       </c>
+      <c r="D148" t="s">
+        <v>429</v>
+      </c>
       <c r="E148" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F148" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="G148" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" t="s">
         <v>155</v>
       </c>
+      <c r="D149" t="s">
+        <v>426</v>
+      </c>
       <c r="E149" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F149" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="G149" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>941</v>
+        <v>948</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" t="s">
         <v>156</v>
       </c>
+      <c r="D150" t="s">
+        <v>429</v>
+      </c>
       <c r="E150" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F150" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="G150" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>942</v>
+        <v>949</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" t="s">
         <v>157</v>
       </c>
+      <c r="D151" t="s">
+        <v>426</v>
+      </c>
       <c r="E151" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F151" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="G151" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>943</v>
+        <v>950</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" t="s">
         <v>158</v>
       </c>
+      <c r="D152" t="s">
+        <v>429</v>
+      </c>
       <c r="E152" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F152" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="G152" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
         <v>159</v>
       </c>
+      <c r="D153" t="s">
+        <v>429</v>
+      </c>
       <c r="E153" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F153" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="G153" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>945</v>
+        <v>952</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" t="s">
         <v>160</v>
       </c>
+      <c r="D154" t="s">
+        <v>429</v>
+      </c>
       <c r="E154" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F154" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="G154" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>946</v>
+        <v>953</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
         <v>161</v>
       </c>
+      <c r="D155" t="s">
+        <v>426</v>
+      </c>
       <c r="E155" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F155" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="G155" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>947</v>
+        <v>954</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" t="s">
         <v>162</v>
       </c>
+      <c r="D156" t="s">
+        <v>429</v>
+      </c>
       <c r="E156" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F156" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="G156" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>948</v>
+        <v>955</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" t="s">
         <v>163</v>
       </c>
+      <c r="D157" t="s">
+        <v>429</v>
+      </c>
       <c r="E157" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F157" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="G157" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>949</v>
+        <v>956</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" t="s">
         <v>164</v>
       </c>
+      <c r="D158" t="s">
+        <v>429</v>
+      </c>
       <c r="E158" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F158" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="G158" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>950</v>
+        <v>957</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" t="s">
         <v>165</v>
       </c>
+      <c r="D159" t="s">
+        <v>429</v>
+      </c>
       <c r="E159" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F159" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="G159" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" t="s">
         <v>166</v>
       </c>
+      <c r="D160" t="s">
+        <v>429</v>
+      </c>
       <c r="E160" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F160" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="G160" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" t="s">
         <v>167</v>
       </c>
+      <c r="D161" t="s">
+        <v>429</v>
+      </c>
       <c r="E161" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F161" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="G161" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
         <v>168</v>
       </c>
+      <c r="D162" t="s">
+        <v>429</v>
+      </c>
       <c r="E162" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F162" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="G162" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" t="s">
         <v>169</v>
       </c>
+      <c r="D163" t="s">
+        <v>429</v>
+      </c>
       <c r="E163" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F163" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="G163" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" t="s">
         <v>170</v>
       </c>
+      <c r="D164" t="s">
+        <v>429</v>
+      </c>
       <c r="E164" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F164" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="G164" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>956</v>
+        <v>963</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" t="s">
         <v>171</v>
       </c>
+      <c r="D165" t="s">
+        <v>429</v>
+      </c>
       <c r="E165" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F165" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="G165" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" t="s">
         <v>172</v>
       </c>
+      <c r="D166" t="s">
+        <v>429</v>
+      </c>
       <c r="E166" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F166" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="G166" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>958</v>
+        <v>965</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" t="s">
         <v>173</v>
       </c>
+      <c r="D167" t="s">
+        <v>429</v>
+      </c>
       <c r="E167" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F167" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="G167" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>959</v>
+        <v>966</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" t="s">
         <v>174</v>
       </c>
+      <c r="D168" t="s">
+        <v>429</v>
+      </c>
       <c r="E168" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F168" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="G168" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>960</v>
+        <v>967</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
         <v>175</v>
       </c>
+      <c r="D169" t="s">
+        <v>429</v>
+      </c>
       <c r="E169" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F169" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="G169" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>961</v>
+        <v>968</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" t="s">
         <v>176</v>
       </c>
+      <c r="D170" t="s">
+        <v>429</v>
+      </c>
       <c r="E170" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F170" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="G170" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>962</v>
+        <v>969</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
         <v>177</v>
       </c>
+      <c r="D171" t="s">
+        <v>429</v>
+      </c>
       <c r="E171" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F171" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="G171" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>963</v>
+        <v>970</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
         <v>178</v>
       </c>
+      <c r="D172" t="s">
+        <v>426</v>
+      </c>
       <c r="E172" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F172" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="G172" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>964</v>
+        <v>971</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
         <v>179</v>
       </c>
+      <c r="D173" t="s">
+        <v>429</v>
+      </c>
       <c r="E173" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F173" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="G173" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>965</v>
+        <v>972</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
         <v>180</v>
       </c>
+      <c r="D174" t="s">
+        <v>429</v>
+      </c>
       <c r="E174" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F174" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="G174" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
         <v>181</v>
       </c>
+      <c r="D175" t="s">
+        <v>429</v>
+      </c>
       <c r="E175" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F175" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="G175" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
         <v>182</v>
       </c>
+      <c r="D176" t="s">
+        <v>429</v>
+      </c>
       <c r="E176" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F176" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="G176" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
         <v>183</v>
       </c>
+      <c r="D177" t="s">
+        <v>429</v>
+      </c>
       <c r="E177" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F177" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="G177" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" t="s">
         <v>184</v>
       </c>
+      <c r="D178" t="s">
+        <v>429</v>
+      </c>
       <c r="E178" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F178" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="G178" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>970</v>
+        <v>977</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" t="s">
         <v>185</v>
       </c>
+      <c r="D179" t="s">
+        <v>429</v>
+      </c>
       <c r="E179" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F179" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="G179" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>971</v>
+        <v>978</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" t="s">
         <v>186</v>
       </c>
+      <c r="D180" t="s">
+        <v>429</v>
+      </c>
       <c r="E180" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F180" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="G180" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>972</v>
+        <v>979</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
         <v>187</v>
       </c>
+      <c r="D181" t="s">
+        <v>429</v>
+      </c>
       <c r="E181" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F181" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="G181" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>973</v>
+        <v>980</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
         <v>188</v>
       </c>
+      <c r="D182" t="s">
+        <v>429</v>
+      </c>
       <c r="E182" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F182" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="G182" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>974</v>
+        <v>981</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
         <v>189</v>
       </c>
+      <c r="D183" t="s">
+        <v>429</v>
+      </c>
       <c r="E183" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F183" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="G183" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
         <v>190</v>
       </c>
+      <c r="D184" t="s">
+        <v>429</v>
+      </c>
       <c r="E184" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F184" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="G184" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>976</v>
+        <v>983</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" t="s">
         <v>191</v>
       </c>
+      <c r="D185" t="s">
+        <v>429</v>
+      </c>
       <c r="E185" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F185" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="G185" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>977</v>
+        <v>984</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" t="s">
         <v>192</v>
       </c>
+      <c r="D186" t="s">
+        <v>429</v>
+      </c>
       <c r="E186" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F186" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="G186" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" t="s">
         <v>193</v>
       </c>
+      <c r="D187" t="s">
+        <v>429</v>
+      </c>
       <c r="E187" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F187" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="G187" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>979</v>
+        <v>986</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" t="s">
         <v>194</v>
       </c>
+      <c r="D188" t="s">
+        <v>429</v>
+      </c>
       <c r="E188" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F188" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="G188" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
         <v>195</v>
       </c>
+      <c r="D189" t="s">
+        <v>426</v>
+      </c>
       <c r="E189" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F189" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="G189" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
     </row>
     <row r="190" spans="1:8">
       <c r="A190" t="s">
         <v>196</v>
       </c>
+      <c r="D190" t="s">
+        <v>429</v>
+      </c>
       <c r="E190" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F190" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="G190" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>982</v>
+        <v>989</v>
       </c>
     </row>
     <row r="191" spans="1:8">
       <c r="A191" t="s">
         <v>197</v>
       </c>
+      <c r="D191" t="s">
+        <v>429</v>
+      </c>
       <c r="E191" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F191" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="G191" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>983</v>
+        <v>990</v>
       </c>
     </row>
     <row r="192" spans="1:8">
       <c r="A192" t="s">
         <v>198</v>
       </c>
+      <c r="D192" t="s">
+        <v>429</v>
+      </c>
       <c r="E192" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F192" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="G192" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>984</v>
+        <v>991</v>
       </c>
     </row>
     <row r="193" spans="1:8">
       <c r="A193" t="s">
         <v>199</v>
       </c>
+      <c r="D193" t="s">
+        <v>429</v>
+      </c>
       <c r="E193" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F193" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="G193" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>985</v>
+        <v>992</v>
       </c>
     </row>
     <row r="194" spans="1:8">
       <c r="A194" t="s">
         <v>200</v>
       </c>
+      <c r="D194" t="s">
+        <v>429</v>
+      </c>
       <c r="E194" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F194" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="G194" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
     </row>
     <row r="195" spans="1:8">
       <c r="A195" t="s">
         <v>201</v>
       </c>
+      <c r="D195" t="s">
+        <v>429</v>
+      </c>
       <c r="E195" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F195" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="G195" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
     </row>
     <row r="196" spans="1:8">
       <c r="A196" t="s">
         <v>202</v>
       </c>
+      <c r="D196" t="s">
+        <v>429</v>
+      </c>
       <c r="E196" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F196" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="G196" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" t="s">
         <v>203</v>
       </c>
+      <c r="D197" t="s">
+        <v>429</v>
+      </c>
       <c r="E197" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F197" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="G197" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" t="s">
         <v>204</v>
       </c>
+      <c r="D198" t="s">
+        <v>429</v>
+      </c>
       <c r="E198" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F198" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="G198" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>990</v>
+        <v>997</v>
       </c>
     </row>
     <row r="199" spans="1:8">
       <c r="A199" t="s">
         <v>205</v>
       </c>
+      <c r="D199" t="s">
+        <v>429</v>
+      </c>
       <c r="E199" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F199" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="G199" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" t="s">
         <v>206</v>
       </c>
+      <c r="D200" t="s">
+        <v>429</v>
+      </c>
       <c r="E200" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F200" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="G200" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>992</v>
+        <v>999</v>
       </c>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" t="s">
         <v>207</v>
       </c>
+      <c r="D201" t="s">
+        <v>429</v>
+      </c>
       <c r="E201" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F201" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="G201" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>993</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" t="s">
         <v>208</v>
       </c>
+      <c r="D202" t="s">
+        <v>429</v>
+      </c>
       <c r="E202" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F202" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="G202" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>994</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" t="s">
         <v>209</v>
       </c>
+      <c r="D203" t="s">
+        <v>429</v>
+      </c>
       <c r="E203" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F203" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="G203" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="204" spans="1:8">
       <c r="A204" t="s">
         <v>210</v>
       </c>
+      <c r="D204" t="s">
+        <v>426</v>
+      </c>
       <c r="E204" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F204" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="G204" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>996</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="205" spans="1:8">
       <c r="A205" t="s">
         <v>211</v>
       </c>
+      <c r="D205" t="s">
+        <v>429</v>
+      </c>
       <c r="E205" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F205" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="G205" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="206" spans="1:8">
       <c r="A206" t="s">
         <v>212</v>
       </c>
+      <c r="D206" t="s">
+        <v>429</v>
+      </c>
       <c r="E206" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F206" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="G206" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>998</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="207" spans="1:8">
       <c r="A207" t="s">
         <v>213</v>
       </c>
+      <c r="D207" t="s">
+        <v>429</v>
+      </c>
       <c r="E207" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F207" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="G207" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>999</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="208" spans="1:8">
       <c r="A208" t="s">
         <v>214</v>
       </c>
+      <c r="D208" t="s">
+        <v>429</v>
+      </c>
       <c r="E208" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F208" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="G208" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>1000</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" t="s">
         <v>215</v>
       </c>
+      <c r="D209" t="s">
+        <v>429</v>
+      </c>
       <c r="E209" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F209" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="G209" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>1001</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
         <v>216</v>
       </c>
+      <c r="D210" t="s">
+        <v>429</v>
+      </c>
       <c r="E210" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F210" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="G210" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>1002</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
         <v>217</v>
       </c>
+      <c r="D211" t="s">
+        <v>428</v>
+      </c>
       <c r="E211" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F211" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="G211" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>1003</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" t="s">
         <v>218</v>
       </c>
+      <c r="D212" t="s">
+        <v>426</v>
+      </c>
       <c r="E212" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F212" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="G212" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>1004</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" t="s">
         <v>219</v>
       </c>
+      <c r="D213" t="s">
+        <v>426</v>
+      </c>
       <c r="E213" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F213" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="G213" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="214" spans="1:8">
       <c r="A214" t="s">
         <v>220</v>
       </c>
+      <c r="D214" t="s">
+        <v>426</v>
+      </c>
       <c r="E214" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F214" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="G214" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>1006</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="215" spans="1:8">
       <c r="A215" t="s">
         <v>221</v>
       </c>
+      <c r="D215" t="s">
+        <v>429</v>
+      </c>
       <c r="E215" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F215" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="G215" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>1007</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="216" spans="1:8">
       <c r="A216" t="s">
         <v>222</v>
       </c>
+      <c r="D216" t="s">
+        <v>429</v>
+      </c>
       <c r="E216" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F216" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="G216" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>1008</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="217" spans="1:8">
       <c r="A217" t="s">
         <v>223</v>
       </c>
+      <c r="D217" t="s">
+        <v>428</v>
+      </c>
       <c r="E217" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F217" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="G217" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>1009</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="218" spans="1:8">
       <c r="A218" t="s">
         <v>224</v>
       </c>
+      <c r="D218" t="s">
+        <v>430</v>
+      </c>
       <c r="E218" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F218" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="G218" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>1010</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="219" spans="1:8">
       <c r="A219" t="s">
         <v>225</v>
       </c>
+      <c r="D219" t="s">
+        <v>429</v>
+      </c>
       <c r="E219" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F219" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="G219" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>1011</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="220" spans="1:8">
       <c r="A220" t="s">
         <v>226</v>
       </c>
+      <c r="D220" t="s">
+        <v>425</v>
+      </c>
       <c r="E220" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F220" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="G220" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>1012</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="221" spans="1:8">
       <c r="A221" t="s">
         <v>227</v>
       </c>
+      <c r="D221" t="s">
+        <v>431</v>
+      </c>
       <c r="E221" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F221" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="G221" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>1013</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="222" spans="1:8">
       <c r="A222" t="s">
         <v>228</v>
       </c>
+      <c r="D222" t="s">
+        <v>426</v>
+      </c>
       <c r="E222" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F222" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="G222" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>1014</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="223" spans="1:8">
       <c r="A223" t="s">
         <v>229</v>
       </c>
+      <c r="D223" t="s">
+        <v>426</v>
+      </c>
       <c r="E223" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F223" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="G223" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>1015</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="224" spans="1:8">
       <c r="A224" t="s">
         <v>230</v>
       </c>
+      <c r="D224" t="s">
+        <v>426</v>
+      </c>
       <c r="E224" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F224" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="G224" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>1016</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="225" spans="1:8">
       <c r="A225" t="s">
         <v>231</v>
       </c>
+      <c r="D225" t="s">
+        <v>429</v>
+      </c>
       <c r="E225" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F225" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="G225" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>1017</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="226" spans="1:8">
       <c r="A226" t="s">
         <v>232</v>
       </c>
+      <c r="D226" t="s">
+        <v>429</v>
+      </c>
       <c r="E226" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F226" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="G226" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="227" spans="1:8">
       <c r="A227" t="s">
         <v>233</v>
       </c>
+      <c r="D227" t="s">
+        <v>429</v>
+      </c>
       <c r="E227" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F227" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="G227" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>1019</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="228" spans="1:8">
       <c r="A228" t="s">
         <v>234</v>
       </c>
+      <c r="D228" t="s">
+        <v>429</v>
+      </c>
       <c r="E228" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F228" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="G228" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>1020</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="229" spans="1:8">
       <c r="A229" t="s">
         <v>235</v>
       </c>
+      <c r="D229" t="s">
+        <v>426</v>
+      </c>
       <c r="E229" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F229" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="G229" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>1021</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="230" spans="1:8">
       <c r="A230" t="s">
         <v>236</v>
       </c>
+      <c r="D230" t="s">
+        <v>431</v>
+      </c>
       <c r="E230" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F230" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="G230" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>1022</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="231" spans="1:8">
       <c r="A231" t="s">
         <v>237</v>
       </c>
+      <c r="D231" t="s">
+        <v>429</v>
+      </c>
       <c r="E231" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F231" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="G231" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>1023</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="232" spans="1:8">
       <c r="A232" t="s">
         <v>238</v>
       </c>
+      <c r="D232" t="s">
+        <v>431</v>
+      </c>
       <c r="E232" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F232" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="G232" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>1024</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="233" spans="1:8">
       <c r="A233" t="s">
         <v>239</v>
       </c>
+      <c r="D233" t="s">
+        <v>429</v>
+      </c>
       <c r="E233" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F233" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="G233" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>1025</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="234" spans="1:8">
       <c r="A234" t="s">
         <v>240</v>
       </c>
+      <c r="D234" t="s">
+        <v>429</v>
+      </c>
       <c r="E234" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F234" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="G234" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="235" spans="1:8">
       <c r="A235" t="s">
         <v>241</v>
       </c>
+      <c r="D235" t="s">
+        <v>429</v>
+      </c>
       <c r="E235" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F235" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="G235" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>1027</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="236" spans="1:8">
       <c r="A236" t="s">
         <v>242</v>
       </c>
+      <c r="D236" t="s">
+        <v>429</v>
+      </c>
       <c r="E236" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F236" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="G236" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>1028</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="237" spans="1:8">
       <c r="A237" t="s">
         <v>243</v>
       </c>
+      <c r="D237" t="s">
+        <v>429</v>
+      </c>
       <c r="E237" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F237" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="G237" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>1029</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="238" spans="1:8">
       <c r="A238" t="s">
         <v>244</v>
       </c>
+      <c r="D238" t="s">
+        <v>429</v>
+      </c>
       <c r="E238" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F238" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="G238" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>1030</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="239" spans="1:8">
       <c r="A239" t="s">
         <v>245</v>
       </c>
+      <c r="D239" t="s">
+        <v>429</v>
+      </c>
       <c r="E239" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F239" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="G239" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>1031</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="240" spans="1:8">
       <c r="A240" t="s">
         <v>246</v>
       </c>
+      <c r="D240" t="s">
+        <v>429</v>
+      </c>
       <c r="E240" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F240" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="G240" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="241" spans="1:8">
       <c r="A241" t="s">
         <v>247</v>
       </c>
+      <c r="D241" t="s">
+        <v>429</v>
+      </c>
       <c r="E241" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F241" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="G241" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>1033</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -8553,68 +9294,80 @@
       <c r="C242" t="s">
         <v>424</v>
       </c>
+      <c r="D242" t="s">
+        <v>429</v>
+      </c>
       <c r="E242" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F242" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="G242" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>1034</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="243" spans="1:8">
       <c r="A243" t="s">
         <v>249</v>
       </c>
+      <c r="D243" t="s">
+        <v>429</v>
+      </c>
       <c r="E243" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F243" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="G243" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>1035</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="244" spans="1:8">
       <c r="A244" t="s">
         <v>250</v>
       </c>
+      <c r="D244" t="s">
+        <v>429</v>
+      </c>
       <c r="E244" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F244" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="G244" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>1036</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="245" spans="1:8">
       <c r="A245" t="s">
         <v>251</v>
       </c>
+      <c r="D245" t="s">
+        <v>426</v>
+      </c>
       <c r="E245" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F245" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="G245" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>1037</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -8627,17 +9380,20 @@
       <c r="C246" t="s">
         <v>417</v>
       </c>
+      <c r="D246" t="s">
+        <v>429</v>
+      </c>
       <c r="E246" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F246" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="G246" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>1038</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="247" spans="1:8">
@@ -8650,2414 +9406,2840 @@
       <c r="C247" t="s">
         <v>417</v>
       </c>
+      <c r="D247" t="s">
+        <v>429</v>
+      </c>
       <c r="E247" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F247" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="G247" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>1039</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="248" spans="1:8">
       <c r="A248" t="s">
         <v>254</v>
       </c>
+      <c r="D248" t="s">
+        <v>429</v>
+      </c>
       <c r="E248" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F248" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="G248" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>1040</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="249" spans="1:8">
       <c r="A249" t="s">
         <v>255</v>
       </c>
+      <c r="D249" t="s">
+        <v>429</v>
+      </c>
       <c r="E249" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F249" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="G249" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>1041</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="250" spans="1:8">
       <c r="A250" t="s">
         <v>256</v>
       </c>
+      <c r="D250" t="s">
+        <v>430</v>
+      </c>
       <c r="E250" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F250" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="G250" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>1042</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="251" spans="1:8">
       <c r="A251" t="s">
         <v>257</v>
       </c>
+      <c r="D251" t="s">
+        <v>429</v>
+      </c>
       <c r="E251" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F251" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="G251" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>1043</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="252" spans="1:8">
       <c r="A252" t="s">
         <v>258</v>
       </c>
+      <c r="D252" t="s">
+        <v>429</v>
+      </c>
       <c r="E252" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F252" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="G252" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>1044</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="253" spans="1:8">
       <c r="A253" t="s">
         <v>259</v>
       </c>
+      <c r="D253" t="s">
+        <v>426</v>
+      </c>
       <c r="E253" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F253" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="G253" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>1045</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="254" spans="1:8">
       <c r="A254" t="s">
         <v>260</v>
       </c>
+      <c r="D254" t="s">
+        <v>429</v>
+      </c>
       <c r="E254" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F254" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="G254" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>1046</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="255" spans="1:8">
       <c r="A255" t="s">
         <v>261</v>
       </c>
+      <c r="D255" t="s">
+        <v>426</v>
+      </c>
       <c r="E255" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F255" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="G255" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>1047</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="256" spans="1:8">
       <c r="A256" t="s">
         <v>262</v>
       </c>
+      <c r="D256" t="s">
+        <v>429</v>
+      </c>
       <c r="E256" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F256" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="G256" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>1048</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="257" spans="1:8">
       <c r="A257" t="s">
         <v>263</v>
       </c>
+      <c r="D257" t="s">
+        <v>429</v>
+      </c>
       <c r="E257" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F257" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="G257" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>1049</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="258" spans="1:8">
       <c r="A258" t="s">
         <v>264</v>
       </c>
+      <c r="D258" t="s">
+        <v>426</v>
+      </c>
       <c r="E258" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F258" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="G258" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>1050</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="259" spans="1:8">
       <c r="A259" t="s">
         <v>265</v>
       </c>
+      <c r="D259" t="s">
+        <v>429</v>
+      </c>
       <c r="E259" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F259" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="G259" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>1051</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="260" spans="1:8">
       <c r="A260" t="s">
         <v>266</v>
       </c>
+      <c r="D260" t="s">
+        <v>429</v>
+      </c>
       <c r="E260" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F260" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="G260" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>1052</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="261" spans="1:8">
       <c r="A261" t="s">
         <v>267</v>
       </c>
+      <c r="D261" t="s">
+        <v>429</v>
+      </c>
       <c r="E261" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F261" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="G261" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>1053</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="262" spans="1:8">
       <c r="A262" t="s">
         <v>268</v>
       </c>
+      <c r="D262" t="s">
+        <v>426</v>
+      </c>
       <c r="E262" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F262" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="G262" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>1054</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="263" spans="1:8">
       <c r="A263" t="s">
         <v>269</v>
       </c>
+      <c r="D263" t="s">
+        <v>426</v>
+      </c>
       <c r="E263" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F263" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="G263" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>1055</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="264" spans="1:8">
       <c r="A264" t="s">
         <v>270</v>
       </c>
+      <c r="D264" t="s">
+        <v>429</v>
+      </c>
       <c r="E264" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F264" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="G264" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>1056</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="265" spans="1:8">
       <c r="A265" t="s">
         <v>271</v>
       </c>
+      <c r="D265" t="s">
+        <v>429</v>
+      </c>
       <c r="E265" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F265" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="G265" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>1057</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="266" spans="1:8">
       <c r="A266" t="s">
         <v>272</v>
       </c>
+      <c r="D266" t="s">
+        <v>429</v>
+      </c>
       <c r="E266" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F266" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="G266" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="267" spans="1:8">
       <c r="A267" t="s">
         <v>273</v>
       </c>
+      <c r="D267" t="s">
+        <v>429</v>
+      </c>
       <c r="E267" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F267" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="G267" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>1059</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="268" spans="1:8">
       <c r="A268" t="s">
         <v>274</v>
       </c>
+      <c r="D268" t="s">
+        <v>431</v>
+      </c>
       <c r="E268" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F268" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="G268" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>1060</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="269" spans="1:8">
       <c r="A269" t="s">
         <v>275</v>
       </c>
+      <c r="D269" t="s">
+        <v>426</v>
+      </c>
       <c r="E269" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F269" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="G269" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="270" spans="1:8">
       <c r="A270" t="s">
         <v>276</v>
       </c>
+      <c r="D270" t="s">
+        <v>429</v>
+      </c>
       <c r="E270" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F270" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="G270" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>1062</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="271" spans="1:8">
       <c r="A271" t="s">
         <v>277</v>
       </c>
+      <c r="D271" t="s">
+        <v>429</v>
+      </c>
       <c r="E271" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F271" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="G271" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>1063</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="272" spans="1:8">
       <c r="A272" t="s">
         <v>278</v>
       </c>
+      <c r="D272" t="s">
+        <v>426</v>
+      </c>
       <c r="E272" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F272" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="G272" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>1064</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="273" spans="1:8">
       <c r="A273" t="s">
         <v>279</v>
       </c>
+      <c r="D273" t="s">
+        <v>426</v>
+      </c>
       <c r="E273" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F273" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="G273" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>1065</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="274" spans="1:8">
       <c r="A274" t="s">
         <v>280</v>
       </c>
+      <c r="D274" t="s">
+        <v>429</v>
+      </c>
       <c r="E274" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F274" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="G274" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>1066</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="275" spans="1:8">
       <c r="A275" t="s">
         <v>281</v>
       </c>
+      <c r="D275" t="s">
+        <v>429</v>
+      </c>
       <c r="E275" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F275" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="G275" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>1067</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="276" spans="1:8">
       <c r="A276" t="s">
         <v>282</v>
       </c>
+      <c r="D276" t="s">
+        <v>429</v>
+      </c>
       <c r="E276" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F276" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="G276" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>1068</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="277" spans="1:8">
       <c r="A277" t="s">
         <v>283</v>
       </c>
+      <c r="D277" t="s">
+        <v>426</v>
+      </c>
       <c r="E277" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F277" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="G277" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>1069</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="278" spans="1:8">
       <c r="A278" t="s">
         <v>284</v>
       </c>
+      <c r="D278" t="s">
+        <v>431</v>
+      </c>
       <c r="E278" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F278" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="G278" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>1070</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="279" spans="1:8">
       <c r="A279" t="s">
         <v>285</v>
       </c>
+      <c r="D279" t="s">
+        <v>427</v>
+      </c>
       <c r="E279" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F279" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="G279" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>1071</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="280" spans="1:8">
       <c r="A280" t="s">
         <v>286</v>
       </c>
+      <c r="D280" t="s">
+        <v>429</v>
+      </c>
       <c r="E280" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F280" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="G280" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>1072</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="281" spans="1:8">
       <c r="A281" t="s">
         <v>287</v>
       </c>
+      <c r="D281" t="s">
+        <v>429</v>
+      </c>
       <c r="E281" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F281" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="G281" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>1073</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="282" spans="1:8">
       <c r="A282" t="s">
         <v>288</v>
       </c>
+      <c r="D282" t="s">
+        <v>429</v>
+      </c>
       <c r="E282" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F282" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="G282" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>1074</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="283" spans="1:8">
       <c r="A283" t="s">
         <v>289</v>
       </c>
+      <c r="D283" t="s">
+        <v>429</v>
+      </c>
       <c r="E283" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F283" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="G283" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H283" s="2" t="s">
-        <v>1075</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="284" spans="1:8">
       <c r="A284" t="s">
         <v>290</v>
       </c>
+      <c r="D284" t="s">
+        <v>429</v>
+      </c>
       <c r="E284" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F284" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="G284" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H284" s="2" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="285" spans="1:8">
       <c r="A285" t="s">
         <v>291</v>
       </c>
+      <c r="D285" t="s">
+        <v>429</v>
+      </c>
       <c r="E285" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F285" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="G285" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="H285" s="2" t="s">
-        <v>1077</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="286" spans="1:8">
       <c r="A286" t="s">
         <v>292</v>
       </c>
+      <c r="D286" t="s">
+        <v>429</v>
+      </c>
       <c r="E286" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F286" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="G286" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H286" s="2" t="s">
-        <v>1078</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="287" spans="1:8">
       <c r="A287" t="s">
         <v>293</v>
       </c>
+      <c r="D287" t="s">
+        <v>429</v>
+      </c>
       <c r="E287" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F287" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="G287" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="288" spans="1:8">
       <c r="A288" t="s">
         <v>294</v>
       </c>
+      <c r="D288" t="s">
+        <v>426</v>
+      </c>
       <c r="E288" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F288" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="G288" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H288" s="2" t="s">
-        <v>1080</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="289" spans="1:8">
       <c r="A289" t="s">
         <v>295</v>
       </c>
+      <c r="D289" t="s">
+        <v>429</v>
+      </c>
       <c r="E289" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F289" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="G289" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>1081</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="290" spans="1:8">
       <c r="A290" t="s">
         <v>296</v>
       </c>
+      <c r="D290" t="s">
+        <v>429</v>
+      </c>
       <c r="E290" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F290" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="G290" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H290" s="2" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="291" spans="1:8">
       <c r="A291" t="s">
         <v>297</v>
       </c>
+      <c r="D291" t="s">
+        <v>429</v>
+      </c>
       <c r="E291" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F291" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="G291" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="292" spans="1:8">
       <c r="A292" t="s">
         <v>298</v>
       </c>
+      <c r="D292" t="s">
+        <v>429</v>
+      </c>
       <c r="E292" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F292" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="G292" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>1084</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="293" spans="1:8">
       <c r="A293" t="s">
         <v>299</v>
       </c>
+      <c r="D293" t="s">
+        <v>429</v>
+      </c>
       <c r="E293" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F293" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="G293" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="H293" s="2" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="294" spans="1:8">
       <c r="A294" t="s">
         <v>300</v>
       </c>
+      <c r="D294" t="s">
+        <v>426</v>
+      </c>
       <c r="E294" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F294" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="G294" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="295" spans="1:8">
       <c r="A295" t="s">
         <v>301</v>
       </c>
+      <c r="D295" t="s">
+        <v>429</v>
+      </c>
       <c r="E295" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F295" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="G295" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>1087</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="296" spans="1:8">
       <c r="A296" t="s">
         <v>302</v>
       </c>
+      <c r="D296" t="s">
+        <v>429</v>
+      </c>
       <c r="E296" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F296" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="G296" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="297" spans="1:8">
       <c r="A297" t="s">
         <v>303</v>
       </c>
+      <c r="D297" t="s">
+        <v>429</v>
+      </c>
       <c r="E297" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F297" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="G297" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="298" spans="1:8">
       <c r="A298" t="s">
         <v>304</v>
       </c>
+      <c r="D298" t="s">
+        <v>429</v>
+      </c>
       <c r="E298" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F298" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="G298" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>1090</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="299" spans="1:8">
       <c r="A299" t="s">
         <v>305</v>
       </c>
+      <c r="D299" t="s">
+        <v>429</v>
+      </c>
       <c r="E299" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F299" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="G299" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="300" spans="1:8">
       <c r="A300" t="s">
         <v>306</v>
       </c>
+      <c r="D300" t="s">
+        <v>429</v>
+      </c>
       <c r="E300" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F300" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="G300" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="301" spans="1:8">
       <c r="A301" t="s">
         <v>307</v>
       </c>
+      <c r="D301" t="s">
+        <v>429</v>
+      </c>
       <c r="E301" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F301" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="G301" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="302" spans="1:8">
       <c r="A302" t="s">
         <v>308</v>
       </c>
+      <c r="D302" t="s">
+        <v>429</v>
+      </c>
       <c r="E302" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F302" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="G302" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="303" spans="1:8">
       <c r="A303" t="s">
         <v>309</v>
       </c>
+      <c r="D303" t="s">
+        <v>426</v>
+      </c>
       <c r="E303" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F303" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="G303" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="304" spans="1:8">
       <c r="A304" t="s">
         <v>310</v>
       </c>
+      <c r="D304" t="s">
+        <v>429</v>
+      </c>
       <c r="E304" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F304" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="G304" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>1096</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="305" spans="1:8">
       <c r="A305" t="s">
         <v>311</v>
       </c>
+      <c r="D305" t="s">
+        <v>429</v>
+      </c>
       <c r="E305" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F305" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="G305" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>1097</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="306" spans="1:8">
       <c r="A306" t="s">
         <v>312</v>
       </c>
+      <c r="D306" t="s">
+        <v>429</v>
+      </c>
       <c r="E306" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F306" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="G306" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="307" spans="1:8">
       <c r="A307" t="s">
         <v>313</v>
       </c>
+      <c r="D307" t="s">
+        <v>429</v>
+      </c>
       <c r="E307" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F307" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="G307" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="308" spans="1:8">
       <c r="A308" t="s">
         <v>314</v>
       </c>
+      <c r="D308" t="s">
+        <v>429</v>
+      </c>
       <c r="E308" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F308" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="G308" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>1100</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="309" spans="1:8">
       <c r="A309" t="s">
         <v>315</v>
       </c>
+      <c r="D309" t="s">
+        <v>429</v>
+      </c>
       <c r="E309" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F309" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="G309" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>1101</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="310" spans="1:8">
       <c r="A310" t="s">
         <v>316</v>
       </c>
+      <c r="D310" t="s">
+        <v>430</v>
+      </c>
       <c r="E310" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F310" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="G310" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="311" spans="1:8">
       <c r="A311" t="s">
         <v>317</v>
       </c>
+      <c r="D311" t="s">
+        <v>429</v>
+      </c>
       <c r="E311" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F311" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="G311" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="312" spans="1:8">
       <c r="A312" t="s">
         <v>318</v>
       </c>
+      <c r="D312" t="s">
+        <v>429</v>
+      </c>
       <c r="E312" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F312" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="G312" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="313" spans="1:8">
       <c r="A313" t="s">
         <v>319</v>
       </c>
+      <c r="D313" t="s">
+        <v>429</v>
+      </c>
       <c r="E313" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F313" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="G313" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>1105</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="314" spans="1:8">
       <c r="A314" t="s">
         <v>320</v>
       </c>
+      <c r="D314" t="s">
+        <v>429</v>
+      </c>
       <c r="E314" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F314" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="G314" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>1106</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="315" spans="1:8">
       <c r="A315" t="s">
         <v>321</v>
       </c>
+      <c r="D315" t="s">
+        <v>429</v>
+      </c>
       <c r="E315" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F315" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="G315" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="316" spans="1:8">
       <c r="A316" t="s">
         <v>322</v>
       </c>
+      <c r="D316" t="s">
+        <v>429</v>
+      </c>
       <c r="E316" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F316" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="G316" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="317" spans="1:8">
       <c r="A317" t="s">
         <v>323</v>
       </c>
+      <c r="D317" t="s">
+        <v>429</v>
+      </c>
       <c r="E317" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F317" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="G317" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>1109</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="318" spans="1:8">
       <c r="A318" t="s">
         <v>324</v>
       </c>
+      <c r="D318" t="s">
+        <v>431</v>
+      </c>
       <c r="E318" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F318" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="G318" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>1110</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="319" spans="1:8">
       <c r="A319" t="s">
         <v>325</v>
       </c>
+      <c r="D319" t="s">
+        <v>429</v>
+      </c>
       <c r="E319" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F319" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="G319" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>1111</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="320" spans="1:8">
       <c r="A320" t="s">
         <v>326</v>
       </c>
+      <c r="D320" t="s">
+        <v>429</v>
+      </c>
       <c r="E320" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F320" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="G320" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>1112</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="321" spans="1:8">
       <c r="A321" t="s">
         <v>327</v>
       </c>
+      <c r="D321" t="s">
+        <v>429</v>
+      </c>
       <c r="E321" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F321" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="G321" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>1113</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="322" spans="1:8">
       <c r="A322" t="s">
         <v>328</v>
       </c>
+      <c r="D322" t="s">
+        <v>429</v>
+      </c>
       <c r="E322" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F322" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="G322" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>1114</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="323" spans="1:8">
       <c r="A323" t="s">
         <v>329</v>
       </c>
+      <c r="D323" t="s">
+        <v>429</v>
+      </c>
       <c r="E323" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F323" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="G323" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>1115</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="324" spans="1:8">
       <c r="A324" t="s">
         <v>330</v>
       </c>
+      <c r="D324" t="s">
+        <v>428</v>
+      </c>
       <c r="E324" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F324" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="G324" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="325" spans="1:8">
       <c r="A325" t="s">
         <v>331</v>
       </c>
+      <c r="D325" t="s">
+        <v>429</v>
+      </c>
       <c r="E325" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F325" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="G325" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="326" spans="1:8">
       <c r="A326" t="s">
         <v>332</v>
       </c>
+      <c r="D326" t="s">
+        <v>429</v>
+      </c>
       <c r="E326" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F326" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="G326" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>1118</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="327" spans="1:8">
       <c r="A327" t="s">
         <v>333</v>
       </c>
+      <c r="D327" t="s">
+        <v>429</v>
+      </c>
       <c r="E327" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F327" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="G327" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>1119</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="328" spans="1:8">
       <c r="A328" t="s">
         <v>334</v>
       </c>
+      <c r="D328" t="s">
+        <v>426</v>
+      </c>
       <c r="E328" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F328" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="G328" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>1120</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="329" spans="1:8">
       <c r="A329" t="s">
         <v>335</v>
       </c>
+      <c r="D329" t="s">
+        <v>431</v>
+      </c>
       <c r="E329" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F329" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="G329" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>1121</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="330" spans="1:8">
       <c r="A330" t="s">
         <v>336</v>
       </c>
+      <c r="D330" t="s">
+        <v>429</v>
+      </c>
       <c r="E330" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F330" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="G330" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="331" spans="1:8">
       <c r="A331" t="s">
         <v>337</v>
       </c>
+      <c r="D331" t="s">
+        <v>429</v>
+      </c>
       <c r="E331" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F331" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="G331" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>1123</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="332" spans="1:8">
       <c r="A332" t="s">
         <v>338</v>
       </c>
+      <c r="D332" t="s">
+        <v>429</v>
+      </c>
       <c r="E332" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F332" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="G332" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="333" spans="1:8">
       <c r="A333" t="s">
         <v>339</v>
       </c>
+      <c r="D333" t="s">
+        <v>429</v>
+      </c>
       <c r="E333" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F333" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="G333" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>1125</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="334" spans="1:8">
       <c r="A334" t="s">
         <v>340</v>
       </c>
+      <c r="D334" t="s">
+        <v>429</v>
+      </c>
       <c r="E334" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F334" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="G334" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>1126</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="335" spans="1:8">
       <c r="A335" t="s">
         <v>341</v>
       </c>
+      <c r="D335" t="s">
+        <v>429</v>
+      </c>
       <c r="E335" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F335" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="G335" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>1127</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="336" spans="1:8">
       <c r="A336" t="s">
         <v>342</v>
       </c>
+      <c r="D336" t="s">
+        <v>429</v>
+      </c>
       <c r="E336" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F336" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="G336" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>1128</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="337" spans="1:8">
       <c r="A337" t="s">
         <v>343</v>
       </c>
+      <c r="D337" t="s">
+        <v>428</v>
+      </c>
       <c r="E337" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F337" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="G337" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>1129</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="338" spans="1:8">
       <c r="A338" t="s">
         <v>344</v>
       </c>
+      <c r="D338" t="s">
+        <v>430</v>
+      </c>
       <c r="E338" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F338" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="G338" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>1130</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="339" spans="1:8">
       <c r="A339" t="s">
         <v>345</v>
       </c>
+      <c r="D339" t="s">
+        <v>429</v>
+      </c>
       <c r="E339" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F339" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="G339" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>1131</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="340" spans="1:8">
       <c r="A340" t="s">
         <v>346</v>
       </c>
+      <c r="D340" t="s">
+        <v>429</v>
+      </c>
       <c r="E340" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F340" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="G340" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="341" spans="1:8">
       <c r="A341" t="s">
         <v>347</v>
       </c>
+      <c r="D341" t="s">
+        <v>429</v>
+      </c>
       <c r="E341" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F341" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="G341" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>1133</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="342" spans="1:8">
       <c r="A342" t="s">
         <v>348</v>
       </c>
+      <c r="D342" t="s">
+        <v>429</v>
+      </c>
       <c r="E342" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F342" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="G342" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>1134</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="343" spans="1:8">
       <c r="A343" t="s">
         <v>349</v>
       </c>
+      <c r="D343" t="s">
+        <v>426</v>
+      </c>
       <c r="E343" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F343" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="G343" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>1135</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="344" spans="1:8">
       <c r="A344" t="s">
         <v>350</v>
       </c>
+      <c r="D344" t="s">
+        <v>429</v>
+      </c>
       <c r="E344" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F344" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="G344" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>1136</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="345" spans="1:8">
       <c r="A345" t="s">
         <v>351</v>
       </c>
+      <c r="D345" t="s">
+        <v>429</v>
+      </c>
       <c r="E345" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F345" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="G345" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="H345" s="2" t="s">
-        <v>1137</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="346" spans="1:8">
       <c r="A346" t="s">
         <v>352</v>
       </c>
+      <c r="D346" t="s">
+        <v>429</v>
+      </c>
       <c r="E346" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F346" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="G346" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H346" s="2" t="s">
-        <v>1138</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="347" spans="1:8">
       <c r="A347" t="s">
         <v>353</v>
       </c>
+      <c r="D347" t="s">
+        <v>429</v>
+      </c>
       <c r="E347" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F347" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="G347" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H347" s="2" t="s">
-        <v>1139</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="348" spans="1:8">
       <c r="A348" t="s">
         <v>354</v>
       </c>
+      <c r="D348" t="s">
+        <v>429</v>
+      </c>
       <c r="E348" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F348" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="G348" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H348" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="349" spans="1:8">
       <c r="A349" t="s">
         <v>355</v>
       </c>
+      <c r="D349" t="s">
+        <v>429</v>
+      </c>
       <c r="E349" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F349" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="G349" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>1141</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="350" spans="1:8">
       <c r="A350" t="s">
         <v>356</v>
       </c>
+      <c r="D350" t="s">
+        <v>429</v>
+      </c>
       <c r="E350" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F350" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="G350" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H350" s="2" t="s">
-        <v>1142</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="351" spans="1:8">
       <c r="A351" t="s">
         <v>357</v>
       </c>
+      <c r="D351" t="s">
+        <v>428</v>
+      </c>
       <c r="E351" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F351" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="G351" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="H351" s="2" t="s">
-        <v>1143</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="352" spans="1:8">
       <c r="A352" t="s">
         <v>358</v>
       </c>
+      <c r="D352" t="s">
+        <v>429</v>
+      </c>
       <c r="E352" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F352" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="G352" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H352" s="2" t="s">
-        <v>1144</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="353" spans="1:8">
       <c r="A353" t="s">
         <v>359</v>
       </c>
+      <c r="D353" t="s">
+        <v>431</v>
+      </c>
       <c r="E353" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F353" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="G353" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="H353" s="2" t="s">
-        <v>1145</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="354" spans="1:8">
       <c r="A354" t="s">
         <v>360</v>
       </c>
+      <c r="D354" t="s">
+        <v>429</v>
+      </c>
       <c r="E354" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F354" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="G354" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H354" s="2" t="s">
-        <v>1146</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="355" spans="1:8">
       <c r="A355" t="s">
         <v>361</v>
       </c>
+      <c r="D355" t="s">
+        <v>426</v>
+      </c>
       <c r="E355" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F355" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="G355" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H355" s="2" t="s">
-        <v>1147</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="356" spans="1:8">
       <c r="A356" t="s">
         <v>362</v>
       </c>
+      <c r="D356" t="s">
+        <v>429</v>
+      </c>
       <c r="E356" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F356" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="G356" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H356" s="2" t="s">
-        <v>1148</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="357" spans="1:8">
       <c r="A357" t="s">
         <v>363</v>
       </c>
+      <c r="D357" t="s">
+        <v>431</v>
+      </c>
       <c r="E357" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F357" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="G357" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="H357" s="2" t="s">
-        <v>1149</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="358" spans="1:8">
       <c r="A358" t="s">
         <v>364</v>
       </c>
+      <c r="D358" t="s">
+        <v>429</v>
+      </c>
       <c r="E358" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F358" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="G358" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="H358" s="2" t="s">
-        <v>1150</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="359" spans="1:8">
       <c r="A359" t="s">
         <v>365</v>
       </c>
+      <c r="D359" t="s">
+        <v>429</v>
+      </c>
       <c r="E359" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F359" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="G359" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H359" s="2" t="s">
-        <v>1151</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="360" spans="1:8">
       <c r="A360" t="s">
         <v>366</v>
       </c>
+      <c r="D360" t="s">
+        <v>429</v>
+      </c>
       <c r="E360" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F360" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="G360" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H360" s="2" t="s">
-        <v>1152</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="361" spans="1:8">
       <c r="A361" t="s">
         <v>367</v>
       </c>
+      <c r="D361" t="s">
+        <v>429</v>
+      </c>
       <c r="E361" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F361" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="G361" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H361" s="2" t="s">
-        <v>1153</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="362" spans="1:8">
       <c r="A362" t="s">
         <v>368</v>
       </c>
+      <c r="D362" t="s">
+        <v>429</v>
+      </c>
       <c r="E362" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F362" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="G362" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H362" s="2" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="363" spans="1:8">
       <c r="A363" t="s">
         <v>369</v>
       </c>
+      <c r="D363" t="s">
+        <v>431</v>
+      </c>
       <c r="E363" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F363" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="G363" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H363" s="2" t="s">
-        <v>1155</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="364" spans="1:8">
       <c r="A364" t="s">
         <v>370</v>
       </c>
+      <c r="D364" t="s">
+        <v>429</v>
+      </c>
       <c r="E364" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F364" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="G364" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H364" s="2" t="s">
-        <v>1156</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="365" spans="1:8">
       <c r="A365" t="s">
         <v>371</v>
       </c>
+      <c r="D365" t="s">
+        <v>429</v>
+      </c>
       <c r="E365" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F365" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="G365" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H365" s="2" t="s">
-        <v>1157</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="366" spans="1:8">
       <c r="A366" t="s">
         <v>372</v>
       </c>
+      <c r="D366" t="s">
+        <v>429</v>
+      </c>
       <c r="E366" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F366" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="G366" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H366" s="2" t="s">
-        <v>1158</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="367" spans="1:8">
       <c r="A367" t="s">
         <v>373</v>
       </c>
+      <c r="D367" t="s">
+        <v>426</v>
+      </c>
       <c r="E367" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F367" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="G367" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H367" s="2" t="s">
-        <v>1159</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="368" spans="1:8">
       <c r="A368" t="s">
         <v>374</v>
       </c>
+      <c r="D368" t="s">
+        <v>429</v>
+      </c>
       <c r="E368" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F368" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="G368" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="H368" s="2" t="s">
-        <v>1160</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="369" spans="1:8">
       <c r="A369" t="s">
         <v>375</v>
       </c>
+      <c r="D369" t="s">
+        <v>428</v>
+      </c>
       <c r="E369" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F369" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="G369" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H369" s="2" t="s">
-        <v>1161</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="370" spans="1:8">
       <c r="A370" t="s">
         <v>376</v>
       </c>
+      <c r="D370" t="s">
+        <v>427</v>
+      </c>
       <c r="E370" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F370" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="G370" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H370" s="2" t="s">
-        <v>1162</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="371" spans="1:8">
       <c r="A371" t="s">
         <v>377</v>
       </c>
+      <c r="D371" t="s">
+        <v>429</v>
+      </c>
       <c r="E371" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F371" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="G371" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="H371" s="2" t="s">
-        <v>1163</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="372" spans="1:8">
       <c r="A372" t="s">
         <v>378</v>
       </c>
+      <c r="D372" t="s">
+        <v>429</v>
+      </c>
       <c r="E372" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F372" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="G372" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H372" s="2" t="s">
-        <v>1164</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="373" spans="1:8">
       <c r="A373" t="s">
         <v>379</v>
       </c>
+      <c r="D373" t="s">
+        <v>429</v>
+      </c>
       <c r="E373" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F373" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="G373" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="H373" s="2" t="s">
-        <v>1165</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="374" spans="1:8">
       <c r="A374" t="s">
         <v>380</v>
       </c>
+      <c r="D374" t="s">
+        <v>429</v>
+      </c>
       <c r="E374" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F374" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="G374" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H374" s="2" t="s">
-        <v>1166</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="375" spans="1:8">
       <c r="A375" t="s">
         <v>381</v>
       </c>
+      <c r="D375" t="s">
+        <v>429</v>
+      </c>
       <c r="E375" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F375" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="G375" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H375" s="2" t="s">
-        <v>1167</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="376" spans="1:8">
       <c r="A376" t="s">
         <v>382</v>
       </c>
+      <c r="D376" t="s">
+        <v>426</v>
+      </c>
       <c r="E376" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F376" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="G376" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="H376" s="2" t="s">
-        <v>1168</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="377" spans="1:8">
       <c r="A377" t="s">
         <v>383</v>
       </c>
+      <c r="D377" t="s">
+        <v>429</v>
+      </c>
       <c r="E377" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F377" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="G377" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H377" s="2" t="s">
-        <v>1169</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="378" spans="1:8">
       <c r="A378" t="s">
         <v>384</v>
       </c>
+      <c r="D378" t="s">
+        <v>426</v>
+      </c>
       <c r="E378" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F378" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="G378" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H378" s="2" t="s">
-        <v>1170</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="379" spans="1:8">
       <c r="A379" t="s">
         <v>385</v>
       </c>
+      <c r="D379" t="s">
+        <v>429</v>
+      </c>
       <c r="E379" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F379" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="G379" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H379" s="2" t="s">
-        <v>1171</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="380" spans="1:8">
       <c r="A380" t="s">
         <v>386</v>
       </c>
+      <c r="D380" t="s">
+        <v>429</v>
+      </c>
       <c r="E380" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F380" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="G380" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H380" s="2" t="s">
-        <v>1172</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="381" spans="1:8">
       <c r="A381" t="s">
         <v>387</v>
       </c>
+      <c r="D381" t="s">
+        <v>429</v>
+      </c>
       <c r="E381" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F381" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="G381" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H381" s="2" t="s">
-        <v>1173</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="382" spans="1:8">
       <c r="A382" t="s">
         <v>388</v>
       </c>
+      <c r="D382" t="s">
+        <v>429</v>
+      </c>
       <c r="E382" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F382" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="G382" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H382" s="2" t="s">
-        <v>1174</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="383" spans="1:8">
       <c r="A383" t="s">
         <v>389</v>
       </c>
+      <c r="D383" t="s">
+        <v>431</v>
+      </c>
       <c r="E383" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F383" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="G383" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="H383" s="2" t="s">
-        <v>1175</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="384" spans="1:8">
       <c r="A384" t="s">
         <v>390</v>
       </c>
+      <c r="D384" t="s">
+        <v>426</v>
+      </c>
       <c r="E384" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F384" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="G384" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="H384" s="2" t="s">
-        <v>1176</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="385" spans="1:8">
       <c r="A385" t="s">
         <v>391</v>
       </c>
+      <c r="D385" t="s">
+        <v>429</v>
+      </c>
       <c r="E385" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F385" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="G385" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H385" s="2" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="386" spans="1:8">
       <c r="A386" t="s">
         <v>392</v>
       </c>
+      <c r="D386" t="s">
+        <v>426</v>
+      </c>
       <c r="E386" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F386" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="G386" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H386" s="2" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="387" spans="1:8">
       <c r="A387" t="s">
         <v>393</v>
       </c>
+      <c r="D387" t="s">
+        <v>429</v>
+      </c>
       <c r="E387" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F387" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="G387" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="H387" s="2" t="s">
-        <v>1179</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="388" spans="1:8">
       <c r="A388" t="s">
         <v>394</v>
       </c>
+      <c r="D388" t="s">
+        <v>426</v>
+      </c>
       <c r="E388" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F388" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="G388" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="H388" s="2" t="s">
-        <v>1180</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="389" spans="1:8">
@@ -11070,255 +12252,300 @@
       <c r="C389" t="s">
         <v>419</v>
       </c>
+      <c r="D389" t="s">
+        <v>429</v>
+      </c>
       <c r="E389" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F389" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="G389" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H389" s="2" t="s">
-        <v>1181</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="390" spans="1:8">
       <c r="A390" t="s">
         <v>396</v>
       </c>
+      <c r="D390" t="s">
+        <v>429</v>
+      </c>
       <c r="E390" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F390" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="G390" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H390" s="2" t="s">
-        <v>1182</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="391" spans="1:8">
       <c r="A391" t="s">
         <v>397</v>
       </c>
+      <c r="D391" t="s">
+        <v>429</v>
+      </c>
       <c r="E391" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F391" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="G391" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="H391" s="2" t="s">
-        <v>1183</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="392" spans="1:8">
       <c r="A392" t="s">
         <v>398</v>
       </c>
+      <c r="D392" t="s">
+        <v>429</v>
+      </c>
       <c r="E392" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F392" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="G392" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="H392" s="2" t="s">
-        <v>1184</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="393" spans="1:8">
       <c r="A393" t="s">
         <v>399</v>
       </c>
+      <c r="D393" t="s">
+        <v>429</v>
+      </c>
       <c r="E393" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F393" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="G393" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H393" s="2" t="s">
-        <v>1185</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="394" spans="1:8">
       <c r="A394" t="s">
         <v>400</v>
       </c>
+      <c r="D394" t="s">
+        <v>431</v>
+      </c>
       <c r="E394" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F394" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="G394" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="H394" s="2" t="s">
-        <v>1186</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="395" spans="1:8">
       <c r="A395" t="s">
         <v>401</v>
       </c>
+      <c r="D395" t="s">
+        <v>429</v>
+      </c>
       <c r="E395" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F395" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="G395" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="H395" s="2" t="s">
-        <v>1187</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="396" spans="1:8">
       <c r="A396" t="s">
         <v>402</v>
       </c>
+      <c r="D396" t="s">
+        <v>429</v>
+      </c>
       <c r="E396" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F396" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="G396" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H396" s="2" t="s">
-        <v>1188</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="397" spans="1:8">
       <c r="A397" t="s">
         <v>403</v>
       </c>
+      <c r="D397" t="s">
+        <v>429</v>
+      </c>
       <c r="E397" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F397" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="G397" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="H397" s="2" t="s">
-        <v>1189</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="398" spans="1:8">
       <c r="A398" t="s">
         <v>404</v>
       </c>
+      <c r="D398" t="s">
+        <v>429</v>
+      </c>
       <c r="E398" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F398" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="G398" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H398" s="2" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="399" spans="1:8">
       <c r="A399" t="s">
         <v>405</v>
       </c>
+      <c r="D399" t="s">
+        <v>429</v>
+      </c>
       <c r="E399" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F399" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="G399" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="H399" s="2" t="s">
-        <v>1191</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="400" spans="1:8">
       <c r="A400" t="s">
         <v>406</v>
       </c>
+      <c r="D400" t="s">
+        <v>429</v>
+      </c>
       <c r="E400" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F400" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="G400" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H400" s="2" t="s">
-        <v>1192</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="401" spans="1:8">
       <c r="A401" t="s">
         <v>407</v>
       </c>
+      <c r="D401" t="s">
+        <v>429</v>
+      </c>
       <c r="E401" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F401" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="G401" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H401" s="2" t="s">
-        <v>1193</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="402" spans="1:8">
       <c r="A402" t="s">
         <v>408</v>
       </c>
+      <c r="D402" t="s">
+        <v>429</v>
+      </c>
       <c r="E402" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F402" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="G402" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="H402" s="2" t="s">
-        <v>1194</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="403" spans="1:8">
       <c r="A403" t="s">
         <v>409</v>
       </c>
+      <c r="D403" t="s">
+        <v>429</v>
+      </c>
       <c r="E403" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F403" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="G403" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="H403" s="2" t="s">
-        <v>1195</v>
+        <v>1202</v>
       </c>
     </row>
   </sheetData>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H453"/>
+  <dimension ref="A1:H451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,12 +476,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2309,7 +2309,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>zahraugccreator0</t>
+          <t>pamela1987x</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2319,12 +2319,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2334,24 +2334,24 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-14 11:38:07</t>
+          <t>2026-08-04 08:14:05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zahraugccreator0</t>
+          <t>https://www.tiktok.com/@pamela1987x</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pamela1987x</t>
+          <t>zahraugccreator0</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-04 08:14:05</t>
+          <t>2026-08-14 11:38:07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@pamela1987x</t>
+          <t>https://www.tiktok.com/@zahraugccreator0</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -6761,7 +6761,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>lovelylis6</t>
+          <t>tatajatoba</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6771,12 +6771,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-15 07:43:05</t>
+          <t>2026-08-15 21:03:05</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -6796,14 +6796,14 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lovelylis6</t>
+          <t>https://www.tiktok.com/@tatajatoba</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>tatajatoba</t>
+          <t>lovelylis6</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-15 21:03:05</t>
+          <t>2026-08-15 07:43:05</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tatajatoba</t>
+          <t>https://www.tiktok.com/@lovelylis6</t>
         </is>
       </c>
     </row>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -7349,7 +7349,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>amymademebuyit</t>
+          <t>stefaniaiqra</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7364,34 +7364,34 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-08-10 09:26:13</t>
+          <t>2026-08-15 16:38:05</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amymademebuyit</t>
+          <t>https://www.tiktok.com/@stefaniaiqra</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>stefaniaiqra</t>
+          <t>amymademebuyit</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -7416,17 +7416,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-08-15 16:38:05</t>
+          <t>2026-08-10 09:26:13</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@stefaniaiqra</t>
+          <t>https://www.tiktok.com/@amymademebuyit</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -8273,7 +8273,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>lorrainepritchard1hotmai</t>
+          <t>chubby.nonny</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8283,39 +8283,39 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-08-15 02:10:05</t>
+          <t>2026-08-13 22:49:05</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lorrainepritchard1hotmai</t>
+          <t>https://www.tiktok.com/@chubby.nonny</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>chubby.nonny</t>
+          <t>lorrainepritchard1hotmai</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8325,32 +8325,32 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-08-13 22:49:05</t>
+          <t>2026-08-15 02:10:05</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chubby.nonny</t>
+          <t>https://www.tiktok.com/@lorrainepritchard1hotmai</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>naijahsdeals</t>
+          <t>life.in.a.reno</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8451,12 +8451,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -8466,24 +8466,24 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-08-15 08:57:07</t>
+          <t>2026-08-10 13:55:05</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@naijahsdeals</t>
+          <t>https://www.tiktok.com/@life.in.a.reno</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>life.in.a.reno</t>
+          <t>naijahsdeals</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -8508,17 +8508,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-10 13:55:05</t>
+          <t>2026-08-15 08:57:07</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@life.in.a.reno</t>
+          <t>https://www.tiktok.com/@naijahsdeals</t>
         </is>
       </c>
     </row>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -8735,116 +8735,116 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>teexvnn</t>
+          <t>gabbytiktokfinds</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-08-06 22:39:00</t>
+          <t>2026-08-13 20:42:05</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teexvnn</t>
+          <t>https://www.tiktok.com/@gabbytiktokfinds</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>temi4t</t>
+          <t>gennyiceevablazas</t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-08-11 08:40:06</t>
+          <t>2026-08-14 22:04:04</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@temi4t</t>
+          <t>https://www.tiktok.com/@gennyiceevablazas</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>temitayo0835</t>
+          <t>gillian.stevenson2</t>
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-08-12 14:54:19</t>
+          <t>2026-08-15 08:13:02</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@temitayo0835</t>
+          <t>https://www.tiktok.com/@gillian.stevenson2</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>temmiedee68</t>
+          <t>gla1890</t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -8854,24 +8854,24 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-08-14 18:09:35</t>
+          <t>2026-08-06 14:48:00</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@temmiedee68</t>
+          <t>https://www.tiktok.com/@gla1890</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>temmit7</t>
+          <t>gladysadjei43</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -8888,24 +8888,24 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-08-02 10:56:06</t>
+          <t>2026-08-04 19:48:23</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@temmit7</t>
+          <t>https://www.tiktok.com/@gladysadjei43</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>bimpy134</t>
+          <t>globalgee73</t>
         </is>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -8922,126 +8922,126 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-08-05 14:24:00</t>
+          <t>2026-08-02 14:48:45</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bimpy134</t>
+          <t>https://www.tiktok.com/@globalgee73</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>affiliateproductlinks</t>
+          <t>grabthedeal123</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-08-13 23:30:05</t>
+          <t>2026-08-02 22:40:50</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@affiliateproductlinks</t>
+          <t>https://www.tiktok.com/@grabthedeal123</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>afia7773</t>
+          <t>traetari1</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-08-12 13:41:03</t>
+          <t>2026-08-04 20:57:53</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@afia7773</t>
+          <t>https://www.tiktok.com/@traetari1</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>agyeibeauty31</t>
+          <t>triplehoney8</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-08-15 01:11:24</t>
+          <t>2026-08-05 09:12:57</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@agyeibeauty31</t>
+          <t>https://www.tiktok.com/@triplehoney8</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>emjems1</t>
+          <t>harryhav1</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
@@ -9053,46 +9053,46 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-08-14 07:41:05</t>
+          <t>2026-08-06 16:39:06</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@emjems1</t>
+          <t>https://www.tiktok.com/@harryhav1</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>enny5839</t>
+          <t>hazeraqureshy</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-08-14 19:31:16</t>
+          <t>2026-08-14 18:50:49</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -9102,14 +9102,14 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@enny5839</t>
+          <t>https://www.tiktok.com/@hazeraqureshy</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ernescoralzamor99</t>
+          <t>healthylifechanges</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -9121,22 +9121,22 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-08-14 00:44:21</t>
+          <t>2026-08-11 08:14:07</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ernescoralzamor99</t>
+          <t>https://www.tiktok.com/@healthylifechanges</t>
         </is>
       </c>
     </row>
@@ -9177,41 +9177,41 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>fatumaahmed914</t>
+          <t>yasminsar_110</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-08-10 02:48:38</t>
+          <t>2026-08-02 16:53:08</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fatumaahmed914</t>
+          <t>https://www.tiktok.com/@yasminsar_110</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>walex0880</t>
+          <t>yemisi_81</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-08-04 21:35:53</t>
+          <t>2026-08-04 10:04:07</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -9238,89 +9238,89 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@walex0880</t>
+          <t>https://www.tiktok.com/@yemisi_81</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>user.okikiwealth</t>
+          <t>zainab36576</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-08-01 13:23:25</t>
+          <t>2026-08-10 08:56:01</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user.okikiwealth</t>
+          <t>https://www.tiktok.com/@zainab36576</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>user18539263935775</t>
+          <t>emjems1</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-08-06 03:48:43</t>
+          <t>2026-08-14 07:41:05</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user18539263935775</t>
+          <t>https://www.tiktok.com/@emjems1</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>user2133928667610</t>
+          <t>enny5839</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -9330,58 +9330,58 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-08-04 22:38:37</t>
+          <t>2026-08-14 19:31:16</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2133928667610</t>
+          <t>https://www.tiktok.com/@enny5839</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>user22378493319474</t>
+          <t>ernescoralzamor99</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-08-06 08:27:00</t>
+          <t>2026-08-14 00:44:21</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user22378493319474</t>
+          <t>https://www.tiktok.com/@ernescoralzamor99</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>user2940653632458</t>
+          <t>user.okikiwealth</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -9398,24 +9398,24 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-08-02 09:13:03</t>
+          <t>2026-08-01 13:23:25</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2940653632458</t>
+          <t>https://www.tiktok.com/@user.okikiwealth</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>adunola.prestige</t>
+          <t>user18539263935775</t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -9432,31 +9432,31 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>2026-08-01 08:08:54</t>
+          <t>2026-08-06 03:48:43</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adunola.prestige</t>
+          <t>https://www.tiktok.com/@user18539263935775</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>itsh1yk</t>
+          <t>user2133928667610</t>
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -9466,65 +9466,65 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2026-08-14 05:47:05</t>
+          <t>2026-08-04 22:38:37</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itsh1yk</t>
+          <t>https://www.tiktok.com/@user2133928667610</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>dzidzor2</t>
+          <t>user22378493319474</t>
         </is>
       </c>
       <c r="B221" t="inlineStr"/>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2026-08-12 11:19:50</t>
+          <t>2026-08-06 08:27:00</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dzidzor2</t>
+          <t>https://www.tiktok.com/@user22378493319474</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>edith_braids23</t>
+          <t>user2940653632458</t>
         </is>
       </c>
       <c r="B222" t="inlineStr"/>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -9534,65 +9534,73 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-08-11 14:28:03</t>
+          <t>2026-08-02 09:13:03</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@edith_braids23</t>
+          <t>https://www.tiktok.com/@user2940653632458</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>craigbaker83</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr"/>
-      <c r="C223" t="inlineStr"/>
+          <t>em_j_10</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-08-06 16:31:52</t>
+          <t>2026-08-10 12:52:05</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@craigbaker83</t>
+          <t>https://www.tiktok.com/@em_j_10</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>iuliana.paun</t>
+          <t>heyitslindaxo</t>
         </is>
       </c>
       <c r="B224" t="inlineStr"/>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -9602,99 +9610,99 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2026-08-01 11:27:45</t>
+          <t>2026-08-11 08:47:05</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@iuliana.paun</t>
+          <t>https://www.tiktok.com/@heyitslindaxo</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>izzu.mama</t>
+          <t>hunbea91</t>
         </is>
       </c>
       <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-14 06:16:05</t>
+          <t>2026-08-07 12:08:05</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@izzu.mama</t>
+          <t>https://www.tiktok.com/@hunbea91</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>j_backupp123</t>
+          <t>i.sho03</t>
         </is>
       </c>
       <c r="B226" t="inlineStr"/>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-08-06 17:01:55</t>
+          <t>2026-08-14 22:51:16</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@j_backupp123</t>
+          <t>https://www.tiktok.com/@i.sho03</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>globalgee73</t>
+          <t>igbagbomi</t>
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -9704,31 +9712,31 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-08-02 14:48:45</t>
+          <t>2026-08-14 00:16:05</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@globalgee73</t>
+          <t>https://www.tiktok.com/@igbagbomi</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>grabthedeal123</t>
+          <t>inkednurseshop</t>
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -9738,31 +9746,31 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2026-08-02 22:40:50</t>
+          <t>2026-08-08 22:25:05</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@grabthedeal123</t>
+          <t>https://www.tiktok.com/@inkednurseshop</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>gurds_hundal</t>
+          <t>itsh1yk</t>
         </is>
       </c>
       <c r="B229" t="inlineStr"/>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -9772,24 +9780,24 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>2026-08-01 08:56:14</t>
+          <t>2026-08-14 05:47:05</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gurds_hundal</t>
+          <t>https://www.tiktok.com/@itsh1yk</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>hajiafolakekoleosorasaq</t>
+          <t>iuliana.paun</t>
         </is>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -9806,41 +9814,41 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2026-08-02 13:17:59</t>
+          <t>2026-08-01 11:27:45</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hajiafolakekoleosorasaq</t>
+          <t>https://www.tiktok.com/@iuliana.paun</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>halalqueen786</t>
+          <t>izzu.mama</t>
         </is>
       </c>
       <c r="B231" t="inlineStr"/>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-08-14 21:39:33</t>
+          <t>2026-08-14 06:16:05</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -9850,21 +9858,21 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@halalqueen786</t>
+          <t>https://www.tiktok.com/@izzu.mama</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>harfi93z</t>
+          <t>j_backupp123</t>
         </is>
       </c>
       <c r="B232" t="inlineStr"/>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -9874,31 +9882,31 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-08-03 11:38:05</t>
+          <t>2026-08-06 17:01:55</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@harfi93z</t>
+          <t>https://www.tiktok.com/@j_backupp123</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>harryhav1</t>
+          <t>gurds_hundal</t>
         </is>
       </c>
       <c r="B233" t="inlineStr"/>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -9908,58 +9916,58 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2026-08-06 16:39:06</t>
+          <t>2026-08-01 08:56:14</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@harryhav1</t>
+          <t>https://www.tiktok.com/@gurds_hundal</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>hazeraqureshy</t>
+          <t>hajiafolakekoleosorasaq</t>
         </is>
       </c>
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2026-08-14 18:50:49</t>
+          <t>2026-08-02 13:17:59</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hazeraqureshy</t>
+          <t>https://www.tiktok.com/@hajiafolakekoleosorasaq</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>healthylifechanges</t>
+          <t>halalqueen786</t>
         </is>
       </c>
       <c r="B235" t="inlineStr"/>
@@ -9971,63 +9979,63 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2026-08-11 08:14:07</t>
+          <t>2026-08-14 21:39:33</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@healthylifechanges</t>
+          <t>https://www.tiktok.com/@halalqueen786</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>joodjood758</t>
+          <t>harfi93z</t>
         </is>
       </c>
       <c r="B236" t="inlineStr"/>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2026-08-09 01:27:55</t>
+          <t>2026-08-03 11:38:05</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@joodjood758</t>
+          <t>https://www.tiktok.com/@harfi93z</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>joseeskobar3</t>
+          <t>ladyoginni</t>
         </is>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -10044,65 +10052,73 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-08-05 00:55:05</t>
+          <t>2026-08-02 17:06:03</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@joseeskobar3</t>
+          <t>https://www.tiktok.com/@ladyoginni</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>junethebrand</t>
+          <t>lifeassamantha</t>
         </is>
       </c>
       <c r="B238" t="inlineStr"/>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-08-14 07:25:06</t>
+          <t>2026-08-09 22:47:05</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@junethebrand</t>
+          <t>https://www.tiktok.com/@lifeassamantha</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>kalisworld_yt</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr"/>
-      <c r="C239" t="inlineStr"/>
+          <t>lifeoflucy94</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -10112,31 +10128,31 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-08-11 19:53:06</t>
+          <t>2026-08-10 12:37:05</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kalisworld_yt</t>
+          <t>https://www.tiktok.com/@lifeoflucy94</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>heyitslindaxo</t>
+          <t>jasmineleahxox</t>
         </is>
       </c>
       <c r="B240" t="inlineStr"/>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -10146,92 +10162,92 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>2026-08-11 08:47:05</t>
+          <t>2026-08-07 22:48:05</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@heyitslindaxo</t>
+          <t>https://www.tiktok.com/@jasmineleahxox</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>hunbea91</t>
+          <t>jasontiktok4589</t>
         </is>
       </c>
       <c r="B241" t="inlineStr"/>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>2026-08-07 12:08:05</t>
+          <t>2026-08-05 09:08:16</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hunbea91</t>
+          <t>https://www.tiktok.com/@jasontiktok4589</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>i.sho03</t>
+          <t>jeanny_uch</t>
         </is>
       </c>
       <c r="B242" t="inlineStr"/>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>2026-08-14 22:51:16</t>
+          <t>2026-08-03 20:12:45</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@i.sho03</t>
+          <t>https://www.tiktok.com/@jeanny_uch</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>igbagbomi</t>
+          <t>joodjood758</t>
         </is>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -10243,36 +10259,36 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>2026-08-14 00:16:05</t>
+          <t>2026-08-09 01:27:55</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@igbagbomi</t>
+          <t>https://www.tiktok.com/@joodjood758</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>inkednurseshop</t>
+          <t>joseeskobar3</t>
         </is>
       </c>
       <c r="B244" t="inlineStr"/>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -10282,24 +10298,24 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>2026-08-08 22:25:05</t>
+          <t>2026-08-05 00:55:05</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@inkednurseshop</t>
+          <t>https://www.tiktok.com/@joseeskobar3</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>jasmineleahxox</t>
+          <t>junethebrand</t>
         </is>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -10311,70 +10327,70 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>2026-08-07 22:48:05</t>
+          <t>2026-08-14 07:25:06</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jasmineleahxox</t>
+          <t>https://www.tiktok.com/@junethebrand</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>jasontiktok4589</t>
+          <t>kalisworld_yt</t>
         </is>
       </c>
       <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>2026-08-05 09:08:16</t>
+          <t>2026-08-11 19:53:06</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jasontiktok4589</t>
+          <t>https://www.tiktok.com/@kalisworld_yt</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>jeanny_uch</t>
+          <t>kashmirri8</t>
         </is>
       </c>
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -10384,24 +10400,24 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>2026-08-03 20:12:45</t>
+          <t>2026-08-06 09:58:13</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jeanny_uch</t>
+          <t>https://www.tiktok.com/@kashmirri8</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>kayskirado</t>
+          <t>katalinguti</t>
         </is>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -10418,66 +10434,58 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>2026-08-03 20:45:36</t>
+          <t>2026-08-04 07:12:10</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kayskirado</t>
+          <t>https://www.tiktok.com/@katalinguti</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>kazza1992</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>dawn294066</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
+      <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-08-15 01:48:05</t>
+          <t>2026-08-01 21:06:12</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kazza1992</t>
+          <t>https://www.tiktok.com/@dawn294066</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>khadijamukhtar621</t>
+          <t>dealcheffinds</t>
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
@@ -10494,24 +10502,24 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>2026-08-14 13:30:35</t>
+          <t>2026-08-12 07:04:05</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@khadijamukhtar621</t>
+          <t>https://www.tiktok.com/@dealcheffinds</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>khurramsoori</t>
+          <t>dejaysol</t>
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -10528,65 +10536,65 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2026-08-03 07:41:43</t>
+          <t>2026-08-01 19:37:01</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@khurramsoori</t>
+          <t>https://www.tiktok.com/@dejaysol</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>kingmxn</t>
+          <t>deliciousmunch_</t>
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2026-08-11 19:53:06</t>
+          <t>2026-08-05 11:59:54</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kingmxn</t>
+          <t>https://www.tiktok.com/@deliciousmunch_</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>vickyvickss3</t>
+          <t>delilah1910</t>
         </is>
       </c>
       <c r="B253" t="inlineStr"/>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -10596,58 +10604,58 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2026-08-11 17:41:09</t>
+          <t>2026-08-09 19:46:17</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vickyvickss3</t>
+          <t>https://www.tiktok.com/@delilah1910</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>victoriaookoro</t>
+          <t>denelos1</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>2026-08-01 07:47:19</t>
+          <t>2026-08-07 07:52:06</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@victoriaookoro</t>
+          <t>https://www.tiktok.com/@denelos1</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>viralnestdailydeals</t>
+          <t>dipu.vyas</t>
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -10664,24 +10672,24 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>2026-08-05 09:39:06</t>
+          <t>2026-08-07 14:45:52</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@viralnestdailydeals</t>
+          <t>https://www.tiktok.com/@dipu.vyas</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>champagnnne20</t>
+          <t>kavi5ll</t>
         </is>
       </c>
       <c r="B256" t="inlineStr"/>
@@ -10698,7 +10706,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>2026-08-03 21:16:29</t>
+          <t>2026-08-03 07:40:33</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -10708,21 +10716,21 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@champagnnne20</t>
+          <t>https://www.tiktok.com/@kavi5ll</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>chanda_cart</t>
+          <t>kayskirado</t>
         </is>
       </c>
       <c r="B257" t="inlineStr"/>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -10732,58 +10740,66 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-07 14:50:05</t>
+          <t>2026-08-03 20:45:36</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chanda_cart</t>
+          <t>https://www.tiktok.com/@kayskirado</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>cherylboateng</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr"/>
-      <c r="C258" t="inlineStr"/>
+          <t>kazza1992</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>2026-08-07 07:09:09</t>
+          <t>2026-08-15 01:48:05</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cherylboateng</t>
+          <t>https://www.tiktok.com/@kazza1992</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>chillimilli385</t>
+          <t>khadijamukhtar621</t>
         </is>
       </c>
       <c r="B259" t="inlineStr"/>
@@ -10800,31 +10816,31 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>2026-08-09 15:57:05</t>
+          <t>2026-08-14 13:30:35</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chillimilli385</t>
+          <t>https://www.tiktok.com/@khadijamukhtar621</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>vytyglrl</t>
+          <t>khurramsoori</t>
         </is>
       </c>
       <c r="B260" t="inlineStr"/>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -10834,31 +10850,31 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>2026-08-01 01:52:28</t>
+          <t>2026-08-03 07:41:43</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vytyglrl</t>
+          <t>https://www.tiktok.com/@khurramsoori</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>cupcake88807</t>
+          <t>kingmxn</t>
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -10868,31 +10884,31 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>2026-08-12 08:45:34</t>
+          <t>2026-08-11 19:53:06</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cupcake88807</t>
+          <t>https://www.tiktok.com/@kingmxn</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>cutebells14</t>
+          <t>kollinton777</t>
         </is>
       </c>
       <c r="B262" t="inlineStr"/>
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -10902,7 +10918,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>2026-08-11 08:40:06</t>
+          <t>2026-08-11 19:56:12</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -10912,55 +10928,55 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cutebells14</t>
+          <t>https://www.tiktok.com/@kollinton777</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>cynthiaadeolaobaf</t>
+          <t>kymfragrancehouse</t>
         </is>
       </c>
       <c r="B263" t="inlineStr"/>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>2026-08-02 08:36:28</t>
+          <t>2026-08-06 15:46:06</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cynthiaadeolaobaf</t>
+          <t>https://www.tiktok.com/@kymfragrancehouse</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>florida_745</t>
+          <t>maame.yaa8943</t>
         </is>
       </c>
       <c r="B264" t="inlineStr"/>
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -10970,31 +10986,31 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>2026-08-03 23:59:55</t>
+          <t>2026-08-12 01:19:22</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@florida_745</t>
+          <t>https://www.tiktok.com/@maame.yaa8943</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>funmilayoyinloye</t>
+          <t>mabinty_kamara</t>
         </is>
       </c>
       <c r="B265" t="inlineStr"/>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -11004,92 +11020,92 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-08-04 20:44:06</t>
+          <t>2026-08-06 12:24:38</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@funmilayoyinloye</t>
+          <t>https://www.tiktok.com/@mabinty_kamara</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>gabbytiktokfinds</t>
+          <t>maecacuenca</t>
         </is>
       </c>
       <c r="B266" t="inlineStr"/>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>2026-08-13 20:42:05</t>
+          <t>2026-08-06 18:20:18</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gabbytiktokfinds</t>
+          <t>https://www.tiktok.com/@maecacuenca</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>gennyiceevablazas</t>
+          <t>mahder810</t>
         </is>
       </c>
       <c r="B267" t="inlineStr"/>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>2026-08-14 22:04:04</t>
+          <t>2026-08-05 22:53:35</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gennyiceevablazas</t>
+          <t>https://www.tiktok.com/@mahder810</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>gillian.stevenson2</t>
+          <t>mammyoeqvs3</t>
         </is>
       </c>
       <c r="B268" t="inlineStr"/>
@@ -11106,24 +11122,24 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>2026-08-15 08:13:02</t>
+          <t>2026-08-13 16:08:17</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gillian.stevenson2</t>
+          <t>https://www.tiktok.com/@mammyoeqvs3</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>gla1890</t>
+          <t>mark.hyde2</t>
         </is>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -11140,100 +11156,92 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>2026-08-06 14:48:00</t>
+          <t>2026-08-02 09:49:39</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gla1890</t>
+          <t>https://www.tiktok.com/@mark.hyde2</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>gladysadjei43</t>
+          <t>martinalast</t>
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>2026-08-04 19:48:23</t>
+          <t>2026-08-13 11:03:49</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gladysadjei43</t>
+          <t>https://www.tiktok.com/@martinalast</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>em_j_10</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>marvel_ola21</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+      <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>2026-08-10 12:52:05</t>
+          <t>2026-08-07 12:08:06</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@em_j_10</t>
+          <t>https://www.tiktok.com/@marvel_ola21</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>beekaylux20</t>
+          <t>michm603</t>
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -11250,31 +11258,31 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>2026-08-05 23:21:36</t>
+          <t>2026-08-03 17:23:30</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beekaylux20</t>
+          <t>https://www.tiktok.com/@michm603</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>kollinton777</t>
+          <t>lisa.lashes</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -11284,7 +11292,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-08-11 19:56:12</t>
+          <t>2026-08-11 19:53:05</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -11294,14 +11302,14 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kollinton777</t>
+          <t>https://www.tiktok.com/@lisa.lashes</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>kashmirri8</t>
+          <t>lisajwildes</t>
         </is>
       </c>
       <c r="B274" t="inlineStr"/>
@@ -11318,24 +11326,24 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>2026-08-06 09:58:13</t>
+          <t>2026-08-01 17:16:21</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kashmirri8</t>
+          <t>https://www.tiktok.com/@lisajwildes</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>katalinguti</t>
+          <t>livinglegend839</t>
         </is>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -11352,24 +11360,24 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>2026-08-04 07:12:10</t>
+          <t>2026-08-02 23:14:52</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@katalinguti</t>
+          <t>https://www.tiktok.com/@livinglegend839</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>kavi5ll</t>
+          <t>look23320</t>
         </is>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -11386,17 +11394,17 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>2026-08-03 07:40:33</t>
+          <t>2026-08-02 09:59:42</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kavi5ll</t>
+          <t>https://www.tiktok.com/@look23320</t>
         </is>
       </c>
     </row>
@@ -11505,41 +11513,41 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>dawn294066</t>
+          <t>fatoutouray13</t>
         </is>
       </c>
       <c r="B280" t="inlineStr"/>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-08-01 21:06:12</t>
+          <t>2026-08-09 20:50:33</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dawn294066</t>
+          <t>https://www.tiktok.com/@fatoutouray13</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>dealcheffinds</t>
+          <t>fatumaahmed914</t>
         </is>
       </c>
       <c r="B281" t="inlineStr"/>
@@ -11551,29 +11559,29 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>2026-08-12 07:04:05</t>
+          <t>2026-08-10 02:48:38</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dealcheffinds</t>
+          <t>https://www.tiktok.com/@fatumaahmed914</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>dejaysol</t>
+          <t>felixpowez0</t>
         </is>
       </c>
       <c r="B282" t="inlineStr"/>
@@ -11590,31 +11598,31 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>2026-08-01 19:37:01</t>
+          <t>2026-08-02 05:46:54</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dejaysol</t>
+          <t>https://www.tiktok.com/@felixpowez0</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>deliciousmunch_</t>
+          <t>fentonadventure</t>
         </is>
       </c>
       <c r="B283" t="inlineStr"/>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -11624,65 +11632,65 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>2026-08-05 11:59:54</t>
+          <t>2026-08-12 18:12:07</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@deliciousmunch_</t>
+          <t>https://www.tiktok.com/@fentonadventure</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>delilah1910</t>
+          <t>florida_745</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>2026-08-09 19:46:17</t>
+          <t>2026-08-03 23:59:55</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@delilah1910</t>
+          <t>https://www.tiktok.com/@florida_745</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>look23320</t>
+          <t>funmilayoyinloye</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -11692,24 +11700,24 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>2026-08-02 09:59:42</t>
+          <t>2026-08-04 20:44:06</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@look23320</t>
+          <t>https://www.tiktok.com/@funmilayoyinloye</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>muhammedasif380</t>
+          <t>christinemaughan4</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
@@ -11726,24 +11734,24 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>2026-08-06 08:34:46</t>
+          <t>2026-08-05 16:46:16</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@muhammedasif380</t>
+          <t>https://www.tiktok.com/@christinemaughan4</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>mummsyboy</t>
+          <t>coolestinfluencer1</t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -11760,92 +11768,100 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>2026-08-10 05:20:18</t>
+          <t>2026-08-06 15:49:05</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mummsyboy</t>
+          <t>https://www.tiktok.com/@coolestinfluencer1</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>andreadavies903</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr"/>
-      <c r="C288" t="inlineStr"/>
+          <t>courage.ik</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>2026-08-01 22:54:24</t>
+          <t>2026-08-15 14:23:05</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@andreadavies903</t>
+          <t>https://www.tiktok.com/@courage.ik</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>annamarie_s</t>
+          <t>courtneygirlmum</t>
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-07 14:50:05</t>
+          <t>2026-08-14 00:17:05</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@annamarie_s</t>
+          <t>https://www.tiktok.com/@courtneygirlmum</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>annwakonyo82</t>
+          <t>craigbaker83</t>
         </is>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -11862,183 +11878,167 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>2026-08-03 08:01:11</t>
+          <t>2026-08-06 16:31:52</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@annwakonyo82</t>
+          <t>https://www.tiktok.com/@craigbaker83</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>arinolavictory</t>
+          <t>cupcake88807</t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>2026-08-01 12:59:45</t>
+          <t>2026-08-12 08:45:34</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@arinolavictory</t>
+          <t>https://www.tiktok.com/@cupcake88807</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ash01703</t>
+          <t>cutebells14</t>
         </is>
       </c>
       <c r="B292" t="inlineStr"/>
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>2026-08-04 08:26:07</t>
+          <t>2026-08-11 08:40:06</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ash01703</t>
+          <t>https://www.tiktok.com/@cutebells14</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>azizanso</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>loyrodatips</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr"/>
+      <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>2026-08-04 17:14:44</t>
+          <t>2026-08-15 12:26:23</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@azizanso</t>
+          <t>https://www.tiktok.com/@loyrodatips</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>beautycontrol_by_nikky1</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>miglenasabeva123</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr"/>
+      <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>2026-08-04 11:31:54</t>
+          <t>2026-08-07 19:19:21</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beautycontrol_by_nikky1</t>
+          <t>https://www.tiktok.com/@miglenasabeva123</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>bee.finds_</t>
+          <t>mosesademola05</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -12048,58 +12048,58 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>2026-08-04 08:14:06</t>
+          <t>2026-08-06 17:17:21</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bee.finds_</t>
+          <t>https://www.tiktok.com/@mosesademola05</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>mammyoeqvs3</t>
+          <t>mosh77265</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>2026-08-13 16:08:17</t>
+          <t>2026-08-05 00:04:34</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mammyoeqvs3</t>
+          <t>https://www.tiktok.com/@mosh77265</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>mark.hyde2</t>
+          <t>motunrayo.adelowo</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -12116,99 +12116,99 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>2026-08-02 09:49:39</t>
+          <t>2026-08-03 13:30:07</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mark.hyde2</t>
+          <t>https://www.tiktok.com/@motunrayo.adelowo</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>martinalast</t>
+          <t>muhammedasif380</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-08-13 11:03:49</t>
+          <t>2026-08-06 08:34:46</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@martinalast</t>
+          <t>https://www.tiktok.com/@muhammedasif380</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>nikkib2311</t>
+          <t>chrisnnamani7</t>
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>2026-08-14 22:13:05</t>
+          <t>2026-08-07 08:50:04</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nikkib2311</t>
+          <t>https://www.tiktok.com/@chrisnnamani7</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>nikky_vibez</t>
+          <t>dorathy.ochokwu</t>
         </is>
       </c>
       <c r="B300" t="inlineStr"/>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -12218,65 +12218,65 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>2026-08-11 12:48:54</t>
+          <t>2026-08-04 16:17:55</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nikky_vibez</t>
+          <t>https://www.tiktok.com/@dorathy.ochokwu</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>nipay3foon123</t>
+          <t>dorinepride</t>
         </is>
       </c>
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>2026-08-12 23:16:58</t>
+          <t>2026-08-02 17:19:48</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nipay3foon123</t>
+          <t>https://www.tiktok.com/@dorinepride</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>marvel_ola21</t>
+          <t>dreamcatcher00730</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -12286,58 +12286,58 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>2026-08-07 12:08:06</t>
+          <t>2026-08-06 15:31:17</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@marvel_ola21</t>
+          <t>https://www.tiktok.com/@dreamcatcher00730</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>kymfragrancehouse</t>
+          <t>drlove925</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06</t>
+          <t>2026-08-07 13:22:06</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kymfragrancehouse</t>
+          <t>https://www.tiktok.com/@drlove925</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ladyoginni</t>
+          <t>dwellingtonx</t>
         </is>
       </c>
       <c r="B304" t="inlineStr"/>
@@ -12354,104 +12354,104 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>2026-08-02 17:06:03</t>
+          <t>2026-08-01 10:36:28</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ladyoginni</t>
+          <t>https://www.tiktok.com/@dwellingtonx</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>lifeassamantha</t>
+          <t>dzidzor2</t>
         </is>
       </c>
       <c r="B305" t="inlineStr"/>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>2026-08-09 22:47:05</t>
+          <t>2026-08-12 11:19:50</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifeassamantha</t>
+          <t>https://www.tiktok.com/@dzidzor2</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>lifeoflucy94</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>edith_braids23</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr"/>
+      <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>2026-08-10 12:37:05</t>
+          <t>2026-08-11 14:28:03</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifeoflucy94</t>
+          <t>https://www.tiktok.com/@edith_braids23</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>lisa.lashes</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr"/>
-      <c r="C307" t="inlineStr"/>
+          <t>facelessliligood</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D307" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -12464,24 +12464,24 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-08-11 19:53:05</t>
+          <t>2026-08-10 10:47:15</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lisa.lashes</t>
+          <t>https://www.tiktok.com/@facelessliligood</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>lisajwildes</t>
+          <t>fainaksalih</t>
         </is>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -12498,31 +12498,31 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>2026-08-01 17:16:21</t>
+          <t>2026-08-07 14:00:12</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lisajwildes</t>
+          <t>https://www.tiktok.com/@fainaksalih</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>livinglegend839</t>
+          <t>chanda_cart</t>
         </is>
       </c>
       <c r="B309" t="inlineStr"/>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -12532,41 +12532,41 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>2026-08-02 23:14:52</t>
+          <t>2026-08-07 14:50:05</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@livinglegend839</t>
+          <t>https://www.tiktok.com/@chanda_cart</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>miglenasabeva123</t>
+          <t>cherylboateng</t>
         </is>
       </c>
       <c r="B310" t="inlineStr"/>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>2026-08-07 19:19:21</t>
+          <t>2026-08-07 07:09:09</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -12576,14 +12576,14 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@miglenasabeva123</t>
+          <t>https://www.tiktok.com/@cherylboateng</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>benjalooywd</t>
+          <t>cynthiaadeolaobaf</t>
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -12600,92 +12600,92 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-08-03 09:06:41</t>
+          <t>2026-08-02 08:36:28</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benjalooywd</t>
+          <t>https://www.tiktok.com/@cynthiaadeolaobaf</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>mosesademola05</t>
+          <t>mummsyboy</t>
         </is>
       </c>
       <c r="B312" t="inlineStr"/>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>2026-08-06 17:17:21</t>
+          <t>2026-08-10 05:20:18</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mosesademola05</t>
+          <t>https://www.tiktok.com/@mummsyboy</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>mosh77265</t>
+          <t>nadia98154</t>
         </is>
       </c>
       <c r="B313" t="inlineStr"/>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>2026-08-05 00:04:34</t>
+          <t>2026-08-15 04:36:05</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mosh77265</t>
+          <t>https://www.tiktok.com/@nadia98154</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>motunrayo.adelowo</t>
+          <t>nafisatu_allassani</t>
         </is>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -12702,31 +12702,39 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>2026-08-03 13:30:07</t>
+          <t>2026-08-01 16:56:10</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@motunrayo.adelowo</t>
+          <t>https://www.tiktok.com/@nafisatu_allassani</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>nafisatu_allassani</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr"/>
-      <c r="C315" t="inlineStr"/>
+          <t>neavemariep</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -12736,31 +12744,31 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>2026-08-01 16:56:10</t>
+          <t>2026-08-14 20:25:05</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nafisatu_allassani</t>
+          <t>https://www.tiktok.com/@neavemariep</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>berniceamong</t>
+          <t>nenyebourdillon</t>
         </is>
       </c>
       <c r="B316" t="inlineStr"/>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -12770,49 +12778,41 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>2026-08-03 15:51:52</t>
+          <t>2026-08-01 06:39:16</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@berniceamong</t>
+          <t>https://www.tiktok.com/@nenyebourdillon</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>neavemariep</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>nikkib2311</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr"/>
+      <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>2026-08-14 20:25:05</t>
+          <t>2026-08-14 22:13:05</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -12822,21 +12822,21 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@neavemariep</t>
+          <t>https://www.tiktok.com/@nikkib2311</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>nenyebourdillon</t>
+          <t>nikky_vibez</t>
         </is>
       </c>
       <c r="B318" t="inlineStr"/>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -12846,24 +12846,24 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>2026-08-01 06:39:16</t>
+          <t>2026-08-11 12:48:54</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nenyebourdillon</t>
+          <t>https://www.tiktok.com/@nikky_vibez</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>adunni__taylor</t>
+          <t>nipay3foon123</t>
         </is>
       </c>
       <c r="B319" t="inlineStr"/>
@@ -12875,36 +12875,36 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>2026-08-06 16:07:06</t>
+          <t>2026-08-12 23:16:58</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adunni__taylor</t>
+          <t>https://www.tiktok.com/@nipay3foon123</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>nadia98154</t>
+          <t>nish_93syeda</t>
         </is>
       </c>
       <c r="B320" t="inlineStr"/>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -12914,65 +12914,65 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>2026-08-15 04:36:05</t>
+          <t>2026-08-02 12:33:41</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nadia98154</t>
+          <t>https://www.tiktok.com/@nish_93syeda</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>loyrodatips</t>
+          <t>nisham010</t>
         </is>
       </c>
       <c r="B321" t="inlineStr"/>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-15 12:26:23</t>
+          <t>2026-08-01 06:41:58</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@loyrodatips</t>
+          <t>https://www.tiktok.com/@nisham010</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>maame.yaa8943</t>
+          <t>norashkute</t>
         </is>
       </c>
       <c r="B322" t="inlineStr"/>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -12982,58 +12982,58 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>2026-08-12 01:19:22</t>
+          <t>2026-08-05 19:03:41</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maame.yaa8943</t>
+          <t>https://www.tiktok.com/@norashkute</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>mabinty_kamara</t>
+          <t>midas5267</t>
         </is>
       </c>
       <c r="B323" t="inlineStr"/>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>2026-08-06 12:24:38</t>
+          <t>2026-08-15 02:57:38</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mabinty_kamara</t>
+          <t>https://www.tiktok.com/@midas5267</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>maecacuenca</t>
+          <t>queenc023</t>
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -13050,24 +13050,24 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>2026-08-06 18:20:18</t>
+          <t>2026-08-02 23:20:03</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maecacuenca</t>
+          <t>https://www.tiktok.com/@queenc023</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>mahder810</t>
+          <t>queenlady7354</t>
         </is>
       </c>
       <c r="B325" t="inlineStr"/>
@@ -13084,31 +13084,31 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>2026-08-05 22:53:35</t>
+          <t>2026-08-07 07:05:09</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mahder810</t>
+          <t>https://www.tiktok.com/@queenlady7354</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>courtneygirlmum</t>
+          <t>quentinnke</t>
         </is>
       </c>
       <c r="B326" t="inlineStr"/>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -13118,58 +13118,58 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>2026-08-14 00:17:05</t>
+          <t>2026-08-06 18:38:45</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@courtneygirlmum</t>
+          <t>https://www.tiktok.com/@quentinnke</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>blessing91726</t>
+          <t>octimove</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>2026-08-08 08:05:43</t>
+          <t>2026-08-06 20:35:34</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blessing91726</t>
+          <t>https://www.tiktok.com/@octimove</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>blesswithlove1</t>
+          <t>odubele.2177</t>
         </is>
       </c>
       <c r="B328" t="inlineStr"/>
@@ -13186,31 +13186,31 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>2026-08-02 17:56:53</t>
+          <t>2026-08-04 10:42:50</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blesswithlove1</t>
+          <t>https://www.tiktok.com/@odubele.2177</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>bobbin.sense</t>
+          <t>off.duty.ninja6</t>
         </is>
       </c>
       <c r="B329" t="inlineStr"/>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -13220,24 +13220,24 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>2026-08-05 09:39:08</t>
+          <t>2026-08-14 17:30:05</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bobbin.sense</t>
+          <t>https://www.tiktok.com/@off.duty.ninja6</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>bolaji.lukas</t>
+          <t>ogboduprincess1</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -13254,31 +13254,31 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>2026-08-03 20:46:20</t>
+          <t>2026-08-06 10:18:22</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bolaji.lukas</t>
+          <t>https://www.tiktok.com/@ogboduprincess1</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>radical818</t>
+          <t>okemorenikerachea</t>
         </is>
       </c>
       <c r="B331" t="inlineStr"/>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -13288,24 +13288,24 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-08-08 12:59:20</t>
+          <t>2026-08-12 09:21:47</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@radical818</t>
+          <t>https://www.tiktok.com/@okemorenikerachea</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>octimove</t>
+          <t>bozia247</t>
         </is>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -13322,24 +13322,24 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>2026-08-06 20:35:34</t>
+          <t>2026-08-02 15:51:28</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@octimove</t>
+          <t>https://www.tiktok.com/@bozia247</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>odubele.2177</t>
+          <t>bukola_sole</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -13356,58 +13356,58 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>2026-08-04 10:42:50</t>
+          <t>2026-08-02 22:15:14</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@odubele.2177</t>
+          <t>https://www.tiktok.com/@bukola_sole</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>off.duty.ninja6</t>
+          <t>bukolaadee</t>
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
       <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>2026-08-14 17:30:05</t>
+          <t>2026-08-08 09:20:44</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@off.duty.ninja6</t>
+          <t>https://www.tiktok.com/@bukolaadee</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>ogboduprincess1</t>
+          <t>busivincent</t>
         </is>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -13424,7 +13424,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>2026-08-06 10:18:22</t>
+          <t>2026-08-06 14:40:06</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -13434,21 +13434,21 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ogboduprincess1</t>
+          <t>https://www.tiktok.com/@busivincent</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>nish_93syeda</t>
+          <t>carinadyarte</t>
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
       <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -13458,24 +13458,24 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>2026-08-02 12:33:41</t>
+          <t>2026-08-15 17:25:05</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nish_93syeda</t>
+          <t>https://www.tiktok.com/@carinadyarte</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>nisham010</t>
+          <t>carolducasse2</t>
         </is>
       </c>
       <c r="B337" t="inlineStr"/>
@@ -13492,7 +13492,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>2026-08-01 06:41:58</t>
+          <t>2026-08-01 12:23:54</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -13502,48 +13502,48 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nisham010</t>
+          <t>https://www.tiktok.com/@carolducasse2</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>_clarahayes</t>
+          <t>celestialcreations1981</t>
         </is>
       </c>
       <c r="B338" t="inlineStr"/>
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>2026-08-10 19:37:05</t>
+          <t>2026-08-05 11:42:44</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_clarahayes</t>
+          <t>https://www.tiktok.com/@celestialcreations1981</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>norashkute</t>
+          <t>champagnnne20</t>
         </is>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -13560,24 +13560,24 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>2026-08-05 19:03:41</t>
+          <t>2026-08-03 21:16:29</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@norashkute</t>
+          <t>https://www.tiktok.com/@champagnnne20</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>michm603</t>
+          <t>teexvnn</t>
         </is>
       </c>
       <c r="B340" t="inlineStr"/>
@@ -13594,31 +13594,31 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>2026-08-03 17:23:30</t>
+          <t>2026-08-06 22:39:00</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@michm603</t>
+          <t>https://www.tiktok.com/@teexvnn</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>midas5267</t>
+          <t>bexbestbuys</t>
         </is>
       </c>
       <c r="B341" t="inlineStr"/>
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -13628,58 +13628,58 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-08-15 02:57:38</t>
+          <t>2026-08-11 19:53:05</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@midas5267</t>
+          <t>https://www.tiktok.com/@bexbestbuys</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>oluwafunke.taiwo3</t>
+          <t>bignastrolytic</t>
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-08-14 08:40:13</t>
+          <t>2026-08-05 22:42:33</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluwafunke.taiwo3</t>
+          <t>https://www.tiktok.com/@bignastrolytic</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>adeola.omoshalewa</t>
+          <t>bimpy134</t>
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
@@ -13696,7 +13696,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>2026-08-05 22:58:05</t>
+          <t>2026-08-05 14:24:00</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -13706,55 +13706,55 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adeola.omoshalewa</t>
+          <t>https://www.tiktok.com/@bimpy134</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>owoblow2010</t>
+          <t>blessedmimi_</t>
         </is>
       </c>
       <c r="B344" t="inlineStr"/>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>2026-08-09 11:18:52</t>
+          <t>2026-08-07 12:08:07</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@owoblow2010</t>
+          <t>https://www.tiktok.com/@blessedmimi_</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>rinajadupatel</t>
+          <t>chillimilli385</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -13764,65 +13764,65 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>2026-08-03 23:12:58</t>
+          <t>2026-08-09 15:57:05</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rinajadupatel</t>
+          <t>https://www.tiktok.com/@chillimilli385</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>rubz3364</t>
+          <t>olabisismd</t>
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>2026-08-02 19:26:30</t>
+          <t>2026-08-12 07:46:02</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rubz3364</t>
+          <t>https://www.tiktok.com/@olabisismd</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>rukkyani1</t>
+          <t>ollie.in.yorkshire</t>
         </is>
       </c>
       <c r="B347" t="inlineStr"/>
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -13832,126 +13832,126 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>2026-08-07 15:30:26</t>
+          <t>2026-08-10 12:53:05</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rukkyani1</t>
+          <t>https://www.tiktok.com/@ollie.in.yorkshire</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>sabbira26</t>
+          <t>olori305</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>2026-08-05 20:52:32</t>
+          <t>2026-08-15 12:09:44</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sabbira26</t>
+          <t>https://www.tiktok.com/@olori305</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>saheed.david</t>
+          <t>oluwafunke.taiwo3</t>
         </is>
       </c>
       <c r="B349" t="inlineStr"/>
       <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>2026-08-06 19:31:13</t>
+          <t>2026-08-14 08:40:13</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@saheed.david</t>
+          <t>https://www.tiktok.com/@oluwafunke.taiwo3</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>pammie115</t>
+          <t>owoblow2010</t>
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
       <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>2026-08-02 20:52:59</t>
+          <t>2026-08-09 11:18:52</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@pammie115</t>
+          <t>https://www.tiktok.com/@owoblow2010</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>patriciahoward372</t>
+          <t>pammie115</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -13968,177 +13968,177 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>2026-08-05 07:35:54</t>
+          <t>2026-08-02 20:52:59</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@patriciahoward372</t>
+          <t>https://www.tiktok.com/@pammie115</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>preety.vault</t>
+          <t>patriciahoward372</t>
         </is>
       </c>
       <c r="B352" t="inlineStr"/>
       <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>2026-08-11 19:53:07</t>
+          <t>2026-08-05 07:35:54</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@preety.vault</t>
+          <t>https://www.tiktok.com/@patriciahoward372</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>chrisnnamani7</t>
+          <t>preety.vault</t>
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
       <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-07 08:50:04</t>
+          <t>2026-08-11 19:53:07</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chrisnnamani7</t>
+          <t>https://www.tiktok.com/@preety.vault</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>christinemaughan4</t>
+          <t>prettybrown_muje</t>
         </is>
       </c>
       <c r="B354" t="inlineStr"/>
       <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>2026-08-05 16:46:16</t>
+          <t>2026-08-10 06:36:09</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@christinemaughan4</t>
+          <t>https://www.tiktok.com/@prettybrown_muje</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>adeolamustapha973</t>
+          <t>prophetessjudith06</t>
         </is>
       </c>
       <c r="B355" t="inlineStr"/>
       <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>2026-08-11 20:36:48</t>
+          <t>2026-08-04 22:40:33</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adeolamustapha973</t>
+          <t>https://www.tiktok.com/@prophetessjudith06</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>coolestinfluencer1</t>
+          <t>saheed.david</t>
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
       <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>2026-08-06 15:49:05</t>
+          <t>2026-08-06 19:31:13</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
@@ -14148,56 +14148,48 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@coolestinfluencer1</t>
+          <t>https://www.tiktok.com/@saheed.david</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>courage.ik</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>saiqa14486</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr"/>
+      <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>2026-08-15 14:23:05</t>
+          <t>2026-08-02 09:09:21</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@courage.ik</t>
+          <t>https://www.tiktok.com/@saiqa14486</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>quentinnke</t>
+          <t>salma.ibrahim588</t>
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
@@ -14214,7 +14206,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>2026-08-06 18:38:45</t>
+          <t>2026-08-06 17:20:21</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -14224,63 +14216,55 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@quentinnke</t>
+          <t>https://www.tiktok.com/@salma.ibrahim588</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>r2chybe</t>
+          <t>samiashoaib937</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>2026-08-14 22:37:05</t>
+          <t>2026-08-05 13:12:55</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@r2chybe</t>
+          <t>https://www.tiktok.com/@samiashoaib937</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>rayoajokeade</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>100K-250K</t>
-        </is>
-      </c>
+          <t>shafaq1679</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr"/>
+      <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -14290,65 +14274,65 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>2026-08-04 19:14:41</t>
+          <t>2026-08-15 14:12:05</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rayoajokeade</t>
+          <t>https://www.tiktok.com/@shafaq1679</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>rayplus06</t>
+          <t>shanazahmed452</t>
         </is>
       </c>
       <c r="B361" t="inlineStr"/>
       <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>2026-08-05 23:04:18</t>
+          <t>2026-08-09 20:31:21</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rayplus06</t>
+          <t>https://www.tiktok.com/@shanazahmed452</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>raz_010816</t>
+          <t>temi4t</t>
         </is>
       </c>
       <c r="B362" t="inlineStr"/>
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -14358,24 +14342,24 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>2026-08-15 23:32:17</t>
+          <t>2026-08-11 08:40:06</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@raz_010816</t>
+          <t>https://www.tiktok.com/@temi4t</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>__olabisi1__</t>
+          <t>r2chybe</t>
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -14392,7 +14376,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>2026-08-14 15:21:53</t>
+          <t>2026-08-14 22:37:05</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
@@ -14402,48 +14386,48 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@__olabisi1__</t>
+          <t>https://www.tiktok.com/@r2chybe</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>bozia247</t>
+          <t>radical818</t>
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
       <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-08-02 15:51:28</t>
+          <t>2026-08-08 12:59:20</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bozia247</t>
+          <t>https://www.tiktok.com/@radical818</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>bukola_sole</t>
+          <t>ramat0218</t>
         </is>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -14460,62 +14444,70 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>2026-08-02 22:15:14</t>
+          <t>2026-08-03 10:28:15</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bukola_sole</t>
+          <t>https://www.tiktok.com/@ramat0218</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>bukolaadee</t>
+          <t>rasna2094</t>
         </is>
       </c>
       <c r="B366" t="inlineStr"/>
       <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>2026-08-08 09:20:44</t>
+          <t>2026-08-05 14:13:31</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bukolaadee</t>
+          <t>https://www.tiktok.com/@rasna2094</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>busivincent</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr"/>
-      <c r="C367" t="inlineStr"/>
+          <t>rayoajokeade</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>100K-250K</t>
+        </is>
+      </c>
       <c r="D367" t="inlineStr">
         <is>
           <t>Lemon Ginger</t>
@@ -14528,31 +14520,31 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>2026-08-06 14:40:06</t>
+          <t>2026-08-04 19:14:41</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@busivincent</t>
+          <t>https://www.tiktok.com/@rayoajokeade</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>carinadyarte</t>
+          <t>rayplus06</t>
         </is>
       </c>
       <c r="B368" t="inlineStr"/>
       <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -14562,31 +14554,31 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>2026-08-15 17:25:05</t>
+          <t>2026-08-05 23:04:18</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@carinadyarte</t>
+          <t>https://www.tiktok.com/@rayplus06</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>carolducasse2</t>
+          <t>raz_010816</t>
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
       <c r="C369" t="inlineStr"/>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -14596,160 +14588,160 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>2026-08-01 12:23:54</t>
+          <t>2026-08-15 23:32:17</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@carolducasse2</t>
+          <t>https://www.tiktok.com/@raz_010816</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>okemorenikerachea</t>
+          <t>rinajadupatel</t>
         </is>
       </c>
       <c r="B370" t="inlineStr"/>
       <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>2026-08-12 09:21:47</t>
+          <t>2026-08-03 23:12:58</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@okemorenikerachea</t>
+          <t>https://www.tiktok.com/@rinajadupatel</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>olabisismd</t>
+          <t>berniceamong</t>
         </is>
       </c>
       <c r="B371" t="inlineStr"/>
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>2026-08-12 07:46:02</t>
+          <t>2026-08-03 15:51:52</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@olabisismd</t>
+          <t>https://www.tiktok.com/@berniceamong</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>ollie.in.yorkshire</t>
+          <t>annamarie_s</t>
         </is>
       </c>
       <c r="B372" t="inlineStr"/>
       <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>2026-08-10 12:53:05</t>
+          <t>2026-08-07 14:50:05</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ollie.in.yorkshire</t>
+          <t>https://www.tiktok.com/@annamarie_s</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>olori305</t>
+          <t>annwakonyo82</t>
         </is>
       </c>
       <c r="B373" t="inlineStr"/>
       <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-08-15 12:09:44</t>
+          <t>2026-08-03 08:01:11</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@olori305</t>
+          <t>https://www.tiktok.com/@annwakonyo82</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>yasminsar_110</t>
+          <t>arinolavictory</t>
         </is>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -14766,24 +14758,24 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>2026-08-02 16:53:08</t>
+          <t>2026-08-01 12:59:45</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yasminsar_110</t>
+          <t>https://www.tiktok.com/@arinolavictory</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>yemisi_81</t>
+          <t>ash01703</t>
         </is>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -14800,7 +14792,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-08-04 10:04:07</t>
+          <t>2026-08-04 08:26:07</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -14810,21 +14802,21 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yemisi_81</t>
+          <t>https://www.tiktok.com/@ash01703</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>taiwoawoyemi6</t>
+          <t>temitayo0835</t>
         </is>
       </c>
       <c r="B376" t="inlineStr"/>
       <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -14834,28 +14826,36 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>2026-08-05 09:45:32</t>
+          <t>2026-08-12 14:54:19</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@taiwoawoyemi6</t>
+          <t>https://www.tiktok.com/@temitayo0835</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>abbyades</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr"/>
-      <c r="C377" t="inlineStr"/>
+          <t>azizanso</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D377" t="inlineStr">
         <is>
           <t>Lemon Ginger</t>
@@ -14868,28 +14868,36 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>2026-08-03 13:07:56</t>
+          <t>2026-08-04 17:14:44</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abbyades</t>
+          <t>https://www.tiktok.com/@azizanso</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>saiqa14486</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr"/>
-      <c r="C378" t="inlineStr"/>
+          <t>beautycontrol_by_nikky1</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D378" t="inlineStr">
         <is>
           <t>Lemon Ginger</t>
@@ -14902,99 +14910,99 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>2026-08-02 09:09:21</t>
+          <t>2026-08-04 11:31:54</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@saiqa14486</t>
+          <t>https://www.tiktok.com/@beautycontrol_by_nikky1</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>salma.ibrahim588</t>
+          <t>blessing.steven83</t>
         </is>
       </c>
       <c r="B379" t="inlineStr"/>
       <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>2026-08-06 17:20:21</t>
+          <t>2026-08-07 13:52:34</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@salma.ibrahim588</t>
+          <t>https://www.tiktok.com/@blessing.steven83</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>samiashoaib937</t>
+          <t>blessing91726</t>
         </is>
       </c>
       <c r="B380" t="inlineStr"/>
       <c r="C380" t="inlineStr"/>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>2026-08-05 13:12:55</t>
+          <t>2026-08-08 08:05:43</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samiashoaib937</t>
+          <t>https://www.tiktok.com/@blessing91726</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>shafaq1679</t>
+          <t>blesswithlove1</t>
         </is>
       </c>
       <c r="B381" t="inlineStr"/>
       <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -15004,24 +15012,24 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>2026-08-15 14:12:05</t>
+          <t>2026-08-02 17:56:53</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shafaq1679</t>
+          <t>https://www.tiktok.com/@blesswithlove1</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>shanazahmed452</t>
+          <t>bobbin.sense</t>
         </is>
       </c>
       <c r="B382" t="inlineStr"/>
@@ -15033,29 +15041,29 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>2026-08-09 20:31:21</t>
+          <t>2026-08-05 09:39:08</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shanazahmed452</t>
+          <t>https://www.tiktok.com/@bobbin.sense</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>abosedeisaac7</t>
+          <t>bolaji.lukas</t>
         </is>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -15072,92 +15080,92 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>2026-08-06 22:04:12</t>
+          <t>2026-08-03 20:46:20</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abosedeisaac7</t>
+          <t>https://www.tiktok.com/@bolaji.lukas</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>she.finds.v2</t>
+          <t>temmiedee68</t>
         </is>
       </c>
       <c r="B384" t="inlineStr"/>
       <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>2026-08-11 09:28:05</t>
+          <t>2026-08-14 18:09:35</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@she.finds.v2</t>
+          <t>https://www.tiktok.com/@temmiedee68</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>she.reigns.hair</t>
+          <t>rubz3364</t>
         </is>
       </c>
       <c r="B385" t="inlineStr"/>
       <c r="C385" t="inlineStr"/>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-08 06:42:34</t>
+          <t>2026-08-02 19:26:30</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@she.reigns.hair</t>
+          <t>https://www.tiktok.com/@rubz3364</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>prettybrown_muje</t>
+          <t>rukkyani1</t>
         </is>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -15174,24 +15182,24 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>2026-08-10 06:36:09</t>
+          <t>2026-08-07 15:30:26</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@prettybrown_muje</t>
+          <t>https://www.tiktok.com/@rukkyani1</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>prophetessjudith06</t>
+          <t>sabbira26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -15208,24 +15216,24 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>2026-08-04 22:40:33</t>
+          <t>2026-08-05 20:52:32</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@prophetessjudith06</t>
+          <t>https://www.tiktok.com/@sabbira26</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>queenc023</t>
+          <t>beekaylux20</t>
         </is>
       </c>
       <c r="B388" t="inlineStr"/>
@@ -15242,24 +15250,24 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>2026-08-02 23:20:03</t>
+          <t>2026-08-05 23:21:36</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queenc023</t>
+          <t>https://www.tiktok.com/@beekaylux20</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>queenlady7354</t>
+          <t>benjalooywd</t>
         </is>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -15276,24 +15284,24 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>2026-08-07 07:05:09</t>
+          <t>2026-08-03 09:06:41</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queenlady7354</t>
+          <t>https://www.tiktok.com/@benjalooywd</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>rasna2094</t>
+          <t>soniakelly798</t>
         </is>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -15310,24 +15318,24 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>2026-08-05 14:13:31</t>
+          <t>2026-08-06 18:56:32</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rasna2094</t>
+          <t>https://www.tiktok.com/@soniakelly798</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>teresa_plugs</t>
+          <t>sophia.annan2</t>
         </is>
       </c>
       <c r="B391" t="inlineStr"/>
@@ -15344,31 +15352,31 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>2026-08-03 14:33:13</t>
+          <t>2026-08-06 06:16:15</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teresa_plugs</t>
+          <t>https://www.tiktok.com/@sophia.annan2</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>adamb719</t>
+          <t>stacecaldridge</t>
         </is>
       </c>
       <c r="B392" t="inlineStr"/>
       <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -15378,65 +15386,65 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>2026-08-03 12:14:53</t>
+          <t>2026-08-15 16:51:05</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adamb719</t>
+          <t>https://www.tiktok.com/@stacecaldridge</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>the.love.of.god36</t>
+          <t>stecrawford0</t>
         </is>
       </c>
       <c r="B393" t="inlineStr"/>
       <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>2026-08-12 14:24:43</t>
+          <t>2026-08-02 12:57:01</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@the.love.of.god36</t>
+          <t>https://www.tiktok.com/@stecrawford0</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>the_psy_lif3</t>
+          <t>sulaimon.ashogbon</t>
         </is>
       </c>
       <c r="B394" t="inlineStr"/>
       <c r="C394" t="inlineStr"/>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -15446,58 +15454,58 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>2026-08-08 21:16:05</t>
+          <t>2026-08-01 09:37:26</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@the_psy_lif3</t>
+          <t>https://www.tiktok.com/@sulaimon.ashogbon</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>thea.w.finds</t>
+          <t>taiwoawoyemi6</t>
         </is>
       </c>
       <c r="B395" t="inlineStr"/>
       <c r="C395" t="inlineStr"/>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>2026-08-15 11:08:05</t>
+          <t>2026-08-05 09:45:32</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thea.w.finds</t>
+          <t>https://www.tiktok.com/@taiwoawoyemi6</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>siham19641</t>
+          <t>temmit7</t>
         </is>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -15514,41 +15522,41 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>2026-08-03 22:10:42</t>
+          <t>2026-08-02 10:56:06</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@siham19641</t>
+          <t>https://www.tiktok.com/@temmit7</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>smart_cart_labs</t>
+          <t>teresa_plugs</t>
         </is>
       </c>
       <c r="B397" t="inlineStr"/>
       <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-08-03 09:14:04</t>
+          <t>2026-08-03 14:33:13</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
@@ -15558,21 +15566,21 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@smart_cart_labs</t>
+          <t>https://www.tiktok.com/@teresa_plugs</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>soniakelly798</t>
+          <t>she.finds.v2</t>
         </is>
       </c>
       <c r="B398" t="inlineStr"/>
       <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -15582,92 +15590,92 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>2026-08-06 18:56:32</t>
+          <t>2026-08-11 09:28:05</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@soniakelly798</t>
+          <t>https://www.tiktok.com/@she.finds.v2</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>sophia.annan2</t>
+          <t>she.reigns.hair</t>
         </is>
       </c>
       <c r="B399" t="inlineStr"/>
       <c r="C399" t="inlineStr"/>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>2026-08-06 06:16:15</t>
+          <t>2026-08-08 06:42:34</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sophia.annan2</t>
+          <t>https://www.tiktok.com/@she.reigns.hair</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>blessing.steven83</t>
+          <t>shubnamwarris</t>
         </is>
       </c>
       <c r="B400" t="inlineStr"/>
       <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>2026-08-07 13:52:34</t>
+          <t>2026-08-03 16:48:58</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blessing.steven83</t>
+          <t>https://www.tiktok.com/@shubnamwarris</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>adeadesola26</t>
+          <t>siham19641</t>
         </is>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -15684,65 +15692,65 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>2026-08-07 02:05:32</t>
+          <t>2026-08-03 22:10:42</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adeadesola26</t>
+          <t>https://www.tiktok.com/@siham19641</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>adenike.badejo</t>
+          <t>smart_cart_labs</t>
         </is>
       </c>
       <c r="B402" t="inlineStr"/>
       <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>2026-08-01 18:42:56</t>
+          <t>2026-08-03 09:14:04</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adenike.badejo</t>
+          <t>https://www.tiktok.com/@smart_cart_labs</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>celestialcreations1981</t>
+          <t>andreadavies903</t>
         </is>
       </c>
       <c r="B403" t="inlineStr"/>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -15752,109 +15760,109 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>2026-08-05 11:42:44</t>
+          <t>2026-08-01 22:54:24</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@celestialcreations1981</t>
+          <t>https://www.tiktok.com/@andreadavies903</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>whoisedwina.x</t>
+          <t>ukineboconnect</t>
         </is>
       </c>
       <c r="B404" t="inlineStr"/>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-08-04 20:07:08</t>
+          <t>2026-08-07 12:08:05</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@whoisedwina.x</t>
+          <t>https://www.tiktok.com/@ukineboconnect</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>y_ddraig69</t>
+          <t>adenike.badejo</t>
         </is>
       </c>
       <c r="B405" t="inlineStr"/>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>2026-08-15 17:59:05</t>
+          <t>2026-08-01 18:42:56</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@y_ddraig69</t>
+          <t>https://www.tiktok.com/@adenike.badejo</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>tina4realaffliatemarkete</t>
+          <t>adeola.omoshalewa</t>
         </is>
       </c>
       <c r="B406" t="inlineStr"/>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>2026-08-05 09:39:07</t>
+          <t>2026-08-05 22:58:05</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
@@ -15864,14 +15872,14 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tina4realaffliatemarkete</t>
+          <t>https://www.tiktok.com/@adeola.omoshalewa</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>tinu.ola</t>
+          <t>adeolamustapha973</t>
         </is>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -15888,31 +15896,31 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>2026-08-12 16:40:53</t>
+          <t>2026-08-11 20:36:48</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tinu.ola</t>
+          <t>https://www.tiktok.com/@adeolamustapha973</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>tinugold123</t>
+          <t>adunni__taylor</t>
         </is>
       </c>
       <c r="B408" t="inlineStr"/>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -15922,31 +15930,31 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>2026-08-04 00:42:18</t>
+          <t>2026-08-06 16:07:06</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tinugold123</t>
+          <t>https://www.tiktok.com/@adunni__taylor</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>topproductsreviewed</t>
+          <t>adunola.prestige</t>
         </is>
       </c>
       <c r="B409" t="inlineStr"/>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -15956,31 +15964,31 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-08-07 12:08:07</t>
+          <t>2026-08-01 08:08:54</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@topproductsreviewed</t>
+          <t>https://www.tiktok.com/@adunola.prestige</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>toyinedos</t>
+          <t>the_psy_lif3</t>
         </is>
       </c>
       <c r="B410" t="inlineStr"/>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -15990,58 +15998,58 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>2026-08-04 07:24:05</t>
+          <t>2026-08-08 21:16:05</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@toyinedos</t>
+          <t>https://www.tiktok.com/@the_psy_lif3</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>traetari1</t>
+          <t>thea.w.finds</t>
         </is>
       </c>
       <c r="B411" t="inlineStr"/>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>2026-08-04 20:57:53</t>
+          <t>2026-08-15 11:08:05</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@traetari1</t>
+          <t>https://www.tiktok.com/@thea.w.finds</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>triplehoney8</t>
+          <t>themyturpe4</t>
         </is>
       </c>
       <c r="B412" t="inlineStr"/>
@@ -16058,7 +16066,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>2026-08-05 09:12:57</t>
+          <t>2026-08-05 13:22:07</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
@@ -16068,48 +16076,48 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@triplehoney8</t>
+          <t>https://www.tiktok.com/@themyturpe4</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>dipu.vyas</t>
+          <t>tima_baby89</t>
         </is>
       </c>
       <c r="B413" t="inlineStr"/>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>2026-08-07 14:45:52</t>
+          <t>2026-08-01 00:14:09</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dipu.vyas</t>
+          <t>https://www.tiktok.com/@tima_baby89</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>ade55309</t>
+          <t>tina4realaffliatemarkete</t>
         </is>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -16126,58 +16134,58 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>2026-08-08 12:20:28</t>
+          <t>2026-08-05 09:39:07</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ade55309</t>
+          <t>https://www.tiktok.com/@tina4realaffliatemarkete</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>vibewithname3</t>
+          <t>tinu.ola</t>
         </is>
       </c>
       <c r="B415" t="inlineStr"/>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>2026-08-11 08:58:07</t>
+          <t>2026-08-12 16:40:53</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vibewithname3</t>
+          <t>https://www.tiktok.com/@tinu.ola</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>stacecaldridge</t>
+          <t>tinugold123</t>
         </is>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -16189,29 +16197,29 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>2026-08-15 16:51:05</t>
+          <t>2026-08-04 00:42:18</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@stacecaldridge</t>
+          <t>https://www.tiktok.com/@tinugold123</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>stecrawford0</t>
+          <t>toyinedos</t>
         </is>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -16228,31 +16236,31 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-02 12:57:01</t>
+          <t>2026-08-04 07:24:05</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@stecrawford0</t>
+          <t>https://www.tiktok.com/@toyinedos</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>.beauty.001</t>
+          <t>the.love.of.god36</t>
         </is>
       </c>
       <c r="B418" t="inlineStr"/>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -16262,31 +16270,31 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>2026-08-14 00:31:05</t>
+          <t>2026-08-12 14:24:43</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@.beauty.001</t>
+          <t>https://www.tiktok.com/@the.love.of.god36</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>sulaimon.ashogbon</t>
+          <t>bee.finds_</t>
         </is>
       </c>
       <c r="B419" t="inlineStr"/>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -16296,24 +16304,24 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>2026-08-01 09:37:26</t>
+          <t>2026-08-04 08:14:06</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sulaimon.ashogbon</t>
+          <t>https://www.tiktok.com/@bee.finds_</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>shubnamwarris</t>
+          <t>victoriaookoro</t>
         </is>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -16330,58 +16338,58 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>2026-08-03 16:48:58</t>
+          <t>2026-08-01 07:47:19</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shubnamwarris</t>
+          <t>https://www.tiktok.com/@victoriaookoro</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>ramat0218</t>
+          <t>viralnestdailydeals</t>
         </is>
       </c>
       <c r="B421" t="inlineStr"/>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>2026-08-03 10:28:15</t>
+          <t>2026-08-05 09:39:06</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ramat0218</t>
+          <t>https://www.tiktok.com/@viralnestdailydeals</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>bexbestbuys</t>
+          <t>.beauty.001</t>
         </is>
       </c>
       <c r="B422" t="inlineStr"/>
@@ -16393,70 +16401,70 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>2026-08-11 19:53:05</t>
+          <t>2026-08-14 00:31:05</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bexbestbuys</t>
+          <t>https://www.tiktok.com/@.beauty.001</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>user2997965690229</t>
+          <t>vytyglrl</t>
         </is>
       </c>
       <c r="B423" t="inlineStr"/>
       <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>2026-08-14 19:07:40</t>
+          <t>2026-08-01 01:52:28</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2997965690229</t>
+          <t>https://www.tiktok.com/@vytyglrl</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>user3242536109635</t>
+          <t>waletreasure</t>
         </is>
       </c>
       <c r="B424" t="inlineStr"/>
       <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -16466,66 +16474,58 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>2026-08-03 20:42:18</t>
+          <t>2026-08-11 13:01:50</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user3242536109635</t>
+          <t>https://www.tiktok.com/@waletreasure</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>facelessliligood</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>walex0880</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr"/>
+      <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>2026-08-10 10:47:15</t>
+          <t>2026-08-04 21:35:53</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@facelessliligood</t>
+          <t>https://www.tiktok.com/@walex0880</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>fainaksalih</t>
+          <t>whoisedwina.x</t>
         </is>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -16542,24 +16542,24 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>2026-08-07 14:00:12</t>
+          <t>2026-08-04 20:07:08</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fainaksalih</t>
+          <t>https://www.tiktok.com/@whoisedwina.x</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>fatoutouray13</t>
+          <t>y_ddraig69</t>
         </is>
       </c>
       <c r="B427" t="inlineStr"/>
@@ -16576,24 +16576,24 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>2026-08-09 20:50:33</t>
+          <t>2026-08-15 17:59:05</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fatoutouray13</t>
+          <t>https://www.tiktok.com/@y_ddraig69</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>denelos1</t>
+          <t>user59838594031894</t>
         </is>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -16605,29 +16605,29 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>2026-08-07 07:52:06</t>
+          <t>2026-08-04 13:16:58</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@denelos1</t>
+          <t>https://www.tiktok.com/@user59838594031894</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>user5724531303785</t>
+          <t>user8160294226215</t>
         </is>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -16644,65 +16644,65 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>2026-08-06 06:39:56</t>
+          <t>2026-08-02 20:19:29</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user5724531303785</t>
+          <t>https://www.tiktok.com/@user8160294226215</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>felixpowez0</t>
+          <t>user8234558006158</t>
         </is>
       </c>
       <c r="B430" t="inlineStr"/>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-08-02 05:46:54</t>
+          <t>2026-08-12 07:13:01</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@felixpowez0</t>
+          <t>https://www.tiktok.com/@user8234558006158</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>fentonadventure</t>
+          <t>user9813841001322</t>
         </is>
       </c>
       <c r="B431" t="inlineStr"/>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -16712,65 +16712,65 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>2026-08-12 18:12:07</t>
+          <t>2026-08-02 23:48:31</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fentonadventure</t>
+          <t>https://www.tiktok.com/@user9813841001322</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>dorathy.ochokwu</t>
+          <t>verascuisine_</t>
         </is>
       </c>
       <c r="B432" t="inlineStr"/>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>2026-08-04 16:17:55</t>
+          <t>2026-08-12 07:40:06</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dorathy.ochokwu</t>
+          <t>https://www.tiktok.com/@verascuisine_</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>dorinepride</t>
+          <t>vibewithname3</t>
         </is>
       </c>
       <c r="B433" t="inlineStr"/>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -16780,58 +16780,58 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>2026-08-02 17:19:48</t>
+          <t>2026-08-11 08:58:07</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dorinepride</t>
+          <t>https://www.tiktok.com/@vibewithname3</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>dreamcatcher00730</t>
+          <t>vickyvickss3</t>
         </is>
       </c>
       <c r="B434" t="inlineStr"/>
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>2026-08-06 15:31:17</t>
+          <t>2026-08-11 17:41:09</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dreamcatcher00730</t>
+          <t>https://www.tiktok.com/@vickyvickss3</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>drlove925</t>
+          <t>adeadesola26</t>
         </is>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -16848,7 +16848,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-08-07 13:22:06</t>
+          <t>2026-08-07 02:05:32</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
@@ -16858,48 +16858,48 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@drlove925</t>
+          <t>https://www.tiktok.com/@adeadesola26</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>dwellingtonx</t>
+          <t>user2997965690229</t>
         </is>
       </c>
       <c r="B436" t="inlineStr"/>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>2026-08-01 10:36:28</t>
+          <t>2026-08-14 19:07:40</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dwellingtonx</t>
+          <t>https://www.tiktok.com/@user2997965690229</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>1leics</t>
+          <t>user3242536109635</t>
         </is>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -16916,65 +16916,65 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>2026-08-02 19:13:43</t>
+          <t>2026-08-03 20:42:18</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@1leics</t>
+          <t>https://www.tiktok.com/@user3242536109635</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>103mmc</t>
+          <t>user5724531303785</t>
         </is>
       </c>
       <c r="B438" t="inlineStr"/>
       <c r="C438" t="inlineStr"/>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>2026-08-14 01:23:44</t>
+          <t>2026-08-06 06:39:56</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@103mmc</t>
+          <t>https://www.tiktok.com/@user5724531303785</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>ukineboconnect</t>
+          <t>affiliateproductlinks</t>
         </is>
       </c>
       <c r="B439" t="inlineStr"/>
       <c r="C439" t="inlineStr"/>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -16984,24 +16984,24 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>2026-08-07 12:08:05</t>
+          <t>2026-08-13 23:30:05</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ukineboconnect</t>
+          <t>https://www.tiktok.com/@affiliateproductlinks</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>blessedmimi_</t>
+          <t>afia7773</t>
         </is>
       </c>
       <c r="B440" t="inlineStr"/>
@@ -17013,165 +17013,165 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>2026-08-07 12:08:07</t>
+          <t>2026-08-12 13:41:03</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blessedmimi_</t>
+          <t>https://www.tiktok.com/@afia7773</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>user9813841001322</t>
+          <t>agyeibeauty31</t>
         </is>
       </c>
       <c r="B441" t="inlineStr"/>
       <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>2026-08-02 23:48:31</t>
+          <t>2026-08-15 01:11:24</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user9813841001322</t>
+          <t>https://www.tiktok.com/@agyeibeauty31</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>verascuisine_</t>
+          <t>ah15680</t>
         </is>
       </c>
       <c r="B442" t="inlineStr"/>
       <c r="C442" t="inlineStr"/>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>2026-08-12 07:40:06</t>
+          <t>2026-08-05 12:45:29</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@verascuisine_</t>
+          <t>https://www.tiktok.com/@ah15680</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>zainab36576</t>
+          <t>akadoctor3</t>
         </is>
       </c>
       <c r="B443" t="inlineStr"/>
       <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-08-10 08:56:01</t>
+          <t>2026-08-05 19:44:15</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zainab36576</t>
+          <t>https://www.tiktok.com/@akadoctor3</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>user59838594031894</t>
+          <t>amber_roseeg</t>
         </is>
       </c>
       <c r="B444" t="inlineStr"/>
       <c r="C444" t="inlineStr"/>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>2026-08-04 13:16:58</t>
+          <t>2026-08-10 09:55:05</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user59838594031894</t>
+          <t>https://www.tiktok.com/@amber_roseeg</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>themyturpe4</t>
+          <t>adamb719</t>
         </is>
       </c>
       <c r="B445" t="inlineStr"/>
@@ -17188,31 +17188,31 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>2026-08-05 13:22:07</t>
+          <t>2026-08-03 12:14:53</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@themyturpe4</t>
+          <t>https://www.tiktok.com/@adamb719</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>waletreasure</t>
+          <t>abosedeisaac7</t>
         </is>
       </c>
       <c r="B446" t="inlineStr"/>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -17222,24 +17222,24 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>2026-08-11 13:01:50</t>
+          <t>2026-08-06 22:04:12</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@waletreasure</t>
+          <t>https://www.tiktok.com/@abosedeisaac7</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>user8160294226215</t>
+          <t>abbyades</t>
         </is>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -17256,31 +17256,31 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>2026-08-02 20:19:29</t>
+          <t>2026-08-03 13:07:56</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8160294226215</t>
+          <t>https://www.tiktok.com/@abbyades</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>user8234558006158</t>
+          <t>_clarahayes</t>
         </is>
       </c>
       <c r="B448" t="inlineStr"/>
       <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -17290,58 +17290,58 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>2026-08-12 07:13:01</t>
+          <t>2026-08-10 19:37:05</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8234558006158</t>
+          <t>https://www.tiktok.com/@_clarahayes</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>ah15680</t>
+          <t>__olabisi1__</t>
         </is>
       </c>
       <c r="B449" t="inlineStr"/>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-05 12:45:29</t>
+          <t>2026-08-14 15:21:53</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ah15680</t>
+          <t>https://www.tiktok.com/@__olabisi1__</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>akadoctor3</t>
+          <t>1leics</t>
         </is>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -17358,31 +17358,31 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>2026-08-05 19:44:15</t>
+          <t>2026-08-02 19:13:43</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@akadoctor3</t>
+          <t>https://www.tiktok.com/@1leics</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>amber_roseeg</t>
+          <t>103mmc</t>
         </is>
       </c>
       <c r="B451" t="inlineStr"/>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -17392,85 +17392,17 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>2026-08-10 09:55:05</t>
+          <t>2026-08-14 01:23:44</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amber_roseeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>bignastrolytic</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr"/>
-      <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>Lemon Ginger</t>
-        </is>
-      </c>
-      <c r="E452" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F452" t="inlineStr">
-        <is>
-          <t>2026-08-05 22:42:33</t>
-        </is>
-      </c>
-      <c r="G452" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H452" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@bignastrolytic</t>
-        </is>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>tima_baby89</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr"/>
-      <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>Lemon Ginger</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F453" t="inlineStr">
-        <is>
-          <t>2026-08-01 00:14:09</t>
-        </is>
-      </c>
-      <c r="G453" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H453" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@tima_baby89</t>
+          <t>https://www.tiktok.com/@103mmc</t>
         </is>
       </c>
     </row>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H451"/>
+  <dimension ref="A1:H452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +481,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2309,7 +2309,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pamela1987x</t>
+          <t>zahraugccreator0</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2319,12 +2319,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2334,24 +2334,24 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-04 08:14:05</t>
+          <t>2026-08-14 11:38:07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@pamela1987x</t>
+          <t>https://www.tiktok.com/@zahraugccreator0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>zahraugccreator0</t>
+          <t>pamela1987x</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-14 11:38:07</t>
+          <t>2026-08-04 08:14:05</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zahraugccreator0</t>
+          <t>https://www.tiktok.com/@pamela1987x</t>
         </is>
       </c>
     </row>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6803,7 +6803,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>lovelylis6</t>
+          <t>kurdishshop4</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-15 07:43:05</t>
+          <t>2026-08-15 00:37:05</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -6838,14 +6838,14 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lovelylis6</t>
+          <t>https://www.tiktok.com/@kurdishshop4</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kurdishshop4</t>
+          <t>lovelylis6</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-08-15 00:37:05</t>
+          <t>2026-08-15 07:43:05</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kurdishshop4</t>
+          <t>https://www.tiktok.com/@lovelylis6</t>
         </is>
       </c>
     </row>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7349,7 +7349,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>stefaniaiqra</t>
+          <t>amymademebuyit</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7364,34 +7364,34 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-08-15 16:38:05</t>
+          <t>2026-08-10 09:26:13</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@stefaniaiqra</t>
+          <t>https://www.tiktok.com/@amymademebuyit</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>amymademebuyit</t>
+          <t>stefaniaiqra</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7406,27 +7406,27 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-08-10 09:26:13</t>
+          <t>2026-08-15 16:38:05</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amymademebuyit</t>
+          <t>https://www.tiktok.com/@stefaniaiqra</t>
         </is>
       </c>
     </row>
@@ -7937,7 +7937,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>mira.taute</t>
+          <t>elizabethfallonx</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-08-15 21:35:05</t>
+          <t>2026-08-15 03:10:05</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -7972,14 +7972,14 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mira.taute</t>
+          <t>https://www.tiktok.com/@elizabethfallonx</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>elizabethfallonx</t>
+          <t>mira.taute</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-08-15 03:10:05</t>
+          <t>2026-08-15 21:35:05</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@elizabethfallonx</t>
+          <t>https://www.tiktok.com/@mira.taute</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -8441,7 +8441,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>life.in.a.reno</t>
+          <t>naijahsdeals</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8451,12 +8451,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -8466,24 +8466,24 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-08-10 13:55:05</t>
+          <t>2026-08-15 08:57:07</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@life.in.a.reno</t>
+          <t>https://www.tiktok.com/@naijahsdeals</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>naijahsdeals</t>
+          <t>life.in.a.reno</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -8508,17 +8508,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-15 08:57:07</t>
+          <t>2026-08-10 13:55:05</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@naijahsdeals</t>
+          <t>https://www.tiktok.com/@life.in.a.reno</t>
         </is>
       </c>
     </row>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -8735,14 +8735,14 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>gabbytiktokfinds</t>
+          <t>user8234558006158</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -8752,92 +8752,92 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-08-13 20:42:05</t>
+          <t>2026-08-12 07:13:01</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gabbytiktokfinds</t>
+          <t>https://www.tiktok.com/@user8234558006158</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>gennyiceevablazas</t>
+          <t>user8160294226215</t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-08-14 22:04:04</t>
+          <t>2026-08-02 20:19:29</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gennyiceevablazas</t>
+          <t>https://www.tiktok.com/@user8160294226215</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>gillian.stevenson2</t>
+          <t>user59838594031894</t>
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-08-15 08:13:02</t>
+          <t>2026-08-04 13:16:58</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gillian.stevenson2</t>
+          <t>https://www.tiktok.com/@user59838594031894</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>gla1890</t>
+          <t>christinemaughan4</t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
@@ -8854,24 +8854,24 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-08-06 14:48:00</t>
+          <t>2026-08-05 16:46:16</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gla1890</t>
+          <t>https://www.tiktok.com/@christinemaughan4</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>gladysadjei43</t>
+          <t>user22378493319474</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -8888,24 +8888,24 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-08-04 19:48:23</t>
+          <t>2026-08-06 08:27:00</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gladysadjei43</t>
+          <t>https://www.tiktok.com/@user22378493319474</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>globalgee73</t>
+          <t>user2133928667610</t>
         </is>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -8922,24 +8922,24 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-08-02 14:48:45</t>
+          <t>2026-08-04 22:38:37</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@globalgee73</t>
+          <t>https://www.tiktok.com/@user2133928667610</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>grabthedeal123</t>
+          <t>victoriaookoro</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
@@ -8956,24 +8956,24 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-08-02 22:40:50</t>
+          <t>2026-08-01 07:47:19</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@grabthedeal123</t>
+          <t>https://www.tiktok.com/@victoriaookoro</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>traetari1</t>
+          <t>adeola.omoshalewa</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -8990,24 +8990,24 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-08-04 20:57:53</t>
+          <t>2026-08-05 22:58:05</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@traetari1</t>
+          <t>https://www.tiktok.com/@adeola.omoshalewa</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>triplehoney8</t>
+          <t>adenike.badejo</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -9024,31 +9024,31 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-08-05 09:12:57</t>
+          <t>2026-08-01 18:42:56</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@triplehoney8</t>
+          <t>https://www.tiktok.com/@adenike.badejo</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>harryhav1</t>
+          <t>adeadesola26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -9058,31 +9058,31 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-08-06 16:39:06</t>
+          <t>2026-08-07 02:05:32</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@harryhav1</t>
+          <t>https://www.tiktok.com/@adeadesola26</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>hazeraqureshy</t>
+          <t>.beauty.001</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-08-14 18:50:49</t>
+          <t>2026-08-14 00:31:05</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -9102,48 +9102,48 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hazeraqureshy</t>
+          <t>https://www.tiktok.com/@.beauty.001</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>healthylifechanges</t>
+          <t>amber_roseeg</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-08-11 08:14:07</t>
+          <t>2026-08-10 09:55:05</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@healthylifechanges</t>
+          <t>https://www.tiktok.com/@amber_roseeg</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>helen.che72</t>
+          <t>akadoctor3</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
@@ -9160,58 +9160,58 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-08-03 11:09:13</t>
+          <t>2026-08-05 19:44:15</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@helen.che72</t>
+          <t>https://www.tiktok.com/@akadoctor3</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>yasminsar_110</t>
+          <t>103mmc</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-08-02 16:53:08</t>
+          <t>2026-08-14 01:23:44</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yasminsar_110</t>
+          <t>https://www.tiktok.com/@103mmc</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>yemisi_81</t>
+          <t>walex0880</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-08-04 10:04:07</t>
+          <t>2026-08-04 21:35:53</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -9238,48 +9238,48 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yemisi_81</t>
+          <t>https://www.tiktok.com/@walex0880</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>zainab36576</t>
+          <t>waletreasure</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-08-10 08:56:01</t>
+          <t>2026-08-11 13:01:50</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zainab36576</t>
+          <t>https://www.tiktok.com/@waletreasure</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>emjems1</t>
+          <t>vytyglrl</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -9291,29 +9291,29 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-08-14 07:41:05</t>
+          <t>2026-08-01 01:52:28</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@emjems1</t>
+          <t>https://www.tiktok.com/@vytyglrl</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>enny5839</t>
+          <t>viralnestdailydeals</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -9325,138 +9325,138 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-08-14 19:31:16</t>
+          <t>2026-08-05 09:39:06</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@enny5839</t>
+          <t>https://www.tiktok.com/@viralnestdailydeals</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ernescoralzamor99</t>
+          <t>user2940653632458</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-08-14 00:44:21</t>
+          <t>2026-08-02 09:13:03</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ernescoralzamor99</t>
+          <t>https://www.tiktok.com/@user2940653632458</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>user.okikiwealth</t>
+          <t>stacecaldridge</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-08-01 13:23:25</t>
+          <t>2026-08-15 16:51:05</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user.okikiwealth</t>
+          <t>https://www.tiktok.com/@stacecaldridge</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>user18539263935775</t>
+          <t>gabbytiktokfinds</t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>2026-08-06 03:48:43</t>
+          <t>2026-08-13 20:42:05</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user18539263935775</t>
+          <t>https://www.tiktok.com/@gabbytiktokfinds</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>user2133928667610</t>
+          <t>funmilayoyinloye</t>
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2026-08-04 22:38:37</t>
+          <t>2026-08-04 20:44:06</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -9476,14 +9476,14 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2133928667610</t>
+          <t>https://www.tiktok.com/@funmilayoyinloye</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>user22378493319474</t>
+          <t>florida_745</t>
         </is>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -9500,31 +9500,31 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2026-08-06 08:27:00</t>
+          <t>2026-08-03 23:59:55</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user22378493319474</t>
+          <t>https://www.tiktok.com/@florida_745</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>user2940653632458</t>
+          <t>j_backupp123</t>
         </is>
       </c>
       <c r="B222" t="inlineStr"/>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -9534,73 +9534,65 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-08-02 09:13:03</t>
+          <t>2026-08-06 17:01:55</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2940653632458</t>
+          <t>https://www.tiktok.com/@j_backupp123</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>em_j_10</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>izzu.mama</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-08-10 12:52:05</t>
+          <t>2026-08-14 06:16:05</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@em_j_10</t>
+          <t>https://www.tiktok.com/@izzu.mama</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>heyitslindaxo</t>
+          <t>ah15680</t>
         </is>
       </c>
       <c r="B224" t="inlineStr"/>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -9610,31 +9602,31 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2026-08-11 08:47:05</t>
+          <t>2026-08-05 12:45:29</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@heyitslindaxo</t>
+          <t>https://www.tiktok.com/@ah15680</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>hunbea91</t>
+          <t>agyeibeauty31</t>
         </is>
       </c>
       <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -9644,24 +9636,24 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-07 12:08:05</t>
+          <t>2026-08-15 01:11:24</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hunbea91</t>
+          <t>https://www.tiktok.com/@agyeibeauty31</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>i.sho03</t>
+          <t>afia7773</t>
         </is>
       </c>
       <c r="B226" t="inlineStr"/>
@@ -9678,24 +9670,24 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-08-14 22:51:16</t>
+          <t>2026-08-12 13:41:03</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@i.sho03</t>
+          <t>https://www.tiktok.com/@afia7773</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>igbagbomi</t>
+          <t>affiliateproductlinks</t>
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -9707,36 +9699,36 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-08-14 00:16:05</t>
+          <t>2026-08-13 23:30:05</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@igbagbomi</t>
+          <t>https://www.tiktok.com/@affiliateproductlinks</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>inkednurseshop</t>
+          <t>adunola.prestige</t>
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -9746,31 +9738,31 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2026-08-08 22:25:05</t>
+          <t>2026-08-01 08:08:54</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@inkednurseshop</t>
+          <t>https://www.tiktok.com/@adunola.prestige</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>itsh1yk</t>
+          <t>adunni__taylor</t>
         </is>
       </c>
       <c r="B229" t="inlineStr"/>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -9780,24 +9772,24 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>2026-08-14 05:47:05</t>
+          <t>2026-08-06 16:07:06</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itsh1yk</t>
+          <t>https://www.tiktok.com/@adunni__taylor</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>iuliana.paun</t>
+          <t>1leics</t>
         </is>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -9814,65 +9806,65 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2026-08-01 11:27:45</t>
+          <t>2026-08-02 19:13:43</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@iuliana.paun</t>
+          <t>https://www.tiktok.com/@1leics</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>izzu.mama</t>
+          <t>tina4realaffliatemarkete</t>
         </is>
       </c>
       <c r="B231" t="inlineStr"/>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-08-14 06:16:05</t>
+          <t>2026-08-05 09:39:07</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@izzu.mama</t>
+          <t>https://www.tiktok.com/@tina4realaffliatemarkete</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>j_backupp123</t>
+          <t>tima_baby89</t>
         </is>
       </c>
       <c r="B232" t="inlineStr"/>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -9882,24 +9874,24 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-08-06 17:01:55</t>
+          <t>2026-08-01 00:14:09</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@j_backupp123</t>
+          <t>https://www.tiktok.com/@tima_baby89</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>gurds_hundal</t>
+          <t>user18539263935775</t>
         </is>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -9916,31 +9908,31 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2026-08-01 08:56:14</t>
+          <t>2026-08-06 03:48:43</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gurds_hundal</t>
+          <t>https://www.tiktok.com/@user18539263935775</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>hajiafolakekoleosorasaq</t>
+          <t>annamarie_s</t>
         </is>
       </c>
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -9950,58 +9942,58 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2026-08-02 13:17:59</t>
+          <t>2026-08-07 14:50:05</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hajiafolakekoleosorasaq</t>
+          <t>https://www.tiktok.com/@annamarie_s</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>halalqueen786</t>
+          <t>bozia247</t>
         </is>
       </c>
       <c r="B235" t="inlineStr"/>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2026-08-14 21:39:33</t>
+          <t>2026-08-02 15:51:28</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@halalqueen786</t>
+          <t>https://www.tiktok.com/@bozia247</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>harfi93z</t>
+          <t>bolaji.lukas</t>
         </is>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -10018,7 +10010,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2026-08-03 11:38:05</t>
+          <t>2026-08-03 20:46:20</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -10028,21 +10020,21 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@harfi93z</t>
+          <t>https://www.tiktok.com/@bolaji.lukas</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ladyoginni</t>
+          <t>bobbin.sense</t>
         </is>
       </c>
       <c r="B237" t="inlineStr"/>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -10052,31 +10044,31 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-08-02 17:06:03</t>
+          <t>2026-08-05 09:39:08</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ladyoginni</t>
+          <t>https://www.tiktok.com/@bobbin.sense</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>lifeassamantha</t>
+          <t>blesswithlove1</t>
         </is>
       </c>
       <c r="B238" t="inlineStr"/>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -10086,39 +10078,31 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-08-09 22:47:05</t>
+          <t>2026-08-02 17:56:53</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifeassamantha</t>
+          <t>https://www.tiktok.com/@blesswithlove1</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>lifeoflucy94</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>blessing91726</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
+      <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -10128,41 +10112,41 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-08-10 12:37:05</t>
+          <t>2026-08-08 08:05:43</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifeoflucy94</t>
+          <t>https://www.tiktok.com/@blessing91726</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>jasmineleahxox</t>
+          <t>blessing.steven83</t>
         </is>
       </c>
       <c r="B240" t="inlineStr"/>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>2026-08-07 22:48:05</t>
+          <t>2026-08-07 13:52:34</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -10172,21 +10156,21 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jasmineleahxox</t>
+          <t>https://www.tiktok.com/@blessing.steven83</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>jasontiktok4589</t>
+          <t>blessedmimi_</t>
         </is>
       </c>
       <c r="B241" t="inlineStr"/>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -10196,31 +10180,31 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>2026-08-05 09:08:16</t>
+          <t>2026-08-07 12:08:07</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jasontiktok4589</t>
+          <t>https://www.tiktok.com/@blessedmimi_</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>jeanny_uch</t>
+          <t>bimpy134</t>
         </is>
       </c>
       <c r="B242" t="inlineStr"/>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -10230,99 +10214,99 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>2026-08-03 20:12:45</t>
+          <t>2026-08-05 14:24:00</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jeanny_uch</t>
+          <t>https://www.tiktok.com/@bimpy134</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>joodjood758</t>
+          <t>bignastrolytic</t>
         </is>
       </c>
       <c r="B243" t="inlineStr"/>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>2026-08-09 01:27:55</t>
+          <t>2026-08-05 22:42:33</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@joodjood758</t>
+          <t>https://www.tiktok.com/@bignastrolytic</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>joseeskobar3</t>
+          <t>bexbestbuys</t>
         </is>
       </c>
       <c r="B244" t="inlineStr"/>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>2026-08-05 00:55:05</t>
+          <t>2026-08-11 19:53:05</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@joseeskobar3</t>
+          <t>https://www.tiktok.com/@bexbestbuys</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>junethebrand</t>
+          <t>kalisworld_yt</t>
         </is>
       </c>
       <c r="B245" t="inlineStr"/>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -10332,126 +10316,126 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>2026-08-14 07:25:06</t>
+          <t>2026-08-11 19:53:06</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@junethebrand</t>
+          <t>https://www.tiktok.com/@kalisworld_yt</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>kalisworld_yt</t>
+          <t>gla1890</t>
         </is>
       </c>
       <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>2026-08-11 19:53:06</t>
+          <t>2026-08-06 14:48:00</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kalisworld_yt</t>
+          <t>https://www.tiktok.com/@gla1890</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>kashmirri8</t>
+          <t>gillian.stevenson2</t>
         </is>
       </c>
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>2026-08-06 09:58:13</t>
+          <t>2026-08-15 08:13:02</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kashmirri8</t>
+          <t>https://www.tiktok.com/@gillian.stevenson2</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>katalinguti</t>
+          <t>gennyiceevablazas</t>
         </is>
       </c>
       <c r="B248" t="inlineStr"/>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>2026-08-04 07:12:10</t>
+          <t>2026-08-14 22:04:04</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@katalinguti</t>
+          <t>https://www.tiktok.com/@gennyiceevablazas</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>dawn294066</t>
+          <t>drlove925</t>
         </is>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -10468,31 +10452,31 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-08-01 21:06:12</t>
+          <t>2026-08-07 13:22:06</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dawn294066</t>
+          <t>https://www.tiktok.com/@drlove925</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>dealcheffinds</t>
+          <t>dreamcatcher00730</t>
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -10502,31 +10486,31 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>2026-08-12 07:04:05</t>
+          <t>2026-08-06 15:31:17</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dealcheffinds</t>
+          <t>https://www.tiktok.com/@dreamcatcher00730</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>dejaysol</t>
+          <t>fentonadventure</t>
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -10536,92 +10520,92 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2026-08-01 19:37:01</t>
+          <t>2026-08-12 18:12:07</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dejaysol</t>
+          <t>https://www.tiktok.com/@fentonadventure</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>deliciousmunch_</t>
+          <t>junethebrand</t>
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2026-08-05 11:59:54</t>
+          <t>2026-08-14 07:25:06</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@deliciousmunch_</t>
+          <t>https://www.tiktok.com/@junethebrand</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>delilah1910</t>
+          <t>joseeskobar3</t>
         </is>
       </c>
       <c r="B253" t="inlineStr"/>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2026-08-09 19:46:17</t>
+          <t>2026-08-05 00:55:05</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@delilah1910</t>
+          <t>https://www.tiktok.com/@joseeskobar3</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>denelos1</t>
+          <t>joodjood758</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -10638,24 +10622,24 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>2026-08-07 07:52:06</t>
+          <t>2026-08-09 01:27:55</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@denelos1</t>
+          <t>https://www.tiktok.com/@joodjood758</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>dipu.vyas</t>
+          <t>jeanny_uch</t>
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -10667,29 +10651,29 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>2026-08-07 14:45:52</t>
+          <t>2026-08-03 20:12:45</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dipu.vyas</t>
+          <t>https://www.tiktok.com/@jeanny_uch</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>kavi5ll</t>
+          <t>jasontiktok4589</t>
         </is>
       </c>
       <c r="B256" t="inlineStr"/>
@@ -10706,31 +10690,31 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>2026-08-03 07:40:33</t>
+          <t>2026-08-05 09:08:16</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kavi5ll</t>
+          <t>https://www.tiktok.com/@jasontiktok4589</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>kayskirado</t>
+          <t>jasmineleahxox</t>
         </is>
       </c>
       <c r="B257" t="inlineStr"/>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -10740,36 +10724,28 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-03 20:45:36</t>
+          <t>2026-08-07 22:48:05</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kayskirado</t>
+          <t>https://www.tiktok.com/@jasmineleahxox</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>kazza1992</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>kollinton777</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
+      <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -10782,24 +10758,24 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>2026-08-15 01:48:05</t>
+          <t>2026-08-11 19:56:12</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kazza1992</t>
+          <t>https://www.tiktok.com/@kollinton777</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>khadijamukhtar621</t>
+          <t>kingmxn</t>
         </is>
       </c>
       <c r="B259" t="inlineStr"/>
@@ -10811,22 +10787,22 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>2026-08-14 13:30:35</t>
+          <t>2026-08-11 19:53:06</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@khadijamukhtar621</t>
+          <t>https://www.tiktok.com/@kingmxn</t>
         </is>
       </c>
     </row>
@@ -10867,7 +10843,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>kingmxn</t>
+          <t>khadijamukhtar621</t>
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -10879,33 +10855,41 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>2026-08-11 19:53:06</t>
+          <t>2026-08-14 13:30:35</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kingmxn</t>
+          <t>https://www.tiktok.com/@khadijamukhtar621</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>kollinton777</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr"/>
-      <c r="C262" t="inlineStr"/>
+          <t>kazza1992</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D262" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -10918,24 +10902,24 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>2026-08-11 19:56:12</t>
+          <t>2026-08-15 01:48:05</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kollinton777</t>
+          <t>https://www.tiktok.com/@kazza1992</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>kymfragrancehouse</t>
+          <t>hunbea91</t>
         </is>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -10952,58 +10936,58 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06</t>
+          <t>2026-08-07 12:08:05</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kymfragrancehouse</t>
+          <t>https://www.tiktok.com/@hunbea91</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>maame.yaa8943</t>
+          <t>martinalast</t>
         </is>
       </c>
       <c r="B264" t="inlineStr"/>
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>2026-08-12 01:19:22</t>
+          <t>2026-08-13 11:03:49</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maame.yaa8943</t>
+          <t>https://www.tiktok.com/@martinalast</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>mabinty_kamara</t>
+          <t>mark.hyde2</t>
         </is>
       </c>
       <c r="B265" t="inlineStr"/>
@@ -11020,51 +11004,51 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-08-06 12:24:38</t>
+          <t>2026-08-02 09:49:39</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mabinty_kamara</t>
+          <t>https://www.tiktok.com/@mark.hyde2</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>maecacuenca</t>
+          <t>mammyoeqvs3</t>
         </is>
       </c>
       <c r="B266" t="inlineStr"/>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>2026-08-06 18:20:18</t>
+          <t>2026-08-13 16:08:17</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maecacuenca</t>
+          <t>https://www.tiktok.com/@mammyoeqvs3</t>
         </is>
       </c>
     </row>
@@ -11105,41 +11089,41 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>mammyoeqvs3</t>
+          <t>kayskirado</t>
         </is>
       </c>
       <c r="B268" t="inlineStr"/>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>2026-08-13 16:08:17</t>
+          <t>2026-08-03 20:45:36</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mammyoeqvs3</t>
+          <t>https://www.tiktok.com/@kayskirado</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>mark.hyde2</t>
+          <t>kavi5ll</t>
         </is>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -11156,65 +11140,65 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>2026-08-02 09:49:39</t>
+          <t>2026-08-03 07:40:33</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mark.hyde2</t>
+          <t>https://www.tiktok.com/@kavi5ll</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>martinalast</t>
+          <t>katalinguti</t>
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>2026-08-13 11:03:49</t>
+          <t>2026-08-04 07:12:10</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@martinalast</t>
+          <t>https://www.tiktok.com/@katalinguti</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>marvel_ola21</t>
+          <t>kashmirri8</t>
         </is>
       </c>
       <c r="B271" t="inlineStr"/>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -11224,24 +11208,24 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>2026-08-07 12:08:06</t>
+          <t>2026-08-06 09:58:13</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@marvel_ola21</t>
+          <t>https://www.tiktok.com/@kashmirri8</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>michm603</t>
+          <t>look23320</t>
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -11258,51 +11242,51 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>2026-08-03 17:23:30</t>
+          <t>2026-08-02 09:59:42</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@michm603</t>
+          <t>https://www.tiktok.com/@look23320</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>lisa.lashes</t>
+          <t>livinglegend839</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-08-11 19:53:05</t>
+          <t>2026-08-02 23:14:52</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lisa.lashes</t>
+          <t>https://www.tiktok.com/@livinglegend839</t>
         </is>
       </c>
     </row>
@@ -11343,82 +11327,90 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>livinglegend839</t>
+          <t>lisa.lashes</t>
         </is>
       </c>
       <c r="B275" t="inlineStr"/>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>2026-08-02 23:14:52</t>
+          <t>2026-08-11 19:53:05</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@livinglegend839</t>
+          <t>https://www.tiktok.com/@lisa.lashes</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>look23320</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr"/>
-      <c r="C276" t="inlineStr"/>
+          <t>lifeoflucy94</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>2026-08-02 09:59:42</t>
+          <t>2026-08-10 12:37:05</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@look23320</t>
+          <t>https://www.tiktok.com/@lifeoflucy94</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>cynthiaafonso020</t>
+          <t>lifefindstts</t>
         </is>
       </c>
       <c r="B277" t="inlineStr"/>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -11428,24 +11420,24 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>2026-08-12 11:47:37</t>
+          <t>2026-08-13 19:42:05</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cynthiaafonso020</t>
+          <t>https://www.tiktok.com/@lifefindstts</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>dada.olubunmi</t>
+          <t>lifeassamantha</t>
         </is>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -11457,97 +11449,97 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>2026-08-10 04:05:17</t>
+          <t>2026-08-09 22:47:05</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dada.olubunmi</t>
+          <t>https://www.tiktok.com/@lifeassamantha</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>dailyfindsuk11</t>
+          <t>dwellingtonx</t>
         </is>
       </c>
       <c r="B279" t="inlineStr"/>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>2026-08-15 08:47:06</t>
+          <t>2026-08-01 10:36:28</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailyfindsuk11</t>
+          <t>https://www.tiktok.com/@dwellingtonx</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>fatoutouray13</t>
+          <t>mosesademola05</t>
         </is>
       </c>
       <c r="B280" t="inlineStr"/>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-08-09 20:50:33</t>
+          <t>2026-08-06 17:17:21</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fatoutouray13</t>
+          <t>https://www.tiktok.com/@mosesademola05</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>fatumaahmed914</t>
+          <t>miglenasabeva123</t>
         </is>
       </c>
       <c r="B281" t="inlineStr"/>
@@ -11564,65 +11556,65 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>2026-08-10 02:48:38</t>
+          <t>2026-08-07 19:19:21</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fatumaahmed914</t>
+          <t>https://www.tiktok.com/@miglenasabeva123</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>felixpowez0</t>
+          <t>midas5267</t>
         </is>
       </c>
       <c r="B282" t="inlineStr"/>
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>2026-08-02 05:46:54</t>
+          <t>2026-08-15 02:57:38</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@felixpowez0</t>
+          <t>https://www.tiktok.com/@midas5267</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>fentonadventure</t>
+          <t>michm603</t>
         </is>
       </c>
       <c r="B283" t="inlineStr"/>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -11632,65 +11624,65 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>2026-08-12 18:12:07</t>
+          <t>2026-08-03 17:23:30</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fentonadventure</t>
+          <t>https://www.tiktok.com/@michm603</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>florida_745</t>
+          <t>nipay3foon123</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>2026-08-03 23:59:55</t>
+          <t>2026-08-12 23:16:58</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@florida_745</t>
+          <t>https://www.tiktok.com/@nipay3foon123</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>funmilayoyinloye</t>
+          <t>felixpowez0</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -11700,58 +11692,58 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>2026-08-04 20:44:06</t>
+          <t>2026-08-02 05:46:54</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@funmilayoyinloye</t>
+          <t>https://www.tiktok.com/@felixpowez0</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>christinemaughan4</t>
+          <t>fatumaahmed914</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>2026-08-05 16:46:16</t>
+          <t>2026-08-10 02:48:38</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@christinemaughan4</t>
+          <t>https://www.tiktok.com/@fatumaahmed914</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>coolestinfluencer1</t>
+          <t>fatoutouray13</t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -11768,70 +11760,70 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>2026-08-06 15:49:05</t>
+          <t>2026-08-09 20:50:33</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@coolestinfluencer1</t>
+          <t>https://www.tiktok.com/@fatoutouray13</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>courage.ik</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>fainaksalih</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
+      <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>2026-08-15 14:23:05</t>
+          <t>2026-08-07 14:00:12</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@courage.ik</t>
+          <t>https://www.tiktok.com/@fainaksalih</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>courtneygirlmum</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr"/>
-      <c r="C289" t="inlineStr"/>
+          <t>facelessliligood</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D289" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -11844,92 +11836,92 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-14 00:17:05</t>
+          <t>2026-08-10 10:47:15</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@courtneygirlmum</t>
+          <t>https://www.tiktok.com/@facelessliligood</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>craigbaker83</t>
+          <t>ernescoralzamor99</t>
         </is>
       </c>
       <c r="B290" t="inlineStr"/>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>2026-08-06 16:31:52</t>
+          <t>2026-08-14 00:44:21</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@craigbaker83</t>
+          <t>https://www.tiktok.com/@ernescoralzamor99</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>cupcake88807</t>
+          <t>ladyoginni</t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>2026-08-12 08:45:34</t>
+          <t>2026-08-02 17:06:03</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cupcake88807</t>
+          <t>https://www.tiktok.com/@ladyoginni</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>cutebells14</t>
+          <t>kymfragrancehouse</t>
         </is>
       </c>
       <c r="B292" t="inlineStr"/>
@@ -11946,24 +11938,24 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>2026-08-11 08:40:06</t>
+          <t>2026-08-06 15:46:06</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cutebells14</t>
+          <t>https://www.tiktok.com/@kymfragrancehouse</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>loyrodatips</t>
+          <t>marvel_ola21</t>
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -11975,29 +11967,29 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>2026-08-15 12:26:23</t>
+          <t>2026-08-07 12:08:06</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@loyrodatips</t>
+          <t>https://www.tiktok.com/@marvel_ola21</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>miglenasabeva123</t>
+          <t>harryhav1</t>
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -12009,29 +12001,29 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>2026-08-07 19:19:21</t>
+          <t>2026-08-06 16:39:06</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@miglenasabeva123</t>
+          <t>https://www.tiktok.com/@harryhav1</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>mosesademola05</t>
+          <t>harfi93z</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
@@ -12048,99 +12040,99 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>2026-08-06 17:17:21</t>
+          <t>2026-08-03 11:38:05</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mosesademola05</t>
+          <t>https://www.tiktok.com/@harfi93z</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>mosh77265</t>
+          <t>halalqueen786</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>2026-08-05 00:04:34</t>
+          <t>2026-08-14 21:39:33</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mosh77265</t>
+          <t>https://www.tiktok.com/@halalqueen786</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>motunrayo.adelowo</t>
+          <t>adeolamustapha973</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>2026-08-03 13:30:07</t>
+          <t>2026-08-11 20:36:48</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@motunrayo.adelowo</t>
+          <t>https://www.tiktok.com/@adeolamustapha973</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>muhammedasif380</t>
+          <t>dealcheffinds</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -12150,24 +12142,24 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-08-06 08:34:46</t>
+          <t>2026-08-12 07:04:05</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@muhammedasif380</t>
+          <t>https://www.tiktok.com/@dealcheffinds</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>chrisnnamani7</t>
+          <t>dawn294066</t>
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -12184,92 +12176,92 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>2026-08-07 08:50:04</t>
+          <t>2026-08-01 21:06:12</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chrisnnamani7</t>
+          <t>https://www.tiktok.com/@dawn294066</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>dorathy.ochokwu</t>
+          <t>dailyfindsuk11</t>
         </is>
       </c>
       <c r="B300" t="inlineStr"/>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>2026-08-04 16:17:55</t>
+          <t>2026-08-15 08:47:06</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dorathy.ochokwu</t>
+          <t>https://www.tiktok.com/@dailyfindsuk11</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>dorinepride</t>
+          <t>emjems1</t>
         </is>
       </c>
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>2026-08-02 17:19:48</t>
+          <t>2026-08-14 07:41:05</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dorinepride</t>
+          <t>https://www.tiktok.com/@emjems1</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>dreamcatcher00730</t>
+          <t>maecacuenca</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -12286,7 +12278,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>2026-08-06 15:31:17</t>
+          <t>2026-08-06 18:20:18</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -12296,14 +12288,14 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dreamcatcher00730</t>
+          <t>https://www.tiktok.com/@maecacuenca</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>drlove925</t>
+          <t>mabinty_kamara</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -12320,31 +12312,31 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>2026-08-07 13:22:06</t>
+          <t>2026-08-06 12:24:38</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@drlove925</t>
+          <t>https://www.tiktok.com/@mabinty_kamara</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>dwellingtonx</t>
+          <t>maame.yaa8943</t>
         </is>
       </c>
       <c r="B304" t="inlineStr"/>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -12354,24 +12346,24 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>2026-08-01 10:36:28</t>
+          <t>2026-08-12 01:19:22</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dwellingtonx</t>
+          <t>https://www.tiktok.com/@maame.yaa8943</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>dzidzor2</t>
+          <t>loyrodatips</t>
         </is>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -12388,100 +12380,92 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>2026-08-12 11:19:50</t>
+          <t>2026-08-15 12:26:23</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dzidzor2</t>
+          <t>https://www.tiktok.com/@loyrodatips</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>edith_braids23</t>
+          <t>mummsyboy</t>
         </is>
       </c>
       <c r="B306" t="inlineStr"/>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>2026-08-11 14:28:03</t>
+          <t>2026-08-10 05:20:18</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@edith_braids23</t>
+          <t>https://www.tiktok.com/@mummsyboy</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>facelessliligood</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>muhammedasif380</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr"/>
+      <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-08-10 10:47:15</t>
+          <t>2026-08-06 08:34:46</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@facelessliligood</t>
+          <t>https://www.tiktok.com/@muhammedasif380</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>fainaksalih</t>
+          <t>motunrayo.adelowo</t>
         </is>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -12498,31 +12482,31 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>2026-08-07 14:00:12</t>
+          <t>2026-08-03 13:30:07</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fainaksalih</t>
+          <t>https://www.tiktok.com/@motunrayo.adelowo</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>chanda_cart</t>
+          <t>mosh77265</t>
         </is>
       </c>
       <c r="B309" t="inlineStr"/>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -12532,65 +12516,65 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>2026-08-07 14:50:05</t>
+          <t>2026-08-05 00:04:34</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chanda_cart</t>
+          <t>https://www.tiktok.com/@mosh77265</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>cherylboateng</t>
+          <t>nikkib2311</t>
         </is>
       </c>
       <c r="B310" t="inlineStr"/>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>2026-08-07 07:09:09</t>
+          <t>2026-08-14 22:13:05</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cherylboateng</t>
+          <t>https://www.tiktok.com/@nikkib2311</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>cynthiaadeolaobaf</t>
+          <t>nenyebourdillon</t>
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -12600,28 +12584,36 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-08-02 08:36:28</t>
+          <t>2026-08-01 06:39:16</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cynthiaadeolaobaf</t>
+          <t>https://www.tiktok.com/@nenyebourdillon</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>mummsyboy</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr"/>
-      <c r="C312" t="inlineStr"/>
+          <t>neavemariep</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D312" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -12629,112 +12621,104 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>2026-08-10 05:20:18</t>
+          <t>2026-08-14 20:25:05</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mummsyboy</t>
+          <t>https://www.tiktok.com/@neavemariep</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>nadia98154</t>
+          <t>nafisatu_allassani</t>
         </is>
       </c>
       <c r="B313" t="inlineStr"/>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>2026-08-15 04:36:05</t>
+          <t>2026-08-01 16:56:10</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nadia98154</t>
+          <t>https://www.tiktok.com/@nafisatu_allassani</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>nafisatu_allassani</t>
+          <t>nadia98154</t>
         </is>
       </c>
       <c r="B314" t="inlineStr"/>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>2026-08-01 16:56:10</t>
+          <t>2026-08-15 04:36:05</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nafisatu_allassani</t>
+          <t>https://www.tiktok.com/@nadia98154</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>neavemariep</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>iuliana.paun</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr"/>
+      <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -12744,24 +12728,24 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>2026-08-14 20:25:05</t>
+          <t>2026-08-01 11:27:45</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@neavemariep</t>
+          <t>https://www.tiktok.com/@iuliana.paun</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>nenyebourdillon</t>
+          <t>itsh1yk</t>
         </is>
       </c>
       <c r="B316" t="inlineStr"/>
@@ -12778,65 +12762,65 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>2026-08-01 06:39:16</t>
+          <t>2026-08-14 05:47:05</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nenyebourdillon</t>
+          <t>https://www.tiktok.com/@itsh1yk</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>nikkib2311</t>
+          <t>inkednurseshop</t>
         </is>
       </c>
       <c r="B317" t="inlineStr"/>
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>2026-08-14 22:13:05</t>
+          <t>2026-08-08 22:25:05</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nikkib2311</t>
+          <t>https://www.tiktok.com/@inkednurseshop</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>nikky_vibez</t>
+          <t>igbagbomi</t>
         </is>
       </c>
       <c r="B318" t="inlineStr"/>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -12846,24 +12830,24 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>2026-08-11 12:48:54</t>
+          <t>2026-08-14 00:16:05</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nikky_vibez</t>
+          <t>https://www.tiktok.com/@igbagbomi</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>nipay3foon123</t>
+          <t>i.sho03</t>
         </is>
       </c>
       <c r="B319" t="inlineStr"/>
@@ -12880,65 +12864,65 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>2026-08-12 23:16:58</t>
+          <t>2026-08-14 22:51:16</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nipay3foon123</t>
+          <t>https://www.tiktok.com/@i.sho03</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>nish_93syeda</t>
+          <t>zainab36576</t>
         </is>
       </c>
       <c r="B320" t="inlineStr"/>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>2026-08-02 12:33:41</t>
+          <t>2026-08-10 08:56:01</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nish_93syeda</t>
+          <t>https://www.tiktok.com/@zainab36576</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>nisham010</t>
+          <t>heyitslindaxo</t>
         </is>
       </c>
       <c r="B321" t="inlineStr"/>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -12948,24 +12932,24 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-01 06:41:58</t>
+          <t>2026-08-11 08:47:05</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nisham010</t>
+          <t>https://www.tiktok.com/@heyitslindaxo</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>norashkute</t>
+          <t>helen.che72</t>
         </is>
       </c>
       <c r="B322" t="inlineStr"/>
@@ -12982,24 +12966,24 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>2026-08-05 19:03:41</t>
+          <t>2026-08-03 11:09:13</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@norashkute</t>
+          <t>https://www.tiktok.com/@helen.che72</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>midas5267</t>
+          <t>healthylifechanges</t>
         </is>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -13011,131 +12995,131 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>2026-08-15 02:57:38</t>
+          <t>2026-08-11 08:14:07</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@midas5267</t>
+          <t>https://www.tiktok.com/@healthylifechanges</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>queenc023</t>
+          <t>hazeraqureshy</t>
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>2026-08-02 23:20:03</t>
+          <t>2026-08-14 18:50:49</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queenc023</t>
+          <t>https://www.tiktok.com/@hazeraqureshy</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>queenlady7354</t>
+          <t>prettybrown_muje</t>
         </is>
       </c>
       <c r="B325" t="inlineStr"/>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>2026-08-07 07:05:09</t>
+          <t>2026-08-10 06:36:09</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queenlady7354</t>
+          <t>https://www.tiktok.com/@prettybrown_muje</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>quentinnke</t>
+          <t>preety.vault</t>
         </is>
       </c>
       <c r="B326" t="inlineStr"/>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>2026-08-06 18:38:45</t>
+          <t>2026-08-11 19:53:07</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@quentinnke</t>
+          <t>https://www.tiktok.com/@preety.vault</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>octimove</t>
+          <t>patriciahoward372</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -13152,65 +13136,73 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>2026-08-06 20:35:34</t>
+          <t>2026-08-05 07:35:54</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@octimove</t>
+          <t>https://www.tiktok.com/@patriciahoward372</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>odubele.2177</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr"/>
-      <c r="C328" t="inlineStr"/>
+          <t>em_j_10</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>2026-08-04 10:42:50</t>
+          <t>2026-08-10 12:52:05</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@odubele.2177</t>
+          <t>https://www.tiktok.com/@em_j_10</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>off.duty.ninja6</t>
+          <t>edith_braids23</t>
         </is>
       </c>
       <c r="B329" t="inlineStr"/>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -13220,65 +13212,65 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>2026-08-14 17:30:05</t>
+          <t>2026-08-11 14:28:03</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@off.duty.ninja6</t>
+          <t>https://www.tiktok.com/@edith_braids23</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ogboduprincess1</t>
+          <t>dzidzor2</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>2026-08-06 10:18:22</t>
+          <t>2026-08-12 11:19:50</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ogboduprincess1</t>
+          <t>https://www.tiktok.com/@dzidzor2</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>okemorenikerachea</t>
+          <t>verascuisine_</t>
         </is>
       </c>
       <c r="B331" t="inlineStr"/>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -13288,7 +13280,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-08-12 09:21:47</t>
+          <t>2026-08-12 07:40:06</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -13298,14 +13290,14 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@okemorenikerachea</t>
+          <t>https://www.tiktok.com/@verascuisine_</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>bozia247</t>
+          <t>berniceamong</t>
         </is>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -13322,24 +13314,24 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>2026-08-02 15:51:28</t>
+          <t>2026-08-03 15:51:52</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bozia247</t>
+          <t>https://www.tiktok.com/@berniceamong</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>bukola_sole</t>
+          <t>benjalooywd</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -13356,65 +13348,65 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>2026-08-02 22:15:14</t>
+          <t>2026-08-03 09:06:41</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bukola_sole</t>
+          <t>https://www.tiktok.com/@benjalooywd</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>bukolaadee</t>
+          <t>beekaylux20</t>
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
       <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>2026-08-08 09:20:44</t>
+          <t>2026-08-05 23:21:36</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bukolaadee</t>
+          <t>https://www.tiktok.com/@beekaylux20</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>busivincent</t>
+          <t>bee.finds_</t>
         </is>
       </c>
       <c r="B335" t="inlineStr"/>
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -13424,31 +13416,39 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>2026-08-06 14:40:06</t>
+          <t>2026-08-04 08:14:06</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@busivincent</t>
+          <t>https://www.tiktok.com/@bee.finds_</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>carinadyarte</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr"/>
-      <c r="C336" t="inlineStr"/>
+          <t>beautycontrol_by_nikky1</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -13458,28 +13458,36 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>2026-08-15 17:25:05</t>
+          <t>2026-08-04 11:31:54</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@carinadyarte</t>
+          <t>https://www.tiktok.com/@beautycontrol_by_nikky1</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>carolducasse2</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr"/>
-      <c r="C337" t="inlineStr"/>
+          <t>azizanso</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D337" t="inlineStr">
         <is>
           <t>Lemon Ginger</t>
@@ -13492,31 +13500,31 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>2026-08-01 12:23:54</t>
+          <t>2026-08-04 17:14:44</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@carolducasse2</t>
+          <t>https://www.tiktok.com/@azizanso</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>celestialcreations1981</t>
+          <t>user9813841001322</t>
         </is>
       </c>
       <c r="B338" t="inlineStr"/>
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -13526,24 +13534,24 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>2026-08-05 11:42:44</t>
+          <t>2026-08-02 23:48:31</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@celestialcreations1981</t>
+          <t>https://www.tiktok.com/@user9813841001322</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>champagnnne20</t>
+          <t>ash01703</t>
         </is>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -13560,31 +13568,31 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>2026-08-03 21:16:29</t>
+          <t>2026-08-04 08:26:07</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@champagnnne20</t>
+          <t>https://www.tiktok.com/@ash01703</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>teexvnn</t>
+          <t>nikky_vibez</t>
         </is>
       </c>
       <c r="B340" t="inlineStr"/>
       <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -13594,92 +13602,100 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>2026-08-06 22:39:00</t>
+          <t>2026-08-11 12:48:54</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teexvnn</t>
+          <t>https://www.tiktok.com/@nikky_vibez</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>bexbestbuys</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr"/>
-      <c r="C341" t="inlineStr"/>
+          <t>courage.ik</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-08-11 19:53:05</t>
+          <t>2026-08-15 14:23:05</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bexbestbuys</t>
+          <t>https://www.tiktok.com/@courage.ik</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>bignastrolytic</t>
+          <t>coolestinfluencer1</t>
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-08-05 22:42:33</t>
+          <t>2026-08-06 15:49:05</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bignastrolytic</t>
+          <t>https://www.tiktok.com/@coolestinfluencer1</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>bimpy134</t>
+          <t>dorinepride</t>
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
@@ -13696,31 +13712,31 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>2026-08-05 14:24:00</t>
+          <t>2026-08-02 17:19:48</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bimpy134</t>
+          <t>https://www.tiktok.com/@dorinepride</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>blessedmimi_</t>
+          <t>dorathy.ochokwu</t>
         </is>
       </c>
       <c r="B344" t="inlineStr"/>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -13730,31 +13746,31 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>2026-08-07 12:08:07</t>
+          <t>2026-08-04 16:17:55</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blessedmimi_</t>
+          <t>https://www.tiktok.com/@dorathy.ochokwu</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>chillimilli385</t>
+          <t>arinolavictory</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -13764,65 +13780,65 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>2026-08-09 15:57:05</t>
+          <t>2026-08-01 12:59:45</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chillimilli385</t>
+          <t>https://www.tiktok.com/@arinolavictory</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>olabisismd</t>
+          <t>annwakonyo82</t>
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>2026-08-12 07:46:02</t>
+          <t>2026-08-03 08:01:11</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@olabisismd</t>
+          <t>https://www.tiktok.com/@annwakonyo82</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>ollie.in.yorkshire</t>
+          <t>olabisismd</t>
         </is>
       </c>
       <c r="B347" t="inlineStr"/>
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -13832,24 +13848,24 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>2026-08-10 12:53:05</t>
+          <t>2026-08-12 07:46:02</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ollie.in.yorkshire</t>
+          <t>https://www.tiktok.com/@olabisismd</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>olori305</t>
+          <t>okemorenikerachea</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -13866,92 +13882,92 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>2026-08-15 12:09:44</t>
+          <t>2026-08-12 09:21:47</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@olori305</t>
+          <t>https://www.tiktok.com/@okemorenikerachea</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>oluwafunke.taiwo3</t>
+          <t>ogboduprincess1</t>
         </is>
       </c>
       <c r="B349" t="inlineStr"/>
       <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>2026-08-14 08:40:13</t>
+          <t>2026-08-06 10:18:22</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluwafunke.taiwo3</t>
+          <t>https://www.tiktok.com/@ogboduprincess1</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>owoblow2010</t>
+          <t>off.duty.ninja6</t>
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
       <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>2026-08-09 11:18:52</t>
+          <t>2026-08-14 17:30:05</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@owoblow2010</t>
+          <t>https://www.tiktok.com/@off.duty.ninja6</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>pammie115</t>
+          <t>odubele.2177</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -13968,24 +13984,24 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>2026-08-02 20:52:59</t>
+          <t>2026-08-04 10:42:50</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@pammie115</t>
+          <t>https://www.tiktok.com/@odubele.2177</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>patriciahoward372</t>
+          <t>octimove</t>
         </is>
       </c>
       <c r="B352" t="inlineStr"/>
@@ -14002,92 +14018,92 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>2026-08-05 07:35:54</t>
+          <t>2026-08-06 20:35:34</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@patriciahoward372</t>
+          <t>https://www.tiktok.com/@octimove</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>preety.vault</t>
+          <t>norashkute</t>
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
       <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-11 19:53:07</t>
+          <t>2026-08-05 19:03:41</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@preety.vault</t>
+          <t>https://www.tiktok.com/@norashkute</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>prettybrown_muje</t>
+          <t>nisham010</t>
         </is>
       </c>
       <c r="B354" t="inlineStr"/>
       <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>2026-08-10 06:36:09</t>
+          <t>2026-08-01 06:41:58</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@prettybrown_muje</t>
+          <t>https://www.tiktok.com/@nisham010</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>prophetessjudith06</t>
+          <t>nish_93syeda</t>
         </is>
       </c>
       <c r="B355" t="inlineStr"/>
@@ -14104,24 +14120,24 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>2026-08-04 22:40:33</t>
+          <t>2026-08-02 12:33:41</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@prophetessjudith06</t>
+          <t>https://www.tiktok.com/@nish_93syeda</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>saheed.david</t>
+          <t>prophetessjudith06</t>
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -14138,24 +14154,24 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>2026-08-06 19:31:13</t>
+          <t>2026-08-04 22:40:33</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@saheed.david</t>
+          <t>https://www.tiktok.com/@prophetessjudith06</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>saiqa14486</t>
+          <t>quentinnke</t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -14172,24 +14188,24 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>2026-08-02 09:09:21</t>
+          <t>2026-08-06 18:38:45</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@saiqa14486</t>
+          <t>https://www.tiktok.com/@quentinnke</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>salma.ibrahim588</t>
+          <t>queenlady7354</t>
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
@@ -14206,24 +14222,24 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>2026-08-06 17:20:21</t>
+          <t>2026-08-07 07:05:09</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@salma.ibrahim588</t>
+          <t>https://www.tiktok.com/@queenlady7354</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>samiashoaib937</t>
+          <t>queenc023</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -14240,31 +14256,31 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>2026-08-05 13:12:55</t>
+          <t>2026-08-02 23:20:03</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samiashoaib937</t>
+          <t>https://www.tiktok.com/@queenc023</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>shafaq1679</t>
+          <t>samiashoaib937</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
       <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -14274,65 +14290,65 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>2026-08-15 14:12:05</t>
+          <t>2026-08-05 13:12:55</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shafaq1679</t>
+          <t>https://www.tiktok.com/@samiashoaib937</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>shanazahmed452</t>
+          <t>salma.ibrahim588</t>
         </is>
       </c>
       <c r="B361" t="inlineStr"/>
       <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>2026-08-09 20:31:21</t>
+          <t>2026-08-06 17:20:21</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shanazahmed452</t>
+          <t>https://www.tiktok.com/@salma.ibrahim588</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>temi4t</t>
+          <t>saiqa14486</t>
         </is>
       </c>
       <c r="B362" t="inlineStr"/>
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -14342,58 +14358,58 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>2026-08-11 08:40:06</t>
+          <t>2026-08-02 09:09:21</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@temi4t</t>
+          <t>https://www.tiktok.com/@saiqa14486</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>r2chybe</t>
+          <t>pammie115</t>
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
       <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>2026-08-14 22:37:05</t>
+          <t>2026-08-02 20:52:59</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@r2chybe</t>
+          <t>https://www.tiktok.com/@pammie115</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>radical818</t>
+          <t>owoblow2010</t>
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
@@ -14410,134 +14426,126 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-08-08 12:59:20</t>
+          <t>2026-08-09 11:18:52</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@radical818</t>
+          <t>https://www.tiktok.com/@owoblow2010</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>ramat0218</t>
+          <t>oluwafunke.taiwo3</t>
         </is>
       </c>
       <c r="B365" t="inlineStr"/>
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>2026-08-03 10:28:15</t>
+          <t>2026-08-14 08:40:13</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ramat0218</t>
+          <t>https://www.tiktok.com/@oluwafunke.taiwo3</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>rasna2094</t>
+          <t>olori305</t>
         </is>
       </c>
       <c r="B366" t="inlineStr"/>
       <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>2026-08-05 14:13:31</t>
+          <t>2026-08-15 12:09:44</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rasna2094</t>
+          <t>https://www.tiktok.com/@olori305</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>rayoajokeade</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>100K-250K</t>
-        </is>
-      </c>
+          <t>ollie.in.yorkshire</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr"/>
+      <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>2026-08-04 19:14:41</t>
+          <t>2026-08-10 12:53:05</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rayoajokeade</t>
+          <t>https://www.tiktok.com/@ollie.in.yorkshire</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>rayplus06</t>
+          <t>rinajadupatel</t>
         </is>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -14554,17 +14562,17 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>2026-08-05 23:04:18</t>
+          <t>2026-08-03 23:12:58</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rayplus06</t>
+          <t>https://www.tiktok.com/@rinajadupatel</t>
         </is>
       </c>
     </row>
@@ -14605,7 +14613,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>rinajadupatel</t>
+          <t>rayplus06</t>
         </is>
       </c>
       <c r="B370" t="inlineStr"/>
@@ -14622,28 +14630,36 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>2026-08-03 23:12:58</t>
+          <t>2026-08-05 23:04:18</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rinajadupatel</t>
+          <t>https://www.tiktok.com/@rayplus06</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>berniceamong</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr"/>
-      <c r="C371" t="inlineStr"/>
+          <t>rayoajokeade</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>100K-250K</t>
+        </is>
+      </c>
       <c r="D371" t="inlineStr">
         <is>
           <t>Lemon Ginger</t>
@@ -14656,126 +14672,126 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>2026-08-03 15:51:52</t>
+          <t>2026-08-04 19:14:41</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@berniceamong</t>
+          <t>https://www.tiktok.com/@rayoajokeade</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>annamarie_s</t>
+          <t>courtneygirlmum</t>
         </is>
       </c>
       <c r="B372" t="inlineStr"/>
       <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>2026-08-07 14:50:05</t>
+          <t>2026-08-14 00:17:05</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@annamarie_s</t>
+          <t>https://www.tiktok.com/@courtneygirlmum</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>annwakonyo82</t>
+          <t>she.reigns.hair</t>
         </is>
       </c>
       <c r="B373" t="inlineStr"/>
       <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-08-03 08:01:11</t>
+          <t>2026-08-08 06:42:34</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@annwakonyo82</t>
+          <t>https://www.tiktok.com/@she.reigns.hair</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>arinolavictory</t>
+          <t>she.finds.v2</t>
         </is>
       </c>
       <c r="B374" t="inlineStr"/>
       <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>2026-08-01 12:59:45</t>
+          <t>2026-08-11 09:28:05</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@arinolavictory</t>
+          <t>https://www.tiktok.com/@she.finds.v2</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>ash01703</t>
+          <t>champagnnne20</t>
         </is>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -14792,31 +14808,31 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-08-04 08:26:07</t>
+          <t>2026-08-03 21:16:29</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ash01703</t>
+          <t>https://www.tiktok.com/@champagnnne20</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>temitayo0835</t>
+          <t>celestialcreations1981</t>
         </is>
       </c>
       <c r="B376" t="inlineStr"/>
       <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -14826,36 +14842,28 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>2026-08-12 14:54:19</t>
+          <t>2026-08-05 11:42:44</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@temitayo0835</t>
+          <t>https://www.tiktok.com/@celestialcreations1981</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>azizanso</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>carolducasse2</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr"/>
+      <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
           <t>Lemon Ginger</t>
@@ -14868,39 +14876,31 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>2026-08-04 17:14:44</t>
+          <t>2026-08-01 12:23:54</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@azizanso</t>
+          <t>https://www.tiktok.com/@carolducasse2</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>beautycontrol_by_nikky1</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>carinadyarte</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr"/>
+      <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -14910,58 +14910,58 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>2026-08-04 11:31:54</t>
+          <t>2026-08-15 17:25:05</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beautycontrol_by_nikky1</t>
+          <t>https://www.tiktok.com/@carinadyarte</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>blessing.steven83</t>
+          <t>busivincent</t>
         </is>
       </c>
       <c r="B379" t="inlineStr"/>
       <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>2026-08-07 13:52:34</t>
+          <t>2026-08-06 14:40:06</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blessing.steven83</t>
+          <t>https://www.tiktok.com/@busivincent</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>blessing91726</t>
+          <t>dipu.vyas</t>
         </is>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -14978,58 +14978,58 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>2026-08-08 08:05:43</t>
+          <t>2026-08-07 14:45:52</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blessing91726</t>
+          <t>https://www.tiktok.com/@dipu.vyas</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>blesswithlove1</t>
+          <t>denelos1</t>
         </is>
       </c>
       <c r="B381" t="inlineStr"/>
       <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>2026-08-02 17:56:53</t>
+          <t>2026-08-07 07:52:06</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blesswithlove1</t>
+          <t>https://www.tiktok.com/@denelos1</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>bobbin.sense</t>
+          <t>delilah1910</t>
         </is>
       </c>
       <c r="B382" t="inlineStr"/>
@@ -15041,29 +15041,29 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>2026-08-05 09:39:08</t>
+          <t>2026-08-09 19:46:17</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bobbin.sense</t>
+          <t>https://www.tiktok.com/@delilah1910</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>bolaji.lukas</t>
+          <t>deliciousmunch_</t>
         </is>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -15080,31 +15080,31 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>2026-08-03 20:46:20</t>
+          <t>2026-08-05 11:59:54</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bolaji.lukas</t>
+          <t>https://www.tiktok.com/@deliciousmunch_</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>temmiedee68</t>
+          <t>dejaysol</t>
         </is>
       </c>
       <c r="B384" t="inlineStr"/>
       <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -15114,24 +15114,24 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>2026-08-14 18:09:35</t>
+          <t>2026-08-01 19:37:01</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@temmiedee68</t>
+          <t>https://www.tiktok.com/@dejaysol</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>rubz3364</t>
+          <t>rasna2094</t>
         </is>
       </c>
       <c r="B385" t="inlineStr"/>
@@ -15148,194 +15148,194 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-02 19:26:30</t>
+          <t>2026-08-05 14:13:31</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rubz3364</t>
+          <t>https://www.tiktok.com/@rasna2094</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>rukkyani1</t>
+          <t>ramat0218</t>
         </is>
       </c>
       <c r="B386" t="inlineStr"/>
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>2026-08-07 15:30:26</t>
+          <t>2026-08-03 10:28:15</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rukkyani1</t>
+          <t>https://www.tiktok.com/@ramat0218</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>sabbira26</t>
+          <t>radical818</t>
         </is>
       </c>
       <c r="B387" t="inlineStr"/>
       <c r="C387" t="inlineStr"/>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>2026-08-05 20:52:32</t>
+          <t>2026-08-08 12:59:20</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sabbira26</t>
+          <t>https://www.tiktok.com/@radical818</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>beekaylux20</t>
+          <t>r2chybe</t>
         </is>
       </c>
       <c r="B388" t="inlineStr"/>
       <c r="C388" t="inlineStr"/>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>2026-08-05 23:21:36</t>
+          <t>2026-08-14 22:37:05</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beekaylux20</t>
+          <t>https://www.tiktok.com/@r2chybe</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>benjalooywd</t>
+          <t>cutebells14</t>
         </is>
       </c>
       <c r="B389" t="inlineStr"/>
       <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>2026-08-03 09:06:41</t>
+          <t>2026-08-11 08:40:06</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benjalooywd</t>
+          <t>https://www.tiktok.com/@cutebells14</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>soniakelly798</t>
+          <t>cupcake88807</t>
         </is>
       </c>
       <c r="B390" t="inlineStr"/>
       <c r="C390" t="inlineStr"/>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>2026-08-06 18:56:32</t>
+          <t>2026-08-12 08:45:34</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@soniakelly798</t>
+          <t>https://www.tiktok.com/@cupcake88807</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>sophia.annan2</t>
+          <t>craigbaker83</t>
         </is>
       </c>
       <c r="B391" t="inlineStr"/>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>2026-08-06 06:16:15</t>
+          <t>2026-08-06 16:31:52</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
@@ -15362,14 +15362,14 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sophia.annan2</t>
+          <t>https://www.tiktok.com/@craigbaker83</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>stacecaldridge</t>
+          <t>shanazahmed452</t>
         </is>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -15381,36 +15381,36 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>2026-08-15 16:51:05</t>
+          <t>2026-08-09 20:31:21</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@stacecaldridge</t>
+          <t>https://www.tiktok.com/@shanazahmed452</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>stecrawford0</t>
+          <t>shafaq1679</t>
         </is>
       </c>
       <c r="B393" t="inlineStr"/>
       <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -15420,24 +15420,24 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>2026-08-02 12:57:01</t>
+          <t>2026-08-15 14:12:05</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@stecrawford0</t>
+          <t>https://www.tiktok.com/@shafaq1679</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>sulaimon.ashogbon</t>
+          <t>taiwoawoyemi6</t>
         </is>
       </c>
       <c r="B394" t="inlineStr"/>
@@ -15454,24 +15454,24 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>2026-08-01 09:37:26</t>
+          <t>2026-08-05 09:45:32</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sulaimon.ashogbon</t>
+          <t>https://www.tiktok.com/@taiwoawoyemi6</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>taiwoawoyemi6</t>
+          <t>sulaimon.ashogbon</t>
         </is>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -15488,24 +15488,24 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>2026-08-05 09:45:32</t>
+          <t>2026-08-01 09:37:26</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@taiwoawoyemi6</t>
+          <t>https://www.tiktok.com/@sulaimon.ashogbon</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>temmit7</t>
+          <t>stecrawford0</t>
         </is>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -15522,7 +15522,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>2026-08-02 10:56:06</t>
+          <t>2026-08-02 12:57:01</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
@@ -15532,14 +15532,14 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@temmit7</t>
+          <t>https://www.tiktok.com/@stecrawford0</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>teresa_plugs</t>
+          <t>saheed.david</t>
         </is>
       </c>
       <c r="B397" t="inlineStr"/>
@@ -15556,31 +15556,31 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-08-03 14:33:13</t>
+          <t>2026-08-06 19:31:13</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teresa_plugs</t>
+          <t>https://www.tiktok.com/@saheed.david</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>she.finds.v2</t>
+          <t>sabbira26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr"/>
       <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -15590,24 +15590,24 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>2026-08-11 09:28:05</t>
+          <t>2026-08-05 20:52:32</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@she.finds.v2</t>
+          <t>https://www.tiktok.com/@sabbira26</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>she.reigns.hair</t>
+          <t>rukkyani1</t>
         </is>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -15624,24 +15624,24 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>2026-08-08 06:42:34</t>
+          <t>2026-08-07 15:30:26</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@she.reigns.hair</t>
+          <t>https://www.tiktok.com/@rukkyani1</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>shubnamwarris</t>
+          <t>rubz3364</t>
         </is>
       </c>
       <c r="B400" t="inlineStr"/>
@@ -15658,24 +15658,24 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>2026-08-03 16:48:58</t>
+          <t>2026-08-02 19:26:30</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shubnamwarris</t>
+          <t>https://www.tiktok.com/@rubz3364</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>siham19641</t>
+          <t>soniakelly798</t>
         </is>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -15692,17 +15692,17 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>2026-08-03 22:10:42</t>
+          <t>2026-08-06 18:56:32</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@siham19641</t>
+          <t>https://www.tiktok.com/@soniakelly798</t>
         </is>
       </c>
     </row>
@@ -15743,7 +15743,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>andreadavies903</t>
+          <t>siham19641</t>
         </is>
       </c>
       <c r="B403" t="inlineStr"/>
@@ -15760,58 +15760,58 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>2026-08-01 22:54:24</t>
+          <t>2026-08-03 22:10:42</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@andreadavies903</t>
+          <t>https://www.tiktok.com/@siham19641</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>ukineboconnect</t>
+          <t>shubnamwarris</t>
         </is>
       </c>
       <c r="B404" t="inlineStr"/>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-08-07 12:08:05</t>
+          <t>2026-08-03 16:48:58</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ukineboconnect</t>
+          <t>https://www.tiktok.com/@shubnamwarris</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>adenike.badejo</t>
+          <t>chrisnnamani7</t>
         </is>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -15828,31 +15828,31 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>2026-08-01 18:42:56</t>
+          <t>2026-08-07 08:50:04</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adenike.badejo</t>
+          <t>https://www.tiktok.com/@chrisnnamani7</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>adeola.omoshalewa</t>
+          <t>chillimilli385</t>
         </is>
       </c>
       <c r="B406" t="inlineStr"/>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -15862,65 +15862,65 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>2026-08-05 22:58:05</t>
+          <t>2026-08-09 15:57:05</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adeola.omoshalewa</t>
+          <t>https://www.tiktok.com/@chillimilli385</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>adeolamustapha973</t>
+          <t>cherylboateng</t>
         </is>
       </c>
       <c r="B407" t="inlineStr"/>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>2026-08-11 20:36:48</t>
+          <t>2026-08-07 07:09:09</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adeolamustapha973</t>
+          <t>https://www.tiktok.com/@cherylboateng</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>adunni__taylor</t>
+          <t>chanda_cart</t>
         </is>
       </c>
       <c r="B408" t="inlineStr"/>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -15930,31 +15930,31 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>2026-08-06 16:07:06</t>
+          <t>2026-08-07 14:50:05</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adunni__taylor</t>
+          <t>https://www.tiktok.com/@chanda_cart</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>adunola.prestige</t>
+          <t>temmiedee68</t>
         </is>
       </c>
       <c r="B409" t="inlineStr"/>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -15964,24 +15964,24 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-08-01 08:08:54</t>
+          <t>2026-08-14 18:09:35</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adunola.prestige</t>
+          <t>https://www.tiktok.com/@temmiedee68</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>the_psy_lif3</t>
+          <t>temitayo0835</t>
         </is>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -15998,58 +15998,58 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>2026-08-08 21:16:05</t>
+          <t>2026-08-12 14:54:19</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@the_psy_lif3</t>
+          <t>https://www.tiktok.com/@temitayo0835</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>thea.w.finds</t>
+          <t>temi4t</t>
         </is>
       </c>
       <c r="B411" t="inlineStr"/>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>2026-08-15 11:08:05</t>
+          <t>2026-08-11 08:40:06</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thea.w.finds</t>
+          <t>https://www.tiktok.com/@temi4t</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>themyturpe4</t>
+          <t>teexvnn</t>
         </is>
       </c>
       <c r="B412" t="inlineStr"/>
@@ -16066,24 +16066,24 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>2026-08-05 13:22:07</t>
+          <t>2026-08-06 22:39:00</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@themyturpe4</t>
+          <t>https://www.tiktok.com/@teexvnn</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>tima_baby89</t>
+          <t>adamb719</t>
         </is>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -16100,92 +16100,92 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>2026-08-01 00:14:09</t>
+          <t>2026-08-03 12:14:53</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tima_baby89</t>
+          <t>https://www.tiktok.com/@adamb719</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>tina4realaffliatemarkete</t>
+          <t>abosedeisaac7</t>
         </is>
       </c>
       <c r="B414" t="inlineStr"/>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>2026-08-05 09:39:07</t>
+          <t>2026-08-06 22:04:12</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tina4realaffliatemarkete</t>
+          <t>https://www.tiktok.com/@abosedeisaac7</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>tinu.ola</t>
+          <t>abbyades</t>
         </is>
       </c>
       <c r="B415" t="inlineStr"/>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>2026-08-12 16:40:53</t>
+          <t>2026-08-03 13:07:56</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tinu.ola</t>
+          <t>https://www.tiktok.com/@abbyades</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>tinugold123</t>
+          <t>bukolaadee</t>
         </is>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -16197,29 +16197,29 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>2026-08-04 00:42:18</t>
+          <t>2026-08-08 09:20:44</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tinugold123</t>
+          <t>https://www.tiktok.com/@bukolaadee</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>toyinedos</t>
+          <t>bukola_sole</t>
         </is>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -16236,31 +16236,31 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-04 07:24:05</t>
+          <t>2026-08-02 22:15:14</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@toyinedos</t>
+          <t>https://www.tiktok.com/@bukola_sole</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>the.love.of.god36</t>
+          <t>dada.olubunmi</t>
         </is>
       </c>
       <c r="B418" t="inlineStr"/>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -16270,24 +16270,24 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>2026-08-12 14:24:43</t>
+          <t>2026-08-10 04:05:17</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@the.love.of.god36</t>
+          <t>https://www.tiktok.com/@dada.olubunmi</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>bee.finds_</t>
+          <t>cynthiaafonso020</t>
         </is>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -16299,29 +16299,29 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>2026-08-04 08:14:06</t>
+          <t>2026-08-12 11:47:37</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bee.finds_</t>
+          <t>https://www.tiktok.com/@cynthiaafonso020</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>victoriaookoro</t>
+          <t>cynthiaadeolaobaf</t>
         </is>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -16338,65 +16338,65 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>2026-08-01 07:47:19</t>
+          <t>2026-08-02 08:36:28</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@victoriaookoro</t>
+          <t>https://www.tiktok.com/@cynthiaadeolaobaf</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>viralnestdailydeals</t>
+          <t>andreadavies903</t>
         </is>
       </c>
       <c r="B421" t="inlineStr"/>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>2026-08-05 09:39:06</t>
+          <t>2026-08-01 22:54:24</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@viralnestdailydeals</t>
+          <t>https://www.tiktok.com/@andreadavies903</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>.beauty.001</t>
+          <t>yemisi_81</t>
         </is>
       </c>
       <c r="B422" t="inlineStr"/>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -16406,65 +16406,65 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>2026-08-14 00:31:05</t>
+          <t>2026-08-04 10:04:07</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@.beauty.001</t>
+          <t>https://www.tiktok.com/@yemisi_81</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>vytyglrl</t>
+          <t>vickyvickss3</t>
         </is>
       </c>
       <c r="B423" t="inlineStr"/>
       <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>2026-08-01 01:52:28</t>
+          <t>2026-08-11 17:41:09</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vytyglrl</t>
+          <t>https://www.tiktok.com/@vickyvickss3</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>waletreasure</t>
+          <t>yasminsar_110</t>
         </is>
       </c>
       <c r="B424" t="inlineStr"/>
       <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -16474,51 +16474,51 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>2026-08-11 13:01:50</t>
+          <t>2026-08-02 16:53:08</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@waletreasure</t>
+          <t>https://www.tiktok.com/@yasminsar_110</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>walex0880</t>
+          <t>y_ddraig69</t>
         </is>
       </c>
       <c r="B425" t="inlineStr"/>
       <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>2026-08-04 21:35:53</t>
+          <t>2026-08-15 17:59:05</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@walex0880</t>
+          <t>https://www.tiktok.com/@y_ddraig69</t>
         </is>
       </c>
     </row>
@@ -16559,75 +16559,75 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>y_ddraig69</t>
+          <t>user.okikiwealth</t>
         </is>
       </c>
       <c r="B427" t="inlineStr"/>
       <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>2026-08-15 17:59:05</t>
+          <t>2026-08-01 13:23:25</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@y_ddraig69</t>
+          <t>https://www.tiktok.com/@user.okikiwealth</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>user59838594031894</t>
+          <t>ukineboconnect</t>
         </is>
       </c>
       <c r="B428" t="inlineStr"/>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>2026-08-04 13:16:58</t>
+          <t>2026-08-07 12:08:05</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user59838594031894</t>
+          <t>https://www.tiktok.com/@ukineboconnect</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>user8160294226215</t>
+          <t>triplehoney8</t>
         </is>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -16644,58 +16644,58 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>2026-08-02 20:19:29</t>
+          <t>2026-08-05 09:12:57</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8160294226215</t>
+          <t>https://www.tiktok.com/@triplehoney8</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>user8234558006158</t>
+          <t>traetari1</t>
         </is>
       </c>
       <c r="B430" t="inlineStr"/>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-08-12 07:13:01</t>
+          <t>2026-08-04 20:57:53</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8234558006158</t>
+          <t>https://www.tiktok.com/@traetari1</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>user9813841001322</t>
+          <t>toyinedos</t>
         </is>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -16712,24 +16712,24 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>2026-08-02 23:48:31</t>
+          <t>2026-08-04 07:24:05</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user9813841001322</t>
+          <t>https://www.tiktok.com/@toyinedos</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>verascuisine_</t>
+          <t>tinugold123</t>
         </is>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -16741,63 +16741,63 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>2026-08-12 07:40:06</t>
+          <t>2026-08-04 00:42:18</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@verascuisine_</t>
+          <t>https://www.tiktok.com/@tinugold123</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>vibewithname3</t>
+          <t>tinu.ola</t>
         </is>
       </c>
       <c r="B433" t="inlineStr"/>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>2026-08-11 08:58:07</t>
+          <t>2026-08-12 16:40:53</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vibewithname3</t>
+          <t>https://www.tiktok.com/@tinu.ola</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>vickyvickss3</t>
+          <t>user2997965690229</t>
         </is>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -16814,24 +16814,24 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>2026-08-11 17:41:09</t>
+          <t>2026-08-14 19:07:40</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vickyvickss3</t>
+          <t>https://www.tiktok.com/@user2997965690229</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>adeadesola26</t>
+          <t>user3242536109635</t>
         </is>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -16848,58 +16848,58 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-08-07 02:05:32</t>
+          <t>2026-08-03 20:42:18</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adeadesola26</t>
+          <t>https://www.tiktok.com/@user3242536109635</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>user2997965690229</t>
+          <t>user5724531303785</t>
         </is>
       </c>
       <c r="B436" t="inlineStr"/>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>2026-08-14 19:07:40</t>
+          <t>2026-08-06 06:39:56</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2997965690229</t>
+          <t>https://www.tiktok.com/@user5724531303785</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>user3242536109635</t>
+          <t>sophia.annan2</t>
         </is>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -16916,24 +16916,24 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>2026-08-03 20:42:18</t>
+          <t>2026-08-06 06:16:15</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user3242536109635</t>
+          <t>https://www.tiktok.com/@sophia.annan2</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>user5724531303785</t>
+          <t>themyturpe4</t>
         </is>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -16950,24 +16950,24 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>2026-08-06 06:39:56</t>
+          <t>2026-08-05 13:22:07</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user5724531303785</t>
+          <t>https://www.tiktok.com/@themyturpe4</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>affiliateproductlinks</t>
+          <t>thea.w.finds</t>
         </is>
       </c>
       <c r="B439" t="inlineStr"/>
@@ -16984,58 +16984,58 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>2026-08-13 23:30:05</t>
+          <t>2026-08-15 11:08:05</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@affiliateproductlinks</t>
+          <t>https://www.tiktok.com/@thea.w.finds</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>afia7773</t>
+          <t>the_psy_lif3</t>
         </is>
       </c>
       <c r="B440" t="inlineStr"/>
       <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>2026-08-12 13:41:03</t>
+          <t>2026-08-08 21:16:05</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@afia7773</t>
+          <t>https://www.tiktok.com/@the_psy_lif3</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>agyeibeauty31</t>
+          <t>the.love.of.god36</t>
         </is>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -17052,24 +17052,24 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>2026-08-15 01:11:24</t>
+          <t>2026-08-12 14:24:43</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@agyeibeauty31</t>
+          <t>https://www.tiktok.com/@the.love.of.god36</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>ah15680</t>
+          <t>teresa_plugs</t>
         </is>
       </c>
       <c r="B442" t="inlineStr"/>
@@ -17086,24 +17086,24 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>2026-08-05 12:45:29</t>
+          <t>2026-08-03 14:33:13</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ah15680</t>
+          <t>https://www.tiktok.com/@teresa_plugs</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>akadoctor3</t>
+          <t>temmit7</t>
         </is>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -17120,58 +17120,58 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-08-05 19:44:15</t>
+          <t>2026-08-02 10:56:06</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@akadoctor3</t>
+          <t>https://www.tiktok.com/@temmit7</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>amber_roseeg</t>
+          <t>hajiafolakekoleosorasaq</t>
         </is>
       </c>
       <c r="B444" t="inlineStr"/>
       <c r="C444" t="inlineStr"/>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>2026-08-10 09:55:05</t>
+          <t>2026-08-02 13:17:59</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amber_roseeg</t>
+          <t>https://www.tiktok.com/@hajiafolakekoleosorasaq</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>adamb719</t>
+          <t>gurds_hundal</t>
         </is>
       </c>
       <c r="B445" t="inlineStr"/>
@@ -17188,24 +17188,24 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>2026-08-03 12:14:53</t>
+          <t>2026-08-01 08:56:14</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adamb719</t>
+          <t>https://www.tiktok.com/@gurds_hundal</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>abosedeisaac7</t>
+          <t>grabthedeal123</t>
         </is>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -17222,31 +17222,31 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>2026-08-06 22:04:12</t>
+          <t>2026-08-02 22:40:50</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abosedeisaac7</t>
+          <t>https://www.tiktok.com/@grabthedeal123</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>abbyades</t>
+          <t>enny5839</t>
         </is>
       </c>
       <c r="B447" t="inlineStr"/>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -17256,126 +17256,126 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>2026-08-03 13:07:56</t>
+          <t>2026-08-14 19:31:16</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abbyades</t>
+          <t>https://www.tiktok.com/@enny5839</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>_clarahayes</t>
+          <t>globalgee73</t>
         </is>
       </c>
       <c r="B448" t="inlineStr"/>
       <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>2026-08-10 19:37:05</t>
+          <t>2026-08-02 14:48:45</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_clarahayes</t>
+          <t>https://www.tiktok.com/@globalgee73</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>__olabisi1__</t>
+          <t>gladysadjei43</t>
         </is>
       </c>
       <c r="B449" t="inlineStr"/>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-14 15:21:53</t>
+          <t>2026-08-04 19:48:23</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@__olabisi1__</t>
+          <t>https://www.tiktok.com/@gladysadjei43</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>1leics</t>
+          <t>_clarahayes</t>
         </is>
       </c>
       <c r="B450" t="inlineStr"/>
       <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>2026-08-02 19:13:43</t>
+          <t>2026-08-10 19:37:05</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@1leics</t>
+          <t>https://www.tiktok.com/@_clarahayes</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>103mmc</t>
+          <t>__olabisi1__</t>
         </is>
       </c>
       <c r="B451" t="inlineStr"/>
@@ -17392,7 +17392,7 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>2026-08-14 01:23:44</t>
+          <t>2026-08-14 15:21:53</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
@@ -17402,7 +17402,41 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@103mmc</t>
+          <t>https://www.tiktok.com/@__olabisi1__</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>vibewithname3</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr"/>
+      <c r="C452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Hibiscus</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Free sample from seller</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>2026-08-11 08:58:07</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@vibewithname3</t>
         </is>
       </c>
     </row>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -859,7 +859,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -12125,7 +12125,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -14929,7 +14929,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
@@ -16355,7 +16355,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -9462,7 +9462,7 @@
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -12125,7 +12125,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -13595,7 +13595,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -14113,7 +14113,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -15803,7 +15803,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -3085,7 +3085,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H203"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kkk29760</t>
+          <t>krystal_kei</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -639,39 +639,39 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>100K-250K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-15 20:31:05</t>
+          <t>2026-08-27 08:36:58</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kkk29760</t>
+          <t>https://www.tiktok.com/@krystal_kei</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>krystal_kei</t>
+          <t>ojay_ibrahim</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -681,54 +681,54 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-27 08:36:58</t>
+          <t>2026-08-20 00:28:09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@krystal_kei</t>
+          <t>https://www.tiktok.com/@ojay_ibrahim</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>royalmaame.20</t>
+          <t>baudace</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -738,118 +738,118 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-20 00:01:09</t>
+          <t>2026-08-16 09:31:05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@royalmaame.20</t>
+          <t>https://www.tiktok.com/@baudace</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kessyufuoma8</t>
+          <t>savewithsaitama</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-25 23:13:09</t>
+          <t>2026-08-19 11:39:14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kessyufuoma8</t>
+          <t>https://www.tiktok.com/@savewithsaitama</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>the_okhegwais1</t>
+          <t>husna.findss</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-15 06:56:05</t>
+          <t>2026-08-20 02:22:09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@the_okhegwais1</t>
+          <t>https://www.tiktok.com/@husna.findss</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ojay_ibrahim</t>
+          <t>hollynjakesjourney</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>100K-250K</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -864,24 +864,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-20 00:28:09</t>
+          <t>2026-08-19 10:01:09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ojay_ibrahim</t>
+          <t>https://www.tiktok.com/@hollynjakesjourney</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>baudace</t>
+          <t>oli_070707</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -901,29 +901,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-16 09:31:05</t>
+          <t>2026-08-16 18:51:05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@baudace</t>
+          <t>https://www.tiktok.com/@oli_070707</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>savewithsaitama</t>
+          <t>procrastinator834</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -948,24 +948,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-19 11:39:14</t>
+          <t>2026-08-19 10:10:10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@savewithsaitama</t>
+          <t>https://www.tiktok.com/@procrastinator834</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bitzandbatz1</t>
+          <t>cola_098</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -980,34 +980,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-21 01:23:09</t>
+          <t>2026-08-19 01:55:09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bitzandbatz1</t>
+          <t>https://www.tiktok.com/@cola_098</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>asabiade506</t>
+          <t>earnwithtrisjay</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1022,34 +1022,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-15 10:29:05</t>
+          <t>2026-08-22 18:43:09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@asabiade506</t>
+          <t>https://www.tiktok.com/@earnwithtrisjay</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gemmalsagar</t>
+          <t>bethanyjolife</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1074,24 +1074,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-15 08:14:05</t>
+          <t>2026-08-19 10:01:09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gemmalsagar</t>
+          <t>https://www.tiktok.com/@bethanyjolife</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nooreadan891</t>
+          <t>nawaxiuke</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1116,24 +1116,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-15 16:41:06</t>
+          <t>2026-08-18 18:25:09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nooreadan891</t>
+          <t>https://www.tiktok.com/@nawaxiuke</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>husna.findss</t>
+          <t>mzmx_eza</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-20 02:22:09</t>
+          <t>2026-08-21 19:31:09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1168,14 +1168,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@husna.findss</t>
+          <t>https://www.tiktok.com/@mzmx_eza</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hollynjakesjourney</t>
+          <t>gomah.rufi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>100K-250K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-19 10:01:09</t>
+          <t>2026-08-20 06:59:09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1210,24 +1210,24 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hollynjakesjourney</t>
+          <t>https://www.tiktok.com/@gomah.rufi</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>oli_070707</t>
+          <t>chelsea..gallagherxox</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>50K-100K</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-16 18:51:05</t>
+          <t>2026-08-17 12:03:05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1252,29 +1252,29 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oli_070707</t>
+          <t>https://www.tiktok.com/@chelsea..gallagherxox</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>procrastinator834</t>
+          <t>trendvault8888</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1284,39 +1284,39 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-19 10:10:10</t>
+          <t>2026-08-22 20:37:09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@procrastinator834</t>
+          <t>https://www.tiktok.com/@trendvault8888</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rubythegoat676</t>
+          <t>lifewithlucylou_x</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-15 16:11:05</t>
+          <t>2026-08-16 08:08:05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1336,66 +1336,66 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rubythegoat676</t>
+          <t>https://www.tiktok.com/@lifewithlucylou_x</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cola_098</t>
+          <t>cornelsimpson</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-19 01:55:09</t>
+          <t>2026-08-18 19:22:09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cola_098</t>
+          <t>https://www.tiktok.com/@cornelsimpson</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>earnwithtrisjay</t>
+          <t>maigee</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1405,34 +1405,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-22 18:43:09</t>
+          <t>2026-08-17 04:14:05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@earnwithtrisjay</t>
+          <t>https://www.tiktok.com/@maigee</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rw8824</t>
+          <t>abbymaycock</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1442,39 +1442,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-15 23:50:05</t>
+          <t>2026-08-27 19:48:24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rw8824</t>
+          <t>https://www.tiktok.com/@abbymaycock</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bethanyjolife</t>
+          <t>povshopperr</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1494,34 +1494,34 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-19 10:01:09</t>
+          <t>2026-08-16 21:05:05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bethanyjolife</t>
+          <t>https://www.tiktok.com/@povshopperr</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nawaxiuke</t>
+          <t>barkstreetboys_</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1531,39 +1531,39 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-18 18:25:09</t>
+          <t>2026-08-20 12:47:09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nawaxiuke</t>
+          <t>https://www.tiktok.com/@barkstreetboys_</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mzmx_eza</t>
+          <t>lifewithsabz</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1578,39 +1578,39 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-21 19:31:09</t>
+          <t>2026-08-17 14:17:05</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mzmx_eza</t>
+          <t>https://www.tiktok.com/@lifewithsabz</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>gomah.rufi</t>
+          <t>hirahannan_official</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>250K-500K</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1620,29 +1620,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-20 06:59:09</t>
+          <t>2026-08-29 11:13:09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gomah.rufi</t>
+          <t>https://www.tiktok.com/@hirahannan_official</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tkhxn1</t>
+          <t>deeqa.luul57</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1662,71 +1662,71 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-17 10:03:07</t>
+          <t>2026-08-27 12:32:00</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tkhxn1</t>
+          <t>https://www.tiktok.com/@deeqa.luul57</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tcsparkles</t>
+          <t>aj_tech_london</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-15 17:06:05</t>
+          <t>2026-08-17 00:15:05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tcsparkles</t>
+          <t>https://www.tiktok.com/@aj_tech_london</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>vicpatty87</t>
+          <t>ai_influencer_uk</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1746,29 +1746,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-15 18:35:05</t>
+          <t>2026-08-18 10:28:08</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vicpatty87</t>
+          <t>https://www.tiktok.com/@ai_influencer_uk</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>zarnish.fatima986</t>
+          <t>dmc523</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1788,34 +1788,34 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-15 20:10:05</t>
+          <t>2026-08-28 20:15:51</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zarnish.fatima986</t>
+          <t>https://www.tiktok.com/@dmc523</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>chelsea..gallagherxox</t>
+          <t>allthingsshereen</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>50K-100K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-17 12:03:05</t>
+          <t>2026-08-18 21:48:09</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1840,66 +1840,66 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chelsea..gallagherxox</t>
+          <t>https://www.tiktok.com/@allthingsshereen</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>trendvault8888</t>
+          <t>get2realbayo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-22 20:37:09</t>
+          <t>2026-08-17 18:01:40</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@trendvault8888</t>
+          <t>https://www.tiktok.com/@get2realbayo</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tess_banks_</t>
+          <t>globe_trot_with_neelam</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1914,39 +1914,39 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-15 20:47:06</t>
+          <t>2026-08-19 15:43:09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tess_banks_</t>
+          <t>https://www.tiktok.com/@globe_trot_with_neelam</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>lifewithlucylou_x</t>
+          <t>aqsa1288</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1956,39 +1956,39 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-16 08:08:05</t>
+          <t>2026-08-26 18:23:09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifewithlucylou_x</t>
+          <t>https://www.tiktok.com/@aqsa1288</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cornelsimpson</t>
+          <t>y.kitos</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1998,71 +1998,71 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-18 19:22:09</t>
+          <t>2026-08-16 16:28:05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cornelsimpson</t>
+          <t>https://www.tiktok.com/@y.kitos</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>maigee</t>
+          <t>laurenjones38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-17 04:14:05</t>
+          <t>2026-08-16 21:14:05</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maigee</t>
+          <t>https://www.tiktok.com/@laurenjones38</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>abbymaycock</t>
+          <t>nurseudy</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2082,39 +2082,39 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-27 19:48:24</t>
+          <t>2026-08-20 10:20:29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abbymaycock</t>
+          <t>https://www.tiktok.com/@nurseudy</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>povshopperr</t>
+          <t>glowguide786</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-16 21:05:05</t>
+          <t>2026-08-17 18:17:05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@povshopperr</t>
+          <t>https://www.tiktok.com/@glowguide786</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>barkstreetboys_</t>
+          <t>unboxirl</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2166,29 +2166,29 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-20 12:47:09</t>
+          <t>2026-08-16 03:14:05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@barkstreetboys_</t>
+          <t>https://www.tiktok.com/@unboxirl</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>lifewithsabz</t>
+          <t>lifewithsesede</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2208,29 +2208,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-17 14:17:05</t>
+          <t>2026-08-21 15:56:09</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifewithsabz</t>
+          <t>https://www.tiktok.com/@lifewithsesede</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>jimmynocapdeals</t>
+          <t>nailajinam</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2240,44 +2240,44 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-15 11:48:06</t>
+          <t>2026-08-25 15:39:09</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jimmynocapdeals</t>
+          <t>https://www.tiktok.com/@nailajinam</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>hirahannan_official</t>
+          <t>kittyqu1n_x</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>250K-500K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2292,39 +2292,39 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-29 11:13:09</t>
+          <t>2026-08-19 18:06:09</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hirahannan_official</t>
+          <t>https://www.tiktok.com/@kittyqu1n_x</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>deeqa.luul57</t>
+          <t>thedealsdrops</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2334,39 +2334,39 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-27 12:32:00</t>
+          <t>2026-08-16 05:21:05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@deeqa.luul57</t>
+          <t>https://www.tiktok.com/@thedealsdrops</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>thetravelsblogg</t>
+          <t>ibironkealonge</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-16 22:17:05</t>
+          <t>2026-08-19 04:08:33</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thetravelsblogg</t>
+          <t>https://www.tiktok.com/@ibironkealonge</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>aj_tech_london</t>
+          <t>afshanjindani</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2413,34 +2413,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-17 00:15:05</t>
+          <t>2026-08-26 12:00:09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@aj_tech_london</t>
+          <t>https://www.tiktok.com/@afshanjindani</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ai_influencer_uk</t>
+          <t>courtney19xo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2460,29 +2460,29 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-18 10:28:08</t>
+          <t>2026-08-27 18:42:23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ai_influencer_uk</t>
+          <t>https://www.tiktok.com/@courtney19xo</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>dmc523</t>
+          <t>sallystoresgiftsho</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2497,34 +2497,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-28 20:15:51</t>
+          <t>2026-08-16 19:32:05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dmc523</t>
+          <t>https://www.tiktok.com/@sallystoresgiftsho</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>allthingsshereen</t>
+          <t>r9oce</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2544,71 +2544,71 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-18 21:48:09</t>
+          <t>2026-08-16 16:20:05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@allthingsshereen</t>
+          <t>https://www.tiktok.com/@r9oce</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>get2realbayo</t>
+          <t>mtmccluskey</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-17 18:01:40</t>
+          <t>2026-08-20 06:36:09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@get2realbayo</t>
+          <t>https://www.tiktok.com/@mtmccluskey</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>jessicalouisekx</t>
+          <t>uzmaashfaq</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2628,36 +2628,28 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-15 21:05:05</t>
+          <t>2026-08-18 01:04:05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jessicalouisekx</t>
+          <t>https://www.tiktok.com/@uzmaashfaq</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>testedforyou6</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>£100-£200</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>aabi0116</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -2665,83 +2657,67 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-15 20:32:05</t>
+          <t>2026-08-19 21:02:51</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@testedforyou6</t>
+          <t>https://www.tiktok.com/@aabi0116</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>aqsa1288</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>£100-£200</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>abeehaamir24</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-26 18:23:09</t>
+          <t>2026-08-30 10:05:16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@aqsa1288</t>
+          <t>https://www.tiktok.com/@abeehaamir24</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>y.kitos</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>£100-£200</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>4nnabel5.2</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2754,7 +2730,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-16 16:28:05</t>
+          <t>2026-08-17 13:34:55</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2764,26 +2740,18 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@y.kitos</t>
+          <t>https://www.tiktok.com/@4nnabel5.2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>laurenjones38</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>£100-£200</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>gallodiopfall</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -2791,44 +2759,36 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-16 21:14:05</t>
+          <t>2026-08-22 13:48:46</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@laurenjones38</t>
+          <t>https://www.tiktok.com/@gallodiopfall</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>nurseudy</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>£100-£200</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>folasalewa</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2838,123 +2798,99 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-20 10:20:29</t>
+          <t>2026-08-20 07:06:47</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nurseudy</t>
+          <t>https://www.tiktok.com/@folasalewa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>justukthingsofficial</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>£100-£200</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>fffysigs0719</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-15 14:40:05</t>
+          <t>2026-08-27 16:41:03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@justukthingsofficial</t>
+          <t>https://www.tiktok.com/@fffysigs0719</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>itz_ab18</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>£100-£200</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>famidak1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-15 13:19:05</t>
+          <t>2026-08-27 15:54:45</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itz_ab18</t>
+          <t>https://www.tiktok.com/@famidak1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>glowguide786</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>£100-£200</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+          <t>erosa76</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2964,39 +2900,31 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-17 18:17:05</t>
+          <t>2026-08-16 16:42:12</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@glowguide786</t>
+          <t>https://www.tiktok.com/@erosa76</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>unboxirl</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>£100-£200</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>ennyluv76</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3006,81 +2934,65 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-16 03:14:05</t>
+          <t>2026-08-30 08:31:46</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@unboxirl</t>
+          <t>https://www.tiktok.com/@ennyluv76</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>lifewithsesede</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>£50-£100</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>emwinghareadun</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-21 15:56:09</t>
+          <t>2026-08-23 09:11:57</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifewithsesede</t>
+          <t>https://www.tiktok.com/@emwinghareadun</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>elizabethfallonx</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>£50-£100</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>25K-50K</t>
-        </is>
-      </c>
+          <t>dlp7831</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3090,81 +3002,65 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-15 03:10:05</t>
+          <t>2026-08-28 08:11:22</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@elizabethfallonx</t>
+          <t>https://www.tiktok.com/@dlp7831</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>nailajinam</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>£50-£100</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>daliayasmin77</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-25 15:39:09</t>
+          <t>2026-08-27 22:31:42</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nailajinam</t>
+          <t>https://www.tiktok.com/@daliayasmin77</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kittyqu1n_x</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>£50-£100</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>dimples7219</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3174,36 +3070,28 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-19 18:06:09</t>
+          <t>2026-08-25 08:40:28</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kittyqu1n_x</t>
+          <t>https://www.tiktok.com/@dimples7219</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>thedealsdrops</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>£50-£100</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>delboy_trotter1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -3216,36 +3104,28 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-16 05:21:05</t>
+          <t>2026-08-25 16:12:46</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thedealsdrops</t>
+          <t>https://www.tiktok.com/@delboy_trotter1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ibironkealonge</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>£50-£100</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>debrazerf</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3258,39 +3138,31 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-19 04:08:33</t>
+          <t>2026-08-27 19:29:33</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ibironkealonge</t>
+          <t>https://www.tiktok.com/@debrazerf</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>afshanjindani</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>david.adetokunbo2</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3300,39 +3172,31 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-26 12:00:09</t>
+          <t>2026-08-26 22:15:55</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@afshanjindani</t>
+          <t>https://www.tiktok.com/@david.adetokunbo2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>courtney19xo</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>cocobeank</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3342,36 +3206,28 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-27 18:42:23</t>
+          <t>2026-08-18 08:24:28</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@courtney19xo</t>
+          <t>https://www.tiktok.com/@cocobeank</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>sallystoresgiftsho</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>claraeg01</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3379,113 +3235,97 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-16 19:32:05</t>
+          <t>2026-08-28 08:29:29</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sallystoresgiftsho</t>
+          <t>https://www.tiktok.com/@claraeg01</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>mtmccluskey</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>constance.yeboah6</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-20 06:36:09</t>
+          <t>2026-08-17 12:49:15</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mtmccluskey</t>
+          <t>https://www.tiktok.com/@constance.yeboah6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>r9oce</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>beebee9537</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-16 16:20:05</t>
+          <t>2026-08-30 13:59:25</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@r9oce</t>
+          <t>https://www.tiktok.com/@beebee9537</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>uzmaashfaq</t>
+          <t>banksofmay</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3500,49 +3340,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-18 01:04:05</t>
+          <t>2026-08-29 18:39:38</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uzmaashfaq</t>
+          <t>https://www.tiktok.com/@banksofmay</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ayezakhan10</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>25K-50K</t>
-        </is>
-      </c>
+          <t>bhavnathaker2</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3552,7 +3384,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-15 21:20:05</t>
+          <t>2026-08-16 11:21:11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3562,14 +3394,14 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ayezakhan10</t>
+          <t>https://www.tiktok.com/@bhavnathaker2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>itzmallncll</t>
+          <t>cocoleta7</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3586,24 +3418,24 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-22 20:43:48</t>
+          <t>2026-08-27 06:32:26</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itzmallncll</t>
+          <t>https://www.tiktok.com/@cocoleta7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>invalid58</t>
+          <t>choky23_og</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3620,24 +3452,24 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:16</t>
+          <t>2026-08-20 23:26:17</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@invalid58</t>
+          <t>https://www.tiktok.com/@choky23_og</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>health.wise.media</t>
+          <t>biglindathompson</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3654,31 +3486,31 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-24 02:13:31</t>
+          <t>2026-08-22 13:10:08</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@health.wise.media</t>
+          <t>https://www.tiktok.com/@biglindathompson</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>gillian.stevenson2</t>
+          <t>adwoab1913</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3688,31 +3520,31 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-15 08:13:02</t>
+          <t>2026-08-19 23:17:45</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gillian.stevenson2</t>
+          <t>https://www.tiktok.com/@adwoab1913</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>gretswithnoregrets_</t>
+          <t>abenaduncan1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3722,7 +3554,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-27 18:41:31</t>
+          <t>2026-08-28 12:54:46</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3732,21 +3564,21 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gretswithnoregrets_</t>
+          <t>https://www.tiktok.com/@abenaduncan1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>haashim737</t>
+          <t>afolabi.aisha4</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3756,24 +3588,24 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-22 17:53:39</t>
+          <t>2026-08-20 17:18:27</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@haashim737</t>
+          <t>https://www.tiktok.com/@afolabi.aisha4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>hamidaahmed028</t>
+          <t>adeadun77</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3790,24 +3622,24 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-27 22:12:14</t>
+          <t>2026-08-23 16:32:57</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hamidaahmed028</t>
+          <t>https://www.tiktok.com/@adeadun77</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>hawaallen</t>
+          <t>akuapapabi364</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3824,31 +3656,31 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-16 20:32:25</t>
+          <t>2026-08-30 17:55:54</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hawaallen</t>
+          <t>https://www.tiktok.com/@akuapapabi364</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>dlp7831</t>
+          <t>ajikeace</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3858,24 +3690,24 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-28 08:11:22</t>
+          <t>2026-08-19 23:14:41</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dlp7831</t>
+          <t>https://www.tiktok.com/@ajikeace</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>emwinghareadun</t>
+          <t>almay230</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3892,58 +3724,58 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-23 09:11:57</t>
+          <t>2026-08-18 08:15:58</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@emwinghareadun</t>
+          <t>https://www.tiktok.com/@almay230</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>famidak1</t>
+          <t>annie.mahn</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-27 15:54:45</t>
+          <t>2026-08-30 18:11:22</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@famidak1</t>
+          <t>https://www.tiktok.com/@annie.mahn</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>erosa76</t>
+          <t>babamayerrajkonna67</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3960,24 +3792,24 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-16 16:42:12</t>
+          <t>2026-08-16 20:43:38</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@erosa76</t>
+          <t>https://www.tiktok.com/@babamayerrajkonna67</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>fffysigs0719</t>
+          <t>bablybegum8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3994,31 +3826,31 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-27 16:41:03</t>
+          <t>2026-08-24 08:59:43</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fffysigs0719</t>
+          <t>https://www.tiktok.com/@bablybegum8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>folasalewa</t>
+          <t>1_newherit</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4028,7 +3860,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-20 07:06:47</t>
+          <t>2026-08-21 09:46:32</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4038,48 +3870,48 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@folasalewa</t>
+          <t>https://www.tiktok.com/@1_newherit</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>gallodiopfall</t>
+          <t>__sunshine__75</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-22 13:48:46</t>
+          <t>2026-08-17 12:34:09</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gallodiopfall</t>
+          <t>https://www.tiktok.com/@__sunshine__75</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>genxstartingover</t>
+          <t>adefunkemayowaoso1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -4096,31 +3928,31 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-27 18:41:09</t>
+          <t>2026-08-25 12:03:26</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@genxstartingover</t>
+          <t>https://www.tiktok.com/@adefunkemayowaoso1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>delboy_trotter1</t>
+          <t>1967095zkm</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4130,58 +3962,66 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-25 16:12:46</t>
+          <t>2026-08-22 14:37:48</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@delboy_trotter1</t>
+          <t>https://www.tiktok.com/@1967095zkm</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>debrazerf</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
+          <t>leez50</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-27 19:29:33</t>
+          <t>2026-08-16 18:34:49</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@debrazerf</t>
+          <t>https://www.tiktok.com/@leez50</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>dimples7219</t>
+          <t>lady.p3600</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -4198,7 +4038,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-25 08:40:28</t>
+          <t>2026-08-26 15:34:27</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4208,21 +4048,21 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dimples7219</t>
+          <t>https://www.tiktok.com/@lady.p3600</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>almay230</t>
+          <t>kinibabes</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4232,65 +4072,65 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-18 08:15:58</t>
+          <t>2026-08-21 08:38:27</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@almay230</t>
+          <t>https://www.tiktok.com/@kinibabes</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>agyeibeauty31</t>
+          <t>kaymama31</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-15 01:11:24</t>
+          <t>2026-08-30 10:22:50</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@agyeibeauty31</t>
+          <t>https://www.tiktok.com/@kaymama31</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>afolabi.aisha4</t>
+          <t>jossy3851</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4300,24 +4140,24 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-20 17:18:27</t>
+          <t>2026-08-19 04:00:14</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@afolabi.aisha4</t>
+          <t>https://www.tiktok.com/@jossy3851</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>biglindathompson</t>
+          <t>jay25084</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4334,24 +4174,24 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-22 13:10:08</t>
+          <t>2026-08-25 10:06:52</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@biglindathompson</t>
+          <t>https://www.tiktok.com/@jay25084</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>bhavnathaker2</t>
+          <t>jaofficial10</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4368,24 +4208,24 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-16 11:21:11</t>
+          <t>2026-08-28 11:15:31</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bhavnathaker2</t>
+          <t>https://www.tiktok.com/@jaofficial10</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>cocobeank</t>
+          <t>macouly1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4402,31 +4242,39 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-18 08:24:28</t>
+          <t>2026-08-29 10:33:10</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cocobeank</t>
+          <t>https://www.tiktok.com/@macouly1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>claraeg01</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
+          <t>lexijoh0</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4436,31 +4284,39 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-28 08:29:29</t>
+          <t>2026-08-18 21:31:09</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@claraeg01</t>
+          <t>https://www.tiktok.com/@lexijoh0</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>choky23_og</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr"/>
+          <t>loved262</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4470,7 +4326,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-20 23:26:17</t>
+          <t>2026-08-21 03:28:48</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4480,14 +4336,14 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@choky23_og</t>
+          <t>https://www.tiktok.com/@loved262</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>cocoleta7</t>
+          <t>maame.sika58</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4504,73 +4360,65 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-27 06:32:26</t>
+          <t>2026-08-16 11:13:15</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cocoleta7</t>
+          <t>https://www.tiktok.com/@maame.sika58</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>constance.yeboah6</t>
+          <t>lexysluxurytravel</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-17 12:49:15</t>
+          <t>2026-08-27 13:48:00</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@constance.yeboah6</t>
+          <t>https://www.tiktok.com/@lexysluxurytravel</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>courage.ik</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>mohplace</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4580,31 +4428,31 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-15 14:23:05</t>
+          <t>2026-08-19 23:48:01</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@courage.ik</t>
+          <t>https://www.tiktok.com/@mohplace</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>daliayasmin77</t>
+          <t>missberry.kayamatauk</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4614,24 +4462,24 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-27 22:31:42</t>
+          <t>2026-08-26 13:15:36</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@daliayasmin77</t>
+          <t>https://www.tiktok.com/@missberry.kayamatauk</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>david.adetokunbo2</t>
+          <t>mila0701c7c</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4648,31 +4496,31 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:55</t>
+          <t>2026-08-25 05:11:12</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@david.adetokunbo2</t>
+          <t>https://www.tiktok.com/@mila0701c7c</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ajikeace</t>
+          <t>kemotee07</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4682,28 +4530,36 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-19 23:14:41</t>
+          <t>2026-08-24 11:49:41</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ajikeace</t>
+          <t>https://www.tiktok.com/@kemotee07</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>babamayerrajkonna67</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr"/>
+          <t>joyfulpraisejp</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -4716,36 +4572,28 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-16 20:43:38</t>
+          <t>2026-08-21 18:19:01</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@babamayerrajkonna67</t>
+          <t>https://www.tiktok.com/@joyfulpraisejp</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>banksofmay</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>judyluv42</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -4758,24 +4606,24 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-29 18:39:38</t>
+          <t>2026-08-25 10:31:30</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@banksofmay</t>
+          <t>https://www.tiktok.com/@judyluv42</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>bablybegum8</t>
+          <t>kasongo.babe</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4792,28 +4640,36 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-24 08:59:43</t>
+          <t>2026-08-16 10:26:48</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bablybegum8</t>
+          <t>https://www.tiktok.com/@kasongo.babe</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>abenaduncan1</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr"/>
+          <t>jakuradabest</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D112" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -4826,24 +4682,24 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-28 12:54:46</t>
+          <t>2026-08-19 21:04:38</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abenaduncan1</t>
+          <t>https://www.tiktok.com/@jakuradabest</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>adeadun77</t>
+          <t>itzmallncll</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4860,58 +4716,58 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-23 16:32:57</t>
+          <t>2026-08-22 20:43:48</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adeadun77</t>
+          <t>https://www.tiktok.com/@itzmallncll</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>adefunkemayowaoso1</t>
+          <t>invalid58</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-25 12:03:26</t>
+          <t>2026-08-28 17:24:16</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adefunkemayowaoso1</t>
+          <t>https://www.tiktok.com/@invalid58</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>19602026zkm</t>
+          <t>health.wise.media</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -4928,31 +4784,31 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-22 14:37:48</t>
+          <t>2026-08-24 02:13:31</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@19602026zkm</t>
+          <t>https://www.tiktok.com/@health.wise.media</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1_newherit</t>
+          <t>hawaallen</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4962,24 +4818,24 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-21 09:46:32</t>
+          <t>2026-08-16 20:32:25</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@1_newherit</t>
+          <t>https://www.tiktok.com/@hawaallen</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>4nnabel5.2</t>
+          <t>hamidaahmed028</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4996,24 +4852,24 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-17 13:34:55</t>
+          <t>2026-08-27 22:12:14</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@4nnabel5.2</t>
+          <t>https://www.tiktok.com/@hamidaahmed028</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>__sunshine__75</t>
+          <t>haashim737</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -5030,24 +4886,24 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-17 12:34:09</t>
+          <t>2026-08-22 17:53:39</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@__sunshine__75</t>
+          <t>https://www.tiktok.com/@haashim737</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>aabi0116</t>
+          <t>gretswithnoregrets_</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -5064,24 +4920,24 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-08-19 21:02:51</t>
+          <t>2026-08-27 18:41:31</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@aabi0116</t>
+          <t>https://www.tiktok.com/@gretswithnoregrets_</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>adwoab1913</t>
+          <t>genxstartingover</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -5093,71 +4949,63 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-08-19 23:17:45</t>
+          <t>2026-08-27 18:41:09</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adwoab1913</t>
+          <t>https://www.tiktok.com/@genxstartingover</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>leez50</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>ovwomani22</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-16 18:34:49</t>
+          <t>2026-08-28 18:04:58</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@leez50</t>
+          <t>https://www.tiktok.com/@ovwomani22</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>jossy3851</t>
+          <t>omolexx</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -5174,36 +5022,28 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-19 04:00:14</t>
+          <t>2026-08-19 10:35:25</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jossy3851</t>
+          <t>https://www.tiktok.com/@omolexx</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>joyfulpraisejp</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>oluwaseyifunmi988</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5216,31 +5056,31 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-21 18:19:01</t>
+          <t>2026-08-23 01:54:34</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@joyfulpraisejp</t>
+          <t>https://www.tiktok.com/@oluwaseyifunmi988</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>mamacassyxo</t>
+          <t>nene16241</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5250,24 +5090,24 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-27 16:05:15</t>
+          <t>2026-08-19 20:58:27</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mamacassyxo</t>
+          <t>https://www.tiktok.com/@nene16241</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>macouly1</t>
+          <t>nikkigossal29</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -5284,7 +5124,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-29 10:33:10</t>
+          <t>2026-08-30 17:46:28</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -5294,14 +5134,14 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@macouly1</t>
+          <t>https://www.tiktok.com/@nikkigossal29</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>maame.sika58</t>
+          <t>nasirpatel690</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5318,24 +5158,24 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-16 11:13:15</t>
+          <t>2026-08-29 00:44:35</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maame.sika58</t>
+          <t>https://www.tiktok.com/@nasirpatel690</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>loyrodatips</t>
+          <t>nazya641</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -5352,7 +5192,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-15 12:26:23</t>
+          <t>2026-08-16 12:55:07</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5362,29 +5202,21 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@loyrodatips</t>
+          <t>https://www.tiktok.com/@nazya641</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>loved262</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>nellyedwin54</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5394,31 +5226,31 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-21 03:28:48</t>
+          <t>2026-08-30 13:16:24</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@loved262</t>
+          <t>https://www.tiktok.com/@nellyedwin54</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>lady.p3600</t>
+          <t>mutimba21</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5428,39 +5260,31 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-26 15:34:27</t>
+          <t>2026-08-21 09:40:43</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lady.p3600</t>
+          <t>https://www.tiktok.com/@mutimba21</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>lexijoh0</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>mamacassyxo</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -5470,24 +5294,24 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-18 21:31:09</t>
+          <t>2026-08-27 16:05:15</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lexijoh0</t>
+          <t>https://www.tiktok.com/@mamacassyxo</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>lexysluxurytravel</t>
+          <t>mandoki72</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5504,31 +5328,31 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-08-27 13:48:00</t>
+          <t>2026-08-26 21:17:58</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lexysluxurytravel</t>
+          <t>https://www.tiktok.com/@mandoki72</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kinibabes</t>
+          <t>manoor_303</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5538,70 +5362,70 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-08-21 08:38:27</t>
+          <t>2026-08-23 07:41:43</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kinibabes</t>
+          <t>https://www.tiktok.com/@manoor_303</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kasongo.babe</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
-      <c r="C133" t="inlineStr"/>
+          <t>maria_london7</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-16 10:26:48</t>
+          <t>2026-08-22 20:57:09</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kasongo.babe</t>
+          <t>https://www.tiktok.com/@maria_london7</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kazza1992</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>pubby1amob</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5614,28 +5438,36 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-08-15 01:48:05</t>
+          <t>2026-08-27 18:28:59</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kazza1992</t>
+          <t>https://www.tiktok.com/@pubby1amob</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kemotee07</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr"/>
+          <t>redbloodchurch1</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D135" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5648,24 +5480,24 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-08-24 11:49:41</t>
+          <t>2026-08-29 15:02:18</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kemotee07</t>
+          <t>https://www.tiktok.com/@redbloodchurch1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>jay25084</t>
+          <t>queen.of.boys42</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5682,28 +5514,36 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-08-25 10:06:52</t>
+          <t>2026-08-29 18:27:02</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jay25084</t>
+          <t>https://www.tiktok.com/@queen.of.boys42</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>judyluv42</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
-      <c r="C137" t="inlineStr"/>
+          <t>saliya_94</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D137" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5716,31 +5556,39 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-08-25 10:31:30</t>
+          <t>2026-08-24 14:48:07</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@judyluv42</t>
+          <t>https://www.tiktok.com/@saliya_94</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>jaofficial10</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr"/>
+          <t>saletok</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5750,66 +5598,58 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-28 11:15:31</t>
+          <t>2026-08-19 13:01:11</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jaofficial10</t>
+          <t>https://www.tiktok.com/@saletok</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>jakuradabest</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>sabbathina38</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-08-19 21:04:38</t>
+          <t>2026-08-25 16:09:05</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jakuradabest</t>
+          <t>https://www.tiktok.com/@sabbathina38</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>pubby1amob</t>
+          <t>rifat5073</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5826,24 +5666,24 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-08-27 18:28:59</t>
+          <t>2026-08-21 20:29:46</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@pubby1amob</t>
+          <t>https://www.tiktok.com/@rifat5073</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>princesslizy2010</t>
+          <t>sharansaleem</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5860,36 +5700,28 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-08-26 20:03:55</t>
+          <t>2026-08-29 11:45:48</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princesslizy2010</t>
+          <t>https://www.tiktok.com/@sharansaleem</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>princess_wumi</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>sharl44</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5902,36 +5734,28 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-29 08:38:03</t>
+          <t>2026-08-19 21:09:47</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princess_wumi</t>
+          <t>https://www.tiktok.com/@sharl44</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>priceless3481</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>school.kid4</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5944,24 +5768,24 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-08-16 19:40:34</t>
+          <t>2026-08-21 07:43:15</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@priceless3481</t>
+          <t>https://www.tiktok.com/@school.kid4</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>phillipbennett92</t>
+          <t>shakirakhan296</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -5978,24 +5802,24 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-08-22 18:41:01</t>
+          <t>2026-08-28 23:38:18</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@phillipbennett92</t>
+          <t>https://www.tiktok.com/@shakirakhan296</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>oluwaseyifunmi988</t>
+          <t>sheenyajohnston</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -6012,58 +5836,58 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-08-23 01:54:34</t>
+          <t>2026-08-17 11:36:48</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluwaseyifunmi988</t>
+          <t>https://www.tiktok.com/@sheenyajohnston</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>omolexx</t>
+          <t>sharonhiggins46</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-19 10:35:25</t>
+          <t>2026-08-28 20:19:57</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@omolexx</t>
+          <t>https://www.tiktok.com/@sharonhiggins46</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ovwomani22</t>
+          <t>shurlar347</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -6080,24 +5904,24 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-28 18:04:58</t>
+          <t>2026-08-27 14:53:08</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ovwomani22</t>
+          <t>https://www.tiktok.com/@shurlar347</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>olori305</t>
+          <t>remmyc64</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -6114,31 +5938,39 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-08-15 12:09:44</t>
+          <t>2026-08-24 16:17:42</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@olori305</t>
+          <t>https://www.tiktok.com/@remmyc64</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>missberry.kayamatauk</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
-      <c r="C149" t="inlineStr"/>
+          <t>priceless3481</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -6148,28 +5980,36 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-08-26 13:15:36</t>
+          <t>2026-08-16 19:40:34</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@missberry.kayamatauk</t>
+          <t>https://www.tiktok.com/@priceless3481</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>mila0701c7c</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr"/>
+          <t>princess_wumi</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D150" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6182,31 +6022,31 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-08-25 05:11:12</t>
+          <t>2026-08-29 08:38:03</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mila0701c7c</t>
+          <t>https://www.tiktok.com/@princess_wumi</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>mutimba21</t>
+          <t>princesslizy2010</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -6216,65 +6056,73 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-08-21 09:40:43</t>
+          <t>2026-08-26 20:03:55</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mutimba21</t>
+          <t>https://www.tiktok.com/@princesslizy2010</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>nadia81549</t>
+          <t>phillipbennett92</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-15 04:36:05</t>
+          <t>2026-08-22 18:41:01</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nadia81549</t>
+          <t>https://www.tiktok.com/@phillipbennett92</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>nasirpatel690</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr"/>
-      <c r="C153" t="inlineStr"/>
+          <t>teepalace27</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -6284,24 +6132,24 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-29 00:44:35</t>
+          <t>2026-08-17 00:03:05</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nasirpatel690</t>
+          <t>https://www.tiktok.com/@teepalace27</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>nazya641</t>
+          <t>syna8627</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -6318,31 +6166,31 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-08-16 12:55:07</t>
+          <t>2026-08-19 11:54:40</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nazya641</t>
+          <t>https://www.tiktok.com/@syna8627</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>nene16241</t>
+          <t>soul_rebel4</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -6352,24 +6200,24 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-08-19 20:58:27</t>
+          <t>2026-08-25 20:55:08</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nene16241</t>
+          <t>https://www.tiktok.com/@soul_rebel4</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>manoor_303</t>
+          <t>sukhdeepkaur343</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -6386,24 +6234,24 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-08-23 07:41:43</t>
+          <t>2026-08-27 15:52:29</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@manoor_303</t>
+          <t>https://www.tiktok.com/@sukhdeepkaur343</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>maria_london7</t>
+          <t>skyviewbm</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6413,12 +6261,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -6428,24 +6276,24 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-08-22 20:57:09</t>
+          <t>2026-08-30 16:29:14</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maria_london7</t>
+          <t>https://www.tiktok.com/@skyviewbm</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>mandoki72</t>
+          <t>trending_gists_omoola</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -6462,24 +6310,24 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-08-26 21:17:58</t>
+          <t>2026-08-30 21:32:52</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mandoki72</t>
+          <t>https://www.tiktok.com/@trending_gists_omoola</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>midas5267</t>
+          <t>tran.le455</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -6496,92 +6344,92 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-08-15 02:57:38</t>
+          <t>2026-08-28 14:45:25</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@midas5267</t>
+          <t>https://www.tiktok.com/@tran.le455</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>mohplace</t>
+          <t>to_biiiii1</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-08-19 23:48:01</t>
+          <t>2026-08-16 08:30:35</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mohplace</t>
+          <t>https://www.tiktok.com/@to_biiiii1</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>sabbathina38</t>
+          <t>user4423713561101</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-25 16:09:05</t>
+          <t>2026-08-28 10:55:03</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sabbathina38</t>
+          <t>https://www.tiktok.com/@user4423713561101</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>shakirakhan296</t>
+          <t>user4961074980381</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -6598,92 +6446,92 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-08-28 23:38:18</t>
+          <t>2026-08-28 21:55:56</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shakirakhan296</t>
+          <t>https://www.tiktok.com/@user4961074980381</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>raz_010816</t>
+          <t>user596114145414</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-08-15 23:32:17</t>
+          <t>2026-08-28 18:57:06</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@raz_010816</t>
+          <t>https://www.tiktok.com/@user596114145414</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>shafaq1679</t>
+          <t>user6166966793526</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-08-15 14:12:05</t>
+          <t>2026-08-19 08:27:54</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shafaq1679</t>
+          <t>https://www.tiktok.com/@user6166966793526</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>school.kid4</t>
+          <t>user62832717591475</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -6700,39 +6548,31 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-08-21 07:43:15</t>
+          <t>2026-08-19 07:17:04</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@school.kid4</t>
+          <t>https://www.tiktok.com/@user62832717591475</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>saletok</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>uky1090</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6742,36 +6582,28 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-08-19 13:01:11</t>
+          <t>2026-08-28 01:37:24</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@saletok</t>
+          <t>https://www.tiktok.com/@uky1090</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>saliya_94</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>user1660073803243</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6784,24 +6616,24 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-08-24 14:48:07</t>
+          <t>2026-08-18 12:13:34</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@saliya_94</t>
+          <t>https://www.tiktok.com/@user1660073803243</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>remmyc64</t>
+          <t>user26963863682186</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -6818,31 +6650,31 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-08-24 16:17:42</t>
+          <t>2026-08-27 16:29:12</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@remmyc64</t>
+          <t>https://www.tiktok.com/@user26963863682186</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>rifat5073</t>
+          <t>user9578635552261</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6852,36 +6684,28 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-08-21 20:29:46</t>
+          <t>2026-08-19 23:12:13</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rifat5073</t>
+          <t>https://www.tiktok.com/@user9578635552261</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>redbloodchurch1</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>user6878452250754</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6894,24 +6718,24 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-08-29 15:02:18</t>
+          <t>2026-08-21 19:07:07</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@redbloodchurch1</t>
+          <t>https://www.tiktok.com/@user6878452250754</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>queen.of.boys42</t>
+          <t>user6651682812259</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -6928,73 +6752,65 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-08-29 18:27:02</t>
+          <t>2026-08-28 00:17:19</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queen.of.boys42</t>
+          <t>https://www.tiktok.com/@user6651682812259</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>syna8627</t>
+          <t>user_steeze</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-19 11:54:40</t>
+          <t>2026-08-30 17:59:09</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@syna8627</t>
+          <t>https://www.tiktok.com/@user_steeze</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>teepalace27</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>wellnesswithuzo</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -7004,96 +6820,104 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:05</t>
+          <t>2026-08-24 06:46:02</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teepalace27</t>
+          <t>https://www.tiktok.com/@wellnesswithuzo</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>sharl44</t>
+          <t>willow_mama23</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-08-19 21:09:47</t>
+          <t>2026-08-16 20:16:05</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sharl44</t>
+          <t>https://www.tiktok.com/@willow_mama23</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>sharonhiggins46</t>
+          <t>userparidil008</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-08-28 20:19:57</t>
+          <t>2026-08-18 18:04:14</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sharonhiggins46</t>
+          <t>https://www.tiktok.com/@userparidil008</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>sheenyajohnston</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr"/>
-      <c r="C176" t="inlineStr"/>
+          <t>veronpoks</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D176" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -7106,31 +6930,31 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-08-17 11:36:48</t>
+          <t>2026-08-30 14:08:12</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sheenyajohnston</t>
+          <t>https://www.tiktok.com/@veronpoks</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>shurlar347</t>
+          <t>xheyitsbeccax</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -7140,24 +6964,24 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-08-27 14:53:08</t>
+          <t>2026-08-16 00:58:05</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shurlar347</t>
+          <t>https://www.tiktok.com/@xheyitsbeccax</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>soul_rebel4</t>
+          <t>worldbestkaffy</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
@@ -7174,41 +6998,49 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-08-25 20:55:08</t>
+          <t>2026-08-19 18:23:52</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@soul_rebel4</t>
+          <t>https://www.tiktok.com/@worldbestkaffy</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>sukhdeepkaur343</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr"/>
-      <c r="C179" t="inlineStr"/>
+          <t>yemliz2024</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-08-27 15:52:29</t>
+          <t>2026-08-28 01:21:10</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -7218,14 +7050,14 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sukhdeepkaur343</t>
+          <t>https://www.tiktok.com/@yemliz2024</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>sharansaleem</t>
+          <t>yawa.kludje</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -7242,24 +7074,24 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-08-29 11:45:48</t>
+          <t>2026-08-19 02:09:54</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sharansaleem</t>
+          <t>https://www.tiktok.com/@yawa.kludje</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>user26963863682186</t>
+          <t>yxsna_98</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
@@ -7276,24 +7108,24 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-08-27 16:29:12</t>
+          <t>2026-08-30 12:46:22</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user26963863682186</t>
+          <t>https://www.tiktok.com/@yxsna_98</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>user4961074980381</t>
+          <t>zaynabee__flawless</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -7310,24 +7142,24 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-08-28 21:55:56</t>
+          <t>2026-08-19 02:26:48</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user4961074980381</t>
+          <t>https://www.tiktok.com/@zaynabee__flawless</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>user4423713561101</t>
+          <t>zotouzotou</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -7344,31 +7176,31 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-08-28 10:55:03</t>
+          <t>2026-08-22 13:11:18</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user4423713561101</t>
+          <t>https://www.tiktok.com/@zotouzotou</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>tran.le455</t>
+          <t>zozadex</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -7378,669 +7210,15 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-08-28 14:45:25</t>
+          <t>2026-08-20 12:56:57</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@tran.le455</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>to_biiiii1</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr"/>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-08-16 08:30:35</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@to_biiiii1</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>uky1090</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr"/>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-08-28 01:37:24</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uky1090</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>user1660073803243</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr"/>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-08-18 12:13:34</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user1660073803243</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>user6878452250754</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr"/>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-08-21 19:07:07</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user6878452250754</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>user6651682812259</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr"/>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-08-28 00:17:19</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user6651682812259</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>user62832717591475</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr"/>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-08-19 07:17:04</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user62832717591475</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>user6166966793526</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr"/>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-08-19 08:27:54</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user6166966793526</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>user596114145414</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr"/>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2026-08-28 18:57:06</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user596114145414</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>wellnesswithuzo</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr"/>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>2026-08-24 06:46:02</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@wellnesswithuzo</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>userparidil008</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr"/>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>2026-08-18 18:04:14</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@userparidil008</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>user9578635552261</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr"/>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>2026-08-19 23:12:13</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user9578635552261</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>xheyitsbeccax</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr"/>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>2026-08-16 00:58:05</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@xheyitsbeccax</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>worldbestkaffy</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr"/>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>2026-08-19 18:23:52</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@worldbestkaffy</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>willow_mama23</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr"/>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>2026-08-16 20:16:05</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@willow_mama23</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>yawa.kludje</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr"/>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>2026-08-19 02:09:54</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@yawa.kludje</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>yemliz2024</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>2026-08-28 01:21:10</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@yemliz2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>zaynabee__flawless</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr"/>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>2026-08-19 02:26:48</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@zaynabee__flawless</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>zotouzotou</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr"/>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>2026-08-22 13:11:18</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@zotouzotou</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>zozadex</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr"/>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>2026-08-20 12:56:57</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@zozadex</t>
         </is>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="769">
   <si>
     <t>handle</t>
   </si>
@@ -5835,6 +5835,9 @@
       <c r="A128" t="s">
         <v>134</v>
       </c>
+      <c r="B128" t="s">
+        <v>268</v>
+      </c>
       <c r="D128" t="s">
         <v>277</v>
       </c>
@@ -6327,6 +6330,9 @@
     <row r="151" spans="1:8">
       <c r="A151" t="s">
         <v>157</v>
+      </c>
+      <c r="B151" t="s">
+        <v>268</v>
       </c>
       <c r="D151" t="s">
         <v>280</v>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H215"/>
+  <dimension ref="A1:H214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,7 +523,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cornelia.tik.tok</t>
+          <t>kingdom.wins</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-02 11:49:04</t>
+          <t>2026-09-02 18:11:02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cornelia.tik.tok</t>
+          <t>https://www.tiktok.com/@kingdom.wins</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kingdom.wins</t>
+          <t>blondie19834</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1578,24 +1578,24 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-02 18:11:02</t>
+          <t>2026-09-01 09:33:03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kingdom.wins</t>
+          <t>https://www.tiktok.com/@blondie19834</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>blondie19834</t>
+          <t>sheena.tt</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1605,12 +1605,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-01 09:33:03</t>
+          <t>2026-09-01 09:36:04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1630,14 +1630,14 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blondie19834</t>
+          <t>https://www.tiktok.com/@sheena.tt</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sheena.tt</t>
+          <t>amb3rin0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-01 09:36:04</t>
+          <t>2026-09-01 09:36:02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1672,14 +1672,14 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sheena.tt</t>
+          <t>https://www.tiktok.com/@amb3rin0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>amb3rin0</t>
+          <t>emma1503021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-01 09:36:02</t>
+          <t>2026-09-01 09:39:02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amb3rin0</t>
+          <t>https://www.tiktok.com/@emma1503021</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>emma1503021</t>
+          <t>veganmamaloves</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-01 09:39:02</t>
+          <t>2026-09-02 18:11:02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@emma1503021</t>
+          <t>https://www.tiktok.com/@veganmamaloves</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>veganmamaloves</t>
+          <t>katie_chronicles2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1788,24 +1788,24 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-02 18:11:02</t>
+          <t>2026-09-01 10:54:02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@veganmamaloves</t>
+          <t>https://www.tiktok.com/@katie_chronicles2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>katie_chronicles2</t>
+          <t>lottieeve5</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-01 10:54:02</t>
+          <t>2026-09-01 10:59:04</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1840,14 +1840,14 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@katie_chronicles2</t>
+          <t>https://www.tiktok.com/@lottieeve5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>lottieeve5</t>
+          <t>kaytyssidemission</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1857,12 +1857,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-01 10:59:04</t>
+          <t>2026-09-01 11:02:03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1882,14 +1882,14 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lottieeve5</t>
+          <t>https://www.tiktok.com/@kaytyssidemission</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kaytyssidemission</t>
+          <t>paulatiktokseller</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-01 11:02:03</t>
+          <t>2026-09-01 10:59:02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1924,14 +1924,14 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaytyssidemission</t>
+          <t>https://www.tiktok.com/@paulatiktokseller</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>paulatiktokseller</t>
+          <t>hirahannan_official</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>250K-500K</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1956,24 +1956,24 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-01 10:59:02</t>
+          <t>2026-08-29 11:13:09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@paulatiktokseller</t>
+          <t>https://www.tiktok.com/@hirahannan_official</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>hirahannan_official</t>
+          <t>deeqa.luul57</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>250K-500K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1998,39 +1998,39 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-29 11:13:09</t>
+          <t>2026-08-27 12:32:00</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hirahannan_official</t>
+          <t>https://www.tiktok.com/@deeqa.luul57</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>deeqa.luul57</t>
+          <t>kim.foster1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2040,24 +2040,24 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-27 12:32:00</t>
+          <t>2026-09-01 11:08:04</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@deeqa.luul57</t>
+          <t>https://www.tiktok.com/@kim.foster1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kim.foster1</t>
+          <t>blondielovinglife</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2067,22 +2067,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Moringa Capsules By</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-01 11:08:04</t>
+          <t>2026-09-01 11:35:02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2092,14 +2092,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kim.foster1</t>
+          <t>https://www.tiktok.com/@blondielovinglife</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>blondielovinglife</t>
+          <t>aqsa1288</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Moringa Capsules By</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2124,24 +2124,24 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:02</t>
+          <t>2026-08-26 18:23:09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blondielovinglife</t>
+          <t>https://www.tiktok.com/@aqsa1288</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>aqsa1288</t>
+          <t>melissaboyle5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2151,39 +2151,39 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-26 18:23:09</t>
+          <t>2026-09-01 11:26:03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@aqsa1288</t>
+          <t>https://www.tiktok.com/@melissaboyle5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>melissaboyle5</t>
+          <t>domddo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:03</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2218,14 +2218,14 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@melissaboyle5</t>
+          <t>https://www.tiktok.com/@domddo</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>domddo</t>
+          <t>itsrhi22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2260,14 +2260,14 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@domddo</t>
+          <t>https://www.tiktok.com/@itsrhi22</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>itsrhi22</t>
+          <t>queenofsobrietyuk</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2302,24 +2302,24 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itsrhi22</t>
+          <t>https://www.tiktok.com/@queenofsobrietyuk</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>queenofsobrietyuk</t>
+          <t>tammyleek24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2344,39 +2344,39 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queenofsobrietyuk</t>
+          <t>https://www.tiktok.com/@tammyleek24</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>tammyleek24</t>
+          <t>leahswarbrick0</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Moringa Capsules By</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 11:35:03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tammyleek24</t>
+          <t>https://www.tiktok.com/@leahswarbrick0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>leahswarbrick0</t>
+          <t>shaunineale</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2403,22 +2403,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Moringa Capsules By</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:03</t>
+          <t>2026-09-01 11:39:02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2428,14 +2428,14 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@leahswarbrick0</t>
+          <t>https://www.tiktok.com/@shaunineale</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>shaunineale</t>
+          <t>h3ather.mcl</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2445,39 +2445,39 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-01 11:39:02</t>
+          <t>2026-09-02 18:18:02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shaunineale</t>
+          <t>https://www.tiktok.com/@h3ather.mcl</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>h3ather.mcl</t>
+          <t>wildwilkinsonsxx</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2492,34 +2492,34 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-02 18:18:02</t>
+          <t>2026-09-01 11:26:03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@h3ather.mcl</t>
+          <t>https://www.tiktok.com/@wildwilkinsonsxx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>wildwilkinsonsxx</t>
+          <t>tashajaynereviews</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:03</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2554,14 +2554,14 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wildwilkinsonsxx</t>
+          <t>https://www.tiktok.com/@tashajaynereviews</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>tashajaynereviews</t>
+          <t>ella.jaynefit</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-09-01 12:03:03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tashajaynereviews</t>
+          <t>https://www.tiktok.com/@ella.jaynefit</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ella.jaynefit</t>
+          <t>afshanjindani</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2628,24 +2628,24 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:03</t>
+          <t>2026-08-26 12:00:09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ella.jaynefit</t>
+          <t>https://www.tiktok.com/@afshanjindani</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>afshanjindani</t>
+          <t>eshafatima1421</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2670,24 +2670,24 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-26 12:00:09</t>
+          <t>2026-09-01 12:03:03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@afshanjindani</t>
+          <t>https://www.tiktok.com/@eshafatima1421</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>eshafatima1421</t>
+          <t>courtney19xo</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2712,24 +2712,24 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:03</t>
+          <t>2026-08-27 18:42:23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@eshafatima1421</t>
+          <t>https://www.tiktok.com/@courtney19xo</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>courtney19xo</t>
+          <t>ambslouise99</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2754,24 +2754,24 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-27 18:42:23</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@courtney19xo</t>
+          <t>https://www.tiktok.com/@ambslouise99</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ambslouise99</t>
+          <t>jazzzyjay360</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 12:14:02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ambslouise99</t>
+          <t>https://www.tiktok.com/@jazzzyjay360</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>jazzzyjay360</t>
+          <t>teheamyytehe</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-01 12:14:02</t>
+          <t>2026-09-01 11:26:02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2848,14 +2848,14 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jazzzyjay360</t>
+          <t>https://www.tiktok.com/@teheamyytehe</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>teheamyytehe</t>
+          <t>isloo7</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2880,24 +2880,24 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:02</t>
+          <t>2026-09-02 18:18:02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teheamyytehe</t>
+          <t>https://www.tiktok.com/@isloo7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>isloo7</t>
+          <t>vonni349</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2917,29 +2917,29 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-02 18:18:02</t>
+          <t>2026-09-01 12:03:03</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@isloo7</t>
+          <t>https://www.tiktok.com/@vonni349</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>sarahorvathova22</t>
+          <t>sonix_luv</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>50K-100K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:02</t>
+          <t>2026-09-01 10:35:21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2974,14 +2974,14 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarahorvathova22</t>
+          <t>https://www.tiktok.com/@sonix_luv</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>vonni349</t>
+          <t>bellavidafacial</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>50K-100K</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3001,12 +3001,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:03</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3016,29 +3016,21 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vonni349</t>
+          <t>https://www.tiktok.com/@bellavidafacial</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>sonix_luv</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>abeehaamir24</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3048,39 +3040,31 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-01 10:35:21</t>
+          <t>2026-08-30 10:05:16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sonix_luv</t>
+          <t>https://www.tiktok.com/@abeehaamir24</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bellavidafacial</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>50K-100K</t>
-        </is>
-      </c>
+          <t>abenaduncan1</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3090,24 +3074,24 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-08-28 12:54:46</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bellavidafacial</t>
+          <t>https://www.tiktok.com/@abenaduncan1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>abenaduncan1</t>
+          <t>adeadun77</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3124,36 +3108,28 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-28 12:54:46</t>
+          <t>2026-08-23 16:32:57</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abenaduncan1</t>
+          <t>https://www.tiktok.com/@adeadun77</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>alina_marchidan</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+          <t>1967095zkm</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3166,58 +3142,58 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-08-22 14:37:48</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@alina_marchidan</t>
+          <t>https://www.tiktok.com/@1967095zkm</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1967095zkm</t>
+          <t>adefunkemayowaoso1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-22 14:37:48</t>
+          <t>2026-08-25 12:03:26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@1967095zkm</t>
+          <t>https://www.tiktok.com/@adefunkemayowaoso1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>abeehaamir24</t>
+          <t>akuapapabi364</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -3234,7 +3210,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-30 10:05:16</t>
+          <t>2026-08-30 17:55:54</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3244,52 +3220,68 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abeehaamir24</t>
+          <t>https://www.tiktok.com/@akuapapabi364</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>adefunkemayowaoso1</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
+          <t>alina_marchidan</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-25 12:03:26</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adefunkemayowaoso1</t>
+          <t>https://www.tiktok.com/@alina_marchidan</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>adeadun77</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
+          <t>amykirks.1</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3302,28 +3294,36 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-23 16:32:57</t>
+          <t>2026-09-01 11:26:03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adeadun77</t>
+          <t>https://www.tiktok.com/@amykirks.1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>akuapapabi364</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
+          <t>banksofmay</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3336,73 +3336,65 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-30 17:55:54</t>
+          <t>2026-08-29 18:39:38</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@akuapapabi364</t>
+          <t>https://www.tiktok.com/@banksofmay</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>beauty_by_ash_attire</t>
+          <t>bablybegum8</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-02 16:24:16</t>
+          <t>2026-08-24 08:59:43</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beauty_by_ash_attire</t>
+          <t>https://www.tiktok.com/@bablybegum8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>banksofmay</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>aysh.707</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3412,24 +3404,24 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-29 18:39:38</t>
+          <t>2026-09-04 08:44:03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@banksofmay</t>
+          <t>https://www.tiktok.com/@aysh.707</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>bablybegum8</t>
+          <t>annie.mahn</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3446,24 +3438,24 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-24 08:59:43</t>
+          <t>2026-08-30 18:11:22</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bablybegum8</t>
+          <t>https://www.tiktok.com/@annie.mahn</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>aysh.707</t>
+          <t>cornelia.tik.tokshop</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3480,24 +3472,24 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:03</t>
+          <t>2026-09-02 11:49:04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@aysh.707</t>
+          <t>https://www.tiktok.com/@cornelia.tik.tokshop</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>annie.mahn</t>
+          <t>beebee9537</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3514,7 +3506,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-30 18:11:22</t>
+          <t>2026-08-30 13:59:25</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3524,55 +3516,55 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@annie.mahn</t>
+          <t>https://www.tiktok.com/@beebee9537</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>cocoleta7</t>
+          <t>bisbis046</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-27 06:32:26</t>
+          <t>2026-09-03 09:57:56</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cocoleta7</t>
+          <t>https://www.tiktok.com/@bisbis046</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>daliayasmin77</t>
+          <t>dailygooods</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3582,31 +3574,31 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-27 22:31:42</t>
+          <t>2026-09-04 08:44:02</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@daliayasmin77</t>
+          <t>https://www.tiktok.com/@dailygooods</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>dailygooods</t>
+          <t>debrazerf</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3616,31 +3608,31 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:02</t>
+          <t>2026-08-27 19:29:33</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailygooods</t>
+          <t>https://www.tiktok.com/@debrazerf</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>delboy_trotter1</t>
+          <t>cocoleta7</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3650,17 +3642,17 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-25 16:12:46</t>
+          <t>2026-08-27 06:32:26</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@delboy_trotter1</t>
+          <t>https://www.tiktok.com/@cocoleta7</t>
         </is>
       </c>
     </row>
@@ -3743,34 +3735,42 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>beebee9537</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
+          <t>chlo._evans</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-30 13:59:25</t>
+          <t>2026-08-31 11:52:47</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beebee9537</t>
+          <t>https://www.tiktok.com/@chlo._evans</t>
         </is>
       </c>
     </row>
@@ -3887,19 +3887,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>amykirks.1</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>jaofficial10</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3912,31 +3904,31 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:03</t>
+          <t>2026-08-28 11:15:31</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amykirks.1</t>
+          <t>https://www.tiktok.com/@jaofficial10</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>jaofficial10</t>
+          <t>jadey032</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3946,31 +3938,31 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-28 11:15:31</t>
+          <t>2026-09-04 08:44:03</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jaofficial10</t>
+          <t>https://www.tiktok.com/@jadey032</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>jadey032</t>
+          <t>itzmallncll</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3980,24 +3972,24 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:03</t>
+          <t>2026-08-22 20:43:48</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jadey032</t>
+          <t>https://www.tiktok.com/@itzmallncll</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>itzmallncll</t>
+          <t>itsneema5</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -4014,31 +4006,39 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-22 20:43:48</t>
+          <t>2026-08-31 16:27:16</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itzmallncll</t>
+          <t>https://www.tiktok.com/@itsneema5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>itsneema5</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
+          <t>irrelevantlyliving</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4048,36 +4048,28 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-31 16:27:16</t>
+          <t>2026-09-01 11:35:03</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itsneema5</t>
+          <t>https://www.tiktok.com/@irrelevantlyliving</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>irrelevantlyliving</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>is.colonel</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -4090,31 +4082,39 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:03</t>
+          <t>2026-09-05 23:55:02</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@irrelevantlyliving</t>
+          <t>https://www.tiktok.com/@is.colonel</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>is.colonel</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
+          <t>ijvpeanuts</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4124,39 +4124,31 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-05 23:55:02</t>
+          <t>2026-09-01 10:35:04</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@is.colonel</t>
+          <t>https://www.tiktok.com/@ijvpeanuts</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ijvpeanuts</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>invalid58</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4166,24 +4158,24 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-01 10:35:04</t>
+          <t>2026-08-28 17:24:16</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ijvpeanuts</t>
+          <t>https://www.tiktok.com/@invalid58</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>invalid58</t>
+          <t>heyuser060</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -4195,36 +4187,36 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:16</t>
+          <t>2026-09-01 17:21:20</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@invalid58</t>
+          <t>https://www.tiktok.com/@heyuser060</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>heyuser060</t>
+          <t>helenbest0</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4234,41 +4226,41 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-01 17:21:20</t>
+          <t>2026-08-31 06:52:19</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@heyuser060</t>
+          <t>https://www.tiktok.com/@helenbest0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>helenbest0</t>
+          <t>iamgawjus</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-31 06:52:19</t>
+          <t>2026-08-31 22:07:29</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4278,14 +4270,14 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@helenbest0</t>
+          <t>https://www.tiktok.com/@iamgawjus</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>iamgawjus</t>
+          <t>homewithlauren_</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4302,27 +4294,31 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-31 22:07:29</t>
+          <t>2026-09-03 10:12:03</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@iamgawjus</t>
+          <t>https://www.tiktok.com/@homewithlauren_</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>homewithlauren_</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
+          <t>health.wise.media</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
@@ -4336,31 +4332,27 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:03</t>
+          <t>2026-08-24 02:13:31</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@homewithlauren_</t>
+          <t>https://www.tiktok.com/@health.wise.media</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>health.wise.media</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>haashim737</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
@@ -4374,24 +4366,24 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-24 02:13:31</t>
+          <t>2026-08-22 17:53:39</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@health.wise.media</t>
+          <t>https://www.tiktok.com/@haashim737</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>haashim737</t>
+          <t>hamidaahmed028</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4408,28 +4400,36 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-22 17:53:39</t>
+          <t>2026-08-27 22:12:14</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@haashim737</t>
+          <t>https://www.tiktok.com/@hamidaahmed028</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>hamidaahmed028</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr"/>
+          <t>hannahtigg1</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -4442,24 +4442,24 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-27 22:12:14</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hamidaahmed028</t>
+          <t>https://www.tiktok.com/@hannahtigg1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>hannahtigg1</t>
+          <t>erico2006</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 22:26:53</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4494,60 +4494,52 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hannahtigg1</t>
+          <t>https://www.tiktok.com/@erico2006</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>famidak1</t>
+          <t>ennyluv76</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-27 15:54:45</t>
+          <t>2026-08-30 08:31:46</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@famidak1</t>
+          <t>https://www.tiktok.com/@ennyluv76</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>erico2006</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>emwinghareadun</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -4560,31 +4552,35 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-01 22:26:53</t>
+          <t>2026-08-23 09:11:57</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@erico2006</t>
+          <t>https://www.tiktok.com/@emwinghareadun</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ennyluv76</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
+          <t>gretswithnoregrets_</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4594,31 +4590,27 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-30 08:31:46</t>
+          <t>2026-08-27 18:41:31</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ennyluv76</t>
+          <t>https://www.tiktok.com/@gretswithnoregrets_</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>gretswithnoregrets_</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>gallodiopfall</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
@@ -4627,165 +4619,165 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-27 18:41:31</t>
+          <t>2026-08-22 13:48:46</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gretswithnoregrets_</t>
+          <t>https://www.tiktok.com/@gallodiopfall</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>gallodiopfall</t>
+          <t>fffysigs0719</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-22 13:48:46</t>
+          <t>2026-08-27 16:41:03</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gallodiopfall</t>
+          <t>https://www.tiktok.com/@fffysigs0719</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>fffysigs0719</t>
+          <t>finda9095</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-27 16:41:03</t>
+          <t>2026-09-01 13:23:27</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fffysigs0719</t>
+          <t>https://www.tiktok.com/@finda9095</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>finda9095</t>
+          <t>fissysbakestudio</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-09-01 13:23:27</t>
+          <t>2026-08-31 21:21:04</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@finda9095</t>
+          <t>https://www.tiktok.com/@fissysbakestudio</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>fissysbakestudio</t>
+          <t>famidak1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-31 21:21:04</t>
+          <t>2026-08-27 15:54:45</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fissysbakestudio</t>
+          <t>https://www.tiktok.com/@famidak1</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>felistass577</t>
+          <t>david.adetokunbo2</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4802,24 +4794,24 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-01 11:50:12</t>
+          <t>2026-08-26 22:15:55</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@felistass577</t>
+          <t>https://www.tiktok.com/@david.adetokunbo2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>debrazerf</t>
+          <t>darkness10145</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4831,29 +4823,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-27 19:29:33</t>
+          <t>2026-09-01 19:15:07</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@debrazerf</t>
+          <t>https://www.tiktok.com/@darkness10145</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>david.adetokunbo2</t>
+          <t>daliayasmin77</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4870,24 +4862,24 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:55</t>
+          <t>2026-08-27 22:31:42</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@david.adetokunbo2</t>
+          <t>https://www.tiktok.com/@daliayasmin77</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>darkness10145</t>
+          <t>dlp7831</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -4899,29 +4891,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-01 19:15:07</t>
+          <t>2026-08-28 08:11:22</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@darkness10145</t>
+          <t>https://www.tiktok.com/@dlp7831</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>dlp7831</t>
+          <t>dimples7219</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4938,27 +4930,31 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-28 08:11:22</t>
+          <t>2026-08-25 08:40:28</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dlp7831</t>
+          <t>https://www.tiktok.com/@dimples7219</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>dimples7219</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr"/>
+          <t>designer_suits</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
@@ -4972,35 +4968,31 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-25 08:40:28</t>
+          <t>2026-08-31 19:59:15</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dimples7219</t>
+          <t>https://www.tiktok.com/@designer_suits</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>designer_suits</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>delboy_trotter1</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5010,58 +5002,58 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-31 19:59:15</t>
+          <t>2026-08-25 16:12:46</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@designer_suits</t>
+          <t>https://www.tiktok.com/@delboy_trotter1</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>emwinghareadun</t>
+          <t>beauty_by_ash_attire</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-08-23 09:11:57</t>
+          <t>2026-09-02 16:24:16</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@emwinghareadun</t>
+          <t>https://www.tiktok.com/@beauty_by_ash_attire</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>bisbis046</t>
+          <t>maisiefinds0</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -5073,75 +5065,75 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-03 09:57:56</t>
+          <t>2026-09-04 08:44:04</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bisbis046</t>
+          <t>https://www.tiktok.com/@maisiefinds0</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>chlo._evans</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+          <t>macouly1</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-31 11:52:47</t>
+          <t>2026-08-29 10:33:10</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chlo._evans</t>
+          <t>https://www.tiktok.com/@macouly1</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>macouly1</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr"/>
+          <t>mabes746</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D122" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5154,31 +5146,39 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-29 10:33:10</t>
+          <t>2026-09-01 11:35:04</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@macouly1</t>
+          <t>https://www.tiktok.com/@mabes746</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>maisiefinds0</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
+          <t>lydiaburnettxx</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>25K-50K</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5188,36 +5188,28 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:04</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maisiefinds0</t>
+          <t>https://www.tiktok.com/@lydiaburnettxx</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>lydiaburnettxx</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>25K-50K</t>
-        </is>
-      </c>
+          <t>martigergeraldine</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5230,112 +5222,104 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-08-31 11:05:55</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lydiaburnettxx</t>
+          <t>https://www.tiktok.com/@martigergeraldine</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>martigergeraldine</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr"/>
-      <c r="C125" t="inlineStr"/>
+          <t>maria_london7</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-31 11:05:55</t>
+          <t>2026-08-22 20:57:09</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@martigergeraldine</t>
+          <t>https://www.tiktok.com/@maria_london7</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>maria_london7</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>mamarie146</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-22 20:57:09</t>
+          <t>2026-09-01 12:24:32</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maria_london7</t>
+          <t>https://www.tiktok.com/@mamarie146</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>mabes746</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>midlifehiddengems</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5348,24 +5332,24 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:04</t>
+          <t>2026-09-04 22:30:55</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mabes746</t>
+          <t>https://www.tiktok.com/@midlifehiddengems</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>midlifehiddengems</t>
+          <t>maxmeritbackup</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5382,24 +5366,24 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30:55</t>
+          <t>2026-09-01 08:15:09</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@midlifehiddengems</t>
+          <t>https://www.tiktok.com/@maxmeritbackup</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>maxmeritbackup</t>
+          <t>mila0701c7c</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -5416,31 +5400,31 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-09-01 08:15:09</t>
+          <t>2026-08-25 05:11:12</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maxmeritbackup</t>
+          <t>https://www.tiktok.com/@mila0701c7c</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>mila0701c7c</t>
+          <t>mintshopdeals</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -5450,31 +5434,31 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-25 05:11:12</t>
+          <t>2026-09-04 08:44:03</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mila0701c7c</t>
+          <t>https://www.tiktok.com/@mintshopdeals</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>mintshopdeals</t>
+          <t>monpakhi_202</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5484,31 +5468,31 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:03</t>
+          <t>2026-08-31 21:10:55</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mintshopdeals</t>
+          <t>https://www.tiktok.com/@monpakhi_202</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>monpakhi_202</t>
+          <t>missberry.kayamatauk</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5518,31 +5502,31 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-08-31 21:10:55</t>
+          <t>2026-08-26 13:15:36</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@monpakhi_202</t>
+          <t>https://www.tiktok.com/@missberry.kayamatauk</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>missberry.kayamatauk</t>
+          <t>manoor_303</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5552,24 +5536,24 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-26 13:15:36</t>
+          <t>2026-08-23 07:41:43</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@missberry.kayamatauk</t>
+          <t>https://www.tiktok.com/@manoor_303</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>manoor_303</t>
+          <t>mandoki72</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5586,126 +5570,126 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-08-23 07:41:43</t>
+          <t>2026-08-26 21:17:58</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@manoor_303</t>
+          <t>https://www.tiktok.com/@mandoki72</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>mamarie146</t>
+          <t>mamacassyxo</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-09-01 12:24:32</t>
+          <t>2026-08-27 16:05:15</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mamarie146</t>
+          <t>https://www.tiktok.com/@mamacassyxo</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>mamacassyxo</t>
+          <t>lady_dash07</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-08-27 16:05:15</t>
+          <t>2026-09-05 21:11:23</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mamacassyxo</t>
+          <t>https://www.tiktok.com/@lady_dash07</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>lady_dash07</t>
+          <t>kemotee07</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-09-05 21:11:23</t>
+          <t>2026-08-24 11:49:41</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lady_dash07</t>
+          <t>https://www.tiktok.com/@kemotee07</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kemotee07</t>
+          <t>lady.p3600</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5722,24 +5706,24 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-24 11:49:41</t>
+          <t>2026-08-26 15:34:27</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kemotee07</t>
+          <t>https://www.tiktok.com/@lady.p3600</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>lady.p3600</t>
+          <t>judyluv42</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -5756,28 +5740,36 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-08-26 15:34:27</t>
+          <t>2026-08-25 10:31:30</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lady.p3600</t>
+          <t>https://www.tiktok.com/@judyluv42</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>judyluv42</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
-      <c r="C140" t="inlineStr"/>
+          <t>lifeofladyluna</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D140" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5790,36 +5782,28 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-08-25 10:31:30</t>
+          <t>2026-09-01 11:26:02</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@judyluv42</t>
+          <t>https://www.tiktok.com/@lifeofladyluna</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>lifeofladyluna</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>lexysluxurytravel</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5832,24 +5816,24 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:02</t>
+          <t>2026-08-27 13:48:00</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifeofladyluna</t>
+          <t>https://www.tiktok.com/@lexysluxurytravel</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>lexysluxurytravel</t>
+          <t>laurenandsophiesjigglejo</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -5866,31 +5850,31 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-27 13:48:00</t>
+          <t>2026-09-03 10:12:08</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lexysluxurytravel</t>
+          <t>https://www.tiktok.com/@laurenandsophiesjigglejo</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>laurenandsophiesjigglejo</t>
+          <t>liz059019</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5900,7 +5884,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:08</t>
+          <t>2026-09-03 10:05:06</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5910,48 +5894,48 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@laurenandsophiesjigglejo</t>
+          <t>https://www.tiktok.com/@liz059019</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>liz059019</t>
+          <t>lifesabeach83</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-09-03 10:05:06</t>
+          <t>2026-09-01 16:37:08</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@liz059019</t>
+          <t>https://www.tiktok.com/@lifesabeach83</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>lifesabeach83</t>
+          <t>lovemystarsign</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -5968,7 +5952,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-09-01 16:37:08</t>
+          <t>2026-09-01 18:46:55</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5978,18 +5962,26 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifesabeach83</t>
+          <t>https://www.tiktok.com/@lovemystarsign</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>lovemystarsign</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
-      <c r="C146" t="inlineStr"/>
+          <t>kiesha11matthews</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D146" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5997,12 +5989,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-01 18:46:55</t>
+          <t>2026-09-01 11:35:02</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -6012,60 +6004,60 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lovemystarsign</t>
+          <t>https://www.tiktok.com/@kiesha11matthews</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kiesha11matthews</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>kaymama31</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:02</t>
+          <t>2026-08-30 10:22:50</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kiesha11matthews</t>
+          <t>https://www.tiktok.com/@kaymama31</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kaymama31</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr"/>
+          <t>kaurjas608</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D148" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -6073,29 +6065,29 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-08-30 10:22:50</t>
+          <t>2026-09-01 10:36:07</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaymama31</t>
+          <t>https://www.tiktok.com/@kaurjas608</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kaurjas608</t>
+          <t>katiewanderlust</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6105,7 +6097,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6120,7 +6112,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-09-01 10:36:07</t>
+          <t>2026-09-01 12:14:02</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -6130,26 +6122,18 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaurjas608</t>
+          <t>https://www.tiktok.com/@katiewanderlust</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>katiewanderlust</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>jay25084</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6162,24 +6146,24 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-09-01 12:14:02</t>
+          <t>2026-08-25 10:06:52</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@katiewanderlust</t>
+          <t>https://www.tiktok.com/@jay25084</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>jay25084</t>
+          <t>pubby1amob</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -6196,27 +6180,31 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-08-25 10:06:52</t>
+          <t>2026-08-27 18:28:59</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jay25084</t>
+          <t>https://www.tiktok.com/@pubby1amob</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>pubby1amob</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
+          <t>princesslizy2010</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
@@ -6230,24 +6218,24 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-27 18:28:59</t>
+          <t>2026-08-26 20:03:55</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@pubby1amob</t>
+          <t>https://www.tiktok.com/@princesslizy2010</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>princesslizy2010</t>
+          <t>princess_wumi</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6255,7 +6243,11 @@
           <t>£0-£50</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr"/>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D153" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6268,36 +6260,28 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-26 20:03:55</t>
+          <t>2026-08-29 08:38:03</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princesslizy2010</t>
+          <t>https://www.tiktok.com/@princess_wumi</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>princess_wumi</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>pm37896</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6310,24 +6294,24 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-08-29 08:38:03</t>
+          <t>2026-08-28 00:17:19</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princess_wumi</t>
+          <t>https://www.tiktok.com/@pm37896</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>pm37896</t>
+          <t>phillipbennett92</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -6344,24 +6328,24 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-08-28 00:17:19</t>
+          <t>2026-08-22 18:41:01</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@pm37896</t>
+          <t>https://www.tiktok.com/@phillipbennett92</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>phillipbennett92</t>
+          <t>ovwomani22</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -6378,31 +6362,31 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-08-22 18:41:01</t>
+          <t>2026-08-28 18:04:58</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@phillipbennett92</t>
+          <t>https://www.tiktok.com/@ovwomani22</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ovwomani22</t>
+          <t>nutster58</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -6412,31 +6396,31 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-08-28 18:04:58</t>
+          <t>2026-09-01 08:36:44</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ovwomani22</t>
+          <t>https://www.tiktok.com/@nutster58</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>nutster58</t>
+          <t>oluwaseyifunmi988</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -6446,24 +6430,24 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-09-01 08:36:44</t>
+          <t>2026-08-23 01:54:34</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nutster58</t>
+          <t>https://www.tiktok.com/@oluwaseyifunmi988</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>oluwaseyifunmi988</t>
+          <t>nikkigossal29</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -6480,24 +6464,24 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-08-23 01:54:34</t>
+          <t>2026-08-30 17:46:28</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluwaseyifunmi988</t>
+          <t>https://www.tiktok.com/@nikkigossal29</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>nikkigossal29</t>
+          <t>ness69280</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -6514,24 +6498,24 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-08-30 17:46:28</t>
+          <t>2026-09-03 10:09:03</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nikkigossal29</t>
+          <t>https://www.tiktok.com/@ness69280</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ness69280</t>
+          <t>notlikeeveryday</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -6548,31 +6532,39 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-09-03 10:09:03</t>
+          <t>2026-09-04 08:44:04</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ness69280</t>
+          <t>https://www.tiktok.com/@notlikeeveryday</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>notlikeeveryday</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr"/>
-      <c r="C162" t="inlineStr"/>
+          <t>niknak190725</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6582,39 +6574,31 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:04</t>
+          <t>2026-09-01 12:14:04</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@notlikeeveryday</t>
+          <t>https://www.tiktok.com/@niknak190725</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>niknak190725</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>nellyedwin54</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6624,28 +6608,36 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-09-01 12:14:04</t>
+          <t>2026-08-30 13:16:24</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@niknak190725</t>
+          <t>https://www.tiktok.com/@nellyedwin54</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>nellyedwin54</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr"/>
-      <c r="C164" t="inlineStr"/>
+          <t>nathenjump</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D164" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6658,36 +6650,28 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-08-30 13:16:24</t>
+          <t>2026-09-01 14:09:02</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nellyedwin54</t>
+          <t>https://www.tiktok.com/@nathenjump</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>nathenjump</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>moon.x280</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6695,12 +6679,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-09-01 14:09:02</t>
+          <t>2026-09-01 18:11:41</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -6710,14 +6694,14 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nathenjump</t>
+          <t>https://www.tiktok.com/@moon.x280</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>moon.x280</t>
+          <t>nasirpatel690</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
@@ -6729,36 +6713,36 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-01 18:11:41</t>
+          <t>2026-08-29 00:44:35</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@moon.x280</t>
+          <t>https://www.tiktok.com/@nasirpatel690</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>nasirpatel690</t>
+          <t>sarahov72</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6768,28 +6752,36 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-08-29 00:44:35</t>
+          <t>2026-09-01 11:35:02</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nasirpatel690</t>
+          <t>https://www.tiktok.com/@sarahov72</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>mandoki72</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr"/>
-      <c r="C168" t="inlineStr"/>
+          <t>sarah565556</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D168" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6802,36 +6794,28 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-08-26 21:17:58</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mandoki72</t>
+          <t>https://www.tiktok.com/@sarah565556</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>sarah565556</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>samplesquaduk</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -6844,17 +6828,17 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-03 10:16:02</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarah565556</t>
+          <t>https://www.tiktok.com/@samplesquaduk</t>
         </is>
       </c>
     </row>
@@ -6895,14 +6879,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>samplesquaduk</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr"/>
-      <c r="C171" t="inlineStr"/>
+          <t>saliya_94</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -6912,24 +6904,24 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-09-03 10:16:02</t>
+          <t>2026-08-24 14:48:07</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samplesquaduk</t>
+          <t>https://www.tiktok.com/@saliya_94</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>robbomsnvfv</t>
+          <t>shakirakhan296</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
@@ -6941,109 +6933,101 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-09-01 12:37:06</t>
+          <t>2026-08-28 23:38:18</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@robbomsnvfv</t>
+          <t>https://www.tiktok.com/@shakirakhan296</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>shakirakhan296</t>
+          <t>shahzad.akram041</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-28 23:38:18</t>
+          <t>2026-09-03 04:27:22</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shakirakhan296</t>
+          <t>https://www.tiktok.com/@shahzad.akram041</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>shahzad.akram041</t>
+          <t>queen.of.boys42</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-09-03 04:27:22</t>
+          <t>2026-08-29 18:27:02</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shahzad.akram041</t>
+          <t>https://www.tiktok.com/@queen.of.boys42</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>saliya_94</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>rkh250496ad</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -7056,130 +7040,138 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-08-24 14:48:07</t>
+          <t>2026-08-31 17:54:22</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@saliya_94</t>
+          <t>https://www.tiktok.com/@rkh250496ad</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>reviewsbymira44</t>
+          <t>robbomsnvfv</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:03</t>
+          <t>2026-09-01 12:37:06</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@reviewsbymira44</t>
+          <t>https://www.tiktok.com/@robbomsnvfv</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>rkh250496ad</t>
+          <t>sabbathina38</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-08-31 17:54:22</t>
+          <t>2026-08-25 16:09:05</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rkh250496ad</t>
+          <t>https://www.tiktok.com/@sabbathina38</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>sabbathina38</t>
+          <t>rabiaaman21</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-08-25 16:09:05</t>
+          <t>2026-09-01 14:27:46</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sabbathina38</t>
+          <t>https://www.tiktok.com/@rabiaaman21</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>queen.of.boys42</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr"/>
-      <c r="C179" t="inlineStr"/>
+          <t>redbloodchurch1</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D179" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -7192,7 +7184,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-08-29 18:27:02</t>
+          <t>2026-08-29 15:02:18</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -7202,97 +7194,89 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queen.of.boys42</t>
+          <t>https://www.tiktok.com/@redbloodchurch1</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>redbloodchurch1</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>remeradiance</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-08-29 15:02:18</t>
+          <t>2026-09-04 19:49:19</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@redbloodchurch1</t>
+          <t>https://www.tiktok.com/@remeradiance</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>remeradiance</t>
+          <t>remmyc64</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-09-04 19:49:19</t>
+          <t>2026-08-24 16:17:42</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@remeradiance</t>
+          <t>https://www.tiktok.com/@remmyc64</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>remmyc64</t>
+          <t>reviewsbymira44</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -7302,24 +7286,24 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-08-24 16:17:42</t>
+          <t>2026-09-04 08:44:03</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@remmyc64</t>
+          <t>https://www.tiktok.com/@reviewsbymira44</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>rabiaaman21</t>
+          <t>sukhdeepkaur343</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -7336,24 +7320,24 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:46</t>
+          <t>2026-08-27 15:52:29</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rabiaaman21</t>
+          <t>https://www.tiktok.com/@sukhdeepkaur343</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>sukhdeepkaur343</t>
+          <t>soul_rebel4</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
@@ -7370,28 +7354,36 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-08-27 15:52:29</t>
+          <t>2026-08-25 20:55:08</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sukhdeepkaur343</t>
+          <t>https://www.tiktok.com/@soul_rebel4</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>soul_rebel4</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr"/>
-      <c r="C185" t="inlineStr"/>
+          <t>skyviewbm</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D185" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -7404,36 +7396,28 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-08-25 20:55:08</t>
+          <t>2026-08-30 16:29:14</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@soul_rebel4</t>
+          <t>https://www.tiktok.com/@skyviewbm</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>skyviewbm</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>shurlar347</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -7446,31 +7430,31 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-08-30 16:29:14</t>
+          <t>2026-08-27 14:53:08</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@skyviewbm</t>
+          <t>https://www.tiktok.com/@shurlar347</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>shurlar347</t>
+          <t>shezha17</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -7480,31 +7464,31 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-08-27 14:53:08</t>
+          <t>2026-09-01 09:35:01</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shurlar347</t>
+          <t>https://www.tiktok.com/@shezha17</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>shezha17</t>
+          <t>shume.begum8</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -7514,7 +7498,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-09-01 09:35:01</t>
+          <t>2026-09-01 20:33:17</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -7524,14 +7508,14 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shezha17</t>
+          <t>https://www.tiktok.com/@shume.begum8</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>shume.begum8</t>
+          <t>sharansaleem</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -7548,58 +7532,58 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-09-01 20:33:17</t>
+          <t>2026-08-29 11:45:48</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shume.begum8</t>
+          <t>https://www.tiktok.com/@sharansaleem</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>sharansaleem</t>
+          <t>sharonhiggins46</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-08-29 11:45:48</t>
+          <t>2026-08-28 20:19:57</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sharansaleem</t>
+          <t>https://www.tiktok.com/@sharonhiggins46</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>sharonhiggins46</t>
+          <t>seana_montgomery61</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -7611,36 +7595,36 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-08-28 20:19:57</t>
+          <t>2026-09-03 10:12:09</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sharonhiggins46</t>
+          <t>https://www.tiktok.com/@seana_montgomery61</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>seana_montgomery61</t>
+          <t>trending_gists_omoola</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -7650,62 +7634,70 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:09</t>
+          <t>2026-08-30 21:32:52</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@seana_montgomery61</t>
+          <t>https://www.tiktok.com/@trending_gists_omoola</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>trending_gists_omoola</t>
+          <t>turelove730</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-30 21:32:52</t>
+          <t>2026-09-01 14:36:11</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@trending_gists_omoola</t>
+          <t>https://www.tiktok.com/@turelove730</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>turelove730</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr"/>
-      <c r="C194" t="inlineStr"/>
+          <t>ugcbyshristi</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D194" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -7713,12 +7705,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-09-01 14:36:11</t>
+          <t>2026-09-01 12:03:03</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -7728,29 +7720,21 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@turelove730</t>
+          <t>https://www.tiktok.com/@ugcbyshristi</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ugcbyshristi</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>tran.le455</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -7760,228 +7744,228 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:03</t>
+          <t>2026-08-28 14:45:25</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ugcbyshristi</t>
+          <t>https://www.tiktok.com/@tran.le455</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>tran.le455</t>
+          <t>sweetshez1</t>
         </is>
       </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-08-28 14:45:25</t>
+          <t>2026-09-05 18:50:17</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tran.le455</t>
+          <t>https://www.tiktok.com/@sweetshez1</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>sweetshez1</t>
+          <t>tee_y.x</t>
         </is>
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-09-05 18:50:17</t>
+          <t>2026-08-31 00:32:51</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sweetshez1</t>
+          <t>https://www.tiktok.com/@tee_y.x</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>tee_y.x</t>
+          <t>thestoicphoenix</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-08-31 00:32:51</t>
+          <t>2026-09-01 12:03:16</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tee_y.x</t>
+          <t>https://www.tiktok.com/@thestoicphoenix</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>thestoicphoenix</t>
+          <t>user4423713561101</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:16</t>
+          <t>2026-08-28 10:55:03</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thestoicphoenix</t>
+          <t>https://www.tiktok.com/@user4423713561101</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>user4423713561101</t>
+          <t>user2922793729949</t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-08-28 10:55:03</t>
+          <t>2026-09-01 13:14:46</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user4423713561101</t>
+          <t>https://www.tiktok.com/@user2922793729949</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>user2922793729949</t>
+          <t>user26963863682186</t>
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-09-01 13:14:46</t>
+          <t>2026-08-27 16:29:12</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2922793729949</t>
+          <t>https://www.tiktok.com/@user26963863682186</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>user26963863682186</t>
+          <t>uky1090</t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
@@ -7998,75 +7982,83 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-08-27 16:29:12</t>
+          <t>2026-08-28 01:37:24</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user26963863682186</t>
+          <t>https://www.tiktok.com/@uky1090</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>uky1090</t>
+          <t>user_steeze</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-08-28 01:37:24</t>
+          <t>2026-08-30 17:59:09</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uky1090</t>
+          <t>https://www.tiktok.com/@user_steeze</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>user_steeze</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr"/>
-      <c r="C204" t="inlineStr"/>
+          <t>veronpoks</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-08-30 17:59:09</t>
+          <t>2026-08-30 14:08:12</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -8076,26 +8068,18 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user_steeze</t>
+          <t>https://www.tiktok.com/@veronpoks</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>veronpoks</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>user596114145414</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -8108,24 +8092,24 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-08-30 14:08:12</t>
+          <t>2026-08-28 18:57:06</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@veronpoks</t>
+          <t>https://www.tiktok.com/@user596114145414</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>user596114145414</t>
+          <t>user4961074980381</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -8142,7 +8126,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-08-28 18:57:06</t>
+          <t>2026-08-28 21:55:56</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -8152,14 +8136,14 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user596114145414</t>
+          <t>https://www.tiktok.com/@user4961074980381</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>user4961074980381</t>
+          <t>wellnesswithuzo</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -8176,24 +8160,24 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-08-28 21:55:56</t>
+          <t>2026-08-24 06:46:02</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user4961074980381</t>
+          <t>https://www.tiktok.com/@wellnesswithuzo</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>wellnesswithuzo</t>
+          <t>vivianesoizeau</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
@@ -8210,58 +8194,58 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-08-24 06:46:02</t>
+          <t>2026-08-31 16:20:27</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wellnesswithuzo</t>
+          <t>https://www.tiktok.com/@vivianesoizeau</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>vivianesoizeau</t>
+          <t>wolfie1830</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-08-31 16:20:27</t>
+          <t>2026-09-01 11:52:06</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vivianesoizeau</t>
+          <t>https://www.tiktok.com/@wolfie1830</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>wolfie1830</t>
+          <t>withlakisha</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -8273,29 +8257,29 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-09-01 11:52:06</t>
+          <t>2026-09-04 08:44:03</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wolfie1830</t>
+          <t>https://www.tiktok.com/@withlakisha</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>withlakisha</t>
+          <t>xstormx33</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
@@ -8307,63 +8291,63 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:03</t>
+          <t>2026-09-01 10:36:21</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@withlakisha</t>
+          <t>https://www.tiktok.com/@xstormx33</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>xstormx33</t>
+          <t>yxsna_98</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-09-01 10:36:21</t>
+          <t>2026-08-30 12:46:22</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@xstormx33</t>
+          <t>https://www.tiktok.com/@yxsna_98</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>yxsna_98</t>
+          <t>zotouzotou</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -8380,83 +8364,49 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-08-30 12:46:22</t>
+          <t>2026-08-22 13:11:18</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yxsna_98</t>
+          <t>https://www.tiktok.com/@zotouzotou</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>zotouzotou</t>
+          <t>zubairianaz15</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-08-22 13:11:18</t>
+          <t>2026-09-05 22:51:12</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@zotouzotou</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>zubairianaz15</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr"/>
-      <c r="C215" t="inlineStr"/>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>2026-09-05 22:51:12</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@zubairianaz15</t>
         </is>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H214"/>
+  <dimension ref="A1:H193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -545,7 +545,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>lukeyshops</t>
+          <t>lewistiktokshopdeals</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -565,34 +565,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:02</t>
+          <t>2026-08-27 15:31:09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lukeyshops</t>
+          <t>https://www.tiktok.com/@lewistiktokshopdeals</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>lewistiktokshopdeals</t>
+          <t>queennorxy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -602,34 +602,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:09</t>
+          <t>2026-08-31 11:31:09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lewistiktokshopdeals</t>
+          <t>https://www.tiktok.com/@queennorxy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>queennorxy</t>
+          <t>fypdavesdeals</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -639,39 +639,39 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-31 11:31:09</t>
+          <t>2026-08-31 11:31:10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queennorxy</t>
+          <t>https://www.tiktok.com/@fypdavesdeals</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fypdavesdeals</t>
+          <t>krystal_kei</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -686,34 +686,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-31 11:31:10</t>
+          <t>2026-08-27 08:36:58</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fypdavesdeals</t>
+          <t>https://www.tiktok.com/@krystal_kei</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>krystal_kei</t>
+          <t>chloefinds37</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -723,49 +723,49 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-27 08:36:58</t>
+          <t>2026-08-31 11:31:10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@krystal_kei</t>
+          <t>https://www.tiktok.com/@chloefinds37</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>chloefinds37</t>
+          <t>clairlynda.x</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -780,24 +780,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-31 11:31:10</t>
+          <t>2026-09-02 07:40:02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chloefinds37</t>
+          <t>https://www.tiktok.com/@clairlynda.x</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>clairlynda.x</t>
+          <t>ajahnu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -822,24 +822,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-02 07:40:02</t>
+          <t>2026-09-02 11:44:03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clairlynda.x</t>
+          <t>https://www.tiktok.com/@ajahnu</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ajahnu</t>
+          <t>luxuryvibe36</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>100K-250K</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -859,29 +859,29 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-02 11:44:03</t>
+          <t>2026-08-31 11:42:10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ajahnu</t>
+          <t>https://www.tiktok.com/@luxuryvibe36</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>luxuryvibe36</t>
+          <t>muhammadbilal_23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>100K-250K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -901,29 +901,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-31 11:42:10</t>
+          <t>2026-09-02 11:44:03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@luxuryvibe36</t>
+          <t>https://www.tiktok.com/@muhammadbilal_23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>muhammadbilal_23</t>
+          <t>bam.bam5870</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -933,39 +933,39 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-02 11:44:03</t>
+          <t>2026-08-31 11:39:10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@muhammadbilal_23</t>
+          <t>https://www.tiktok.com/@bam.bam5870</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bam.bam5870</t>
+          <t>phil_becs</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -975,39 +975,39 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-31 11:39:10</t>
+          <t>2026-08-31 11:42:09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bam.bam5870</t>
+          <t>https://www.tiktok.com/@phil_becs</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>phil_becs</t>
+          <t>kelliebelchamber</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1032,24 +1032,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-31 11:42:09</t>
+          <t>2026-09-02 18:19:02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@phil_becs</t>
+          <t>https://www.tiktok.com/@kelliebelchamber</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kelliebelchamber</t>
+          <t>crested_kitten</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1074,24 +1074,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-02 18:19:02</t>
+          <t>2026-08-31 11:57:10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kelliebelchamber</t>
+          <t>https://www.tiktok.com/@crested_kitten</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>myownchinny</t>
+          <t>sh28___</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>100K-250K</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1111,29 +1111,29 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-02 11:44:02</t>
+          <t>2026-08-31 11:57:09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@myownchinny</t>
+          <t>https://www.tiktok.com/@sh28___</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>crested_kitten</t>
+          <t>cornishcuppa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1158,24 +1158,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-31 11:57:10</t>
+          <t>2026-09-02 11:44:03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@crested_kitten</t>
+          <t>https://www.tiktok.com/@cornishcuppa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sh28___</t>
+          <t>hayleybumpbear</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>100K-250K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>[] Moringa 1000mg</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1200,24 +1200,24 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-31 11:57:09</t>
+          <t>2026-08-31 12:12:09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sh28___</t>
+          <t>https://www.tiktok.com/@hayleybumpbear</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cornishcuppa</t>
+          <t>amy.l094</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>[] Moringa 1000mg</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1242,24 +1242,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-02 11:44:03</t>
+          <t>2026-08-31 12:07:10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cornishcuppa</t>
+          <t>https://www.tiktok.com/@amy.l094</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>annalizinglife</t>
+          <t>tonks1988</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1284,71 +1284,71 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-02 18:13:02</t>
+          <t>2026-08-31 12:11:09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@annalizinglife</t>
+          <t>https://www.tiktok.com/@tonks1988</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hayleybumpbear</t>
+          <t>kingdom.wins</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[] Moringa 1000mg</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-31 12:12:09</t>
+          <t>2026-09-02 18:11:02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hayleybumpbear</t>
+          <t>https://www.tiktok.com/@kingdom.wins</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>scalelabfinds</t>
+          <t>blondie19834</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1368,29 +1368,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-02 11:44:02</t>
+          <t>2026-09-01 09:33:03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@scalelabfinds</t>
+          <t>https://www.tiktok.com/@blondie19834</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>earnwithtrisjay</t>
+          <t>sheena.tt</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1410,49 +1410,49 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-22 18:43:09</t>
+          <t>2026-09-01 09:36:04</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@earnwithtrisjay</t>
+          <t>https://www.tiktok.com/@sheena.tt</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>amy.l094</t>
+          <t>amb3rin0</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[] Moringa 1000mg</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-31 12:07:10</t>
+          <t>2026-09-01 09:36:02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1462,24 +1462,24 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amy.l094</t>
+          <t>https://www.tiktok.com/@amb3rin0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tonks1988</t>
+          <t>emma1503021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-31 12:11:09</t>
+          <t>2026-09-01 09:39:02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1504,14 +1504,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tonks1988</t>
+          <t>https://www.tiktok.com/@emma1503021</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kingdom.wins</t>
+          <t>veganmamaloves</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1541,34 +1541,34 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kingdom.wins</t>
+          <t>https://www.tiktok.com/@veganmamaloves</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>blondie19834</t>
+          <t>katie_chronicles2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1578,39 +1578,39 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-01 09:33:03</t>
+          <t>2026-09-01 10:54:02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blondie19834</t>
+          <t>https://www.tiktok.com/@katie_chronicles2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>sheena.tt</t>
+          <t>lottieeve5</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1620,29 +1620,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-01 09:36:04</t>
+          <t>2026-09-01 10:59:04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sheena.tt</t>
+          <t>https://www.tiktok.com/@lottieeve5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>amb3rin0</t>
+          <t>kaytyssidemission</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1662,34 +1662,34 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-01 09:36:02</t>
+          <t>2026-09-01 11:02:03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amb3rin0</t>
+          <t>https://www.tiktok.com/@kaytyssidemission</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>emma1503021</t>
+          <t>paulatiktokseller</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1704,34 +1704,34 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-01 09:39:02</t>
+          <t>2026-09-01 10:59:02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@emma1503021</t>
+          <t>https://www.tiktok.com/@paulatiktokseller</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>veganmamaloves</t>
+          <t>hirahannan_official</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>250K-500K</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1746,24 +1746,24 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-02 18:11:02</t>
+          <t>2026-08-29 11:13:09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@veganmamaloves</t>
+          <t>https://www.tiktok.com/@hirahannan_official</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>katie_chronicles2</t>
+          <t>deeqa.luul57</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1788,29 +1788,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-01 10:54:02</t>
+          <t>2026-08-27 12:32:00</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@katie_chronicles2</t>
+          <t>https://www.tiktok.com/@deeqa.luul57</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>lottieeve5</t>
+          <t>kim.foster1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1830,29 +1830,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-01 10:59:04</t>
+          <t>2026-09-01 11:08:04</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lottieeve5</t>
+          <t>https://www.tiktok.com/@kim.foster1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kaytyssidemission</t>
+          <t>blondielovinglife</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1862,44 +1862,44 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Moringa Capsules By</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-01 11:02:03</t>
+          <t>2026-09-01 11:35:02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaytyssidemission</t>
+          <t>https://www.tiktok.com/@blondielovinglife</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>paulatiktokseller</t>
+          <t>aqsa1288</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1909,44 +1909,44 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-01 10:59:02</t>
+          <t>2026-08-26 18:23:09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@paulatiktokseller</t>
+          <t>https://www.tiktok.com/@aqsa1288</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>hirahannan_official</t>
+          <t>domddo</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>250K-500K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-29 11:13:09</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hirahannan_official</t>
+          <t>https://www.tiktok.com/@domddo</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>deeqa.luul57</t>
+          <t>itsrhi22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1998,24 +1998,24 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-27 12:32:00</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@deeqa.luul57</t>
+          <t>https://www.tiktok.com/@itsrhi22</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kim.foster1</t>
+          <t>queenofsobrietyuk</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2040,81 +2040,81 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-01 11:08:04</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kim.foster1</t>
+          <t>https://www.tiktok.com/@queenofsobrietyuk</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>blondielovinglife</t>
+          <t>tammyleek24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Moringa Capsules By</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:02</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blondielovinglife</t>
+          <t>https://www.tiktok.com/@tammyleek24</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>aqsa1288</t>
+          <t>leahswarbrick0</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Moringa Capsules By</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2124,39 +2124,39 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-26 18:23:09</t>
+          <t>2026-09-01 11:35:03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@aqsa1288</t>
+          <t>https://www.tiktok.com/@leahswarbrick0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>melissaboyle5</t>
+          <t>shaunineale</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:03</t>
+          <t>2026-09-01 11:39:02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@melissaboyle5</t>
+          <t>https://www.tiktok.com/@shaunineale</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>domddo</t>
+          <t>wildwilkinsonsxx</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2208,39 +2208,39 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 11:26:03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@domddo</t>
+          <t>https://www.tiktok.com/@wildwilkinsonsxx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>itsrhi22</t>
+          <t>tashajaynereviews</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2250,34 +2250,34 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itsrhi22</t>
+          <t>https://www.tiktok.com/@tashajaynereviews</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>queenofsobrietyuk</t>
+          <t>ella.jaynefit</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2292,39 +2292,39 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 12:03:03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queenofsobrietyuk</t>
+          <t>https://www.tiktok.com/@ella.jaynefit</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>tammyleek24</t>
+          <t>afshanjindani</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2334,24 +2334,24 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-08-26 12:00:09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tammyleek24</t>
+          <t>https://www.tiktok.com/@afshanjindani</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>leahswarbrick0</t>
+          <t>courtney19xo</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2361,39 +2361,39 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Moringa Capsules By</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:03</t>
+          <t>2026-08-27 18:42:23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@leahswarbrick0</t>
+          <t>https://www.tiktok.com/@courtney19xo</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>shaunineale</t>
+          <t>ambslouise99</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2418,24 +2418,24 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-01 11:39:02</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shaunineale</t>
+          <t>https://www.tiktok.com/@ambslouise99</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>h3ather.mcl</t>
+          <t>jazzzyjay360</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2450,34 +2450,34 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-02 18:18:02</t>
+          <t>2026-09-01 12:14:02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@h3ather.mcl</t>
+          <t>https://www.tiktok.com/@jazzzyjay360</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>wildwilkinsonsxx</t>
+          <t>teheamyytehe</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2502,24 +2502,24 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:03</t>
+          <t>2026-09-01 11:26:02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wildwilkinsonsxx</t>
+          <t>https://www.tiktok.com/@teheamyytehe</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>tashajaynereviews</t>
+          <t>isloo7</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-09-02 18:18:02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2554,14 +2554,14 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tashajaynereviews</t>
+          <t>https://www.tiktok.com/@isloo7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ella.jaynefit</t>
+          <t>vonni349</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2591,19 +2591,19 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ella.jaynefit</t>
+          <t>https://www.tiktok.com/@vonni349</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>afshanjindani</t>
+          <t>sonix_luv</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2628,24 +2628,24 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-26 12:00:09</t>
+          <t>2026-09-01 10:35:21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@afshanjindani</t>
+          <t>https://www.tiktok.com/@sonix_luv</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>eshafatima1421</t>
+          <t>bellavidafacial</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2655,12 +2655,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>50K-100K</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2670,39 +2670,31 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:03</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@eshafatima1421</t>
+          <t>https://www.tiktok.com/@bellavidafacial</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>courtney19xo</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>cornelia.tik.tokshop</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2712,36 +2704,28 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-27 18:42:23</t>
+          <t>2026-09-02 11:49:04</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@courtney19xo</t>
+          <t>https://www.tiktok.com/@cornelia.tik.tokshop</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ambslouise99</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>adefunkemayowaoso1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -2749,41 +2733,33 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-08-25 12:03:26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ambslouise99</t>
+          <t>https://www.tiktok.com/@adefunkemayowaoso1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>jazzzyjay360</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>adeadun77</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2796,39 +2772,31 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-01 12:14:02</t>
+          <t>2026-08-23 16:32:57</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jazzzyjay360</t>
+          <t>https://www.tiktok.com/@adeadun77</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>teheamyytehe</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>bablybegum8</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2838,39 +2806,31 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:02</t>
+          <t>2026-08-24 08:59:43</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teheamyytehe</t>
+          <t>https://www.tiktok.com/@bablybegum8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>isloo7</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>annie.mahn</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2880,24 +2840,24 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-02 18:18:02</t>
+          <t>2026-08-30 18:11:22</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@isloo7</t>
+          <t>https://www.tiktok.com/@annie.mahn</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>vonni349</t>
+          <t>amykirks.1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2907,39 +2867,39 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:03</t>
+          <t>2026-09-01 11:26:03</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vonni349</t>
+          <t>https://www.tiktok.com/@amykirks.1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>sonix_luv</t>
+          <t>amyhart2323</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2949,12 +2909,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2964,24 +2924,24 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-01 10:35:21</t>
+          <t>2026-09-01 11:26:02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sonix_luv</t>
+          <t>https://www.tiktok.com/@amyhart2323</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bellavidafacial</t>
+          <t>alina_marchidan</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2991,12 +2951,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>50K-100K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3011,19 +2971,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bellavidafacial</t>
+          <t>https://www.tiktok.com/@alina_marchidan</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>abeehaamir24</t>
+          <t>akuapapabi364</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -3040,24 +3000,24 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-30 10:05:16</t>
+          <t>2026-08-30 17:55:54</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abeehaamir24</t>
+          <t>https://www.tiktok.com/@akuapapabi364</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>abenaduncan1</t>
+          <t>abeehaamir24</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -3074,24 +3034,24 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-28 12:54:46</t>
+          <t>2026-08-30 10:05:16</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abenaduncan1</t>
+          <t>https://www.tiktok.com/@abeehaamir24</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>adeadun77</t>
+          <t>abenaduncan1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3108,24 +3068,24 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-23 16:32:57</t>
+          <t>2026-08-28 12:54:46</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adeadun77</t>
+          <t>https://www.tiktok.com/@abenaduncan1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1967095zkm</t>
+          <t>heyuser060</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -3137,29 +3097,29 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-22 14:37:48</t>
+          <t>2026-09-01 17:21:20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@1967095zkm</t>
+          <t>https://www.tiktok.com/@heyuser060</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>adefunkemayowaoso1</t>
+          <t>helenbest0</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -3176,27 +3136,31 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-25 12:03:26</t>
+          <t>2026-08-31 06:52:19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adefunkemayowaoso1</t>
+          <t>https://www.tiktok.com/@helenbest0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>akuapapabi364</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>health.wise.media</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
@@ -3210,24 +3174,24 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-30 17:55:54</t>
+          <t>2026-08-24 02:13:31</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@akuapapabi364</t>
+          <t>https://www.tiktok.com/@health.wise.media</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>alina_marchidan</t>
+          <t>hannahtigg1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3237,7 +3201,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3252,24 +3216,24 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@alina_marchidan</t>
+          <t>https://www.tiktok.com/@hannahtigg1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>amykirks.1</t>
+          <t>gretswithnoregrets_</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3277,14 +3241,10 @@
           <t>£0-£50</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3294,36 +3254,28 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:03</t>
+          <t>2026-08-27 18:41:31</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amykirks.1</t>
+          <t>https://www.tiktok.com/@gretswithnoregrets_</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>banksofmay</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>hamidaahmed028</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3336,65 +3288,65 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-29 18:39:38</t>
+          <t>2026-08-27 22:12:14</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@banksofmay</t>
+          <t>https://www.tiktok.com/@hamidaahmed028</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>bablybegum8</t>
+          <t>finda9095</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-24 08:59:43</t>
+          <t>2026-09-01 13:23:27</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bablybegum8</t>
+          <t>https://www.tiktok.com/@finda9095</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>aysh.707</t>
+          <t>fissysbakestudio</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3404,24 +3356,24 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:03</t>
+          <t>2026-08-31 21:21:04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@aysh.707</t>
+          <t>https://www.tiktok.com/@fissysbakestudio</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>annie.mahn</t>
+          <t>ennyluv76</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3438,31 +3390,39 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-30 18:11:22</t>
+          <t>2026-08-30 08:31:46</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@annie.mahn</t>
+          <t>https://www.tiktok.com/@ennyluv76</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>cornelia.tik.tokshop</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
+          <t>erico2006</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3472,24 +3432,24 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-02 11:49:04</t>
+          <t>2026-09-01 22:26:53</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cornelia.tik.tokshop</t>
+          <t>https://www.tiktok.com/@erico2006</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>beebee9537</t>
+          <t>fffysigs0719</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3506,24 +3466,24 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-30 13:59:25</t>
+          <t>2026-08-27 16:41:03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beebee9537</t>
+          <t>https://www.tiktok.com/@fffysigs0719</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>bisbis046</t>
+          <t>famidak1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3540,31 +3500,31 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-03 09:57:56</t>
+          <t>2026-08-27 15:54:45</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bisbis046</t>
+          <t>https://www.tiktok.com/@famidak1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>dailygooods</t>
+          <t>emwinghareadun</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3574,27 +3534,31 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:02</t>
+          <t>2026-08-23 09:11:57</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailygooods</t>
+          <t>https://www.tiktok.com/@emwinghareadun</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>debrazerf</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+          <t>designer_suits</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
@@ -3608,31 +3572,31 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-27 19:29:33</t>
+          <t>2026-08-31 19:59:15</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@debrazerf</t>
+          <t>https://www.tiktok.com/@designer_suits</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>cocoleta7</t>
+          <t>delboy_trotter1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3642,24 +3606,24 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-27 06:32:26</t>
+          <t>2026-08-25 16:12:46</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cocoleta7</t>
+          <t>https://www.tiktok.com/@delboy_trotter1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>claraeg01</t>
+          <t>dlp7831</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3676,36 +3640,28 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-28 08:29:29</t>
+          <t>2026-08-28 08:11:22</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@claraeg01</t>
+          <t>https://www.tiktok.com/@dlp7831</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>clairegriff0</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+          <t>dailygooods</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -3718,39 +3674,31 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-09-04 08:44:02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clairegriff0</t>
+          <t>https://www.tiktok.com/@dailygooods</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>chlo._evans</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+          <t>darkness10145</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3760,7 +3708,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-31 11:52:47</t>
+          <t>2026-09-01 19:15:07</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3770,48 +3718,48 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chlo._evans</t>
+          <t>https://www.tiktok.com/@darkness10145</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>bilqeesajokeade</t>
+          <t>david.adetokunbo2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-04 06:06:55</t>
+          <t>2026-08-26 22:15:55</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bilqeesajokeade</t>
+          <t>https://www.tiktok.com/@david.adetokunbo2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>biglindathompson</t>
+          <t>dimples7219</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3828,36 +3776,28 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-22 13:10:08</t>
+          <t>2026-08-25 08:40:28</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@biglindathompson</t>
+          <t>https://www.tiktok.com/@dimples7219</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>amyhart2323</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>daliayasmin77</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3870,24 +3810,24 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:02</t>
+          <t>2026-08-27 22:31:42</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amyhart2323</t>
+          <t>https://www.tiktok.com/@daliayasmin77</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>jaofficial10</t>
+          <t>debrazerf</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3904,31 +3844,31 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-28 11:15:31</t>
+          <t>2026-08-27 19:29:33</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jaofficial10</t>
+          <t>https://www.tiktok.com/@debrazerf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>jadey032</t>
+          <t>beebee9537</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3938,28 +3878,36 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:03</t>
+          <t>2026-08-30 13:59:25</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jadey032</t>
+          <t>https://www.tiktok.com/@beebee9537</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>itzmallncll</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
+          <t>banksofmay</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3972,100 +3920,92 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-22 20:43:48</t>
+          <t>2026-08-29 18:39:38</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itzmallncll</t>
+          <t>https://www.tiktok.com/@banksofmay</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>itsneema5</t>
+          <t>bisbis046</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-31 16:27:16</t>
+          <t>2026-09-03 09:57:56</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itsneema5</t>
+          <t>https://www.tiktok.com/@bisbis046</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>irrelevantlyliving</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>bilqeesajokeade</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:03</t>
+          <t>2026-09-04 06:06:55</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@irrelevantlyliving</t>
+          <t>https://www.tiktok.com/@bilqeesajokeade</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>is.colonel</t>
+          <t>beauty_by_ash_attire</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -4077,29 +4017,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-05 23:55:02</t>
+          <t>2026-09-02 16:24:16</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@is.colonel</t>
+          <t>https://www.tiktok.com/@beauty_by_ash_attire</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ijvpeanuts</t>
+          <t>chlo._evans</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4109,46 +4049,54 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-01 10:35:04</t>
+          <t>2026-08-31 11:52:47</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ijvpeanuts</t>
+          <t>https://www.tiktok.com/@chlo._evans</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>invalid58</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr"/>
+          <t>clairegriff0</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4158,24 +4106,24 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:16</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@invalid58</t>
+          <t>https://www.tiktok.com/@clairegriff0</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>heyuser060</t>
+          <t>claraeg01</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -4187,70 +4135,78 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-01 17:21:20</t>
+          <t>2026-08-28 08:29:29</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@heyuser060</t>
+          <t>https://www.tiktok.com/@claraeg01</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>helenbest0</t>
+          <t>cocoleta7</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-31 06:52:19</t>
+          <t>2026-08-27 06:32:26</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@helenbest0</t>
+          <t>https://www.tiktok.com/@cocoleta7</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>iamgawjus</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
+          <t>kaurjas608</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4260,7 +4216,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-31 22:07:29</t>
+          <t>2026-09-01 10:36:07</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4270,14 +4226,14 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@iamgawjus</t>
+          <t>https://www.tiktok.com/@kaurjas608</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>homewithlauren_</t>
+          <t>lifesabeach83</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4289,29 +4245,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:03</t>
+          <t>2026-09-01 16:37:08</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@homewithlauren_</t>
+          <t>https://www.tiktok.com/@lifesabeach83</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>health.wise.media</t>
+          <t>lifeofladyluna</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4319,7 +4275,11 @@
           <t>£0-£50</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -4332,24 +4292,24 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-24 02:13:31</t>
+          <t>2026-09-01 11:26:02</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@health.wise.media</t>
+          <t>https://www.tiktok.com/@lifeofladyluna</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>haashim737</t>
+          <t>lexysluxurytravel</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4366,24 +4326,24 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-22 17:53:39</t>
+          <t>2026-08-27 13:48:00</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@haashim737</t>
+          <t>https://www.tiktok.com/@lexysluxurytravel</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>hamidaahmed028</t>
+          <t>laurenandsophiesjigglejo</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4400,36 +4360,28 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-27 22:12:14</t>
+          <t>2026-09-03 10:12:08</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hamidaahmed028</t>
+          <t>https://www.tiktok.com/@laurenandsophiesjigglejo</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>hannahtigg1</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>lady.p3600</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -4442,24 +4394,24 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-08-26 15:34:27</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hannahtigg1</t>
+          <t>https://www.tiktok.com/@lady.p3600</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>erico2006</t>
+          <t>mabes746</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4484,24 +4436,24 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-01 22:26:53</t>
+          <t>2026-09-01 11:35:04</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@erico2006</t>
+          <t>https://www.tiktok.com/@mabes746</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ennyluv76</t>
+          <t>lovemystarsign</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4513,33 +4465,41 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-30 08:31:46</t>
+          <t>2026-09-01 18:46:55</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ennyluv76</t>
+          <t>https://www.tiktok.com/@lovemystarsign</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>emwinghareadun</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr"/>
+          <t>lydiaburnettxx</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>25K-50K</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -4552,31 +4512,27 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-23 09:11:57</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@emwinghareadun</t>
+          <t>https://www.tiktok.com/@lydiaburnettxx</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>gretswithnoregrets_</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>mamarie146</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
@@ -4585,63 +4541,63 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-27 18:41:31</t>
+          <t>2026-09-01 12:24:32</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gretswithnoregrets_</t>
+          <t>https://www.tiktok.com/@mamarie146</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>gallodiopfall</t>
+          <t>mandoki72</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-22 13:48:46</t>
+          <t>2026-08-26 21:17:58</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gallodiopfall</t>
+          <t>https://www.tiktok.com/@mandoki72</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>fffysigs0719</t>
+          <t>manoor_303</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4658,58 +4614,58 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-27 16:41:03</t>
+          <t>2026-08-23 07:41:43</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fffysigs0719</t>
+          <t>https://www.tiktok.com/@manoor_303</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>finda9095</t>
+          <t>martigergeraldine</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-01 13:23:27</t>
+          <t>2026-08-31 11:05:55</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@finda9095</t>
+          <t>https://www.tiktok.com/@martigergeraldine</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>fissysbakestudio</t>
+          <t>maxmeritbackup</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4726,7 +4682,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-31 21:21:04</t>
+          <t>2026-09-01 08:15:09</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4736,55 +4692,55 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fissysbakestudio</t>
+          <t>https://www.tiktok.com/@maxmeritbackup</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>famidak1</t>
+          <t>macouly1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-27 15:54:45</t>
+          <t>2026-08-29 10:33:10</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@famidak1</t>
+          <t>https://www.tiktok.com/@macouly1</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>david.adetokunbo2</t>
+          <t>maisiefinds0</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4794,24 +4750,24 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:55</t>
+          <t>2026-09-04 08:44:04</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@david.adetokunbo2</t>
+          <t>https://www.tiktok.com/@maisiefinds0</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>darkness10145</t>
+          <t>mamacassyxo</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4823,36 +4779,36 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-01 19:15:07</t>
+          <t>2026-08-27 16:05:15</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@darkness10145</t>
+          <t>https://www.tiktok.com/@mamacassyxo</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>daliayasmin77</t>
+          <t>missberry.kayamatauk</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4862,31 +4818,39 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-27 22:31:42</t>
+          <t>2026-08-26 13:15:36</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@daliayasmin77</t>
+          <t>https://www.tiktok.com/@missberry.kayamatauk</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>dlp7831</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
-      <c r="C115" t="inlineStr"/>
+          <t>katiewanderlust</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4896,24 +4860,24 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-28 08:11:22</t>
+          <t>2026-09-01 12:14:02</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dlp7831</t>
+          <t>https://www.tiktok.com/@katiewanderlust</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>dimples7219</t>
+          <t>judyluv42</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4930,31 +4894,27 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-25 08:40:28</t>
+          <t>2026-08-25 10:31:30</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dimples7219</t>
+          <t>https://www.tiktok.com/@judyluv42</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>designer_suits</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>jay25084</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
@@ -4968,31 +4928,31 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-31 19:59:15</t>
+          <t>2026-08-25 10:06:52</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@designer_suits</t>
+          <t>https://www.tiktok.com/@jay25084</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>delboy_trotter1</t>
+          <t>jaofficial10</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5002,28 +4962,36 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-25 16:12:46</t>
+          <t>2026-08-28 11:15:31</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@delboy_trotter1</t>
+          <t>https://www.tiktok.com/@jaofficial10</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>beauty_by_ash_attire</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
-      <c r="C119" t="inlineStr"/>
+          <t>irrelevantlyliving</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -5031,29 +4999,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-02 16:24:16</t>
+          <t>2026-09-01 11:35:03</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beauty_by_ash_attire</t>
+          <t>https://www.tiktok.com/@irrelevantlyliving</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>maisiefinds0</t>
+          <t>is.colonel</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -5070,7 +5038,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:04</t>
+          <t>2026-09-05 23:55:02</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -5080,31 +5048,31 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maisiefinds0</t>
+          <t>https://www.tiktok.com/@is.colonel</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>macouly1</t>
+          <t>kaymama31</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-29 10:33:10</t>
+          <t>2026-08-30 10:22:50</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -5114,14 +5082,14 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@macouly1</t>
+          <t>https://www.tiktok.com/@kaymama31</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>mabes746</t>
+          <t>kiesha11matthews</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5131,7 +5099,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5146,36 +5114,28 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:04</t>
+          <t>2026-09-01 11:35:02</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mabes746</t>
+          <t>https://www.tiktok.com/@kiesha11matthews</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>lydiaburnettxx</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>25K-50K</t>
-        </is>
-      </c>
+          <t>kemotee07</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5188,134 +5148,126 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-08-24 11:49:41</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lydiaburnettxx</t>
+          <t>https://www.tiktok.com/@kemotee07</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>martigergeraldine</t>
+          <t>lady_dash07</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-31 11:05:55</t>
+          <t>2026-09-05 21:11:23</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@martigergeraldine</t>
+          <t>https://www.tiktok.com/@lady_dash07</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>maria_london7</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>itsneema5</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-22 20:57:09</t>
+          <t>2026-08-31 16:27:16</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maria_london7</t>
+          <t>https://www.tiktok.com/@itsneema5</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>mamarie146</t>
+          <t>invalid58</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-01 12:24:32</t>
+          <t>2026-08-28 17:24:16</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mamarie146</t>
+          <t>https://www.tiktok.com/@invalid58</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>midlifehiddengems</t>
+          <t>homewithlauren_</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -5332,31 +5284,39 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30:55</t>
+          <t>2026-09-03 10:12:03</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@midlifehiddengems</t>
+          <t>https://www.tiktok.com/@homewithlauren_</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>maxmeritbackup</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
-      <c r="C128" t="inlineStr"/>
+          <t>ijvpeanuts</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5366,24 +5326,24 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-01 08:15:09</t>
+          <t>2026-09-01 10:35:04</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maxmeritbackup</t>
+          <t>https://www.tiktok.com/@ijvpeanuts</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>mila0701c7c</t>
+          <t>iamgawjus</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -5400,31 +5360,31 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-25 05:11:12</t>
+          <t>2026-08-31 22:07:29</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mila0701c7c</t>
+          <t>https://www.tiktok.com/@iamgawjus</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>mintshopdeals</t>
+          <t>pm37896</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -5434,24 +5394,24 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:03</t>
+          <t>2026-08-28 00:17:19</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mintshopdeals</t>
+          <t>https://www.tiktok.com/@pm37896</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>monpakhi_202</t>
+          <t>ovwomani22</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5468,24 +5428,24 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-08-31 21:10:55</t>
+          <t>2026-08-28 18:04:58</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@monpakhi_202</t>
+          <t>https://www.tiktok.com/@ovwomani22</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>missberry.kayamatauk</t>
+          <t>nutster58</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -5502,24 +5462,24 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-08-26 13:15:36</t>
+          <t>2026-09-01 08:36:44</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@missberry.kayamatauk</t>
+          <t>https://www.tiktok.com/@nutster58</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>manoor_303</t>
+          <t>oluwaseyifunmi988</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -5536,24 +5496,24 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-23 07:41:43</t>
+          <t>2026-08-23 01:54:34</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@manoor_303</t>
+          <t>https://www.tiktok.com/@oluwaseyifunmi988</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>mandoki72</t>
+          <t>notlikeeveryday</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5570,31 +5530,39 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-08-26 21:17:58</t>
+          <t>2026-09-04 08:44:04</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mandoki72</t>
+          <t>https://www.tiktok.com/@notlikeeveryday</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>mamacassyxo</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr"/>
+          <t>niknak190725</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5604,58 +5572,58 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-08-27 16:05:15</t>
+          <t>2026-09-01 12:14:04</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mamacassyxo</t>
+          <t>https://www.tiktok.com/@niknak190725</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>lady_dash07</t>
+          <t>ness69280</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-05 21:11:23</t>
+          <t>2026-09-03 10:09:03</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lady_dash07</t>
+          <t>https://www.tiktok.com/@ness69280</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kemotee07</t>
+          <t>nikkigossal29</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5672,24 +5640,24 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-08-24 11:49:41</t>
+          <t>2026-08-30 17:46:28</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kemotee07</t>
+          <t>https://www.tiktok.com/@nikkigossal29</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>lady.p3600</t>
+          <t>nasirpatel690</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5706,24 +5674,24 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-26 15:34:27</t>
+          <t>2026-08-29 00:44:35</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lady.p3600</t>
+          <t>https://www.tiktok.com/@nasirpatel690</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>judyluv42</t>
+          <t>moon.x280</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -5735,41 +5703,33 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-08-25 10:31:30</t>
+          <t>2026-09-01 18:11:41</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@judyluv42</t>
+          <t>https://www.tiktok.com/@moon.x280</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>lifeofladyluna</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>nellyedwin54</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5782,28 +5742,36 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:02</t>
+          <t>2026-08-30 13:16:24</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifeofladyluna</t>
+          <t>https://www.tiktok.com/@nellyedwin54</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>lexysluxurytravel</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr"/>
+          <t>nathenjump</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D141" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5816,24 +5784,24 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-08-27 13:48:00</t>
+          <t>2026-09-01 14:09:02</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lexysluxurytravel</t>
+          <t>https://www.tiktok.com/@nathenjump</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>laurenandsophiesjigglejo</t>
+          <t>monpakhi_202</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -5850,31 +5818,31 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:08</t>
+          <t>2026-08-31 21:10:55</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@laurenandsophiesjigglejo</t>
+          <t>https://www.tiktok.com/@monpakhi_202</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>liz059019</t>
+          <t>midlifehiddengems</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5884,7 +5852,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-09-03 10:05:06</t>
+          <t>2026-09-04 22:30:55</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5894,14 +5862,14 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@liz059019</t>
+          <t>https://www.tiktok.com/@midlifehiddengems</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>lifesabeach83</t>
+          <t>mila0701c7c</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -5913,33 +5881,41 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-09-01 16:37:08</t>
+          <t>2026-08-25 05:11:12</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifesabeach83</t>
+          <t>https://www.tiktok.com/@mila0701c7c</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>lovemystarsign</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
-      <c r="C145" t="inlineStr"/>
+          <t>princess_wumi</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D145" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5947,44 +5923,36 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-09-01 18:46:55</t>
+          <t>2026-08-29 08:38:03</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lovemystarsign</t>
+          <t>https://www.tiktok.com/@princess_wumi</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kiesha11matthews</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>sameeaafillate</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5994,70 +5962,70 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:02</t>
+          <t>2026-09-04 08:44:04</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kiesha11matthews</t>
+          <t>https://www.tiktok.com/@sameeaafillate</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kaymama31</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr"/>
+          <t>saliya_94</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-30 10:22:50</t>
+          <t>2026-08-24 14:48:07</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaymama31</t>
+          <t>https://www.tiktok.com/@saliya_94</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kaurjas608</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>sabbathina38</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -6065,112 +6033,104 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-09-01 10:36:07</t>
+          <t>2026-08-25 16:09:05</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaurjas608</t>
+          <t>https://www.tiktok.com/@sabbathina38</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>katiewanderlust</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>robbomsnvfv</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-09-01 12:14:02</t>
+          <t>2026-09-01 12:37:06</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@katiewanderlust</t>
+          <t>https://www.tiktok.com/@robbomsnvfv</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>jay25084</t>
+          <t>shahzad.akram041</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-08-25 10:06:52</t>
+          <t>2026-09-03 04:27:22</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jay25084</t>
+          <t>https://www.tiktok.com/@shahzad.akram041</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>pubby1amob</t>
+          <t>samplesquaduk</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -6180,24 +6140,24 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-08-27 18:28:59</t>
+          <t>2026-09-03 10:16:02</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@pubby1amob</t>
+          <t>https://www.tiktok.com/@samplesquaduk</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>princesslizy2010</t>
+          <t>sarah565556</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6205,10 +6165,14 @@
           <t>£0-£50</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -6218,24 +6182,24 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-26 20:03:55</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princesslizy2010</t>
+          <t>https://www.tiktok.com/@sarah565556</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>princess_wumi</t>
+          <t>princesslizy2010</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6243,11 +6207,7 @@
           <t>£0-£50</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6260,58 +6220,58 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-29 08:38:03</t>
+          <t>2026-08-26 20:03:55</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princess_wumi</t>
+          <t>https://www.tiktok.com/@princesslizy2010</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>pm37896</t>
+          <t>remeradiance</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-08-28 00:17:19</t>
+          <t>2026-09-04 19:49:19</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@pm37896</t>
+          <t>https://www.tiktok.com/@remeradiance</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>phillipbennett92</t>
+          <t>remmyc64</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -6328,31 +6288,31 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-08-22 18:41:01</t>
+          <t>2026-08-24 16:17:42</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@phillipbennett92</t>
+          <t>https://www.tiktok.com/@remmyc64</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ovwomani22</t>
+          <t>reviewsbymira44</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -6362,31 +6322,31 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-08-28 18:04:58</t>
+          <t>2026-09-04 08:44:03</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ovwomani22</t>
+          <t>https://www.tiktok.com/@reviewsbymira44</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>nutster58</t>
+          <t>rkh250496ad</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -6396,24 +6356,24 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-09-01 08:36:44</t>
+          <t>2026-08-31 17:54:22</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nutster58</t>
+          <t>https://www.tiktok.com/@rkh250496ad</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>oluwaseyifunmi988</t>
+          <t>queen.of.boys42</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -6430,24 +6390,24 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-08-23 01:54:34</t>
+          <t>2026-08-29 18:27:02</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluwaseyifunmi988</t>
+          <t>https://www.tiktok.com/@queen.of.boys42</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>nikkigossal29</t>
+          <t>pubby1amob</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -6464,24 +6424,24 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-08-30 17:46:28</t>
+          <t>2026-08-27 18:28:59</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nikkigossal29</t>
+          <t>https://www.tiktok.com/@pubby1amob</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ness69280</t>
+          <t>rabiaaman21</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -6498,28 +6458,36 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-09-03 10:09:03</t>
+          <t>2026-09-01 14:27:46</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ness69280</t>
+          <t>https://www.tiktok.com/@rabiaaman21</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>notlikeeveryday</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr"/>
-      <c r="C161" t="inlineStr"/>
+          <t>redbloodchurch1</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D161" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6532,39 +6500,31 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:04</t>
+          <t>2026-08-29 15:02:18</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@notlikeeveryday</t>
+          <t>https://www.tiktok.com/@redbloodchurch1</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>niknak190725</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>soul_rebel4</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6574,28 +6534,36 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-09-01 12:14:04</t>
+          <t>2026-08-25 20:55:08</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@niknak190725</t>
+          <t>https://www.tiktok.com/@soul_rebel4</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>nellyedwin54</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr"/>
-      <c r="C163" t="inlineStr"/>
+          <t>skyviewbm</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D163" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6608,36 +6576,28 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-08-30 13:16:24</t>
+          <t>2026-08-30 16:29:14</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nellyedwin54</t>
+          <t>https://www.tiktok.com/@skyviewbm</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>nathenjump</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>shurlar347</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6650,24 +6610,24 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-09-01 14:09:02</t>
+          <t>2026-08-27 14:53:08</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nathenjump</t>
+          <t>https://www.tiktok.com/@shurlar347</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>moon.x280</t>
+          <t>shume.begum8</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -6679,36 +6639,36 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-09-01 18:11:41</t>
+          <t>2026-09-01 20:33:17</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@moon.x280</t>
+          <t>https://www.tiktok.com/@shume.begum8</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>nasirpatel690</t>
+          <t>shezha17</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6718,31 +6678,31 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-08-29 00:44:35</t>
+          <t>2026-09-01 09:35:01</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nasirpatel690</t>
+          <t>https://www.tiktok.com/@shezha17</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>sarahov72</t>
+          <t>shakirakhan296</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6752,36 +6712,28 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:02</t>
+          <t>2026-08-28 23:38:18</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarahov72</t>
+          <t>https://www.tiktok.com/@shakirakhan296</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>sarah565556</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>sharansaleem</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6794,24 +6746,24 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-08-29 11:45:48</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarah565556</t>
+          <t>https://www.tiktok.com/@sharansaleem</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>samplesquaduk</t>
+          <t>sharonhiggins46</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
@@ -6823,29 +6775,29 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-09-03 10:16:02</t>
+          <t>2026-08-28 20:19:57</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samplesquaduk</t>
+          <t>https://www.tiktok.com/@sharonhiggins46</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>sameeaafillate</t>
+          <t>seana_montgomery61</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -6862,36 +6814,28 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:04</t>
+          <t>2026-09-03 10:12:09</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sameeaafillate</t>
+          <t>https://www.tiktok.com/@seana_montgomery61</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>saliya_94</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>tran.le455</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6904,24 +6848,24 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-08-24 14:48:07</t>
+          <t>2026-08-28 14:45:25</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@saliya_94</t>
+          <t>https://www.tiktok.com/@tran.le455</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>shakirakhan296</t>
+          <t>trending_gists_omoola</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
@@ -6938,24 +6882,24 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-28 23:38:18</t>
+          <t>2026-08-30 21:32:52</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shakirakhan296</t>
+          <t>https://www.tiktok.com/@trending_gists_omoola</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>shahzad.akram041</t>
+          <t>turelove730</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -6972,92 +6916,92 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-09-03 04:27:22</t>
+          <t>2026-09-01 14:36:11</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shahzad.akram041</t>
+          <t>https://www.tiktok.com/@turelove730</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>queen.of.boys42</t>
+          <t>thestoicphoenix</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-08-29 18:27:02</t>
+          <t>2026-09-01 12:03:16</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queen.of.boys42</t>
+          <t>https://www.tiktok.com/@thestoicphoenix</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>rkh250496ad</t>
+          <t>sweetshez1</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-08-31 17:54:22</t>
+          <t>2026-09-05 18:50:17</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rkh250496ad</t>
+          <t>https://www.tiktok.com/@sweetshez1</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>robbomsnvfv</t>
+          <t>tee_y.x</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -7069,109 +7013,101 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-09-01 12:37:06</t>
+          <t>2026-08-31 00:32:51</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@robbomsnvfv</t>
+          <t>https://www.tiktok.com/@tee_y.x</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>sabbathina38</t>
+          <t>sukhdeepkaur343</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-08-25 16:09:05</t>
+          <t>2026-08-27 15:52:29</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sabbathina38</t>
+          <t>https://www.tiktok.com/@sukhdeepkaur343</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>rabiaaman21</t>
+          <t>user2922793729949</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:46</t>
+          <t>2026-09-01 13:14:46</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rabiaaman21</t>
+          <t>https://www.tiktok.com/@user2922793729949</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>redbloodchurch1</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>user26963863682186</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -7184,65 +7120,73 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-08-29 15:02:18</t>
+          <t>2026-08-27 16:29:12</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@redbloodchurch1</t>
+          <t>https://www.tiktok.com/@user26963863682186</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>remeradiance</t>
+          <t>uky1090</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-09-04 19:49:19</t>
+          <t>2026-08-28 01:37:24</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@remeradiance</t>
+          <t>https://www.tiktok.com/@uky1090</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>remmyc64</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr"/>
-      <c r="C181" t="inlineStr"/>
+          <t>ugcbyshristi</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -7252,24 +7196,24 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-08-24 16:17:42</t>
+          <t>2026-09-01 12:03:03</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@remmyc64</t>
+          <t>https://www.tiktok.com/@ugcbyshristi</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>reviewsbymira44</t>
+          <t>user_steeze</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -7281,29 +7225,29 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:03</t>
+          <t>2026-08-30 17:59:09</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@reviewsbymira44</t>
+          <t>https://www.tiktok.com/@user_steeze</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>sukhdeepkaur343</t>
+          <t>user596114145414</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -7320,7 +7264,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-08-27 15:52:29</t>
+          <t>2026-08-28 18:57:06</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -7330,14 +7274,14 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sukhdeepkaur343</t>
+          <t>https://www.tiktok.com/@user596114145414</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>soul_rebel4</t>
+          <t>user4423713561101</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
@@ -7354,36 +7298,28 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-08-25 20:55:08</t>
+          <t>2026-08-28 10:55:03</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@soul_rebel4</t>
+          <t>https://www.tiktok.com/@user4423713561101</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>skyviewbm</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>user4961074980381</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -7396,24 +7332,24 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-08-30 16:29:14</t>
+          <t>2026-08-28 21:55:56</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@skyviewbm</t>
+          <t>https://www.tiktok.com/@user4961074980381</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>shurlar347</t>
+          <t>vivianesoizeau</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -7430,31 +7366,39 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-08-27 14:53:08</t>
+          <t>2026-08-31 16:20:27</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shurlar347</t>
+          <t>https://www.tiktok.com/@vivianesoizeau</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>shezha17</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr"/>
-      <c r="C187" t="inlineStr"/>
+          <t>veronpoks</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -7464,31 +7408,31 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-09-01 09:35:01</t>
+          <t>2026-08-30 14:08:12</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shezha17</t>
+          <t>https://www.tiktok.com/@veronpoks</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>shume.begum8</t>
+          <t>withlakisha</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -7498,24 +7442,24 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-09-01 20:33:17</t>
+          <t>2026-09-04 08:44:03</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shume.begum8</t>
+          <t>https://www.tiktok.com/@withlakisha</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>sharansaleem</t>
+          <t>wellnesswithuzo</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -7532,24 +7476,24 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-08-29 11:45:48</t>
+          <t>2026-08-24 06:46:02</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sharansaleem</t>
+          <t>https://www.tiktok.com/@wellnesswithuzo</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>sharonhiggins46</t>
+          <t>wolfie1830</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
@@ -7566,24 +7510,24 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-08-28 20:19:57</t>
+          <t>2026-09-01 11:52:06</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sharonhiggins46</t>
+          <t>https://www.tiktok.com/@wolfie1830</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>seana_montgomery61</t>
+          <t>xstormx33</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -7595,29 +7539,29 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:09</t>
+          <t>2026-09-01 10:36:21</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@seana_montgomery61</t>
+          <t>https://www.tiktok.com/@xstormx33</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>trending_gists_omoola</t>
+          <t>yxsna_98</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -7634,24 +7578,24 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-08-30 21:32:52</t>
+          <t>2026-08-30 12:46:22</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@trending_gists_omoola</t>
+          <t>https://www.tiktok.com/@yxsna_98</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>turelove730</t>
+          <t>zubairianaz15</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
@@ -7668,745 +7612,15 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-09-01 14:36:11</t>
+          <t>2026-09-05 22:51:12</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@turelove730</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>ugcbyshristi</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>2026-09-01 12:03:03</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@ugcbyshristi</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>tran.le455</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr"/>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>2026-08-28 14:45:25</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@tran.le455</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>sweetshez1</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr"/>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>2026-09-05 18:50:17</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@sweetshez1</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>tee_y.x</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr"/>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>2026-08-31 00:32:51</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@tee_y.x</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>thestoicphoenix</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr"/>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>2026-09-01 12:03:16</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@thestoicphoenix</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>user4423713561101</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr"/>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>2026-08-28 10:55:03</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user4423713561101</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>user2922793729949</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr"/>
-      <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>2026-09-01 13:14:46</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user2922793729949</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>user26963863682186</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr"/>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>2026-08-27 16:29:12</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user26963863682186</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>uky1090</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr"/>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>2026-08-28 01:37:24</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uky1090</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>user_steeze</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr"/>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>2026-08-30 17:59:09</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user_steeze</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>veronpoks</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>2026-08-30 14:08:12</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@veronpoks</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>user596114145414</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr"/>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>2026-08-28 18:57:06</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user596114145414</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>user4961074980381</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr"/>
-      <c r="C206" t="inlineStr"/>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:55:56</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user4961074980381</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>wellnesswithuzo</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr"/>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>2026-08-24 06:46:02</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@wellnesswithuzo</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>vivianesoizeau</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr"/>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>2026-08-31 16:20:27</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@vivianesoizeau</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>wolfie1830</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr"/>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>2026-09-01 11:52:06</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@wolfie1830</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>withlakisha</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr"/>
-      <c r="C210" t="inlineStr"/>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>2026-09-04 08:44:03</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@withlakisha</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>xstormx33</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr"/>
-      <c r="C211" t="inlineStr"/>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>2026-09-01 10:36:21</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@xstormx33</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>yxsna_98</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr"/>
-      <c r="C212" t="inlineStr"/>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>2026-08-30 12:46:22</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@yxsna_98</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>zotouzotou</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr"/>
-      <c r="C213" t="inlineStr"/>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>2026-08-22 13:11:18</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@zotouzotou</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>zubairianaz15</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr"/>
-      <c r="C214" t="inlineStr"/>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>2026-09-05 22:51:12</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@zubairianaz15</t>
         </is>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H193"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -755,17 +755,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>chloefinds37</t>
+          <t>clairlynda.x</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -780,24 +780,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-31 11:31:10</t>
+          <t>2026-09-02 07:40:02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chloefinds37</t>
+          <t>https://www.tiktok.com/@clairlynda.x</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>clairlynda.x</t>
+          <t>luxuryvibe36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>100K-250K</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -817,29 +817,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-02 07:40:02</t>
+          <t>2026-08-31 11:42:10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clairlynda.x</t>
+          <t>https://www.tiktok.com/@luxuryvibe36</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ajahnu</t>
+          <t>muhammadbilal_23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ajahnu</t>
+          <t>https://www.tiktok.com/@muhammadbilal_23</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>luxuryvibe36</t>
+          <t>bam.bam5870</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>100K-250K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -906,24 +906,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-31 11:42:10</t>
+          <t>2026-08-31 11:39:10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@luxuryvibe36</t>
+          <t>https://www.tiktok.com/@bam.bam5870</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>muhammadbilal_23</t>
+          <t>phil_becs</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -948,24 +948,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-02 11:44:03</t>
+          <t>2026-08-31 11:42:09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@muhammadbilal_23</t>
+          <t>https://www.tiktok.com/@phil_becs</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bam.bam5870</t>
+          <t>kelliebelchamber</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -980,34 +980,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-31 11:39:10</t>
+          <t>2026-09-02 18:19:02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bam.bam5870</t>
+          <t>https://www.tiktok.com/@kelliebelchamber</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>phil_becs</t>
+          <t>sh28___</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>100K-250K</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1027,29 +1027,29 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-31 11:42:09</t>
+          <t>2026-08-31 11:57:09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@phil_becs</t>
+          <t>https://www.tiktok.com/@sh28___</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kelliebelchamber</t>
+          <t>hayleybumpbear</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1059,39 +1059,39 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>[] Moringa 1000mg</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-02 18:19:02</t>
+          <t>2026-08-31 12:12:09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kelliebelchamber</t>
+          <t>https://www.tiktok.com/@hayleybumpbear</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>crested_kitten</t>
+          <t>amy.l094</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>[] Moringa 1000mg</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1116,24 +1116,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-31 11:57:10</t>
+          <t>2026-08-31 12:07:10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@crested_kitten</t>
+          <t>https://www.tiktok.com/@amy.l094</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sh28___</t>
+          <t>tonks1988</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>100K-250K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1153,34 +1153,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-31 11:57:09</t>
+          <t>2026-08-31 12:11:09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sh28___</t>
+          <t>https://www.tiktok.com/@tonks1988</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cornishcuppa</t>
+          <t>cornelia.tik.tokshop</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1200,81 +1200,81 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-02 11:44:03</t>
+          <t>2026-09-02 11:49:04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cornishcuppa</t>
+          <t>https://www.tiktok.com/@cornelia.tik.tokshop</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>hayleybumpbear</t>
+          <t>kingdom.wins</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[] Moringa 1000mg</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-31 12:12:09</t>
+          <t>2026-09-02 18:11:02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hayleybumpbear</t>
+          <t>https://www.tiktok.com/@kingdom.wins</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>amy.l094</t>
+          <t>blondie19834</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[] Moringa 1000mg</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-31 12:07:10</t>
+          <t>2026-09-01 09:33:03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1294,29 +1294,29 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amy.l094</t>
+          <t>https://www.tiktok.com/@blondie19834</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tonks1988</t>
+          <t>amb3rin0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-31 12:11:09</t>
+          <t>2026-09-01 09:36:02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tonks1988</t>
+          <t>https://www.tiktok.com/@amb3rin0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cornelia.tik.tokshop</t>
+          <t>emma1503021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1368,24 +1368,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-02 11:49:04</t>
+          <t>2026-09-01 09:39:02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cornelia.tik.tokshop</t>
+          <t>https://www.tiktok.com/@emma1503021</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kingdom.wins</t>
+          <t>veganmamaloves</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1415,34 +1415,34 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kingdom.wins</t>
+          <t>https://www.tiktok.com/@veganmamaloves</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>blondie19834</t>
+          <t>katie_chronicles2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1452,39 +1452,39 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-01 09:33:03</t>
+          <t>2026-09-01 10:54:02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blondie19834</t>
+          <t>https://www.tiktok.com/@katie_chronicles2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sheena.tt</t>
+          <t>lottieeve5</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1494,39 +1494,39 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-01 09:36:04</t>
+          <t>2026-09-01 10:59:04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sheena.tt</t>
+          <t>https://www.tiktok.com/@lottieeve5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>amb3rin0</t>
+          <t>paulatiktokseller</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-01 09:36:02</t>
+          <t>2026-09-01 10:59:02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amb3rin0</t>
+          <t>https://www.tiktok.com/@paulatiktokseller</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>emma1503021</t>
+          <t>hirahannan_official</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>250K-500K</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1578,34 +1578,34 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-01 09:39:02</t>
+          <t>2026-08-29 11:13:09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@emma1503021</t>
+          <t>https://www.tiktok.com/@hirahannan_official</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>veganmamaloves</t>
+          <t>kim.foster1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1620,29 +1620,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-02 18:11:02</t>
+          <t>2026-09-01 11:08:04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@veganmamaloves</t>
+          <t>https://www.tiktok.com/@kim.foster1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>katie_chronicles2</t>
+          <t>blondielovinglife</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1652,81 +1652,81 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Moringa Capsules By</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-01 10:54:02</t>
+          <t>2026-09-01 11:35:02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@katie_chronicles2</t>
+          <t>https://www.tiktok.com/@blondielovinglife</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>lottieeve5</t>
+          <t>aqsa1288</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-01 10:59:04</t>
+          <t>2026-08-26 18:23:09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lottieeve5</t>
+          <t>https://www.tiktok.com/@aqsa1288</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kaytyssidemission</t>
+          <t>domddo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1746,36 +1746,32 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-01 11:02:03</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaytyssidemission</t>
+          <t>https://www.tiktok.com/@domddo</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>paulatiktokseller</t>
+          <t>steviekelise</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>£200-£500</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>£100-£200</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -1788,39 +1784,39 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-01 10:59:02</t>
+          <t>2026-09-07 10:44:00</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@paulatiktokseller</t>
+          <t>https://www.tiktok.com/@steviekelise</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>hirahannan_official</t>
+          <t>itsrhi22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>250K-500K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1830,34 +1826,34 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-29 11:13:09</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hirahannan_official</t>
+          <t>https://www.tiktok.com/@itsrhi22</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>deeqa.luul57</t>
+          <t>queenofsobrietyuk</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1872,39 +1868,39 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-27 12:32:00</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@deeqa.luul57</t>
+          <t>https://www.tiktok.com/@queenofsobrietyuk</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kim.foster1</t>
+          <t>tammyleek24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1914,34 +1910,34 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-01 11:08:04</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kim.foster1</t>
+          <t>https://www.tiktok.com/@tammyleek24</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>blondielovinglife</t>
+          <t>leahswarbrick0</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1956,34 +1952,34 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:02</t>
+          <t>2026-09-01 11:35:03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blondielovinglife</t>
+          <t>https://www.tiktok.com/@leahswarbrick0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>aqsa1288</t>
+          <t>shaunineale</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1993,39 +1989,39 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-26 18:23:09</t>
+          <t>2026-09-01 11:39:02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@aqsa1288</t>
+          <t>https://www.tiktok.com/@shaunineale</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>domddo</t>
+          <t>wildwilkinsonsxx</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2040,39 +2036,39 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 11:26:03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@domddo</t>
+          <t>https://www.tiktok.com/@wildwilkinsonsxx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>itsrhi22</t>
+          <t>tashajaynereviews</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2082,34 +2078,34 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itsrhi22</t>
+          <t>https://www.tiktok.com/@tashajaynereviews</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>queenofsobrietyuk</t>
+          <t>ella.jaynefit</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2124,39 +2120,39 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 12:03:03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queenofsobrietyuk</t>
+          <t>https://www.tiktok.com/@ella.jaynefit</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>tammyleek24</t>
+          <t>courtney19xo</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Psyllium Husk Daily Fiber</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2166,24 +2162,24 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-08-27 18:42:23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tammyleek24</t>
+          <t>https://www.tiktok.com/@courtney19xo</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>leahswarbrick0</t>
+          <t>ambslouise99</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2198,34 +2194,34 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Moringa Capsules By</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:03</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@leahswarbrick0</t>
+          <t>https://www.tiktok.com/@ambslouise99</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>shaunineale</t>
+          <t>teheamyytehe</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2235,7 +2231,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2250,24 +2246,24 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-01 11:39:02</t>
+          <t>2026-09-01 11:26:02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shaunineale</t>
+          <t>https://www.tiktok.com/@teheamyytehe</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>wildwilkinsonsxx</t>
+          <t>jazzzyjay360</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2292,24 +2288,24 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:03</t>
+          <t>2026-09-01 12:14:02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wildwilkinsonsxx</t>
+          <t>https://www.tiktok.com/@jazzzyjay360</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>tashajaynereviews</t>
+          <t>isloo7</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2319,7 +2315,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2334,7 +2330,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-09-02 18:18:02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2344,14 +2340,14 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tashajaynereviews</t>
+          <t>https://www.tiktok.com/@isloo7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ella.jaynefit</t>
+          <t>vonni349</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2361,17 +2357,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2381,19 +2377,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ella.jaynefit</t>
+          <t>https://www.tiktok.com/@vonni349</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>afshanjindani</t>
+          <t>sonix_luv</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2408,7 +2404,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2418,24 +2414,24 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-26 12:00:09</t>
+          <t>2026-09-01 10:35:21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@afshanjindani</t>
+          <t>https://www.tiktok.com/@sonix_luv</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>courtney19xo</t>
+          <t>bellavidafacial</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2445,12 +2441,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>50K-100K</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2460,24 +2456,24 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-27 18:42:23</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@courtney19xo</t>
+          <t>https://www.tiktok.com/@bellavidafacial</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ambslouise99</t>
+          <t>alina_marchidan</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2487,12 +2483,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2502,39 +2498,31 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ambslouise99</t>
+          <t>https://www.tiktok.com/@alina_marchidan</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>teheamyytehe</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>abenaduncan1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2544,24 +2532,24 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:02</t>
+          <t>2026-08-28 12:54:46</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teheamyytehe</t>
+          <t>https://www.tiktok.com/@abenaduncan1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>jazzzyjay360</t>
+          <t>hannahtigg1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2571,7 +2559,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2586,39 +2574,31 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-01 12:14:02</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jazzzyjay360</t>
+          <t>https://www.tiktok.com/@hannahtigg1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>isloo7</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>hamidaahmed028</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2628,120 +2608,96 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-02 18:18:02</t>
+          <t>2026-08-27 22:12:14</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@isloo7</t>
+          <t>https://www.tiktok.com/@hamidaahmed028</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>vonni349</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>fissysbakestudio</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:03</t>
+          <t>2026-08-31 21:21:04</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vonni349</t>
+          <t>https://www.tiktok.com/@fissysbakestudio</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>sonix_luv</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>finda9095</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-01 10:35:21</t>
+          <t>2026-09-01 13:23:27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sonix_luv</t>
+          <t>https://www.tiktok.com/@finda9095</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bellavidafacial</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>50K-100K</t>
-        </is>
-      </c>
+          <t>famidak1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -2749,29 +2705,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-08-27 15:54:45</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bellavidafacial</t>
+          <t>https://www.tiktok.com/@famidak1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>adeadun77</t>
+          <t>fffysigs0719</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2788,28 +2744,36 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-23 16:32:57</t>
+          <t>2026-08-27 16:41:03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adeadun77</t>
+          <t>https://www.tiktok.com/@fffysigs0719</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bablybegum8</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
+          <t>erico2006</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2822,24 +2786,24 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-24 08:59:43</t>
+          <t>2026-09-01 22:26:53</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bablybegum8</t>
+          <t>https://www.tiktok.com/@erico2006</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>annie.mahn</t>
+          <t>ennyluv76</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2856,39 +2820,31 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-30 18:11:22</t>
+          <t>2026-08-30 08:31:46</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@annie.mahn</t>
+          <t>https://www.tiktok.com/@ennyluv76</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>amykirks.1</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>delboy_trotter1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2898,24 +2854,24 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:03</t>
+          <t>2026-08-25 16:12:46</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amykirks.1</t>
+          <t>https://www.tiktok.com/@delboy_trotter1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>amyhart2323</t>
+          <t>designer_suits</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2923,11 +2879,7 @@
           <t>£0-£50</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2940,70 +2892,62 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:02</t>
+          <t>2026-08-31 19:59:15</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amyhart2323</t>
+          <t>https://www.tiktok.com/@designer_suits</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>adefunkemayowaoso1</t>
+          <t>dimples7219</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-25 12:03:26</t>
+          <t>2026-08-25 08:40:28</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adefunkemayowaoso1</t>
+          <t>https://www.tiktok.com/@dimples7219</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>alina_marchidan</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+          <t>dlp7831</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3016,24 +2960,24 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-08-28 08:11:22</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@alina_marchidan</t>
+          <t>https://www.tiktok.com/@dlp7831</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>abeehaamir24</t>
+          <t>daliayasmin77</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -3050,24 +2994,24 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-30 10:05:16</t>
+          <t>2026-08-27 22:31:42</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abeehaamir24</t>
+          <t>https://www.tiktok.com/@daliayasmin77</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>abenaduncan1</t>
+          <t>darkness10145</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3079,29 +3023,29 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-28 12:54:46</t>
+          <t>2026-09-01 19:15:07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abenaduncan1</t>
+          <t>https://www.tiktok.com/@darkness10145</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>heyuser060</t>
+          <t>david.adetokunbo2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -3113,143 +3057,131 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-01 17:21:20</t>
+          <t>2026-08-26 22:15:55</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@heyuser060</t>
+          <t>https://www.tiktok.com/@david.adetokunbo2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>helenbest0</t>
+          <t>debrazerf</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-31 06:52:19</t>
+          <t>2026-08-27 19:29:33</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@helenbest0</t>
+          <t>https://www.tiktok.com/@debrazerf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>health.wise.media</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>bisbis046</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-24 02:13:31</t>
+          <t>2026-09-03 09:57:56</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@health.wise.media</t>
+          <t>https://www.tiktok.com/@bisbis046</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>hannahtigg1</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>bilqeesajokeade</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-04 06:06:55</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hannahtigg1</t>
+          <t>https://www.tiktok.com/@bilqeesajokeade</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>gretswithnoregrets_</t>
+          <t>chlo._evans</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3257,37 +3189,41 @@
           <t>£0-£50</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-27 18:41:31</t>
+          <t>2026-08-31 11:52:47</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gretswithnoregrets_</t>
+          <t>https://www.tiktok.com/@chlo._evans</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>hamidaahmed028</t>
+          <t>claraeg01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3304,7 +3240,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-27 22:12:14</t>
+          <t>2026-08-28 08:29:29</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3314,14 +3250,14 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hamidaahmed028</t>
+          <t>https://www.tiktok.com/@claraeg01</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>finda9095</t>
+          <t>dailygooods</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3333,29 +3269,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-01 13:23:27</t>
+          <t>2026-09-04 08:44:02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@finda9095</t>
+          <t>https://www.tiktok.com/@dailygooods</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>fissysbakestudio</t>
+          <t>cocoleta7</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3372,31 +3308,39 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-31 21:21:04</t>
+          <t>2026-08-27 06:32:26</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fissysbakestudio</t>
+          <t>https://www.tiktok.com/@cocoleta7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ennyluv76</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
+          <t>clairegriff0</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3406,70 +3350,70 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-30 08:31:46</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ennyluv76</t>
+          <t>https://www.tiktok.com/@clairegriff0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>erico2006</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>adefunkemayowaoso1</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-01 22:26:53</t>
+          <t>2026-08-25 12:03:26</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@erico2006</t>
+          <t>https://www.tiktok.com/@adefunkemayowaoso1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>fffysigs0719</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
+          <t>amykirks.1</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3482,58 +3426,66 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-27 16:41:03</t>
+          <t>2026-09-01 11:26:03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fffysigs0719</t>
+          <t>https://www.tiktok.com/@amykirks.1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>famidak1</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
+          <t>amyhart2323</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-27 15:54:45</t>
+          <t>2026-09-01 11:26:02</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@famidak1</t>
+          <t>https://www.tiktok.com/@amyhart2323</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>emwinghareadun</t>
+          <t>akuapapabi364</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3550,31 +3502,27 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-23 09:11:57</t>
+          <t>2026-08-30 17:55:54</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@emwinghareadun</t>
+          <t>https://www.tiktok.com/@akuapapabi364</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>designer_suits</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>annie.mahn</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
@@ -3588,31 +3536,31 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-31 19:59:15</t>
+          <t>2026-08-30 18:11:22</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@designer_suits</t>
+          <t>https://www.tiktok.com/@annie.mahn</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>delboy_trotter1</t>
+          <t>bablybegum8</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3622,28 +3570,36 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-25 16:12:46</t>
+          <t>2026-08-24 08:59:43</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@delboy_trotter1</t>
+          <t>https://www.tiktok.com/@bablybegum8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>dlp7831</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
+          <t>banksofmay</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3656,7 +3612,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-28 08:11:22</t>
+          <t>2026-08-29 18:39:38</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3666,14 +3622,14 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dlp7831</t>
+          <t>https://www.tiktok.com/@banksofmay</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>dailygooods</t>
+          <t>beauty_by_ash_attire</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3685,29 +3641,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:02</t>
+          <t>2026-09-02 16:24:16</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailygooods</t>
+          <t>https://www.tiktok.com/@beauty_by_ash_attire</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>darkness10145</t>
+          <t>beebee9537</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3719,29 +3675,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-01 19:15:07</t>
+          <t>2026-08-30 13:59:25</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@darkness10145</t>
+          <t>https://www.tiktok.com/@beebee9537</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>david.adetokunbo2</t>
+          <t>abeehaamir24</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3758,24 +3714,24 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:55</t>
+          <t>2026-08-30 10:05:16</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@david.adetokunbo2</t>
+          <t>https://www.tiktok.com/@abeehaamir24</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>dimples7219</t>
+          <t>laurenandsophiesjigglejo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3792,24 +3748,24 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-25 08:40:28</t>
+          <t>2026-09-03 10:12:08</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dimples7219</t>
+          <t>https://www.tiktok.com/@laurenandsophiesjigglejo</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>daliayasmin77</t>
+          <t>lady.p3600</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3826,65 +3782,73 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-27 22:31:42</t>
+          <t>2026-08-26 15:34:27</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@daliayasmin77</t>
+          <t>https://www.tiktok.com/@lady.p3600</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>debrazerf</t>
+          <t>lady_dash07</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-27 19:29:33</t>
+          <t>2026-09-05 21:11:23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@debrazerf</t>
+          <t>https://www.tiktok.com/@lady_dash07</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>akuapapabi364</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
+          <t>katiewanderlust</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3894,24 +3858,24 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-30 17:55:54</t>
+          <t>2026-09-01 12:14:02</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@akuapapabi364</t>
+          <t>https://www.tiktok.com/@katiewanderlust</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>banksofmay</t>
+          <t>lifeofladyluna</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3921,7 +3885,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3936,31 +3900,31 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-29 18:39:38</t>
+          <t>2026-09-01 11:26:02</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@banksofmay</t>
+          <t>https://www.tiktok.com/@lifeofladyluna</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>bisbis046</t>
+          <t>lifesabeach83</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3970,92 +3934,108 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-03 09:57:56</t>
+          <t>2026-09-01 16:37:08</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bisbis046</t>
+          <t>https://www.tiktok.com/@lifesabeach83</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>bilqeesajokeade</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
+          <t>kiesha11matthews</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-04 06:06:55</t>
+          <t>2026-09-01 11:35:02</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bilqeesajokeade</t>
+          <t>https://www.tiktok.com/@kiesha11matthews</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>beauty_by_ash_attire</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
+          <t>mabes746</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-02 16:24:16</t>
+          <t>2026-09-01 11:35:04</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beauty_by_ash_attire</t>
+          <t>https://www.tiktok.com/@mabes746</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>beebee9537</t>
+          <t>macouly1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -4072,36 +4052,28 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-30 13:59:25</t>
+          <t>2026-08-29 10:33:10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beebee9537</t>
+          <t>https://www.tiktok.com/@macouly1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>clairegriff0</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+          <t>maisiefinds0</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -4114,100 +4086,92 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-09-04 08:44:04</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clairegriff0</t>
+          <t>https://www.tiktok.com/@maisiefinds0</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>chlo._evans</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+          <t>mamacassyxo</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-31 11:52:47</t>
+          <t>2026-08-27 16:05:15</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chlo._evans</t>
+          <t>https://www.tiktok.com/@mamacassyxo</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>claraeg01</t>
+          <t>mamarie146</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-28 08:29:29</t>
+          <t>2026-09-01 12:24:32</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@claraeg01</t>
+          <t>https://www.tiktok.com/@mamarie146</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>cocoleta7</t>
+          <t>mandoki72</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -4224,24 +4188,24 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-27 06:32:26</t>
+          <t>2026-08-26 21:17:58</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cocoleta7</t>
+          <t>https://www.tiktok.com/@mandoki72</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>lifesabeach83</t>
+          <t>lovemystarsign</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4258,36 +4222,28 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-01 16:37:08</t>
+          <t>2026-09-01 18:46:55</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifesabeach83</t>
+          <t>https://www.tiktok.com/@lovemystarsign</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>lifeofladyluna</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>lexysluxurytravel</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -4300,24 +4256,24 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:02</t>
+          <t>2026-08-27 13:48:00</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifeofladyluna</t>
+          <t>https://www.tiktok.com/@lexysluxurytravel</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>lexysluxurytravel</t>
+          <t>jay25084</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4334,24 +4290,24 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-27 13:48:00</t>
+          <t>2026-08-25 10:06:52</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lexysluxurytravel</t>
+          <t>https://www.tiktok.com/@jay25084</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>laurenandsophiesjigglejo</t>
+          <t>jaofficial10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4368,24 +4324,24 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:08</t>
+          <t>2026-08-28 11:15:31</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@laurenandsophiesjigglejo</t>
+          <t>https://www.tiktok.com/@jaofficial10</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>lady.p3600</t>
+          <t>itsneema5</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4402,24 +4358,24 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-26 15:34:27</t>
+          <t>2026-08-31 16:27:16</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lady.p3600</t>
+          <t>https://www.tiktok.com/@itsneema5</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>lady_dash07</t>
+          <t>is.colonel</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4431,41 +4387,33 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-05 21:11:23</t>
+          <t>2026-09-05 23:55:02</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lady_dash07</t>
+          <t>https://www.tiktok.com/@is.colonel</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>mabes746</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>invalid58</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -4478,58 +4426,66 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:04</t>
+          <t>2026-08-28 17:24:16</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mabes746</t>
+          <t>https://www.tiktok.com/@invalid58</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>lovemystarsign</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr"/>
+          <t>irrelevantlyliving</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-01 18:46:55</t>
+          <t>2026-09-01 11:35:03</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lovemystarsign</t>
+          <t>https://www.tiktok.com/@irrelevantlyliving</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>mamacassyxo</t>
+          <t>iamgawjus</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4546,58 +4502,58 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-27 16:05:15</t>
+          <t>2026-08-31 22:07:29</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mamacassyxo</t>
+          <t>https://www.tiktok.com/@iamgawjus</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>mamarie146</t>
+          <t>judyluv42</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-01 12:24:32</t>
+          <t>2026-08-25 10:31:30</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mamarie146</t>
+          <t>https://www.tiktok.com/@judyluv42</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>manoor_303</t>
+          <t>kemotee07</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4614,7 +4570,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-23 07:41:43</t>
+          <t>2026-08-24 11:49:41</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4624,55 +4580,63 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@manoor_303</t>
+          <t>https://www.tiktok.com/@kemotee07</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>mandoki72</t>
+          <t>kaymama31</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-26 21:17:58</t>
+          <t>2026-08-30 10:22:50</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mandoki72</t>
+          <t>https://www.tiktok.com/@kaymama31</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>martigergeraldine</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr"/>
+          <t>kaurjas608</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4682,7 +4646,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-31 11:05:55</t>
+          <t>2026-09-01 10:36:07</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4692,21 +4656,29 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@martigergeraldine</t>
+          <t>https://www.tiktok.com/@kaurjas608</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>macouly1</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr"/>
+          <t>ijvpeanuts</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4716,70 +4688,62 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-29 10:33:10</t>
+          <t>2026-09-01 10:35:04</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@macouly1</t>
+          <t>https://www.tiktok.com/@ijvpeanuts</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>maisiefinds0</t>
+          <t>heyuser060</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:04</t>
+          <t>2026-09-01 17:21:20</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maisiefinds0</t>
+          <t>https://www.tiktok.com/@heyuser060</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>lydiaburnettxx</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>25K-50K</t>
-        </is>
-      </c>
+          <t>homewithlauren_</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -4792,24 +4756,24 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-09-03 10:12:03</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lydiaburnettxx</t>
+          <t>https://www.tiktok.com/@homewithlauren_</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>missberry.kayamatauk</t>
+          <t>helenbest0</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4821,29 +4785,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-26 13:15:36</t>
+          <t>2026-08-31 06:52:19</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@missberry.kayamatauk</t>
+          <t>https://www.tiktok.com/@helenbest0</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>katiewanderlust</t>
+          <t>health.wise.media</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4851,14 +4815,10 @@
           <t>£0-£50</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4868,39 +4828,31 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-01 12:14:02</t>
+          <t>2026-08-24 02:13:31</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@katiewanderlust</t>
+          <t>https://www.tiktok.com/@health.wise.media</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kaurjas608</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>ovwomani22</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4910,24 +4862,24 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-09-01 10:36:07</t>
+          <t>2026-08-28 18:04:58</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaurjas608</t>
+          <t>https://www.tiktok.com/@ovwomani22</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>jay25084</t>
+          <t>ornellabeauty25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4944,31 +4896,31 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-25 10:06:52</t>
+          <t>2026-09-07 22:41:47</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jay25084</t>
+          <t>https://www.tiktok.com/@ornellabeauty25</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>jaofficial10</t>
+          <t>nutster58</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4978,39 +4930,31 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-28 11:15:31</t>
+          <t>2026-09-01 08:36:44</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jaofficial10</t>
+          <t>https://www.tiktok.com/@nutster58</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>irrelevantlyliving</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>notlikeeveryday</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5020,28 +4964,36 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:03</t>
+          <t>2026-09-04 08:44:04</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@irrelevantlyliving</t>
+          <t>https://www.tiktok.com/@notlikeeveryday</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>is.colonel</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr"/>
-      <c r="C120" t="inlineStr"/>
+          <t>niknak190725</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -5054,70 +5006,62 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-05 23:55:02</t>
+          <t>2026-09-01 12:14:04</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@is.colonel</t>
+          <t>https://www.tiktok.com/@niknak190725</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kaymama31</t>
+          <t>nikkigossal29</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-30 10:22:50</t>
+          <t>2026-08-30 17:46:28</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaymama31</t>
+          <t>https://www.tiktok.com/@nikkigossal29</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kiesha11matthews</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>nellyedwin54</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5130,28 +5074,36 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:02</t>
+          <t>2026-08-30 13:16:24</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kiesha11matthews</t>
+          <t>https://www.tiktok.com/@nellyedwin54</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kemotee07</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
+          <t>nathenjump</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5164,24 +5116,24 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-24 11:49:41</t>
+          <t>2026-09-01 14:09:02</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kemotee07</t>
+          <t>https://www.tiktok.com/@nathenjump</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>judyluv42</t>
+          <t>nasirpatel690</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -5198,24 +5150,24 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-25 10:31:30</t>
+          <t>2026-08-29 00:44:35</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@judyluv42</t>
+          <t>https://www.tiktok.com/@nasirpatel690</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>itsneema5</t>
+          <t>mz.jada0</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -5232,24 +5184,24 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-31 16:27:16</t>
+          <t>2026-09-07 21:15:37</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itsneema5</t>
+          <t>https://www.tiktok.com/@mz.jada0</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>invalid58</t>
+          <t>moon.x280</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5261,29 +5213,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:16</t>
+          <t>2026-09-01 18:11:41</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@invalid58</t>
+          <t>https://www.tiktok.com/@moon.x280</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>homewithlauren_</t>
+          <t>monpakhi_202</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -5300,39 +5252,31 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:03</t>
+          <t>2026-08-31 21:10:55</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@homewithlauren_</t>
+          <t>https://www.tiktok.com/@monpakhi_202</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ijvpeanuts</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>mila0701c7c</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5342,31 +5286,31 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-01 10:35:04</t>
+          <t>2026-08-25 05:11:12</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ijvpeanuts</t>
+          <t>https://www.tiktok.com/@mila0701c7c</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>iamgawjus</t>
+          <t>missberry.kayamatauk</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5376,24 +5320,24 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-31 22:07:29</t>
+          <t>2026-08-26 13:15:36</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@iamgawjus</t>
+          <t>https://www.tiktok.com/@missberry.kayamatauk</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>pm37896</t>
+          <t>martigergeraldine</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5410,24 +5354,24 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-28 00:17:19</t>
+          <t>2026-08-31 11:05:55</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@pm37896</t>
+          <t>https://www.tiktok.com/@martigergeraldine</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ovwomani22</t>
+          <t>maxmeritbackup</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5444,31 +5388,39 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-08-28 18:04:58</t>
+          <t>2026-09-01 08:15:09</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ovwomani22</t>
+          <t>https://www.tiktok.com/@maxmeritbackup</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>nutster58</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr"/>
-      <c r="C132" t="inlineStr"/>
+          <t>lydiaburnettxx</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>25K-50K</t>
+        </is>
+      </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5478,58 +5430,58 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-01 08:36:44</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nutster58</t>
+          <t>https://www.tiktok.com/@lydiaburnettxx</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>oluwaseyifunmi988</t>
+          <t>sabbathina38</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-23 01:54:34</t>
+          <t>2026-08-25 16:09:05</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluwaseyifunmi988</t>
+          <t>https://www.tiktok.com/@sabbathina38</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>notlikeeveryday</t>
+          <t>rkh250496ad</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5546,104 +5498,104 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:04</t>
+          <t>2026-08-31 17:54:22</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@notlikeeveryday</t>
+          <t>https://www.tiktok.com/@rkh250496ad</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>niknak190725</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>robbomsnvfv</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-09-01 12:14:04</t>
+          <t>2026-09-01 12:37:06</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@niknak190725</t>
+          <t>https://www.tiktok.com/@robbomsnvfv</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ness69280</t>
+          <t>shahzad.akram041</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-03 10:09:03</t>
+          <t>2026-09-03 04:27:22</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ness69280</t>
+          <t>https://www.tiktok.com/@shahzad.akram041</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>nikkigossal29</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
-      <c r="C137" t="inlineStr"/>
+          <t>saliya_94</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D137" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5656,31 +5608,39 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-08-30 17:46:28</t>
+          <t>2026-08-24 14:48:07</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nikkigossal29</t>
+          <t>https://www.tiktok.com/@saliya_94</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>nasirpatel690</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr"/>
+          <t>sarah565556</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5690,24 +5650,24 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-29 00:44:35</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nasirpatel690</t>
+          <t>https://www.tiktok.com/@sarah565556</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>moon.x280</t>
+          <t>remmyc64</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -5719,29 +5679,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-09-01 18:11:41</t>
+          <t>2026-08-24 16:17:42</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@moon.x280</t>
+          <t>https://www.tiktok.com/@remmyc64</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>nellyedwin54</t>
+          <t>queen.of.boys42</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5758,36 +5718,28 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-08-30 13:16:24</t>
+          <t>2026-08-29 18:27:02</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nellyedwin54</t>
+          <t>https://www.tiktok.com/@queen.of.boys42</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>nathenjump</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>rabiaaman21</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5800,28 +5752,36 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-09-01 14:09:02</t>
+          <t>2026-09-01 14:27:46</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nathenjump</t>
+          <t>https://www.tiktok.com/@rabiaaman21</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>monpakhi_202</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr"/>
+          <t>redbloodchurch1</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D142" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5834,62 +5794,70 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-31 21:10:55</t>
+          <t>2026-08-29 15:02:18</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@monpakhi_202</t>
+          <t>https://www.tiktok.com/@redbloodchurch1</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>maxmeritbackup</t>
+          <t>remeradiance</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-09-01 08:15:09</t>
+          <t>2026-09-04 19:49:19</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maxmeritbackup</t>
+          <t>https://www.tiktok.com/@remeradiance</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>mila0701c7c</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
-      <c r="C144" t="inlineStr"/>
+          <t>princess_wumi</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D144" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5902,24 +5870,24 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-08-25 05:11:12</t>
+          <t>2026-08-29 08:38:03</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mila0701c7c</t>
+          <t>https://www.tiktok.com/@princess_wumi</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>princess_wumi</t>
+          <t>princesslizy2010</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5927,11 +5895,7 @@
           <t>£0-£50</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5944,31 +5908,31 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-08-29 08:38:03</t>
+          <t>2026-08-26 20:03:55</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princess_wumi</t>
+          <t>https://www.tiktok.com/@princesslizy2010</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>sameeaafillate</t>
+          <t>pubby1amob</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5978,36 +5942,28 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:04</t>
+          <t>2026-08-27 18:28:59</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sameeaafillate</t>
+          <t>https://www.tiktok.com/@pubby1amob</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>saliya_94</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>pm37896</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6020,62 +5976,70 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-24 14:48:07</t>
+          <t>2026-08-28 00:17:19</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@saliya_94</t>
+          <t>https://www.tiktok.com/@pm37896</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>sabbathina38</t>
+          <t>soul_rebel4</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-08-25 16:09:05</t>
+          <t>2026-08-25 20:55:08</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sabbathina38</t>
+          <t>https://www.tiktok.com/@soul_rebel4</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>robbomsnvfv</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
-      <c r="C149" t="inlineStr"/>
+          <t>skyviewbm</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D149" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6083,70 +6047,70 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-09-01 12:37:06</t>
+          <t>2026-08-30 16:29:14</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@robbomsnvfv</t>
+          <t>https://www.tiktok.com/@skyviewbm</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>shahzad.akram041</t>
+          <t>shume.begum8</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-09-03 04:27:22</t>
+          <t>2026-09-01 20:33:17</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shahzad.akram041</t>
+          <t>https://www.tiktok.com/@shume.begum8</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>samplesquaduk</t>
+          <t>shurlar347</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -6156,36 +6120,28 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-09-03 10:16:02</t>
+          <t>2026-08-27 14:53:08</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samplesquaduk</t>
+          <t>https://www.tiktok.com/@shurlar347</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>sarah565556</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>shezha17</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -6198,31 +6154,27 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 09:35:01</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarah565556</t>
+          <t>https://www.tiktok.com/@shezha17</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>princesslizy2010</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>shakirakhan296</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
@@ -6236,92 +6188,92 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-26 20:03:55</t>
+          <t>2026-08-28 23:38:18</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princesslizy2010</t>
+          <t>https://www.tiktok.com/@shakirakhan296</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>remeradiance</t>
+          <t>sharansaleem</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-09-04 19:49:19</t>
+          <t>2026-08-29 11:45:48</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@remeradiance</t>
+          <t>https://www.tiktok.com/@sharansaleem</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>remmyc64</t>
+          <t>sharonhiggins46</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-08-24 16:17:42</t>
+          <t>2026-08-28 20:19:57</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@remmyc64</t>
+          <t>https://www.tiktok.com/@sharonhiggins46</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>reviewsbymira44</t>
+          <t>seana_montgomery61</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -6338,24 +6290,24 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:03</t>
+          <t>2026-09-03 10:12:09</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@reviewsbymira44</t>
+          <t>https://www.tiktok.com/@seana_montgomery61</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>rkh250496ad</t>
+          <t>tran.le455</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
@@ -6372,24 +6324,24 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-08-31 17:54:22</t>
+          <t>2026-08-28 14:45:25</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rkh250496ad</t>
+          <t>https://www.tiktok.com/@tran.le455</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>queen.of.boys42</t>
+          <t>trending_gists_omoola</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -6406,7 +6358,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-08-29 18:27:02</t>
+          <t>2026-08-30 21:32:52</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -6416,124 +6368,116 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queen.of.boys42</t>
+          <t>https://www.tiktok.com/@trending_gists_omoola</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>pubby1amob</t>
+          <t>turelove730</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-08-27 18:28:59</t>
+          <t>2026-09-01 14:36:11</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@pubby1amob</t>
+          <t>https://www.tiktok.com/@turelove730</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rabiaaman21</t>
+          <t>thestoicphoenix</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:46</t>
+          <t>2026-09-01 12:03:16</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rabiaaman21</t>
+          <t>https://www.tiktok.com/@thestoicphoenix</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>redbloodchurch1</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>sweetshez1</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-29 15:02:18</t>
+          <t>2026-09-05 18:50:17</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@redbloodchurch1</t>
+          <t>https://www.tiktok.com/@sweetshez1</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>soul_rebel4</t>
+          <t>tee_y.x</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -6550,36 +6494,28 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-08-25 20:55:08</t>
+          <t>2026-08-31 00:32:51</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@soul_rebel4</t>
+          <t>https://www.tiktok.com/@tee_y.x</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>skyviewbm</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>sukhdeepkaur343</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6592,58 +6528,58 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-08-30 16:29:14</t>
+          <t>2026-08-27 15:52:29</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@skyviewbm</t>
+          <t>https://www.tiktok.com/@sukhdeepkaur343</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>shurlar347</t>
+          <t>user2922793729949</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-08-27 14:53:08</t>
+          <t>2026-09-01 13:14:46</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shurlar347</t>
+          <t>https://www.tiktok.com/@user2922793729949</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>shume.begum8</t>
+          <t>user26963863682186</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -6660,31 +6596,31 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-09-01 20:33:17</t>
+          <t>2026-08-27 16:29:12</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shume.begum8</t>
+          <t>https://www.tiktok.com/@user26963863682186</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>shezha17</t>
+          <t>uky1090</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6694,31 +6630,39 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-01 09:35:01</t>
+          <t>2026-08-28 01:37:24</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shezha17</t>
+          <t>https://www.tiktok.com/@uky1090</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>shakirakhan296</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr"/>
-      <c r="C167" t="inlineStr"/>
+          <t>ugcbyshristi</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6728,41 +6672,41 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-08-28 23:38:18</t>
+          <t>2026-09-01 12:03:03</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shakirakhan296</t>
+          <t>https://www.tiktok.com/@ugcbyshristi</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>sharansaleem</t>
+          <t>user_steeze</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-08-29 11:45:48</t>
+          <t>2026-08-30 17:59:09</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -6772,55 +6716,55 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sharansaleem</t>
+          <t>https://www.tiktok.com/@user_steeze</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>sharonhiggins46</t>
+          <t>user596114145414</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-08-28 20:19:57</t>
+          <t>2026-08-28 18:57:06</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sharonhiggins46</t>
+          <t>https://www.tiktok.com/@user596114145414</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>seana_montgomery61</t>
+          <t>user4423713561101</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -6830,24 +6774,24 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:09</t>
+          <t>2026-08-28 10:55:03</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@seana_montgomery61</t>
+          <t>https://www.tiktok.com/@user4423713561101</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>tran.le455</t>
+          <t>user4961074980381</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -6864,24 +6808,24 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-08-28 14:45:25</t>
+          <t>2026-08-28 21:55:56</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tran.le455</t>
+          <t>https://www.tiktok.com/@user4961074980381</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>trending_gists_omoola</t>
+          <t>vivianesoizeau</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
@@ -6898,7 +6842,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-30 21:32:52</t>
+          <t>2026-08-31 16:20:27</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -6908,48 +6852,56 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@trending_gists_omoola</t>
+          <t>https://www.tiktok.com/@vivianesoizeau</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>turelove730</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr"/>
-      <c r="C173" t="inlineStr"/>
+          <t>veronpoks</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-09-01 14:36:11</t>
+          <t>2026-08-30 14:08:12</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@turelove730</t>
+          <t>https://www.tiktok.com/@veronpoks</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>thestoicphoenix</t>
+          <t>withlakisha</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -6961,80 +6913,80 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:16</t>
+          <t>2026-09-04 08:44:03</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thestoicphoenix</t>
+          <t>https://www.tiktok.com/@withlakisha</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>sweetshez1</t>
+          <t>wellnesswithuzo</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-09-05 18:50:17</t>
+          <t>2026-08-24 06:46:02</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sweetshez1</t>
+          <t>https://www.tiktok.com/@wellnesswithuzo</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>tee_y.x</t>
+          <t>wolfie1830</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-08-31 00:32:51</t>
+          <t>2026-09-01 11:52:06</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -7044,599 +6996,107 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tee_y.x</t>
+          <t>https://www.tiktok.com/@wolfie1830</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>sukhdeepkaur343</t>
+          <t>xstormx33</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-08-27 15:52:29</t>
+          <t>2026-09-01 10:36:21</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sukhdeepkaur343</t>
+          <t>https://www.tiktok.com/@xstormx33</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>user2922793729949</t>
+          <t>yxsna_98</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-09-01 13:14:46</t>
+          <t>2026-08-30 12:46:22</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2922793729949</t>
+          <t>https://www.tiktok.com/@yxsna_98</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>user26963863682186</t>
+          <t>zubairianaz15</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-08-27 16:29:12</t>
+          <t>2026-09-05 22:51:12</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user26963863682186</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>uky1090</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr"/>
-      <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-08-28 01:37:24</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uky1090</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>ugcbyshristi</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-09-01 12:03:03</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@ugcbyshristi</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>user_steeze</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr"/>
-      <c r="C182" t="inlineStr"/>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-08-30 17:59:09</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user_steeze</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>user596114145414</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr"/>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-08-28 18:57:06</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user596114145414</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>user4423713561101</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr"/>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-08-28 10:55:03</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user4423713561101</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>user4961074980381</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr"/>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:55:56</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user4961074980381</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>vivianesoizeau</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr"/>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-08-31 16:20:27</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@vivianesoizeau</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>veronpoks</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-08-30 14:08:12</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@veronpoks</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>withlakisha</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr"/>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-09-04 08:44:03</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@withlakisha</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>wellnesswithuzo</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr"/>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-08-24 06:46:02</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@wellnesswithuzo</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>wolfie1830</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr"/>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-09-01 11:52:06</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@wolfie1830</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>xstormx33</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr"/>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-09-01 10:36:21</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@xstormx33</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>yxsna_98</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr"/>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2026-08-30 12:46:22</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@yxsna_98</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>zubairianaz15</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr"/>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>2026-09-05 22:51:12</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@zubairianaz15</t>
         </is>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -587,12 +587,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>lewistiktokshopdeals</t>
+          <t>queennorxy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -602,34 +602,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:09</t>
+          <t>2026-08-31 11:31:09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lewistiktokshopdeals</t>
+          <t>https://www.tiktok.com/@queennorxy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>queennorxy</t>
+          <t>fypdavesdeals</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -639,39 +639,39 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-31 11:31:09</t>
+          <t>2026-08-31 11:31:10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queennorxy</t>
+          <t>https://www.tiktok.com/@fypdavesdeals</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fypdavesdeals</t>
+          <t>krystal_kei</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -686,76 +686,76 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-31 11:31:10</t>
+          <t>2026-08-27 08:36:58</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fypdavesdeals</t>
+          <t>https://www.tiktok.com/@krystal_kei</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>krystal_kei</t>
+          <t>clairlynda.x</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-27 08:36:58</t>
+          <t>2026-09-02 07:40:02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@krystal_kei</t>
+          <t>https://www.tiktok.com/@clairlynda.x</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>clairlynda.x</t>
+          <t>luxuryvibe36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>100K-250K</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -775,29 +775,29 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-02 07:40:02</t>
+          <t>2026-08-31 11:42:10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clairlynda.x</t>
+          <t>https://www.tiktok.com/@luxuryvibe36</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>luxuryvibe36</t>
+          <t>muhammadbilal_23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>100K-250K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -817,29 +817,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-31 11:42:10</t>
+          <t>2026-09-02 11:44:03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@luxuryvibe36</t>
+          <t>https://www.tiktok.com/@muhammadbilal_23</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>muhammadbilal_23</t>
+          <t>bam.bam5870</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -849,39 +849,39 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-02 11:44:03</t>
+          <t>2026-08-31 11:39:10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@muhammadbilal_23</t>
+          <t>https://www.tiktok.com/@bam.bam5870</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bam.bam5870</t>
+          <t>phil_becs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -891,39 +891,39 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-31 11:39:10</t>
+          <t>2026-08-31 11:42:09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bam.bam5870</t>
+          <t>https://www.tiktok.com/@phil_becs</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>phil_becs</t>
+          <t>kelliebelchamber</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -948,24 +948,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-31 11:42:09</t>
+          <t>2026-09-02 18:19:02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@phil_becs</t>
+          <t>https://www.tiktok.com/@kelliebelchamber</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kelliebelchamber</t>
+          <t>sh28___</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -975,39 +975,39 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>100K-250K</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-02 18:19:02</t>
+          <t>2026-08-31 11:57:09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kelliebelchamber</t>
+          <t>https://www.tiktok.com/@sh28___</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sh28___</t>
+          <t>hayleybumpbear</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>100K-250K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>[] Moringa 1000mg</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1032,24 +1032,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-31 11:57:09</t>
+          <t>2026-08-31 12:12:09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sh28___</t>
+          <t>https://www.tiktok.com/@hayleybumpbear</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hayleybumpbear</t>
+          <t>amy.l094</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1069,29 +1069,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-31 12:12:09</t>
+          <t>2026-08-31 12:07:10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hayleybumpbear</t>
+          <t>https://www.tiktok.com/@amy.l094</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>amy.l094</t>
+          <t>tonks1988</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[] Moringa 1000mg</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-31 12:07:10</t>
+          <t>2026-08-31 12:11:09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amy.l094</t>
+          <t>https://www.tiktok.com/@tonks1988</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tonks1988</t>
+          <t>eminence4009</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1158,17 +1158,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-31 12:11:09</t>
+          <t>2026-09-08 10:27:05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tonks1988</t>
+          <t>https://www.tiktok.com/@eminence4009</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>katie_chronicles2</t>
+          <t>lottieeve5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1452,24 +1452,24 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-01 10:54:02</t>
+          <t>2026-09-01 10:59:04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@katie_chronicles2</t>
+          <t>https://www.tiktok.com/@lottieeve5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>lottieeve5</t>
+          <t>hirahannan_official</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>250K-500K</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1494,24 +1494,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-01 10:59:04</t>
+          <t>2026-08-29 11:13:09</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lottieeve5</t>
+          <t>https://www.tiktok.com/@hirahannan_official</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>paulatiktokseller</t>
+          <t>francesslee0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-01 10:59:02</t>
+          <t>2026-09-08 06:50:27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@paulatiktokseller</t>
+          <t>https://www.tiktok.com/@francesslee0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hirahannan_official</t>
+          <t>kim.foster1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>250K-500K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1578,24 +1578,24 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-29 11:13:09</t>
+          <t>2026-09-01 11:08:04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hirahannan_official</t>
+          <t>https://www.tiktok.com/@kim.foster1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kim.foster1</t>
+          <t>blondielovinglife</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1605,39 +1605,39 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Moringa Capsules By</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-01 11:08:04</t>
+          <t>2026-09-01 11:35:02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kim.foster1</t>
+          <t>https://www.tiktok.com/@blondielovinglife</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>blondielovinglife</t>
+          <t>domddo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1652,34 +1652,34 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Moringa Capsules By</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:02</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blondielovinglife</t>
+          <t>https://www.tiktok.com/@domddo</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>aqsa1288</t>
+          <t>steviekelise</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1687,11 +1687,7 @@
           <t>£100-£200</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -1699,29 +1695,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-26 18:23:09</t>
+          <t>2026-09-07 10:44:00</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@aqsa1288</t>
+          <t>https://www.tiktok.com/@steviekelise</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>domddo</t>
+          <t>queenofsobrietyuk</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1751,30 +1747,34 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@domddo</t>
+          <t>https://www.tiktok.com/@queenofsobrietyuk</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>steviekelise</t>
+          <t>tammyleek24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>£100-£200</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>£50-£100</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1784,76 +1784,76 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-07 10:44:00</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@steviekelise</t>
+          <t>https://www.tiktok.com/@tammyleek24</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>itsrhi22</t>
+          <t>leahswarbrick0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Moringa Capsules By</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 11:35:03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itsrhi22</t>
+          <t>https://www.tiktok.com/@leahswarbrick0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>queenofsobrietyuk</t>
+          <t>wildwilkinsonsxx</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1868,39 +1868,39 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 11:26:03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queenofsobrietyuk</t>
+          <t>https://www.tiktok.com/@wildwilkinsonsxx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tammyleek24</t>
+          <t>tashajaynereviews</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1910,24 +1910,24 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tammyleek24</t>
+          <t>https://www.tiktok.com/@tashajaynereviews</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>leahswarbrick0</t>
+          <t>ella.jaynefit</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1942,34 +1942,34 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Moringa Capsules By</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:03</t>
+          <t>2026-09-01 12:03:03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@leahswarbrick0</t>
+          <t>https://www.tiktok.com/@ella.jaynefit</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>shaunineale</t>
+          <t>ambslouise99</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1994,24 +1994,24 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-01 11:39:02</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shaunineale</t>
+          <t>https://www.tiktok.com/@ambslouise99</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>wildwilkinsonsxx</t>
+          <t>jazzzyjay360</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:03</t>
+          <t>2026-09-01 12:14:02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wildwilkinsonsxx</t>
+          <t>https://www.tiktok.com/@jazzzyjay360</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tashajaynereviews</t>
+          <t>teheamyytehe</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2078,24 +2078,24 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-09-01 11:26:02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tashajaynereviews</t>
+          <t>https://www.tiktok.com/@teheamyytehe</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ella.jaynefit</t>
+          <t>isloo7</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:03</t>
+          <t>2026-09-02 18:18:02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2130,14 +2130,14 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ella.jaynefit</t>
+          <t>https://www.tiktok.com/@isloo7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>courtney19xo</t>
+          <t>vonni349</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2152,34 +2152,34 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-27 18:42:23</t>
+          <t>2026-09-01 12:03:03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@courtney19xo</t>
+          <t>https://www.tiktok.com/@vonni349</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ambslouise99</t>
+          <t>sonix_luv</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2204,24 +2204,24 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 10:35:21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ambslouise99</t>
+          <t>https://www.tiktok.com/@sonix_luv</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>teheamyytehe</t>
+          <t>bellavidafacial</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>50K-100K</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2246,39 +2246,31 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:02</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teheamyytehe</t>
+          <t>https://www.tiktok.com/@bellavidafacial</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>jazzzyjay360</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>bellasbeauty07</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2288,36 +2280,28 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-01 12:14:02</t>
+          <t>2026-09-08 10:16:05</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jazzzyjay360</t>
+          <t>https://www.tiktok.com/@bellasbeauty07</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>isloo7</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>beauty_by_ash_attire</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -2325,86 +2309,70 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-02 18:18:02</t>
+          <t>2026-09-02 16:24:16</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@isloo7</t>
+          <t>https://www.tiktok.com/@beauty_by_ash_attire</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>vonni349</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>beebee9537</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:03</t>
+          <t>2026-08-30 13:59:25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vonni349</t>
+          <t>https://www.tiktok.com/@beebee9537</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>sonix_luv</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>abenaduncan1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2414,24 +2382,24 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-01 10:35:21</t>
+          <t>2026-08-28 12:54:46</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sonix_luv</t>
+          <t>https://www.tiktok.com/@abenaduncan1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bellavidafacial</t>
+          <t>amyhart2323</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2441,12 +2409,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>50K-100K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2456,66 +2424,58 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-09-01 11:26:02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bellavidafacial</t>
+          <t>https://www.tiktok.com/@amyhart2323</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>alina_marchidan</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+          <t>adefunkemayowaoso1</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-08-25 12:03:26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@alina_marchidan</t>
+          <t>https://www.tiktok.com/@adefunkemayowaoso1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>abenaduncan1</t>
+          <t>abeehaamir24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2532,36 +2492,28 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-28 12:54:46</t>
+          <t>2026-08-30 10:05:16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abenaduncan1</t>
+          <t>https://www.tiktok.com/@abeehaamir24</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>hannahtigg1</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>fissysbakestudio</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2574,58 +2526,58 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-08-31 21:21:04</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hannahtigg1</t>
+          <t>https://www.tiktok.com/@fissysbakestudio</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>hamidaahmed028</t>
+          <t>finda9095</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-27 22:12:14</t>
+          <t>2026-09-01 13:23:27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hamidaahmed028</t>
+          <t>https://www.tiktok.com/@finda9095</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>fissysbakestudio</t>
+          <t>fffysigs0719</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2642,24 +2594,24 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-31 21:21:04</t>
+          <t>2026-08-27 16:41:03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fissysbakestudio</t>
+          <t>https://www.tiktok.com/@fffysigs0719</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>finda9095</t>
+          <t>famidak1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2676,62 +2628,70 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-01 13:23:27</t>
+          <t>2026-08-27 15:54:45</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@finda9095</t>
+          <t>https://www.tiktok.com/@famidak1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>famidak1</t>
+          <t>ennyluv76</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-27 15:54:45</t>
+          <t>2026-08-30 08:31:46</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@famidak1</t>
+          <t>https://www.tiktok.com/@ennyluv76</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>fffysigs0719</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
+          <t>erico2006</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2744,24 +2704,24 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-27 16:41:03</t>
+          <t>2026-09-01 22:26:53</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fffysigs0719</t>
+          <t>https://www.tiktok.com/@erico2006</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>erico2006</t>
+          <t>designer_suits</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2769,11 +2729,7 @@
           <t>£0-£50</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2786,24 +2742,24 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-01 22:26:53</t>
+          <t>2026-08-31 19:59:15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@erico2006</t>
+          <t>https://www.tiktok.com/@designer_suits</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ennyluv76</t>
+          <t>elizabetho001</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2820,17 +2776,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-30 08:31:46</t>
+          <t>2026-09-08 17:27:54</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ennyluv76</t>
+          <t>https://www.tiktok.com/@elizabetho001</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2815,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2871,14 +2827,10 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>designer_suits</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>dlp7831</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
@@ -2892,17 +2844,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-31 19:59:15</t>
+          <t>2026-08-28 08:11:22</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@designer_suits</t>
+          <t>https://www.tiktok.com/@dlp7831</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2883,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2943,14 +2895,14 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>dlp7831</t>
+          <t>dailygooods</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2960,17 +2912,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-28 08:11:22</t>
+          <t>2026-09-04 08:44:02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dlp7831</t>
+          <t>https://www.tiktok.com/@dailygooods</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2951,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3033,7 +2985,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3067,7 +3019,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3101,7 +3053,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3135,7 +3087,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3147,34 +3099,42 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>bilqeesajokeade</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
+          <t>clairegriff0</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-04 06:06:55</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bilqeesajokeade</t>
+          <t>https://www.tiktok.com/@clairegriff0</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3171,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3223,48 +3183,48 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>claraeg01</t>
+          <t>bilqeesajokeade</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-28 08:29:29</t>
+          <t>2026-09-04 06:06:55</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@claraeg01</t>
+          <t>https://www.tiktok.com/@bilqeesajokeade</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>dailygooods</t>
+          <t>cocoleta7</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3274,31 +3234,31 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:02</t>
+          <t>2026-08-27 06:32:26</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailygooods</t>
+          <t>https://www.tiktok.com/@cocoleta7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>cocoleta7</t>
+          <t>craftyjo72</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3308,39 +3268,31 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-27 06:32:26</t>
+          <t>2026-09-08 10:27:04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cocoleta7</t>
+          <t>https://www.tiktok.com/@craftyjo72</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>clairegriff0</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+          <t>claraeg01</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3350,73 +3302,65 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-08-28 08:29:29</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clairegriff0</t>
+          <t>https://www.tiktok.com/@claraeg01</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>adefunkemayowaoso1</t>
+          <t>akuapapabi364</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-25 12:03:26</t>
+          <t>2026-08-30 17:55:54</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adefunkemayowaoso1</t>
+          <t>https://www.tiktok.com/@akuapapabi364</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>amykirks.1</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>anila_pk_uk</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3426,24 +3370,24 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:03</t>
+          <t>2026-09-08 14:43:04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amykirks.1</t>
+          <t>https://www.tiktok.com/@anila_pk_uk</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>amyhart2323</t>
+          <t>amykirks.1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3468,28 +3412,36 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:02</t>
+          <t>2026-09-01 11:26:03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amyhart2323</t>
+          <t>https://www.tiktok.com/@amykirks.1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>akuapapabi364</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
+          <t>banksofmay</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3502,17 +3454,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-30 17:55:54</t>
+          <t>2026-08-29 18:39:38</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@akuapapabi364</t>
+          <t>https://www.tiktok.com/@banksofmay</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3493,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3553,56 +3505,48 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>bablybegum8</t>
+          <t>be__beauty1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-24 08:59:43</t>
+          <t>2026-09-08 17:18:23</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bablybegum8</t>
+          <t>https://www.tiktok.com/@be__beauty1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>banksofmay</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>is.colonel</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3612,31 +3556,31 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-29 18:39:38</t>
+          <t>2026-09-05 23:55:02</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@banksofmay</t>
+          <t>https://www.tiktok.com/@is.colonel</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>beauty_by_ash_attire</t>
+          <t>heyuser060</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3646,24 +3590,24 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-02 16:24:16</t>
+          <t>2026-09-01 17:21:20</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beauty_by_ash_attire</t>
+          <t>https://www.tiktok.com/@heyuser060</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>beebee9537</t>
+          <t>homewithlauren_</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3680,58 +3624,58 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-30 13:59:25</t>
+          <t>2026-09-03 10:12:03</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beebee9537</t>
+          <t>https://www.tiktok.com/@homewithlauren_</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>abeehaamir24</t>
+          <t>lady_dash07</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-30 10:05:16</t>
+          <t>2026-09-05 21:11:23</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abeehaamir24</t>
+          <t>https://www.tiktok.com/@lady_dash07</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>laurenandsophiesjigglejo</t>
+          <t>lady.p3600</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3748,107 +3692,107 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:08</t>
+          <t>2026-08-26 15:34:27</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@laurenandsophiesjigglejo</t>
+          <t>https://www.tiktok.com/@lady.p3600</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>lady.p3600</t>
+          <t>kaymama31</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-26 15:34:27</t>
+          <t>2026-08-30 10:22:50</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lady.p3600</t>
+          <t>https://www.tiktok.com/@kaymama31</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>lady_dash07</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
+          <t>kiesha11matthews</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-05 21:11:23</t>
+          <t>2026-09-01 11:35:02</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lady_dash07</t>
+          <t>https://www.tiktok.com/@kiesha11matthews</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>katiewanderlust</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>jaofficial10</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3858,36 +3802,28 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-01 12:14:02</t>
+          <t>2026-08-28 11:15:31</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@katiewanderlust</t>
+          <t>https://www.tiktok.com/@jaofficial10</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>lifeofladyluna</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>lexysluxurytravel</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3900,28 +3836,36 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:02</t>
+          <t>2026-08-27 13:48:00</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifeofladyluna</t>
+          <t>https://www.tiktok.com/@lexysluxurytravel</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>lifesabeach83</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
+          <t>lifeofladyluna</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3929,41 +3873,33 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-01 16:37:08</t>
+          <t>2026-09-01 11:26:02</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifesabeach83</t>
+          <t>https://www.tiktok.com/@lifeofladyluna</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kiesha11matthews</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>laurenandsophiesjigglejo</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3976,24 +3912,24 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:02</t>
+          <t>2026-09-03 10:12:08</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kiesha11matthews</t>
+          <t>https://www.tiktok.com/@laurenandsophiesjigglejo</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>mabes746</t>
+          <t>lydiaburnettxx</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4003,7 +3939,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4018,28 +3954,36 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:04</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mabes746</t>
+          <t>https://www.tiktok.com/@lydiaburnettxx</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>macouly1</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
+          <t>mabes746</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -4052,31 +3996,31 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-29 10:33:10</t>
+          <t>2026-09-01 11:35:04</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@macouly1</t>
+          <t>https://www.tiktok.com/@mabes746</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>maisiefinds0</t>
+          <t>macouly1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4086,31 +4030,31 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:04</t>
+          <t>2026-08-29 10:33:10</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maisiefinds0</t>
+          <t>https://www.tiktok.com/@macouly1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>mamacassyxo</t>
+          <t>maisiefinds0</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4120,92 +4064,92 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-27 16:05:15</t>
+          <t>2026-09-04 08:44:04</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mamacassyxo</t>
+          <t>https://www.tiktok.com/@maisiefinds0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mamarie146</t>
+          <t>mamacassyxo</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-01 12:24:32</t>
+          <t>2026-08-27 16:05:15</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mamarie146</t>
+          <t>https://www.tiktok.com/@mamacassyxo</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mandoki72</t>
+          <t>mamarie146</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-26 21:17:58</t>
+          <t>2026-09-01 12:24:32</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mandoki72</t>
+          <t>https://www.tiktok.com/@mamarie146</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>lovemystarsign</t>
+          <t>lifesabeach83</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4222,24 +4166,24 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-01 18:46:55</t>
+          <t>2026-09-01 16:37:08</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lovemystarsign</t>
+          <t>https://www.tiktok.com/@lifesabeach83</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>lexysluxurytravel</t>
+          <t>lovemystarsign</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4251,29 +4195,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-27 13:48:00</t>
+          <t>2026-09-01 18:46:55</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lexysluxurytravel</t>
+          <t>https://www.tiktok.com/@lovemystarsign</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>jay25084</t>
+          <t>martigergeraldine</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4290,31 +4234,39 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-25 10:06:52</t>
+          <t>2026-08-31 11:05:55</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jay25084</t>
+          <t>https://www.tiktok.com/@martigergeraldine</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>jaofficial10</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
+          <t>irrelevantlyliving</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4324,24 +4276,24 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-28 11:15:31</t>
+          <t>2026-09-01 11:35:03</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jaofficial10</t>
+          <t>https://www.tiktok.com/@irrelevantlyliving</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>itsneema5</t>
+          <t>invalid58</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4358,31 +4310,39 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-31 16:27:16</t>
+          <t>2026-08-28 17:24:16</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itsneema5</t>
+          <t>https://www.tiktok.com/@invalid58</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>is.colonel</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr"/>
+          <t>ijvpeanuts</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4392,24 +4352,24 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-05 23:55:02</t>
+          <t>2026-09-01 10:35:04</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@is.colonel</t>
+          <t>https://www.tiktok.com/@ijvpeanuts</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>invalid58</t>
+          <t>iamgawjus</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4426,39 +4386,31 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:16</t>
+          <t>2026-08-31 22:07:29</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@invalid58</t>
+          <t>https://www.tiktok.com/@iamgawjus</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>irrelevantlyliving</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>hrahmancookings</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4468,24 +4420,24 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:03</t>
+          <t>2026-09-08 19:45:29</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@irrelevantlyliving</t>
+          <t>https://www.tiktok.com/@hrahmancookings</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>iamgawjus</t>
+          <t>itsneema5</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4502,24 +4454,24 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-31 22:07:29</t>
+          <t>2026-08-31 16:27:16</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@iamgawjus</t>
+          <t>https://www.tiktok.com/@itsneema5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>judyluv42</t>
+          <t>itsjustthebest</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4536,31 +4488,39 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-25 10:31:30</t>
+          <t>2026-09-08 10:16:05</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@judyluv42</t>
+          <t>https://www.tiktok.com/@itsjustthebest</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kemotee07</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr"/>
-      <c r="C108" t="inlineStr"/>
+          <t>katiewanderlust</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4570,73 +4530,65 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-24 11:49:41</t>
+          <t>2026-09-01 12:14:02</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kemotee07</t>
+          <t>https://www.tiktok.com/@katiewanderlust</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kaymama31</t>
+          <t>judyluv42</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-30 10:22:50</t>
+          <t>2026-08-25 10:31:30</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaymama31</t>
+          <t>https://www.tiktok.com/@judyluv42</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kaurjas608</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>jay25084</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4646,39 +4598,31 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-09-01 10:36:07</t>
+          <t>2026-08-25 10:06:52</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaurjas608</t>
+          <t>https://www.tiktok.com/@jay25084</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ijvpeanuts</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>hamidaahmed028</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4688,28 +4632,36 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-01 10:35:04</t>
+          <t>2026-08-27 22:12:14</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ijvpeanuts</t>
+          <t>https://www.tiktok.com/@hamidaahmed028</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>heyuser060</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr"/>
+          <t>hannahtigg1</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D112" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -4717,36 +4669,36 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-01 17:21:20</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@heyuser060</t>
+          <t>https://www.tiktok.com/@hannahtigg1</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>homewithlauren_</t>
+          <t>healthyageinghq</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4756,17 +4708,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:03</t>
+          <t>2026-09-08 10:27:05</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@homewithlauren_</t>
+          <t>https://www.tiktok.com/@healthyageinghq</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4747,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4807,52 +4759,48 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>health.wise.media</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>greenfields24</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-24 02:13:31</t>
+          <t>2026-09-08 10:27:05</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@health.wise.media</t>
+          <t>https://www.tiktok.com/@greenfields24</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ovwomani22</t>
+          <t>nwabkhan760</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4862,31 +4810,31 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-28 18:04:58</t>
+          <t>2026-09-08 10:27:05</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ovwomani22</t>
+          <t>https://www.tiktok.com/@nwabkhan760</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ornellabeauty25</t>
+          <t>nutster58</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4896,31 +4844,31 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-07 22:41:47</t>
+          <t>2026-09-01 08:36:44</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ornellabeauty25</t>
+          <t>https://www.tiktok.com/@nutster58</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>nutster58</t>
+          <t>notlikeeveryday</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4930,31 +4878,39 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-01 08:36:44</t>
+          <t>2026-09-04 08:44:04</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nutster58</t>
+          <t>https://www.tiktok.com/@notlikeeveryday</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>notlikeeveryday</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
-      <c r="C119" t="inlineStr"/>
+          <t>niknak190725</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4964,39 +4920,31 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:04</t>
+          <t>2026-09-01 12:14:04</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@notlikeeveryday</t>
+          <t>https://www.tiktok.com/@niknak190725</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>niknak190725</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>nikkigossal29</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5006,24 +4954,24 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-01 12:14:04</t>
+          <t>2026-08-30 17:46:28</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@niknak190725</t>
+          <t>https://www.tiktok.com/@nikkigossal29</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>nikkigossal29</t>
+          <t>nellyedwin54</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -5040,28 +4988,36 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-30 17:46:28</t>
+          <t>2026-08-30 13:16:24</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nikkigossal29</t>
+          <t>https://www.tiktok.com/@nellyedwin54</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>nellyedwin54</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr"/>
+          <t>nathenjump</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D122" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5074,36 +5030,28 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-30 13:16:24</t>
+          <t>2026-09-01 14:09:02</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nellyedwin54</t>
+          <t>https://www.tiktok.com/@nathenjump</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>nathenjump</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>nasirpatel690</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5116,24 +5064,24 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-01 14:09:02</t>
+          <t>2026-08-29 00:44:35</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nathenjump</t>
+          <t>https://www.tiktok.com/@nasirpatel690</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>nasirpatel690</t>
+          <t>mz.jada0</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -5150,24 +5098,24 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-29 00:44:35</t>
+          <t>2026-09-07 21:15:37</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nasirpatel690</t>
+          <t>https://www.tiktok.com/@mz.jada0</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>mz.jada0</t>
+          <t>moon.x280</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -5179,29 +5127,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-09-07 21:15:37</t>
+          <t>2026-09-01 18:11:41</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mz.jada0</t>
+          <t>https://www.tiktok.com/@moon.x280</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>moon.x280</t>
+          <t>monpakhi_202</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5213,36 +5161,36 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-01 18:11:41</t>
+          <t>2026-08-31 21:10:55</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@moon.x280</t>
+          <t>https://www.tiktok.com/@monpakhi_202</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>monpakhi_202</t>
+          <t>missberry.kayamatauk</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5252,24 +5200,24 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-31 21:10:55</t>
+          <t>2026-08-26 13:15:36</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@monpakhi_202</t>
+          <t>https://www.tiktok.com/@missberry.kayamatauk</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>mila0701c7c</t>
+          <t>maxmeritbackup</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5286,31 +5234,31 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-25 05:11:12</t>
+          <t>2026-09-01 08:15:09</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mila0701c7c</t>
+          <t>https://www.tiktok.com/@maxmeritbackup</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>missberry.kayamatauk</t>
+          <t>mila0701c7c</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5320,24 +5268,24 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-26 13:15:36</t>
+          <t>2026-08-25 05:11:12</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@missberry.kayamatauk</t>
+          <t>https://www.tiktok.com/@mila0701c7c</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>martigergeraldine</t>
+          <t>mandoki72</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5354,31 +5302,31 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-31 11:05:55</t>
+          <t>2026-08-26 21:17:58</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@martigergeraldine</t>
+          <t>https://www.tiktok.com/@mandoki72</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>maxmeritbackup</t>
+          <t>primefindsuk_</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5388,36 +5336,28 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-01 08:15:09</t>
+          <t>2026-09-08 10:16:05</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maxmeritbackup</t>
+          <t>https://www.tiktok.com/@primefindsuk_</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>lydiaburnettxx</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>25K-50K</t>
-        </is>
-      </c>
+          <t>robbomsnvfv</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5425,104 +5365,104 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-09-01 12:37:06</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lydiaburnettxx</t>
+          <t>https://www.tiktok.com/@robbomsnvfv</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>sabbathina38</t>
+          <t>rkh250496ad</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-25 16:09:05</t>
+          <t>2026-08-31 17:54:22</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sabbathina38</t>
+          <t>https://www.tiktok.com/@rkh250496ad</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>rkh250496ad</t>
+          <t>remeradiance</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-08-31 17:54:22</t>
+          <t>2026-09-04 19:49:19</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rkh250496ad</t>
+          <t>https://www.tiktok.com/@remeradiance</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>robbomsnvfv</t>
+          <t>sabbathina38</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5532,17 +5472,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-09-01 12:37:06</t>
+          <t>2026-08-25 16:09:05</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@robbomsnvfv</t>
+          <t>https://www.tiktok.com/@sabbathina38</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5511,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5583,19 +5523,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>saliya_94</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>shakirakhan296</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5608,17 +5540,17 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-08-24 14:48:07</t>
+          <t>2026-08-28 23:38:18</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@saliya_94</t>
+          <t>https://www.tiktok.com/@shakirakhan296</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5587,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5667,7 +5599,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>remmyc64</t>
+          <t>ornellabeauty25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -5684,24 +5616,24 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-08-24 16:17:42</t>
+          <t>2026-09-07 22:41:47</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@remmyc64</t>
+          <t>https://www.tiktok.com/@ornellabeauty25</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>queen.of.boys42</t>
+          <t>pubby1amob</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5718,27 +5650,31 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-08-29 18:27:02</t>
+          <t>2026-08-27 18:28:59</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queen.of.boys42</t>
+          <t>https://www.tiktok.com/@pubby1amob</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>rabiaaman21</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
+          <t>princesslizy2010</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
@@ -5752,36 +5688,28 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:46</t>
+          <t>2026-08-26 20:03:55</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rabiaaman21</t>
+          <t>https://www.tiktok.com/@princesslizy2010</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>redbloodchurch1</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>queen.of.boys42</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5794,58 +5722,58 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-29 15:02:18</t>
+          <t>2026-08-29 18:27:02</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@redbloodchurch1</t>
+          <t>https://www.tiktok.com/@queen.of.boys42</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>remeradiance</t>
+          <t>rabiaaman21</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-09-04 19:49:19</t>
+          <t>2026-09-01 14:27:46</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@remeradiance</t>
+          <t>https://www.tiktok.com/@rabiaaman21</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>princess_wumi</t>
+          <t>redbloodchurch1</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5870,24 +5798,24 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-08-29 08:38:03</t>
+          <t>2026-08-29 15:02:18</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princess_wumi</t>
+          <t>https://www.tiktok.com/@redbloodchurch1</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>princesslizy2010</t>
+          <t>princess_wumi</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5895,7 +5823,11 @@
           <t>£0-£50</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D145" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5908,24 +5840,24 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-08-26 20:03:55</t>
+          <t>2026-08-29 08:38:03</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princesslizy2010</t>
+          <t>https://www.tiktok.com/@princess_wumi</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>pubby1amob</t>
+          <t>ovwomani22</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -5942,7 +5874,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-27 18:28:59</t>
+          <t>2026-08-28 18:04:58</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5952,7 +5884,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@pubby1amob</t>
+          <t>https://www.tiktok.com/@ovwomani22</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5913,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -5993,14 +5925,14 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>soul_rebel4</t>
+          <t>spyingthedeals</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -6010,36 +5942,28 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-08-25 20:55:08</t>
+          <t>2026-09-08 10:27:03</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@soul_rebel4</t>
+          <t>https://www.tiktok.com/@spyingthedeals</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>skyviewbm</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>soul_rebel4</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6052,24 +5976,24 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-08-30 16:29:14</t>
+          <t>2026-08-25 20:55:08</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@skyviewbm</t>
+          <t>https://www.tiktok.com/@soul_rebel4</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>shume.begum8</t>
+          <t>shurlar347</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -6086,28 +6010,36 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-09-01 20:33:17</t>
+          <t>2026-08-27 14:53:08</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shume.begum8</t>
+          <t>https://www.tiktok.com/@shurlar347</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>shurlar347</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
-      <c r="C151" t="inlineStr"/>
+          <t>skyviewbm</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D151" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6120,31 +6052,31 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-08-27 14:53:08</t>
+          <t>2026-08-30 16:29:14</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shurlar347</t>
+          <t>https://www.tiktok.com/@skyviewbm</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>shezha17</t>
+          <t>shume.begum8</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -6154,31 +6086,31 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-09-01 09:35:01</t>
+          <t>2026-09-01 20:33:17</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shezha17</t>
+          <t>https://www.tiktok.com/@shume.begum8</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>shakirakhan296</t>
+          <t>shezha17</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -6188,17 +6120,17 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-28 23:38:18</t>
+          <t>2026-09-01 09:35:01</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shakirakhan296</t>
+          <t>https://www.tiktok.com/@shezha17</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6159,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6261,7 +6193,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6295,7 +6227,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6329,7 +6261,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6363,7 +6295,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6397,7 +6329,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6431,7 +6363,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6465,7 +6397,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6499,7 +6431,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6533,7 +6465,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6567,7 +6499,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6601,7 +6533,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -6635,7 +6567,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -6677,7 +6609,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -6689,7 +6621,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>user_steeze</t>
+          <t>user9199380</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -6706,24 +6638,24 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-08-30 17:59:09</t>
+          <t>2026-09-08 15:02:55</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user_steeze</t>
+          <t>https://www.tiktok.com/@user9199380</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>user596114145414</t>
+          <t>user4423713561101</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
@@ -6740,24 +6672,24 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-08-28 18:57:06</t>
+          <t>2026-08-28 10:55:03</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user596114145414</t>
+          <t>https://www.tiktok.com/@user4423713561101</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>user4423713561101</t>
+          <t>user596114145414</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -6774,17 +6706,17 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-08-28 10:55:03</t>
+          <t>2026-08-28 18:57:06</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user4423713561101</t>
+          <t>https://www.tiktok.com/@user596114145414</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6745,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -6847,7 +6779,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -6889,7 +6821,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -6901,7 +6833,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>withlakisha</t>
+          <t>user_steeze</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -6913,36 +6845,36 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:03</t>
+          <t>2026-08-30 17:59:09</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@withlakisha</t>
+          <t>https://www.tiktok.com/@user_steeze</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>wellnesswithuzo</t>
+          <t>withlakisha</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6952,17 +6884,17 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-08-24 06:46:02</t>
+          <t>2026-09-04 08:44:03</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wellnesswithuzo</t>
+          <t>https://www.tiktok.com/@withlakisha</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6923,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -7025,7 +6957,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -7059,7 +6991,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -7093,7 +7025,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H179"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -545,91 +545,91 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>midlifehiddengems</t>
+          <t>christinatmitsi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>250K-500K</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30:55</t>
+          <t>2026-09-09 20:51:02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@midlifehiddengems</t>
+          <t>https://www.tiktok.com/@christinatmitsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>queennorxy</t>
+          <t>midlifehiddengems</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-31 11:31:09</t>
+          <t>2026-09-04 22:30:55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queennorxy</t>
+          <t>https://www.tiktok.com/@midlifehiddengems</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>fypdavesdeals</t>
+          <t>queennorxy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -639,39 +639,39 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-31 11:31:10</t>
+          <t>2026-08-31 11:31:09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fypdavesdeals</t>
+          <t>https://www.tiktok.com/@queennorxy</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>krystal_kei</t>
+          <t>fypdavesdeals</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -686,27 +686,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-27 08:36:58</t>
+          <t>2026-08-31 11:31:10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@krystal_kei</t>
+          <t>https://www.tiktok.com/@fypdavesdeals</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>luxuryvibe36</t>
+          <t>muhammadbilal_23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>100K-250K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -775,29 +775,29 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-31 11:42:10</t>
+          <t>2026-09-02 11:44:03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@luxuryvibe36</t>
+          <t>https://www.tiktok.com/@muhammadbilal_23</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>muhammadbilal_23</t>
+          <t>bam.bam5870</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -807,39 +807,39 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-02 11:44:03</t>
+          <t>2026-08-31 11:39:10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@muhammadbilal_23</t>
+          <t>https://www.tiktok.com/@bam.bam5870</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bam.bam5870</t>
+          <t>phil_becs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -849,39 +849,39 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-31 11:39:10</t>
+          <t>2026-08-31 11:42:09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bam.bam5870</t>
+          <t>https://www.tiktok.com/@phil_becs</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>phil_becs</t>
+          <t>kelliebelchamber</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -906,24 +906,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-31 11:42:09</t>
+          <t>2026-09-02 18:19:02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@phil_becs</t>
+          <t>https://www.tiktok.com/@kelliebelchamber</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kelliebelchamber</t>
+          <t>sh28___</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -933,39 +933,39 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>100K-250K</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-02 18:19:02</t>
+          <t>2026-08-31 11:57:09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kelliebelchamber</t>
+          <t>https://www.tiktok.com/@sh28___</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sh28___</t>
+          <t>hayleybumpbear</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -975,12 +975,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>100K-250K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>[] Moringa 1000mg</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -990,24 +990,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-31 11:57:09</t>
+          <t>2026-08-31 12:12:09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sh28___</t>
+          <t>https://www.tiktok.com/@hayleybumpbear</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hayleybumpbear</t>
+          <t>amy.l094</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1032,24 +1032,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-31 12:12:09</t>
+          <t>2026-08-31 12:07:10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hayleybumpbear</t>
+          <t>https://www.tiktok.com/@amy.l094</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>amy.l094</t>
+          <t>tonks1988</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[] Moringa 1000mg</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1074,34 +1074,34 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-31 12:07:10</t>
+          <t>2026-08-31 12:11:09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amy.l094</t>
+          <t>https://www.tiktok.com/@tonks1988</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tonks1988</t>
+          <t>eminence4009</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1116,24 +1116,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-31 12:11:09</t>
+          <t>2026-09-08 10:27:05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tonks1988</t>
+          <t>https://www.tiktok.com/@eminence4009</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>eminence4009</t>
+          <t>cornelia.tik.tokshop</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1158,24 +1158,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-08 10:27:05</t>
+          <t>2026-09-02 11:49:04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@eminence4009</t>
+          <t>https://www.tiktok.com/@cornelia.tik.tokshop</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cornelia.tik.tokshop</t>
+          <t>kingdom.wins</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1200,24 +1200,24 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-02 11:49:04</t>
+          <t>2026-09-02 18:11:02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cornelia.tik.tokshop</t>
+          <t>https://www.tiktok.com/@kingdom.wins</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kingdom.wins</t>
+          <t>blondie19834</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1242,24 +1242,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-02 18:11:02</t>
+          <t>2026-09-01 09:33:03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kingdom.wins</t>
+          <t>https://www.tiktok.com/@blondie19834</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>blondie19834</t>
+          <t>amb3rin0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1284,24 +1284,24 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-01 09:33:03</t>
+          <t>2026-09-01 09:36:02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blondie19834</t>
+          <t>https://www.tiktok.com/@amb3rin0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>amb3rin0</t>
+          <t>emma1503021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1326,39 +1326,39 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-01 09:36:02</t>
+          <t>2026-09-01 09:39:02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amb3rin0</t>
+          <t>https://www.tiktok.com/@emma1503021</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>emma1503021</t>
+          <t>lottieeve5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1368,34 +1368,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-01 09:39:02</t>
+          <t>2026-09-01 10:59:04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@emma1503021</t>
+          <t>https://www.tiktok.com/@lottieeve5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>veganmamaloves</t>
+          <t>hirahannan_official</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>250K-500K</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1410,29 +1410,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-02 18:11:02</t>
+          <t>2026-08-29 11:13:09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@veganmamaloves</t>
+          <t>https://www.tiktok.com/@hirahannan_official</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>lottieeve5</t>
+          <t>kim.foster1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1452,76 +1452,76 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-01 10:59:04</t>
+          <t>2026-09-01 11:08:04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lottieeve5</t>
+          <t>https://www.tiktok.com/@kim.foster1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hirahannan_official</t>
+          <t>blondielovinglife</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>250K-500K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Moringa Capsules By</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-29 11:13:09</t>
+          <t>2026-09-01 11:35:02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hirahannan_official</t>
+          <t>https://www.tiktok.com/@blondielovinglife</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>francesslee0</t>
+          <t>domddo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1536,39 +1536,39 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-08 06:50:27</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@francesslee0</t>
+          <t>https://www.tiktok.com/@domddo</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kim.foster1</t>
+          <t>tammyleek24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1578,34 +1578,34 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-01 11:08:04</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kim.foster1</t>
+          <t>https://www.tiktok.com/@tammyleek24</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>blondielovinglife</t>
+          <t>leahswarbrick0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1620,34 +1620,34 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:02</t>
+          <t>2026-09-01 11:35:03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blondielovinglife</t>
+          <t>https://www.tiktok.com/@leahswarbrick0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>domddo</t>
+          <t>wildwilkinsonsxx</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1662,35 +1662,39 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 11:26:03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@domddo</t>
+          <t>https://www.tiktok.com/@wildwilkinsonsxx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>steviekelise</t>
+          <t>ella.jaynefit</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>£100-£200</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1700,39 +1704,39 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-07 10:44:00</t>
+          <t>2026-09-01 12:03:03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@steviekelise</t>
+          <t>https://www.tiktok.com/@ella.jaynefit</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>queenofsobrietyuk</t>
+          <t>ambslouise99</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1747,34 +1751,34 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queenofsobrietyuk</t>
+          <t>https://www.tiktok.com/@ambslouise99</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tammyleek24</t>
+          <t>teheamyytehe</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1784,24 +1788,24 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 11:26:02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tammyleek24</t>
+          <t>https://www.tiktok.com/@teheamyytehe</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>leahswarbrick0</t>
+          <t>jazzzyjay360</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1816,34 +1820,34 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Moringa Capsules By</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:03</t>
+          <t>2026-09-01 12:14:02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@leahswarbrick0</t>
+          <t>https://www.tiktok.com/@jazzzyjay360</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>wildwilkinsonsxx</t>
+          <t>isloo7</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1853,12 +1857,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1868,7 +1872,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:03</t>
+          <t>2026-09-02 18:18:02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1878,14 +1882,14 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wildwilkinsonsxx</t>
+          <t>https://www.tiktok.com/@isloo7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tashajaynereviews</t>
+          <t>vonni349</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1895,7 +1899,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1905,29 +1909,29 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-09-01 12:03:03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tashajaynereviews</t>
+          <t>https://www.tiktok.com/@vonni349</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ella.jaynefit</t>
+          <t>sonix_luv</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1937,12 +1941,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1952,24 +1956,24 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:03</t>
+          <t>2026-09-01 10:35:21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ella.jaynefit</t>
+          <t>https://www.tiktok.com/@sonix_luv</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ambslouise99</t>
+          <t>bellavidafacial</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1979,7 +1983,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>50K-100K</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1994,81 +1998,65 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ambslouise99</t>
+          <t>https://www.tiktok.com/@bellavidafacial</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>jazzzyjay360</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>be__beauty1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-01 12:14:02</t>
+          <t>2026-09-08 17:18:23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jazzzyjay360</t>
+          <t>https://www.tiktok.com/@be__beauty1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>teheamyytehe</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>akuapapabi364</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2078,39 +2066,31 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:02</t>
+          <t>2026-08-30 17:55:54</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teheamyytehe</t>
+          <t>https://www.tiktok.com/@akuapapabi364</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>isloo7</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>abenaduncan1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2120,66 +2100,58 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-02 18:18:02</t>
+          <t>2026-08-28 12:54:46</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@isloo7</t>
+          <t>https://www.tiktok.com/@abenaduncan1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>vonni349</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>barbaraasiedu771</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:03</t>
+          <t>2026-09-09 21:11:27</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vonni349</t>
+          <t>https://www.tiktok.com/@barbaraasiedu771</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>sonix_luv</t>
+          <t>banksofmay</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2194,7 +2166,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2204,39 +2176,31 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-01 10:35:21</t>
+          <t>2026-08-29 18:39:38</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sonix_luv</t>
+          <t>https://www.tiktok.com/@banksofmay</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bellavidafacial</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>50K-100K</t>
-        </is>
-      </c>
+          <t>annie.mahn</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2246,31 +2210,39 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-08-30 18:11:22</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bellavidafacial</t>
+          <t>https://www.tiktok.com/@annie.mahn</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bellasbeauty07</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
+          <t>amykirks.1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2280,62 +2252,70 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-08 10:16:05</t>
+          <t>2026-09-01 11:26:03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bellasbeauty07</t>
+          <t>https://www.tiktok.com/@amykirks.1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>beauty_by_ash_attire</t>
+          <t>anila_pk_uk</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-02 16:24:16</t>
+          <t>2026-09-08 14:43:04</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beauty_by_ash_attire</t>
+          <t>https://www.tiktok.com/@anila_pk_uk</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>beebee9537</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
+          <t>amyhart2323</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2348,27 +2328,31 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-30 13:59:25</t>
+          <t>2026-09-01 11:26:02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beebee9537</t>
+          <t>https://www.tiktok.com/@amyhart2323</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>abenaduncan1</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>akiatuconteh</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
@@ -2382,24 +2366,24 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-28 12:54:46</t>
+          <t>2026-09-09 07:32:58</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abenaduncan1</t>
+          <t>https://www.tiktok.com/@akiatuconteh</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>amyhart2323</t>
+          <t>erico2006</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2424,58 +2408,58 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:02</t>
+          <t>2026-09-01 22:26:53</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amyhart2323</t>
+          <t>https://www.tiktok.com/@erico2006</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>adefunkemayowaoso1</t>
+          <t>ennyluv76</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-25 12:03:26</t>
+          <t>2026-08-30 08:31:46</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adefunkemayowaoso1</t>
+          <t>https://www.tiktok.com/@ennyluv76</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>abeehaamir24</t>
+          <t>eni_folabi</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2492,24 +2476,24 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-30 10:05:16</t>
+          <t>2026-09-09 11:38:46</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abeehaamir24</t>
+          <t>https://www.tiktok.com/@eni_folabi</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>fissysbakestudio</t>
+          <t>elizabetho001</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2526,58 +2510,58 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-31 21:21:04</t>
+          <t>2026-09-08 17:27:54</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fissysbakestudio</t>
+          <t>https://www.tiktok.com/@elizabetho001</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>finda9095</t>
+          <t>debrazerf</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-01 13:23:27</t>
+          <t>2026-08-27 19:29:33</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@finda9095</t>
+          <t>https://www.tiktok.com/@debrazerf</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>fffysigs0719</t>
+          <t>deckynla</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2594,58 +2578,62 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-27 16:41:03</t>
+          <t>2026-09-09 11:52:15</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fffysigs0719</t>
+          <t>https://www.tiktok.com/@deckynla</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>famidak1</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>designer_suits</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-27 15:54:45</t>
+          <t>2026-08-31 19:59:15</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@famidak1</t>
+          <t>https://www.tiktok.com/@designer_suits</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ennyluv76</t>
+          <t>dlp7831</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2662,36 +2650,28 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-30 08:31:46</t>
+          <t>2026-08-28 08:11:22</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ennyluv76</t>
+          <t>https://www.tiktok.com/@dlp7831</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>erico2006</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>david.adetokunbo2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2704,31 +2684,27 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-01 22:26:53</t>
+          <t>2026-08-26 22:15:55</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@erico2006</t>
+          <t>https://www.tiktok.com/@david.adetokunbo2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>designer_suits</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>darkness10145</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
@@ -2737,12 +2713,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-31 19:59:15</t>
+          <t>2026-09-01 19:15:07</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2752,14 +2728,14 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@designer_suits</t>
+          <t>https://www.tiktok.com/@darkness10145</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>elizabetho001</t>
+          <t>daliayasmin77</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2776,24 +2752,24 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-08 17:27:54</t>
+          <t>2026-08-27 22:31:42</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@elizabetho001</t>
+          <t>https://www.tiktok.com/@daliayasmin77</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>delboy_trotter1</t>
+          <t>dailygooods</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2810,31 +2786,39 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-25 16:12:46</t>
+          <t>2026-09-04 08:44:02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@delboy_trotter1</t>
+          <t>https://www.tiktok.com/@dailygooods</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>dlp7831</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
+          <t>clairegriff0</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2844,24 +2828,24 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-28 08:11:22</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dlp7831</t>
+          <t>https://www.tiktok.com/@clairegriff0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>dimples7219</t>
+          <t>claraeg01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2878,31 +2862,31 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-25 08:40:28</t>
+          <t>2026-08-28 08:29:29</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dimples7219</t>
+          <t>https://www.tiktok.com/@claraeg01</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>dailygooods</t>
+          <t>cocoleta7</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2912,31 +2896,31 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:02</t>
+          <t>2026-08-27 06:32:26</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailygooods</t>
+          <t>https://www.tiktok.com/@cocoleta7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>daliayasmin77</t>
+          <t>craftyjo72</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2946,31 +2930,31 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-27 22:31:42</t>
+          <t>2026-09-08 10:27:04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@daliayasmin77</t>
+          <t>https://www.tiktok.com/@craftyjo72</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>darkness10145</t>
+          <t>beauty_by_ash_attire</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2980,7 +2964,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-01 19:15:07</t>
+          <t>2026-09-02 16:24:16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2990,21 +2974,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@darkness10145</t>
+          <t>https://www.tiktok.com/@beauty_by_ash_attire</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>david.adetokunbo2</t>
+          <t>bellasbeauty07</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3014,65 +2998,65 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:55</t>
+          <t>2026-09-08 10:16:05</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@david.adetokunbo2</t>
+          <t>https://www.tiktok.com/@bellasbeauty07</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>debrazerf</t>
+          <t>bisbis046</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-27 19:29:33</t>
+          <t>2026-09-03 09:57:56</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@debrazerf</t>
+          <t>https://www.tiktok.com/@bisbis046</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>bisbis046</t>
+          <t>bilqeesajokeade</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3082,7 +3066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-03 09:57:56</t>
+          <t>2026-09-04 06:06:55</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3092,14 +3076,14 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bisbis046</t>
+          <t>https://www.tiktok.com/@bilqeesajokeade</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>clairegriff0</t>
+          <t>chlo._evans</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3114,117 +3098,109 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-08-31 11:52:47</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clairegriff0</t>
+          <t>https://www.tiktok.com/@chlo._evans</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>chlo._evans</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+          <t>beebee9537</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-31 11:52:47</t>
+          <t>2026-08-30 13:59:25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chlo._evans</t>
+          <t>https://www.tiktok.com/@beebee9537</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>bilqeesajokeade</t>
+          <t>abeehaamir24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-04 06:06:55</t>
+          <t>2026-08-30 10:05:16</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bilqeesajokeade</t>
+          <t>https://www.tiktok.com/@abeehaamir24</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>cocoleta7</t>
+          <t>healthyageinghq</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3234,31 +3210,31 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-27 06:32:26</t>
+          <t>2026-09-08 10:27:05</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cocoleta7</t>
+          <t>https://www.tiktok.com/@healthyageinghq</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>craftyjo72</t>
+          <t>iamgawjus</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3268,24 +3244,24 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-08 10:27:04</t>
+          <t>2026-08-31 22:07:29</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@craftyjo72</t>
+          <t>https://www.tiktok.com/@iamgawjus</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>claraeg01</t>
+          <t>hrahmancookings</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3302,24 +3278,24 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-28 08:29:29</t>
+          <t>2026-09-08 19:45:29</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@claraeg01</t>
+          <t>https://www.tiktok.com/@hrahmancookings</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>akuapapabi364</t>
+          <t>homewithlauren_</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3336,58 +3312,58 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-30 17:55:54</t>
+          <t>2026-09-03 10:12:03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@akuapapabi364</t>
+          <t>https://www.tiktok.com/@homewithlauren_</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>anila_pk_uk</t>
+          <t>heyuser060</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-08 14:43:04</t>
+          <t>2026-09-01 17:21:20</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@anila_pk_uk</t>
+          <t>https://www.tiktok.com/@heyuser060</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>amykirks.1</t>
+          <t>hannahtigg1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3397,7 +3373,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3412,36 +3388,28 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:03</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amykirks.1</t>
+          <t>https://www.tiktok.com/@hannahtigg1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>banksofmay</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>hamidaahmed028</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3454,41 +3422,41 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-29 18:39:38</t>
+          <t>2026-08-27 22:12:14</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@banksofmay</t>
+          <t>https://www.tiktok.com/@hamidaahmed028</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>annie.mahn</t>
+          <t>helenbest0</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-30 18:11:22</t>
+          <t>2026-08-31 06:52:19</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3498,14 +3466,14 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@annie.mahn</t>
+          <t>https://www.tiktok.com/@helenbest0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>be__beauty1</t>
+          <t>famidak1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3522,31 +3490,39 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-08 17:18:23</t>
+          <t>2026-08-27 15:54:45</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@be__beauty1</t>
+          <t>https://www.tiktok.com/@famidak1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>is.colonel</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
+          <t>kiesha11matthews</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3556,31 +3532,31 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-05 23:55:02</t>
+          <t>2026-09-01 11:35:02</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@is.colonel</t>
+          <t>https://www.tiktok.com/@kiesha11matthews</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>heyuser060</t>
+          <t>kay.h0</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3590,92 +3566,92 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-01 17:21:20</t>
+          <t>2026-09-09 04:27:35</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@heyuser060</t>
+          <t>https://www.tiktok.com/@kay.h0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>homewithlauren_</t>
+          <t>kaymama31</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:03</t>
+          <t>2026-08-30 10:22:50</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@homewithlauren_</t>
+          <t>https://www.tiktok.com/@kaymama31</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>lady_dash07</t>
+          <t>kayyu247</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-05 21:11:23</t>
+          <t>2026-09-09 09:42:51</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lady_dash07</t>
+          <t>https://www.tiktok.com/@kayyu247</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>lady.p3600</t>
+          <t>laurenandsophiesjigglejo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3692,100 +3668,92 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-26 15:34:27</t>
+          <t>2026-09-03 10:12:08</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lady.p3600</t>
+          <t>https://www.tiktok.com/@laurenandsophiesjigglejo</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kaymama31</t>
+          <t>lexysluxurytravel</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-30 10:22:50</t>
+          <t>2026-08-27 13:48:00</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaymama31</t>
+          <t>https://www.tiktok.com/@lexysluxurytravel</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kiesha11matthews</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>lady_dash07</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:02</t>
+          <t>2026-09-05 21:11:23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kiesha11matthews</t>
+          <t>https://www.tiktok.com/@lady_dash07</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>jaofficial10</t>
+          <t>lady.p3600</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3802,70 +3770,62 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-28 11:15:31</t>
+          <t>2026-08-26 15:34:27</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jaofficial10</t>
+          <t>https://www.tiktok.com/@lady.p3600</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>lexysluxurytravel</t>
+          <t>louisahusseymenopauseugc</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-27 13:48:00</t>
+          <t>2026-09-09 08:25:02</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lexysluxurytravel</t>
+          <t>https://www.tiktok.com/@louisahusseymenopauseugc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>lifeofladyluna</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>lovemystarsign</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3873,33 +3833,41 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:02</t>
+          <t>2026-09-01 18:46:55</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifeofladyluna</t>
+          <t>https://www.tiktok.com/@lovemystarsign</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>laurenandsophiesjigglejo</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
+          <t>lydiaburnettxx</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>25K-50K</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3912,24 +3880,24 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:08</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@laurenandsophiesjigglejo</t>
+          <t>https://www.tiktok.com/@lydiaburnettxx</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>lydiaburnettxx</t>
+          <t>mabes746</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3939,7 +3907,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3954,36 +3922,28 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-09-01 11:35:04</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lydiaburnettxx</t>
+          <t>https://www.tiktok.com/@mabes746</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>mabes746</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>macouly1</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3996,31 +3956,31 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:04</t>
+          <t>2026-08-29 10:33:10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mabes746</t>
+          <t>https://www.tiktok.com/@macouly1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>macouly1</t>
+          <t>maisiefinds0</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4030,31 +3990,39 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-29 10:33:10</t>
+          <t>2026-09-04 08:44:04</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@macouly1</t>
+          <t>https://www.tiktok.com/@maisiefinds0</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>maisiefinds0</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
+          <t>lifeofladyluna</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4064,24 +4032,24 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:04</t>
+          <t>2026-09-01 11:26:02</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maisiefinds0</t>
+          <t>https://www.tiktok.com/@lifeofladyluna</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mamacassyxo</t>
+          <t>lifesabeach83</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -4093,22 +4061,22 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-27 16:05:15</t>
+          <t>2026-09-01 16:37:08</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mamacassyxo</t>
+          <t>https://www.tiktok.com/@lifesabeach83</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4105,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4149,7 +4117,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>lifesabeach83</t>
+          <t>mamacassyxo</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4161,29 +4129,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-01 16:37:08</t>
+          <t>2026-08-27 16:05:15</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifesabeach83</t>
+          <t>https://www.tiktok.com/@mamacassyxo</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>lovemystarsign</t>
+          <t>martigergeraldine</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4195,29 +4163,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-09-01 18:46:55</t>
+          <t>2026-08-31 11:05:55</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lovemystarsign</t>
+          <t>https://www.tiktok.com/@martigergeraldine</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>martigergeraldine</t>
+          <t>mandoki72</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4234,39 +4202,31 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-31 11:05:55</t>
+          <t>2026-08-26 21:17:58</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@martigergeraldine</t>
+          <t>https://www.tiktok.com/@mandoki72</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>irrelevantlyliving</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>maxmeritbackup</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4276,31 +4236,31 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:03</t>
+          <t>2026-09-01 08:15:09</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@irrelevantlyliving</t>
+          <t>https://www.tiktok.com/@maxmeritbackup</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>invalid58</t>
+          <t>is.colonel</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4310,17 +4270,17 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:16</t>
+          <t>2026-09-05 23:55:02</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@invalid58</t>
+          <t>https://www.tiktok.com/@is.colonel</t>
         </is>
       </c>
     </row>
@@ -4357,7 +4317,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4369,7 +4329,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>iamgawjus</t>
+          <t>invalid58</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4386,24 +4346,24 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-31 22:07:29</t>
+          <t>2026-08-28 17:24:16</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@iamgawjus</t>
+          <t>https://www.tiktok.com/@invalid58</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>hrahmancookings</t>
+          <t>jaofficial10</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4420,17 +4380,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-08 19:45:29</t>
+          <t>2026-08-28 11:15:31</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hrahmancookings</t>
+          <t>https://www.tiktok.com/@jaofficial10</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4419,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4471,14 +4431,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>itsjustthebest</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
-      <c r="C107" t="inlineStr"/>
+          <t>irrelevantlyliving</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4488,17 +4456,17 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-08 10:16:05</t>
+          <t>2026-09-01 11:35:03</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itsjustthebest</t>
+          <t>https://www.tiktok.com/@irrelevantlyliving</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4503,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4547,7 +4515,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>judyluv42</t>
+          <t>fissysbakestudio</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4564,104 +4532,96 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-25 10:31:30</t>
+          <t>2026-08-31 21:21:04</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@judyluv42</t>
+          <t>https://www.tiktok.com/@fissysbakestudio</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>jay25084</t>
+          <t>greenfields24</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-25 10:06:52</t>
+          <t>2026-09-08 10:27:05</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jay25084</t>
+          <t>https://www.tiktok.com/@greenfields24</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>hamidaahmed028</t>
+          <t>finda9095</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-27 22:12:14</t>
+          <t>2026-09-01 13:23:27</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hamidaahmed028</t>
+          <t>https://www.tiktok.com/@finda9095</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>hannahtigg1</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>fffysigs0719</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -4674,31 +4634,31 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-08-27 16:41:03</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hannahtigg1</t>
+          <t>https://www.tiktok.com/@fffysigs0719</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>healthyageinghq</t>
+          <t>notlikeeveryday</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4708,28 +4668,36 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-08 10:27:05</t>
+          <t>2026-09-04 08:44:04</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@healthyageinghq</t>
+          <t>https://www.tiktok.com/@notlikeeveryday</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>helenbest0</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr"/>
+          <t>niknak190725</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D114" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -4737,12 +4705,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-31 06:52:19</t>
+          <t>2026-09-01 12:14:04</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4752,55 +4720,55 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@helenbest0</t>
+          <t>https://www.tiktok.com/@niknak190725</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>greenfields24</t>
+          <t>nikkigossal29</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-08 10:27:05</t>
+          <t>2026-08-30 17:46:28</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@greenfields24</t>
+          <t>https://www.tiktok.com/@nikkigossal29</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>nwabkhan760</t>
+          <t>nellyedwin54</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4810,31 +4778,39 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-09-08 10:27:05</t>
+          <t>2026-08-30 13:16:24</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nwabkhan760</t>
+          <t>https://www.tiktok.com/@nellyedwin54</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>nutster58</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr"/>
+          <t>nathenjump</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4844,24 +4820,24 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-01 08:36:44</t>
+          <t>2026-09-01 14:09:02</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nutster58</t>
+          <t>https://www.tiktok.com/@nathenjump</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>notlikeeveryday</t>
+          <t>nasirpatel690</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4878,39 +4854,31 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:04</t>
+          <t>2026-08-29 00:44:35</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@notlikeeveryday</t>
+          <t>https://www.tiktok.com/@nasirpatel690</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>niknak190725</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>mz.jada0</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4920,24 +4888,24 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-01 12:14:04</t>
+          <t>2026-09-07 21:15:37</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@niknak190725</t>
+          <t>https://www.tiktok.com/@mz.jada0</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>nikkigossal29</t>
+          <t>moon.x280</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -4949,29 +4917,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-08-30 17:46:28</t>
+          <t>2026-09-01 18:11:41</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nikkigossal29</t>
+          <t>https://www.tiktok.com/@moon.x280</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>nellyedwin54</t>
+          <t>markh_8</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -4988,36 +4956,28 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-30 13:16:24</t>
+          <t>2026-09-09 16:07:49</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nellyedwin54</t>
+          <t>https://www.tiktok.com/@markh_8</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>nathenjump</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>monpakhi_202</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5030,31 +4990,31 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-01 14:09:02</t>
+          <t>2026-08-31 21:10:55</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nathenjump</t>
+          <t>https://www.tiktok.com/@monpakhi_202</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>nasirpatel690</t>
+          <t>missberry.kayamatauk</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5064,28 +5024,36 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-29 00:44:35</t>
+          <t>2026-08-26 13:15:36</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nasirpatel690</t>
+          <t>https://www.tiktok.com/@missberry.kayamatauk</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>mz.jada0</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr"/>
+          <t>princess_wumi</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D124" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5098,24 +5066,24 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-07 21:15:37</t>
+          <t>2026-08-29 08:38:03</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mz.jada0</t>
+          <t>https://www.tiktok.com/@princess_wumi</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>moon.x280</t>
+          <t>ovwomani22</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -5127,29 +5095,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-09-01 18:11:41</t>
+          <t>2026-08-28 18:04:58</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@moon.x280</t>
+          <t>https://www.tiktok.com/@ovwomani22</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>monpakhi_202</t>
+          <t>pm37896</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5166,31 +5134,31 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-31 21:10:55</t>
+          <t>2026-08-28 00:17:19</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@monpakhi_202</t>
+          <t>https://www.tiktok.com/@pm37896</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>missberry.kayamatauk</t>
+          <t>ornellabeauty25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5200,31 +5168,31 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-26 13:15:36</t>
+          <t>2026-09-07 22:41:47</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@missberry.kayamatauk</t>
+          <t>https://www.tiktok.com/@ornellabeauty25</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>maxmeritbackup</t>
+          <t>nutster58</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5234,24 +5202,24 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-01 08:15:09</t>
+          <t>2026-09-01 08:36:44</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maxmeritbackup</t>
+          <t>https://www.tiktok.com/@nutster58</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>mila0701c7c</t>
+          <t>rkh250496ad</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -5268,58 +5236,58 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-25 05:11:12</t>
+          <t>2026-08-31 17:54:22</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mila0701c7c</t>
+          <t>https://www.tiktok.com/@rkh250496ad</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>mandoki72</t>
+          <t>remeradiance</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-26 21:17:58</t>
+          <t>2026-09-04 19:49:19</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mandoki72</t>
+          <t>https://www.tiktok.com/@remeradiance</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>primefindsuk_</t>
+          <t>seana_montgomery61</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5336,17 +5304,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-08 10:16:05</t>
+          <t>2026-09-03 10:12:09</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@primefindsuk_</t>
+          <t>https://www.tiktok.com/@seana_montgomery61</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5343,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5387,7 +5355,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>rkh250496ad</t>
+          <t>sexybaby7657</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -5404,24 +5372,24 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-31 17:54:22</t>
+          <t>2026-09-09 21:00:27</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rkh250496ad</t>
+          <t>https://www.tiktok.com/@sexybaby7657</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>remeradiance</t>
+          <t>shahzad.akram041</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5438,62 +5406,70 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-09-04 19:49:19</t>
+          <t>2026-09-03 04:27:22</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@remeradiance</t>
+          <t>https://www.tiktok.com/@shahzad.akram041</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>sabbathina38</t>
+          <t>shakirakhan296</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-08-25 16:09:05</t>
+          <t>2026-08-28 23:38:18</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sabbathina38</t>
+          <t>https://www.tiktok.com/@shakirakhan296</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>shahzad.akram041</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
+          <t>sarah565556</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D136" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -5501,29 +5477,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-03 04:27:22</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shahzad.akram041</t>
+          <t>https://www.tiktok.com/@sarah565556</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>shakirakhan296</t>
+          <t>sharansaleem</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5540,7 +5516,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-08-28 23:38:18</t>
+          <t>2026-08-29 11:45:48</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5550,14 +5526,14 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shakirakhan296</t>
+          <t>https://www.tiktok.com/@sharansaleem</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>sarah565556</t>
+          <t>princesslizy2010</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5565,14 +5541,10 @@
           <t>£0-£50</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5582,24 +5554,24 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-08-26 20:03:55</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarah565556</t>
+          <t>https://www.tiktok.com/@princesslizy2010</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ornellabeauty25</t>
+          <t>pubby1amob</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -5616,24 +5588,24 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-09-07 22:41:47</t>
+          <t>2026-08-27 18:28:59</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ornellabeauty25</t>
+          <t>https://www.tiktok.com/@pubby1amob</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>pubby1amob</t>
+          <t>queen.of.boys42</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5650,31 +5622,27 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-08-27 18:28:59</t>
+          <t>2026-08-29 18:27:02</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@pubby1amob</t>
+          <t>https://www.tiktok.com/@queen.of.boys42</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>princesslizy2010</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>rabiaaman21</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
@@ -5688,28 +5656,36 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-08-26 20:03:55</t>
+          <t>2026-09-01 14:27:46</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princesslizy2010</t>
+          <t>https://www.tiktok.com/@rabiaaman21</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>queen.of.boys42</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr"/>
+          <t>redbloodchurch1</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D142" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5722,31 +5698,31 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-29 18:27:02</t>
+          <t>2026-08-29 15:02:18</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queen.of.boys42</t>
+          <t>https://www.tiktok.com/@redbloodchurch1</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>rabiaaman21</t>
+          <t>primefindsuk_</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5756,39 +5732,31 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:46</t>
+          <t>2026-09-08 10:16:05</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rabiaaman21</t>
+          <t>https://www.tiktok.com/@primefindsuk_</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>redbloodchurch1</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>nwabkhan760</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5798,36 +5766,28 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-08-29 15:02:18</t>
+          <t>2026-09-08 10:27:05</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@redbloodchurch1</t>
+          <t>https://www.tiktok.com/@nwabkhan760</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>princess_wumi</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>ste.baby6</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5840,31 +5800,31 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-08-29 08:38:03</t>
+          <t>2026-09-09 16:28:17</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princess_wumi</t>
+          <t>https://www.tiktok.com/@ste.baby6</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ovwomani22</t>
+          <t>spyingthedeals</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5874,28 +5834,36 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-28 18:04:58</t>
+          <t>2026-09-08 10:27:03</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ovwomani22</t>
+          <t>https://www.tiktok.com/@spyingthedeals</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>pm37896</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr"/>
+          <t>skyviewbm</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D147" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5908,31 +5876,31 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-28 00:17:19</t>
+          <t>2026-08-30 16:29:14</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@pm37896</t>
+          <t>https://www.tiktok.com/@skyviewbm</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>spyingthedeals</t>
+          <t>shurlar347</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5942,31 +5910,31 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-09-08 10:27:03</t>
+          <t>2026-08-27 14:53:08</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@spyingthedeals</t>
+          <t>https://www.tiktok.com/@shurlar347</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>soul_rebel4</t>
+          <t>shezha17</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5976,24 +5944,24 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-08-25 20:55:08</t>
+          <t>2026-09-01 09:35:01</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@soul_rebel4</t>
+          <t>https://www.tiktok.com/@shezha17</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>shurlar347</t>
+          <t>shume.begum8</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -6010,107 +5978,99 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-08-27 14:53:08</t>
+          <t>2026-09-01 20:33:17</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shurlar347</t>
+          <t>https://www.tiktok.com/@shume.begum8</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>skyviewbm</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>sharonhiggins46</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-08-30 16:29:14</t>
+          <t>2026-08-28 20:19:57</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@skyviewbm</t>
+          <t>https://www.tiktok.com/@sharonhiggins46</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>shume.begum8</t>
+          <t>sweetshez1</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-09-01 20:33:17</t>
+          <t>2026-09-05 18:50:17</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shume.begum8</t>
+          <t>https://www.tiktok.com/@sweetshez1</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>shezha17</t>
+          <t>tran.le455</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -6120,24 +6080,24 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-09-01 09:35:01</t>
+          <t>2026-08-28 14:45:25</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shezha17</t>
+          <t>https://www.tiktok.com/@tran.le455</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>sharansaleem</t>
+          <t>trendaura47</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -6154,58 +6114,58 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-08-29 11:45:48</t>
+          <t>2026-09-09 09:29:07</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sharansaleem</t>
+          <t>https://www.tiktok.com/@trendaura47</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>sharonhiggins46</t>
+          <t>trending_gists_omoola</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-08-28 20:19:57</t>
+          <t>2026-08-30 21:32:52</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sharonhiggins46</t>
+          <t>https://www.tiktok.com/@trending_gists_omoola</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>seana_montgomery61</t>
+          <t>turelove730</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -6217,36 +6177,44 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:09</t>
+          <t>2026-09-01 14:36:11</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@seana_montgomery61</t>
+          <t>https://www.tiktok.com/@turelove730</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>tran.le455</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr"/>
-      <c r="C157" t="inlineStr"/>
+          <t>ugcbyshristi</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -6256,24 +6224,24 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-08-28 14:45:25</t>
+          <t>2026-09-01 12:03:03</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tran.le455</t>
+          <t>https://www.tiktok.com/@ugcbyshristi</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>trending_gists_omoola</t>
+          <t>sukhdeepkaur343</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -6290,51 +6258,51 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-08-30 21:32:52</t>
+          <t>2026-08-27 15:52:29</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@trending_gists_omoola</t>
+          <t>https://www.tiktok.com/@sukhdeepkaur343</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>turelove730</t>
+          <t>tee_y.x</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-09-01 14:36:11</t>
+          <t>2026-08-31 00:32:51</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@turelove730</t>
+          <t>https://www.tiktok.com/@tee_y.x</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6331,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6375,7 +6343,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>sweetshez1</t>
+          <t>user2922793729949</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -6392,24 +6360,24 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-09-05 18:50:17</t>
+          <t>2026-09-01 13:14:46</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sweetshez1</t>
+          <t>https://www.tiktok.com/@user2922793729949</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>tee_y.x</t>
+          <t>user26963863682186</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -6426,24 +6394,24 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-08-31 00:32:51</t>
+          <t>2026-08-27 16:29:12</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tee_y.x</t>
+          <t>https://www.tiktok.com/@user26963863682186</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>sukhdeepkaur343</t>
+          <t>uky1090</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
@@ -6460,7 +6428,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-08-27 15:52:29</t>
+          <t>2026-08-28 01:37:24</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -6470,82 +6438,82 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sukhdeepkaur343</t>
+          <t>https://www.tiktok.com/@uky1090</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>user2922793729949</t>
+          <t>user4423713561101</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-09-01 13:14:46</t>
+          <t>2026-08-28 10:55:03</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2922793729949</t>
+          <t>https://www.tiktok.com/@user4423713561101</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>user26963863682186</t>
+          <t>user_steeze</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-08-27 16:29:12</t>
+          <t>2026-08-30 17:59:09</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user26963863682186</t>
+          <t>https://www.tiktok.com/@user_steeze</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>uky1090</t>
+          <t>user4961074980381</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
@@ -6562,39 +6530,31 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-08-28 01:37:24</t>
+          <t>2026-08-28 21:55:56</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uky1090</t>
+          <t>https://www.tiktok.com/@user4961074980381</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ugcbyshristi</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>user596114145414</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6604,17 +6564,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:03</t>
+          <t>2026-08-28 18:57:06</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ugcbyshristi</t>
+          <t>https://www.tiktok.com/@user596114145414</t>
         </is>
       </c>
     </row>
@@ -6643,7 +6603,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -6655,7 +6615,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>user4423713561101</t>
+          <t>vivianesoizeau</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
@@ -6672,28 +6632,36 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-08-28 10:55:03</t>
+          <t>2026-08-31 16:20:27</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user4423713561101</t>
+          <t>https://www.tiktok.com/@vivianesoizeau</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>user596114145414</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr"/>
-      <c r="C170" t="inlineStr"/>
+          <t>veronpoks</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D170" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6706,24 +6674,24 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-08-28 18:57:06</t>
+          <t>2026-08-30 14:08:12</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user596114145414</t>
+          <t>https://www.tiktok.com/@veronpoks</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>user4961074980381</t>
+          <t>vera77524</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -6740,31 +6708,31 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-08-28 21:55:56</t>
+          <t>2026-09-09 07:38:35</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user4961074980381</t>
+          <t>https://www.tiktok.com/@vera77524</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>vivianesoizeau</t>
+          <t>withlakisha</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -6774,66 +6742,58 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-31 16:20:27</t>
+          <t>2026-09-04 08:44:03</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vivianesoizeau</t>
+          <t>https://www.tiktok.com/@withlakisha</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>veronpoks</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>wolfie1830</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-30 14:08:12</t>
+          <t>2026-09-01 11:52:06</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@veronpoks</t>
+          <t>https://www.tiktok.com/@wolfie1830</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>user_steeze</t>
+          <t>xstormx33</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -6850,31 +6810,31 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-08-30 17:59:09</t>
+          <t>2026-09-01 10:36:21</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user_steeze</t>
+          <t>https://www.tiktok.com/@xstormx33</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>withlakisha</t>
+          <t>yxsna_98</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6884,24 +6844,24 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:03</t>
+          <t>2026-08-30 12:46:22</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@withlakisha</t>
+          <t>https://www.tiktok.com/@yxsna_98</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>wolfie1830</t>
+          <t>zubairianaz15</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -6918,117 +6878,15 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-09-01 11:52:06</t>
+          <t>2026-09-05 22:51:12</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@wolfie1830</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>xstormx33</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr"/>
-      <c r="C177" t="inlineStr"/>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-09-01 10:36:21</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@xstormx33</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>yxsna_98</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr"/>
-      <c r="C178" t="inlineStr"/>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-08-30 12:46:22</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@yxsna_98</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>zubairianaz15</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr"/>
-      <c r="C179" t="inlineStr"/>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-09-05 22:51:12</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@zubairianaz15</t>
         </is>
